--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,7 +781,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C2" s="2">
         <v>46269</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C3" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -933,16 +933,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.8534647213814789</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2.222467764607518</v>
+        <v>2.400270608960956</v>
       </c>
       <c r="H3">
-        <v>1.917535924931897</v>
+        <v>1.928408320178992</v>
       </c>
       <c r="I3">
-        <v>0.4313469226629286</v>
+        <v>0.4329772036798598</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>-0.08925980789073162</v>
+        <v>-0.09550746151652557</v>
       </c>
       <c r="O3">
-        <v>-25.6125704134093</v>
+        <v>-28.96987241320239</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.222467764607518</v>
+        <v>2.400270608960956</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9918750949342574</v>
+        <v>0.9999315107325071</v>
       </c>
       <c r="U3">
-        <v>0.9742663912120111</v>
+        <v>0.9998800412718265</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9980269655042503</v>
+        <v>0.9995349383903913</v>
       </c>
       <c r="Y3">
-        <v>0.9996115611374938</v>
+        <v>0.999643445768793</v>
       </c>
       <c r="Z3">
-        <v>0.001584595633243535</v>
+        <v>0.0001085073784017343</v>
       </c>
       <c r="AA3">
-        <v>0.7699287088893266</v>
+        <v>0.9324241592517576</v>
       </c>
       <c r="AB3">
-        <v>-10.6504711470484</v>
+        <v>-0.9592686334412081</v>
       </c>
       <c r="AC3">
-        <v>-12.99999999999999</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AD3">
-        <v>0.982772927328829</v>
+        <v>0.9998598493608297</v>
       </c>
       <c r="AE3">
-        <v>-0.1848171347833424</v>
+        <v>-0.01674161390484424</v>
       </c>
       <c r="AF3">
-        <v>1.801481244684184</v>
+        <v>1.914657053286112</v>
       </c>
       <c r="AG3">
-        <v>1.800781479358673</v>
+        <v>1.913974374212453</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.8693811765366158</v>
+        <v>0.9657322056629883</v>
       </c>
       <c r="AM3">
-        <v>0.9431664961641471</v>
+        <v>0.980802500865403</v>
       </c>
       <c r="AN3">
-        <v>1.775534307736559</v>
+        <v>1.913248459490064</v>
       </c>
       <c r="AO3">
-        <v>-0.2828761497928835</v>
+        <v>-0.04453097012997838</v>
       </c>
       <c r="AP3">
-        <v>2.361775434609422</v>
+        <v>2.572103441121658</v>
       </c>
       <c r="AQ3">
-        <v>-3.357562199673891</v>
+        <v>-3.634458303085958</v>
       </c>
       <c r="AR3">
-        <v>2.09144541419215</v>
+        <v>2.272213487908998</v>
       </c>
       <c r="AS3">
-        <v>0.03676780140326514</v>
+        <v>0.0367699454151666</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,7 +1061,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C4" s="2">
         <v>46269</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C5" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.2636007990743293</v>
+        <v>0.1652916187970465</v>
       </c>
       <c r="G5">
-        <v>1.326965625014153</v>
+        <v>1.265249584116171</v>
       </c>
       <c r="H5">
-        <v>1.483259053053068</v>
+        <v>1.48808804508149</v>
       </c>
       <c r="I5">
-        <v>0.3305709736473645</v>
+        <v>0.3328844951005255</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,19 +1234,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5">
-        <v>-0.09677239805276622</v>
+        <v>-0.1009330815616983</v>
       </c>
       <c r="O5">
-        <v>-26.35055086528715</v>
+        <v>-27.59619454865325</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.326965625014153</v>
+        <v>1.265249584116171</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>0.7768253538447389</v>
+        <v>0.8830884112597904</v>
       </c>
       <c r="U5">
-        <v>0.7889382675797985</v>
+        <v>0.8215786912494414</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9967642457646022</v>
+        <v>0.997393321490408</v>
       </c>
       <c r="Y5">
-        <v>0.9993069539540662</v>
+        <v>0.9975806534519147</v>
       </c>
       <c r="Z5">
-        <v>0.002542708189464005</v>
+        <v>0.0001873319615066649</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>0.5362757071870204</v>
       </c>
       <c r="AB5">
-        <v>-52.63104527986711</v>
+        <v>-40.46197234739928</v>
       </c>
       <c r="AC5">
-        <v>-17</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AD5">
-        <v>0.6069453030980961</v>
+        <v>0.7608368417853951</v>
       </c>
       <c r="AE5">
-        <v>-0.7947436058548444</v>
+        <v>-0.6489432179952462</v>
       </c>
       <c r="AF5">
-        <v>1.832192258354971</v>
+        <v>1.475454777546457</v>
       </c>
       <c r="AG5">
-        <v>1.830922464754927</v>
+        <v>1.471885141123545</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1309,28 +1309,28 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>0.6065246620556859</v>
+        <v>0.5830136457390457</v>
       </c>
       <c r="AM5">
-        <v>0.874887377985875</v>
+        <v>0.8280291120453563</v>
       </c>
       <c r="AN5">
-        <v>1.163721289215734</v>
+        <v>1.106657712431845</v>
       </c>
       <c r="AO5">
-        <v>-1.407477171735819</v>
+        <v>-0.9700211311844404</v>
       </c>
       <c r="AP5">
-        <v>0.9366970932541001</v>
+        <v>0.9066759669440969</v>
       </c>
       <c r="AQ5">
-        <v>-2.934195662306072</v>
+        <v>-2.787668985716782</v>
       </c>
       <c r="AR5">
-        <v>0.756058952806959</v>
+        <v>0.7286936216643226</v>
       </c>
       <c r="AS5">
-        <v>0.04635764551651293</v>
+        <v>0.04420207090557568</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C6" s="2">
         <v>46269</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C7" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.9186078254815326</v>
+        <v>0.8502707438499056</v>
       </c>
       <c r="H7">
-        <v>1.439914996628222</v>
+        <v>1.44553000769589</v>
       </c>
       <c r="I7">
-        <v>0.3516104592594048</v>
+        <v>0.3544241984565693</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N7">
-        <v>-0.1395470923613386</v>
+        <v>-0.1430722133033969</v>
       </c>
       <c r="O7">
-        <v>-31.2835755493794</v>
+        <v>-32.79592282026289</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.9186078254815326</v>
+        <v>0.8502707438499056</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>0.6167893698679255</v>
+        <v>0.6302822519807366</v>
       </c>
       <c r="U7">
-        <v>0.6774518439681305</v>
+        <v>0.6835214301323543</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9968937128708948</v>
+        <v>0.9986980356772581</v>
       </c>
       <c r="Y7">
-        <v>0.9995865101102562</v>
+        <v>0.9995776669640914</v>
       </c>
       <c r="Z7">
-        <v>0.002692797239361444</v>
+        <v>0.0008796312868333267</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-69.0216477734084</v>
+        <v>-67.6280732430146</v>
       </c>
       <c r="AC7">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="AD7">
-        <v>0.3580151940233368</v>
+        <v>0.3806173303234104</v>
       </c>
       <c r="AE7">
-        <v>-0.9337157602013755</v>
+        <v>-0.9247326358777871</v>
       </c>
       <c r="AF7">
-        <v>2.162667432598103</v>
+        <v>1.894780330838864</v>
       </c>
       <c r="AG7">
-        <v>2.161773191479845</v>
+        <v>1.893980102509361</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1589,28 +1589,28 @@
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>0.3578671583602335</v>
+        <v>0.3804565830507756</v>
       </c>
       <c r="AM7">
-        <v>0.7973894243064548</v>
+        <v>0.8045241285136036</v>
       </c>
       <c r="AN7">
-        <v>0.8363871539247474</v>
+        <v>0.7608842998777121</v>
       </c>
       <c r="AO7">
-        <v>-1.987102177146234</v>
+        <v>-1.73260066518788</v>
       </c>
       <c r="AP7">
-        <v>0.5224674247282514</v>
+        <v>0.5363422346182095</v>
       </c>
       <c r="AQ7">
-        <v>-2.490430584919363</v>
+        <v>-1.987207813225518</v>
       </c>
       <c r="AR7">
-        <v>0.4621968101108876</v>
+        <v>0.440719185432676</v>
       </c>
       <c r="AS7">
-        <v>0.06580274959423874</v>
+        <v>0.06342169347234336</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C8" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.3948205979537826</v>
+        <v>0.4445940546269952</v>
       </c>
       <c r="H8">
-        <v>1.437177129384864</v>
+        <v>1.437489320013096</v>
       </c>
       <c r="I8">
-        <v>0.355963254388616</v>
+        <v>0.3562793903975913</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>-0.0008900411076108866</v>
+        <v>-0.001875982628573232</v>
       </c>
       <c r="O8">
-        <v>-0.2002985935790458</v>
+        <v>-0.4400394873087929</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.3948205979537826</v>
+        <v>0.4445940546269952</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7395504278905823</v>
+        <v>0.7798578699661117</v>
       </c>
       <c r="U8">
-        <v>0.7327718985221117</v>
+        <v>0.7509089809896883</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9955479898089094</v>
+        <v>0.9901575286241514</v>
       </c>
       <c r="Y8">
-        <v>0.9998968238853981</v>
+        <v>0.9998917580197519</v>
       </c>
       <c r="Z8">
-        <v>0.004348834076488783</v>
+        <v>0.009734229395600535</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>76.2784825904794</v>
+        <v>69.19110496674028</v>
       </c>
       <c r="AC8">
-        <v>-20</v>
+        <v>-31.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.2372029942803253</v>
+        <v>0.3552520875871892</v>
       </c>
       <c r="AE8">
-        <v>0.9714601070061745</v>
+        <v>0.9347705356208784</v>
       </c>
       <c r="AF8">
-        <v>0.9874249012701115</v>
+        <v>0.8394404709637894</v>
       </c>
       <c r="AG8">
-        <v>0.9873230226053373</v>
+        <v>0.8393496082649119</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.1185892602985018</v>
+        <v>0.1776068171988708</v>
       </c>
       <c r="AM8">
-        <v>0.5518979704898639</v>
+        <v>0.590344826896922</v>
       </c>
       <c r="AN8">
-        <v>0.2055446885482178</v>
+        <v>0.2482940020501148</v>
       </c>
       <c r="AO8">
-        <v>0.9612997197379524</v>
+        <v>0.7932259820012609</v>
       </c>
       <c r="AP8">
-        <v>0.9259332079045794</v>
+        <v>0.9684795646683404</v>
       </c>
       <c r="AQ8">
-        <v>0.3837967364151892</v>
+        <v>0.2161796770962048</v>
       </c>
       <c r="AR8">
-        <v>0.9065788629734597</v>
+        <v>0.936830457341394</v>
       </c>
       <c r="AS8">
-        <v>0.1281787743608199</v>
+        <v>0.1079527645743192</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C9" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.549014817771017</v>
+        <v>0.7383830957075519</v>
       </c>
       <c r="G9">
-        <v>3.070870196303257</v>
+        <v>3.315084039482191</v>
       </c>
       <c r="H9">
-        <v>3.009483551875388</v>
+        <v>3.015264413579404</v>
       </c>
       <c r="I9">
-        <v>0.6262049643298595</v>
+        <v>0.6288609203032682</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N9">
-        <v>0.5419150963951063</v>
+        <v>0.5617610323352777</v>
       </c>
       <c r="O9">
-        <v>64.51095913890873</v>
+        <v>69.06695751904576</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.070870196303257</v>
+        <v>3.315084039482191</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9948881507480453</v>
+        <v>-0.9959730809498482</v>
       </c>
       <c r="U9">
-        <v>0.9299900733444458</v>
+        <v>0.958839200969604</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9995618646400203</v>
+        <v>0.9969045515782806</v>
       </c>
       <c r="Y9">
-        <v>0.9997527313686917</v>
+        <v>0.9995754007441581</v>
       </c>
       <c r="Z9">
-        <v>0.0001908667286714127</v>
+        <v>0.002670849165877454</v>
       </c>
       <c r="AA9">
-        <v>0.8060787105429703</v>
+        <v>0.9784433336488914</v>
       </c>
       <c r="AB9">
-        <v>171.8478895639152</v>
+        <v>-172.8550226638579</v>
       </c>
       <c r="AC9">
-        <v>4.000000000000005</v>
+        <v>16</v>
       </c>
       <c r="AD9">
-        <v>-0.9898950987814116</v>
+        <v>-0.9922346046624108</v>
       </c>
       <c r="AE9">
-        <v>0.1418015987517047</v>
+        <v>-0.1243804217328009</v>
       </c>
       <c r="AF9">
-        <v>2.344507022383358</v>
+        <v>2.505980097348574</v>
       </c>
       <c r="AG9">
-        <v>2.34392729934084</v>
+        <v>2.504916060064085</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.8936931948413673</v>
+        <v>-0.9811232083644139</v>
       </c>
       <c r="AM9">
-        <v>0.9526322926880262</v>
+        <v>0.9874653868282052</v>
       </c>
       <c r="AN9">
-        <v>-2.317200621738648</v>
+        <v>-2.486799220209178</v>
       </c>
       <c r="AO9">
-        <v>0.3499698600855806</v>
+        <v>-0.2386370094443492</v>
       </c>
       <c r="AP9">
-        <v>-3.880769218498545</v>
+        <v>-4.253807111421811</v>
       </c>
       <c r="AQ9">
-        <v>2.975008256556966</v>
+        <v>3.054540062391226</v>
       </c>
       <c r="AR9">
-        <v>3.628535748176443</v>
+        <v>3.981884980820916</v>
       </c>
       <c r="AS9">
-        <v>0.03643623356022297</v>
+        <v>0.03830034373834421</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C10" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.06357175292922376</v>
+        <v>0.466976522414023</v>
       </c>
       <c r="G10">
-        <v>1.646754074149344</v>
+        <v>2.015694159796184</v>
       </c>
       <c r="H10">
-        <v>2.045483026583271</v>
+        <v>2.045787179778024</v>
       </c>
       <c r="I10">
-        <v>0.4568092866469108</v>
+        <v>0.4556306933982429</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N10">
-        <v>19.53008378016131</v>
+        <v>20.65706814132444</v>
       </c>
       <c r="O10">
-        <v>22.52604818934422</v>
+        <v>24.11397931948173</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.646754074149344</v>
+        <v>2.015694159796184</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.8744581198095189</v>
+        <v>-0.778959500904514</v>
       </c>
       <c r="U10">
-        <v>0.8028025154358138</v>
+        <v>0.8205065222934803</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9862320846376967</v>
+        <v>0.995870422413481</v>
       </c>
       <c r="Y10">
-        <v>0.999042394328587</v>
+        <v>0.9997130740973819</v>
       </c>
       <c r="Z10">
-        <v>0.01281030969089025</v>
+        <v>0.003842651683900855</v>
       </c>
       <c r="AA10">
-        <v>0.4045172305550302</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>-137.0405313824414</v>
+        <v>-126.5952258455755</v>
       </c>
       <c r="AC10">
-        <v>31.00000000000001</v>
+        <v>18</v>
       </c>
       <c r="AD10">
-        <v>-0.7318359683680616</v>
+        <v>-0.5961579783596169</v>
       </c>
       <c r="AE10">
-        <v>-0.6814808254109439</v>
+        <v>-0.8028671526710844</v>
       </c>
       <c r="AF10">
-        <v>1.580929354749255</v>
+        <v>2.376729813125092</v>
       </c>
       <c r="AG10">
-        <v>1.579415447833044</v>
+        <v>2.376047867778182</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.5134459637039459</v>
+        <v>-0.5959869251935731</v>
       </c>
       <c r="AM10">
-        <v>0.7900713387179813</v>
+        <v>0.868858137498096</v>
       </c>
       <c r="AN10">
-        <v>-1.169217851117298</v>
+        <v>-1.44781087598651</v>
       </c>
       <c r="AO10">
-        <v>-1.031464816053185</v>
+        <v>-1.872466266693213</v>
       </c>
       <c r="AP10">
-        <v>-2.357658758448784</v>
+        <v>-2.838133221771392</v>
       </c>
       <c r="AQ10">
-        <v>-0.2336889736355396</v>
+        <v>0.5896476876126722</v>
       </c>
       <c r="AR10">
-        <v>2.360102963382795</v>
+        <v>2.734505105853313</v>
       </c>
       <c r="AS10">
-        <v>0.06698490612299135</v>
+        <v>0.06592554629248365</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C11" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.119541820677235</v>
+        <v>1.037737926002288</v>
       </c>
       <c r="H11">
-        <v>2.517460754662237</v>
+        <v>2.493577000756861</v>
       </c>
       <c r="I11">
-        <v>0.5977485504520954</v>
+        <v>0.5928901914314056</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11">
-        <v>-1851.678855060292</v>
+        <v>-1936.458220189157</v>
       </c>
       <c r="O11">
-        <v>-21.60553064398952</v>
+        <v>-23.01305559859611</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.119541820677235</v>
+        <v>1.037737926002288</v>
       </c>
       <c r="R11" t="s">
         <v>59</v>
@@ -2095,10 +2095,10 @@
         <v>64</v>
       </c>
       <c r="T11">
-        <v>0.7040538250039452</v>
+        <v>0.75060117602011</v>
       </c>
       <c r="U11">
-        <v>0.7166488838727829</v>
+        <v>0.7376234054156443</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9919968081445537</v>
+        <v>0.9956529365421327</v>
       </c>
       <c r="Y11">
-        <v>0.9992986504840303</v>
+        <v>0.9994115048263792</v>
       </c>
       <c r="Z11">
-        <v>0.007301842339476616</v>
+        <v>0.003758568284246477</v>
       </c>
       <c r="AA11">
-        <v>0.7180225199428284</v>
+        <v>0.4550776311383243</v>
       </c>
       <c r="AB11">
-        <v>-62.65883005435044</v>
+        <v>-60.67437586482892</v>
       </c>
       <c r="AC11">
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="AD11">
-        <v>0.4592879529193528</v>
+        <v>0.4897724144346818</v>
       </c>
       <c r="AE11">
-        <v>-0.8882874401358777</v>
+        <v>-0.8718503209030908</v>
       </c>
       <c r="AF11">
-        <v>2.06550865302153</v>
+        <v>1.825826424593748</v>
       </c>
       <c r="AG11">
-        <v>2.064060009527502</v>
+        <v>1.824751934555005</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2149,28 +2149,28 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>0.3942568172314658</v>
+        <v>0.3561187447277421</v>
       </c>
       <c r="AM11">
-        <v>0.7725565058440367</v>
+        <v>0.7291459083404572</v>
       </c>
       <c r="AN11">
-        <v>1.033817696551966</v>
+        <v>0.9620947343368633</v>
       </c>
       <c r="AO11">
-        <v>-1.76904826894771</v>
+        <v>-1.542431762774853</v>
       </c>
       <c r="AP11">
-        <v>0.5619524885783533</v>
+        <v>0.5009769649772509</v>
       </c>
       <c r="AQ11">
-        <v>-3.17769607539686</v>
+        <v>-2.930959714356365</v>
       </c>
       <c r="AR11">
-        <v>0.5214568482096681</v>
+        <v>0.4725572360986167</v>
       </c>
       <c r="AS11">
-        <v>0.05725941126497041</v>
+        <v>0.05730245937896543</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C2" s="2">
         <v>46272</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46269</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.2433881329000335</v>
+        <v>0.3664169303597309</v>
       </c>
       <c r="G2">
-        <v>0.9386445228628102</v>
+        <v>1.002342793513443</v>
       </c>
       <c r="H2">
-        <v>1.071153491147837</v>
+        <v>1.071340881855671</v>
       </c>
       <c r="I2">
-        <v>0.2581894784963443</v>
+        <v>0.2582591062177085</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2">
-        <v>-0.3354238807107995</v>
+        <v>-0.3649027957069002</v>
       </c>
       <c r="O2">
-        <v>-8.968895545955128</v>
+        <v>-9.789102918153155</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.9386445228628102</v>
+        <v>1.002342793513443</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.9999886134501064</v>
+        <v>0.994515672133489</v>
       </c>
       <c r="U2">
-        <v>0.8864448097489284</v>
+        <v>0.9024328318020196</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9994281823122664</v>
+        <v>0.9989865725386777</v>
       </c>
       <c r="Y2">
-        <v>0.9997668550455016</v>
+        <v>0.9997529591519594</v>
       </c>
       <c r="Z2">
-        <v>0.0003386727332351791</v>
+        <v>0.0007663866132816555</v>
       </c>
       <c r="AA2">
-        <v>0.05397374160614632</v>
+        <v>0.169381509783897</v>
       </c>
       <c r="AB2">
-        <v>0.4703143851624944</v>
+        <v>9.920448444963712</v>
       </c>
       <c r="AC2">
-        <v>-5.999999999999996</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>0.9999663101695172</v>
+        <v>0.9850479031788599</v>
       </c>
       <c r="AE2">
-        <v>0.00820844235899219</v>
+        <v>0.1722806676412979</v>
       </c>
       <c r="AF2">
-        <v>0.7688663605380142</v>
+        <v>0.8213177222642499</v>
       </c>
       <c r="AG2">
-        <v>0.7686871032253711</v>
+        <v>0.821114823237631</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.526846256513993</v>
+        <v>0.5758061193326925</v>
       </c>
       <c r="AM2">
-        <v>0.8050287699562102</v>
+        <v>0.8234993582085794</v>
       </c>
       <c r="AN2">
-        <v>0.7682394663389822</v>
+        <v>0.8108816373906355</v>
       </c>
       <c r="AO2">
-        <v>0.01696259708175796</v>
+        <v>0.1251687777128305</v>
       </c>
       <c r="AP2">
-        <v>0.9143838870640846</v>
+        <v>1.017977037020363</v>
       </c>
       <c r="AQ2">
-        <v>-1.661593666137039</v>
+        <v>-1.640169259271452</v>
       </c>
       <c r="AR2">
-        <v>0.7790072515078634</v>
+        <v>0.8820401676251696</v>
       </c>
       <c r="AS2">
-        <v>0.03782847121199816</v>
+        <v>0.03869900270029161</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C3" s="2">
         <v>46272</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46269</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.400270608960956</v>
+        <v>2.603017088231519</v>
       </c>
       <c r="H3">
-        <v>1.928408320178992</v>
+        <v>1.939968106143602</v>
       </c>
       <c r="I3">
-        <v>0.4329772036798598</v>
+        <v>0.4347751532174389</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3">
-        <v>-0.09550746151652557</v>
+        <v>-0.1019046781651708</v>
       </c>
       <c r="O3">
-        <v>-28.96987241320239</v>
+        <v>-32.43158659496232</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.400270608960956</v>
+        <v>2.603017088231519</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9999315107325071</v>
+        <v>0.9902667861457664</v>
       </c>
       <c r="U3">
-        <v>0.9998800412718265</v>
+        <v>0.9955117299807449</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9995349383903913</v>
+        <v>0.9969635476418582</v>
       </c>
       <c r="Y3">
-        <v>0.999643445768793</v>
+        <v>0.9995667048606002</v>
       </c>
       <c r="Z3">
-        <v>0.0001085073784017343</v>
+        <v>0.002603157218741936</v>
       </c>
       <c r="AA3">
-        <v>0.9324241592517576</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>-0.9592686334412081</v>
+        <v>11.32491668756644</v>
       </c>
       <c r="AC3">
-        <v>3.000000000000004</v>
+        <v>16</v>
       </c>
       <c r="AD3">
-        <v>0.9998598493608297</v>
+        <v>0.9805293531091277</v>
       </c>
       <c r="AE3">
-        <v>-0.01674161390484424</v>
+        <v>0.1963725736741146</v>
       </c>
       <c r="AF3">
-        <v>1.914657053286112</v>
+        <v>2.099045165750148</v>
       </c>
       <c r="AG3">
-        <v>1.913974374212453</v>
+        <v>2.098135659682447</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.9657322056629883</v>
+        <v>0.9801044945063867</v>
       </c>
       <c r="AM3">
-        <v>0.980802500865403</v>
+        <v>0.9884276915057459</v>
       </c>
       <c r="AN3">
-        <v>1.913248459490064</v>
+        <v>2.064471096028702</v>
       </c>
       <c r="AO3">
-        <v>-0.04453097012997838</v>
+        <v>0.3423932881954153</v>
       </c>
       <c r="AP3">
-        <v>2.572103441121658</v>
+        <v>2.836125209226585</v>
       </c>
       <c r="AQ3">
-        <v>-3.634458303085958</v>
+        <v>-3.832640055995153</v>
       </c>
       <c r="AR3">
-        <v>2.272213487908998</v>
+        <v>2.513968953375532</v>
       </c>
       <c r="AS3">
-        <v>0.0367699454151666</v>
+        <v>0.0371964075213495</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C4" s="2">
         <v>46272</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46269</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.02266680764321327</v>
+        <v>0.01657963019459711</v>
       </c>
       <c r="H4">
-        <v>2.078328559069164</v>
+        <v>2.078603444657875</v>
       </c>
       <c r="I4">
-        <v>0.4925510102636658</v>
+        <v>0.4924786608804972</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1094,19 +1094,19 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4">
-        <v>-0.2351986705510734</v>
+        <v>-0.2402355136844739</v>
       </c>
       <c r="O4">
-        <v>-8.47999327250842</v>
+        <v>-8.506062700006634</v>
       </c>
       <c r="P4">
-        <v>0.6741866724274798</v>
+        <v>0.6284577328223165</v>
       </c>
       <c r="Q4">
-        <v>0.06956992156242608</v>
+        <v>0.04462380638558195</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>0.6602921187952704</v>
+        <v>0.6496908965436862</v>
       </c>
       <c r="U4">
-        <v>0.6470492783123629</v>
+        <v>0.6422283636159762</v>
       </c>
       <c r="V4" t="s">
         <v>68</v>
@@ -1127,34 +1127,34 @@
         <v>68</v>
       </c>
       <c r="X4">
-        <v>0.9844391095736416</v>
+        <v>0.9838826395771607</v>
       </c>
       <c r="Y4">
-        <v>0.9996712994179653</v>
+        <v>0.9994698406852699</v>
       </c>
       <c r="Z4">
-        <v>0.01523218984432373</v>
+        <v>0.01558720110810918</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-83.67845655133443</v>
+        <v>-85.2836487829335</v>
       </c>
       <c r="AC4">
-        <v>-41.99999999999999</v>
+        <v>-44</v>
       </c>
       <c r="AD4">
-        <v>0.1101080367310409</v>
+        <v>0.0822229282328244</v>
       </c>
       <c r="AE4">
-        <v>-0.993919624641367</v>
+        <v>-0.9966139624111333</v>
       </c>
       <c r="AF4">
-        <v>0.9680903059088</v>
+        <v>0.8118185826057236</v>
       </c>
       <c r="AG4">
-        <v>0.9677720940617855</v>
+        <v>0.8113881894222842</v>
       </c>
       <c r="AH4" t="s">
         <v>70</v>
@@ -1169,28 +1169,28 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>0.05503592207764033</v>
+        <v>0.04108966849076869</v>
       </c>
       <c r="AM4">
-        <v>0.5061050693369583</v>
+        <v>0.4967065775528007</v>
       </c>
       <c r="AN4">
-        <v>0.2001709252836051</v>
+        <v>0.1601042929883315</v>
       </c>
       <c r="AO4">
-        <v>-0.9317671805205791</v>
+        <v>-0.7825234523324572</v>
       </c>
       <c r="AP4">
-        <v>-0.5822557722998513</v>
+        <v>-0.5227757194932624</v>
       </c>
       <c r="AQ4">
-        <v>-1.636158976104565</v>
+        <v>-1.26713315497497</v>
       </c>
       <c r="AR4">
-        <v>0.7054265234644145</v>
+        <v>0.6065858699962972</v>
       </c>
       <c r="AS4">
-        <v>0.1787486431909451</v>
+        <v>0.1851649677126074</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C5" s="2">
         <v>46272</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46269</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.1652916187970465</v>
+        <v>0.1096653187544404</v>
       </c>
       <c r="G5">
-        <v>1.265249584116171</v>
+        <v>1.230944690076117</v>
       </c>
       <c r="H5">
-        <v>1.48808804508149</v>
+        <v>1.492457133107204</v>
       </c>
       <c r="I5">
-        <v>0.3328844951005255</v>
+        <v>0.3349848932159966</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,19 +1234,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5">
-        <v>-0.1009330815616983</v>
+        <v>-0.1048678555225676</v>
       </c>
       <c r="O5">
-        <v>-27.59619454865325</v>
+        <v>-29.46613100483611</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.265249584116171</v>
+        <v>1.230944690076117</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>0.8830884112597904</v>
+        <v>0.9392227807266568</v>
       </c>
       <c r="U5">
-        <v>0.8215786912494414</v>
+        <v>0.8381969984093558</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.997393321490408</v>
+        <v>0.9926628797477552</v>
       </c>
       <c r="Y5">
-        <v>0.9975806534519147</v>
+        <v>0.9963877970767767</v>
       </c>
       <c r="Z5">
-        <v>0.0001873319615066649</v>
+        <v>0.003724917329021471</v>
       </c>
       <c r="AA5">
-        <v>0.5362757071870204</v>
+        <v>0.2813168943633795</v>
       </c>
       <c r="AB5">
-        <v>-40.46197234739928</v>
+        <v>-30.92133310190683</v>
       </c>
       <c r="AC5">
-        <v>5.000000000000007</v>
+        <v>22.00000000000001</v>
       </c>
       <c r="AD5">
-        <v>0.7608368417853951</v>
+        <v>0.857873637963354</v>
       </c>
       <c r="AE5">
-        <v>-0.6489432179952462</v>
+        <v>-0.5138607022214484</v>
       </c>
       <c r="AF5">
-        <v>1.475454777546457</v>
+        <v>1.312452426908651</v>
       </c>
       <c r="AG5">
-        <v>1.471885141123545</v>
+        <v>1.30771158241558</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1309,28 +1309,28 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>0.5830136457390457</v>
+        <v>0.5476187116263899</v>
       </c>
       <c r="AM5">
-        <v>0.8280291120453563</v>
+        <v>0.8059770240761885</v>
       </c>
       <c r="AN5">
-        <v>1.106657712431845</v>
+        <v>1.073903918500121</v>
       </c>
       <c r="AO5">
-        <v>-0.9700211311844404</v>
+        <v>-0.7376161852156446</v>
       </c>
       <c r="AP5">
-        <v>0.9066759669440969</v>
+        <v>0.8950066191053321</v>
       </c>
       <c r="AQ5">
-        <v>-2.787668985716782</v>
+        <v>-2.700938541313292</v>
       </c>
       <c r="AR5">
-        <v>0.7286936216643226</v>
+        <v>0.7179606737755675</v>
       </c>
       <c r="AS5">
-        <v>0.04420207090557568</v>
+        <v>0.04256116774910201</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C6" s="2">
         <v>46272</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46269</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1356,37 +1356,37 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1215937009524473</v>
+        <v>0.1227504124957605</v>
       </c>
       <c r="H6">
-        <v>0.9432871034292907</v>
+        <v>0.9433001337824681</v>
       </c>
       <c r="I6">
-        <v>0.2571431839511639</v>
+        <v>0.257051643633687</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L6">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>-0.3703216696044252</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>-6.667399753677326</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.09735158169315852</v>
+        <v>0.1137245349241522</v>
       </c>
       <c r="Q6">
-        <v>0.1347077095426909</v>
+        <v>0.1385014223374168</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>0.3461365148896858</v>
+        <v>0.3969018922560495</v>
       </c>
       <c r="U6">
-        <v>0.455716061937822</v>
+        <v>0.4535576362848359</v>
       </c>
       <c r="V6" t="s">
         <v>68</v>
@@ -1407,34 +1407,34 @@
         <v>68</v>
       </c>
       <c r="X6">
-        <v>0.995551228104561</v>
+        <v>0.9955663368490487</v>
       </c>
       <c r="Y6">
-        <v>0.9998185209498537</v>
+        <v>0.9998071390784544</v>
       </c>
       <c r="Z6">
-        <v>0.004267292845292703</v>
+        <v>0.004240802229405705</v>
       </c>
       <c r="AA6">
-        <v>0.5563029909034597</v>
+        <v>0.1880285614085631</v>
       </c>
       <c r="AB6">
-        <v>-94.30625840196588</v>
+        <v>-96.85647803352097</v>
       </c>
       <c r="AC6">
-        <v>-21</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD6">
-        <v>-0.07508764863196088</v>
+        <v>-0.119382704170757</v>
       </c>
       <c r="AE6">
-        <v>-0.9971769376710049</v>
+        <v>-0.992848311649306</v>
       </c>
       <c r="AF6">
-        <v>0.9303458402562511</v>
+        <v>0.7873767214187826</v>
       </c>
       <c r="AG6">
-        <v>0.9301770019768538</v>
+        <v>0.7872248672186862</v>
       </c>
       <c r="AH6" t="s">
         <v>70</v>
@@ -1449,28 +1449,28 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>-0.05841896233076303</v>
+        <v>-0.07090135440826592</v>
       </c>
       <c r="AM6">
-        <v>0.5927124787755713</v>
+        <v>0.5380106563305191</v>
       </c>
       <c r="AN6">
-        <v>-0.03085567019374423</v>
+        <v>-0.05377530696909347</v>
       </c>
       <c r="AO6">
-        <v>-0.9256928380483996</v>
+        <v>-0.7820390644770328</v>
       </c>
       <c r="AP6">
-        <v>-0.4875919132620308</v>
+        <v>-0.4085404372394565</v>
       </c>
       <c r="AQ6">
-        <v>-0.617506360995302</v>
+        <v>-0.2464802607138144</v>
       </c>
       <c r="AR6">
-        <v>0.499935264061904</v>
+        <v>0.3924626088054131</v>
       </c>
       <c r="AS6">
-        <v>0.2734059755143843</v>
+        <v>0.2356157725325308</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C7" s="2">
         <v>46272</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46269</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8502707438499056</v>
+        <v>0.9145432411443594</v>
       </c>
       <c r="H7">
-        <v>1.44553000769589</v>
+        <v>1.450610255804733</v>
       </c>
       <c r="I7">
-        <v>0.3544241984565693</v>
+        <v>0.3569679572850659</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7">
-        <v>-0.1430722133033969</v>
+        <v>-0.1463876586164193</v>
       </c>
       <c r="O7">
-        <v>-32.79592282026289</v>
+        <v>-33.97309938880834</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.8502707438499056</v>
+        <v>0.9145432411443594</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>0.6302822519807366</v>
+        <v>0.720610870143059</v>
       </c>
       <c r="U7">
-        <v>0.6835214301323543</v>
+        <v>0.7238971039999447</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9986980356772581</v>
+        <v>0.9981268018448028</v>
       </c>
       <c r="Y7">
-        <v>0.9995776669640914</v>
+        <v>0.9984888497422726</v>
       </c>
       <c r="Z7">
-        <v>0.0008796312868333267</v>
+        <v>0.0003620478974697416</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0.8360836497435948</v>
       </c>
       <c r="AB7">
-        <v>-67.6280732430146</v>
+        <v>-59.38848286026088</v>
       </c>
       <c r="AC7">
-        <v>-10</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AD7">
-        <v>0.3806173303234104</v>
+        <v>0.5092144249490446</v>
       </c>
       <c r="AE7">
-        <v>-0.9247326358777871</v>
+        <v>-0.8606396861775628</v>
       </c>
       <c r="AF7">
-        <v>1.894780330838864</v>
+        <v>1.561370507760722</v>
       </c>
       <c r="AG7">
-        <v>1.893980102509361</v>
+        <v>1.559011042315512</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1589,28 +1589,28 @@
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>0.3804565830507756</v>
+        <v>0.4667737071973243</v>
       </c>
       <c r="AM7">
-        <v>0.8045241285136036</v>
+        <v>0.812129388705314</v>
       </c>
       <c r="AN7">
-        <v>0.7608842998777121</v>
+        <v>0.7685281417255759</v>
       </c>
       <c r="AO7">
-        <v>-1.73260066518788</v>
+        <v>-1.355771977675915</v>
       </c>
       <c r="AP7">
-        <v>0.5363422346182095</v>
+        <v>0.7897851815310688</v>
       </c>
       <c r="AQ7">
-        <v>-1.987207813225518</v>
+        <v>-1.350891593156276</v>
       </c>
       <c r="AR7">
-        <v>0.440719185432676</v>
+        <v>0.737424183407118</v>
       </c>
       <c r="AS7">
-        <v>0.06342169347234336</v>
+        <v>0.04881844091942383</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C8" s="2">
         <v>46272</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46269</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.4445940546269952</v>
+        <v>0.5257793442834557</v>
       </c>
       <c r="H8">
-        <v>1.437489320013096</v>
+        <v>1.437771778200543</v>
       </c>
       <c r="I8">
-        <v>0.3562793903975913</v>
+        <v>0.3564998446067633</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>-0.001875982628573232</v>
+        <v>-0.003080145647887595</v>
       </c>
       <c r="O8">
-        <v>-0.4400394873087929</v>
+        <v>-0.7089525535622916</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4445940546269952</v>
+        <v>0.5257793442834557</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7798578699661117</v>
+        <v>0.8345605825612374</v>
       </c>
       <c r="U8">
-        <v>0.7509089809896883</v>
+        <v>0.775395298077429</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9901575286241514</v>
+        <v>0.9810981667059494</v>
       </c>
       <c r="Y8">
-        <v>0.9998917580197519</v>
+        <v>0.9993721436994882</v>
       </c>
       <c r="Z8">
-        <v>0.009734229395600535</v>
+        <v>0.01827397699353883</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>69.19110496674028</v>
+        <v>58.98259758085585</v>
       </c>
       <c r="AC8">
-        <v>-31.99999999999999</v>
+        <v>-44</v>
       </c>
       <c r="AD8">
-        <v>0.3552520875871892</v>
+        <v>0.5152983981553437</v>
       </c>
       <c r="AE8">
-        <v>0.9347705356208784</v>
+        <v>0.8570108289038925</v>
       </c>
       <c r="AF8">
-        <v>0.8394404709637894</v>
+        <v>0.7236538951625455</v>
       </c>
       <c r="AG8">
-        <v>0.8393496082649119</v>
+        <v>0.7231995445050778</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.1776068171988708</v>
+        <v>0.2574874324047091</v>
       </c>
       <c r="AM8">
-        <v>0.590344826896922</v>
+        <v>0.6404964866540324</v>
       </c>
       <c r="AN8">
-        <v>0.2482940020501148</v>
+        <v>0.3106804279234047</v>
       </c>
       <c r="AO8">
-        <v>0.7932259820012609</v>
+        <v>0.6383908648513057</v>
       </c>
       <c r="AP8">
-        <v>0.9684795646683404</v>
+        <v>1.063794997024615</v>
       </c>
       <c r="AQ8">
-        <v>0.2161796770962048</v>
+        <v>0.1748740564399984</v>
       </c>
       <c r="AR8">
-        <v>0.936830457341394</v>
+        <v>1.032793010352023</v>
       </c>
       <c r="AS8">
-        <v>0.1079527645743192</v>
+        <v>0.09248855391594409</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C9" s="2">
         <v>46272</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46269</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.7383830957075519</v>
+        <v>0.9038475664035587</v>
       </c>
       <c r="G9">
-        <v>3.315084039482191</v>
+        <v>3.53105594817804</v>
       </c>
       <c r="H9">
-        <v>3.015264413579404</v>
+        <v>3.020945889670893</v>
       </c>
       <c r="I9">
-        <v>0.6288609203032682</v>
+        <v>0.6315626252869405</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N9">
-        <v>0.5617610323352777</v>
+        <v>0.5820695800011771</v>
       </c>
       <c r="O9">
-        <v>69.06695751904576</v>
+        <v>75.91386762323701</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.315084039482191</v>
+        <v>3.53105594817804</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9959730809498482</v>
+        <v>-0.9917129125256611</v>
       </c>
       <c r="U9">
-        <v>0.958839200969604</v>
+        <v>0.9817957314688525</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9969045515782806</v>
+        <v>0.9980136378313611</v>
       </c>
       <c r="Y9">
-        <v>0.9995754007441581</v>
+        <v>0.9997911434870851</v>
       </c>
       <c r="Z9">
-        <v>0.002670849165877454</v>
+        <v>0.001777505655723988</v>
       </c>
       <c r="AA9">
-        <v>0.9784433336488914</v>
+        <v>1</v>
       </c>
       <c r="AB9">
-        <v>-172.8550226638579</v>
+        <v>-169.6354953647062</v>
       </c>
       <c r="AC9">
-        <v>16</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AD9">
-        <v>-0.9922346046624108</v>
+        <v>-0.9836831156550757</v>
       </c>
       <c r="AE9">
-        <v>-0.1243804217328009</v>
+        <v>-0.1799097773194191</v>
       </c>
       <c r="AF9">
-        <v>2.505980097348574</v>
+        <v>2.697889675278914</v>
       </c>
       <c r="AG9">
-        <v>2.504916060064085</v>
+        <v>2.697326203449106</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9811232083644139</v>
+        <v>-0.9834776670297267</v>
       </c>
       <c r="AM9">
-        <v>0.9874653868282052</v>
+        <v>0.9893743134434058</v>
       </c>
       <c r="AN9">
-        <v>-2.486799220209178</v>
+        <v>-2.659346103125017</v>
       </c>
       <c r="AO9">
-        <v>-0.2386370094443492</v>
+        <v>-0.4214259324925717</v>
       </c>
       <c r="AP9">
-        <v>-4.253807111421811</v>
+        <v>-4.492511969630058</v>
       </c>
       <c r="AQ9">
-        <v>3.054540062391226</v>
+        <v>3.605115645282452</v>
       </c>
       <c r="AR9">
-        <v>3.981884980820916</v>
+        <v>4.162264000732653</v>
       </c>
       <c r="AS9">
-        <v>0.03830034373834421</v>
+        <v>0.03771680982397817</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C10" s="2">
         <v>46272</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46269</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.466976522414023</v>
+        <v>0.6713171198624325</v>
       </c>
       <c r="G10">
-        <v>2.015694159796184</v>
+        <v>2.202363507106859</v>
       </c>
       <c r="H10">
-        <v>2.045787179778024</v>
+        <v>2.046652624782537</v>
       </c>
       <c r="I10">
-        <v>0.4556306933982429</v>
+        <v>0.4544521949976669</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10">
-        <v>20.65706814132444</v>
+        <v>22.08762140444414</v>
       </c>
       <c r="O10">
-        <v>24.11397931948173</v>
+        <v>21.41459138935036</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.015694159796184</v>
+        <v>2.202363507106859</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.778959500904514</v>
+        <v>-0.7474814155486789</v>
       </c>
       <c r="U10">
-        <v>0.8205065222934803</v>
+        <v>0.8370417231215145</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.995870422413481</v>
+        <v>0.9987133226783429</v>
       </c>
       <c r="Y10">
-        <v>0.9997130740973819</v>
+        <v>0.9999100725809763</v>
       </c>
       <c r="Z10">
-        <v>0.003842651683900855</v>
+        <v>0.001196749902633409</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-126.5952258455755</v>
+        <v>-121.4609328829015</v>
       </c>
       <c r="AC10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>-0.5961579783596169</v>
+        <v>-0.5219170707563664</v>
       </c>
       <c r="AE10">
-        <v>-0.8028671526710844</v>
+        <v>-0.8529962316757876</v>
       </c>
       <c r="AF10">
-        <v>2.376729813125092</v>
+        <v>2.955774704857857</v>
       </c>
       <c r="AG10">
-        <v>2.376047867778182</v>
+        <v>2.955508899667434</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.5959869251935731</v>
+        <v>-0.5218701361012489</v>
       </c>
       <c r="AM10">
-        <v>0.868858137498096</v>
+        <v>0.8464482310779792</v>
       </c>
       <c r="AN10">
-        <v>-1.44781087598651</v>
+        <v>-1.571460909393736</v>
       </c>
       <c r="AO10">
-        <v>-1.872466266693213</v>
+        <v>-2.4989291304811</v>
       </c>
       <c r="AP10">
-        <v>-2.838133221771392</v>
+        <v>-3.155973934756926</v>
       </c>
       <c r="AQ10">
-        <v>0.5896476876126722</v>
+        <v>0.7191873413693028</v>
       </c>
       <c r="AR10">
-        <v>2.734505105853313</v>
+        <v>3.025631969106124</v>
       </c>
       <c r="AS10">
-        <v>0.06592554629248365</v>
+        <v>0.06730277034848185</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C11" s="2">
         <v>46272</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46269</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.037737926002288</v>
+        <v>0.9012724993344023</v>
       </c>
       <c r="H11">
-        <v>2.493577000756861</v>
+        <v>2.47131790628759</v>
       </c>
       <c r="I11">
-        <v>0.5928901914314056</v>
+        <v>0.5876186061208492</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11">
-        <v>-1936.458220189157</v>
+        <v>-2012.452748643014</v>
       </c>
       <c r="O11">
-        <v>-23.01305559859611</v>
+        <v>-24.21193436284993</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.037737926002288</v>
+        <v>0.9012724993344023</v>
       </c>
       <c r="R11" t="s">
         <v>59</v>
@@ -2095,10 +2095,10 @@
         <v>64</v>
       </c>
       <c r="T11">
-        <v>0.75060117602011</v>
+        <v>0.8396326438744856</v>
       </c>
       <c r="U11">
-        <v>0.7376234054156443</v>
+        <v>0.7775815498610414</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9956529365421327</v>
+        <v>0.9980060588095965</v>
       </c>
       <c r="Y11">
-        <v>0.9994115048263792</v>
+        <v>0.9989874404700918</v>
       </c>
       <c r="Z11">
-        <v>0.003758568284246477</v>
+        <v>0.0009813816604953285</v>
       </c>
       <c r="AA11">
-        <v>0.4550776311383243</v>
+        <v>0.05544383545829693</v>
       </c>
       <c r="AB11">
-        <v>-60.67437586482892</v>
+        <v>-56.01739052334261</v>
       </c>
       <c r="AC11">
-        <v>-20</v>
+        <v>-11</v>
       </c>
       <c r="AD11">
-        <v>0.4897724144346818</v>
+        <v>0.5589412466649271</v>
       </c>
       <c r="AE11">
-        <v>-0.8718503209030908</v>
+        <v>-0.8292072616521501</v>
       </c>
       <c r="AF11">
-        <v>1.825826424593748</v>
+        <v>1.466833979433798</v>
       </c>
       <c r="AG11">
-        <v>1.824751934555005</v>
+        <v>1.465348722709129</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2149,28 +2149,28 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>0.3561187447277421</v>
+        <v>0.2946668764127441</v>
       </c>
       <c r="AM11">
-        <v>0.7291459083404572</v>
+        <v>0.669243529618861</v>
       </c>
       <c r="AN11">
-        <v>0.9620947343368633</v>
+        <v>0.8545968567970055</v>
       </c>
       <c r="AO11">
-        <v>-1.542431762774853</v>
+        <v>-1.188568195147521</v>
       </c>
       <c r="AP11">
-        <v>0.5009769649772509</v>
+        <v>0.3498533311468189</v>
       </c>
       <c r="AQ11">
-        <v>-2.930959714356365</v>
+        <v>-2.763163284504506</v>
       </c>
       <c r="AR11">
-        <v>0.4725572360986167</v>
+        <v>0.3955920105007742</v>
       </c>
       <c r="AS11">
-        <v>0.05730245937896543</v>
+        <v>0.06115477091205695</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -190,36 +190,36 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>UP_ACCELERATING</t>
+    <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
   </si>
   <si>
     <t>多头稳态</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>多头加速</t>
+    <t>空头加速</t>
   </si>
   <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
@@ -238,40 +238,40 @@
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
+    <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>DOWN_STEEPENING</t>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
   </si>
   <si>
     <t>上升坡延续</t>
   </si>
   <si>
-    <t>地形转换区</t>
+    <t>下降陡坡形成</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
   </si>
 </sst>
 </file>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C2" s="2">
         <v>46273</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46272</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.3664169303597309</v>
+        <v>0.5193430657141522</v>
       </c>
       <c r="G2">
-        <v>1.002342793513443</v>
+        <v>1.082279446828884</v>
       </c>
       <c r="H2">
-        <v>1.071340881855671</v>
+        <v>1.072283951301478</v>
       </c>
       <c r="I2">
-        <v>0.2582591062177085</v>
+        <v>0.258374129393889</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2">
-        <v>-0.3649027957069002</v>
+        <v>-0.3953015137842225</v>
       </c>
       <c r="O2">
-        <v>-9.789102918153155</v>
+        <v>-11.36974050945886</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.002342793513443</v>
+        <v>1.082279446828884</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.994515672133489</v>
+        <v>0.9760507447377137</v>
       </c>
       <c r="U2">
-        <v>0.9024328318020196</v>
+        <v>0.9170497758265125</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9989865725386777</v>
+        <v>0.9963782815092849</v>
       </c>
       <c r="Y2">
-        <v>0.9997529591519594</v>
+        <v>0.9997019233496741</v>
       </c>
       <c r="Z2">
-        <v>0.0007663866132816555</v>
+        <v>0.003323641840389246</v>
       </c>
       <c r="AA2">
-        <v>0.169381509783897</v>
+        <v>0.395486038893807</v>
       </c>
       <c r="AB2">
-        <v>9.920448444963712</v>
+        <v>19.48089570545192</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AD2">
-        <v>0.9850479031788599</v>
+        <v>0.9427527408593379</v>
       </c>
       <c r="AE2">
-        <v>0.1722806676412979</v>
+        <v>0.3334925330531495</v>
       </c>
       <c r="AF2">
-        <v>0.8213177222642499</v>
+        <v>0.9241680174369504</v>
       </c>
       <c r="AG2">
-        <v>0.821114823237631</v>
+        <v>0.9238925445299745</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.5758061193326925</v>
+        <v>0.6576030694336081</v>
       </c>
       <c r="AM2">
-        <v>0.8234993582085794</v>
+        <v>0.8561915320118576</v>
       </c>
       <c r="AN2">
-        <v>0.8108816373906355</v>
+        <v>0.879279519383606</v>
       </c>
       <c r="AO2">
-        <v>0.1251687777128305</v>
+        <v>0.2734570025611356</v>
       </c>
       <c r="AP2">
-        <v>1.017977037020363</v>
+        <v>1.085511373077254</v>
       </c>
       <c r="AQ2">
-        <v>-1.640169259271452</v>
+        <v>-1.886107645787611</v>
       </c>
       <c r="AR2">
-        <v>0.8820401676251696</v>
+        <v>0.9265917411423564</v>
       </c>
       <c r="AS2">
-        <v>0.03869900270029161</v>
+        <v>0.03751447464727287</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C3" s="2">
         <v>46273</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46272</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.603017088231519</v>
+        <v>2.899548383439985</v>
       </c>
       <c r="H3">
-        <v>1.939968106143602</v>
+        <v>1.951434324331175</v>
       </c>
       <c r="I3">
-        <v>0.4347751532174389</v>
+        <v>0.4368697577802059</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>-0.1019046781651708</v>
+        <v>-0.1084789628855116</v>
       </c>
       <c r="O3">
-        <v>-32.43158659496232</v>
+        <v>-37.31921563821525</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.603017088231519</v>
+        <v>2.899548383439985</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9902667861457664</v>
+        <v>0.9713649670067009</v>
       </c>
       <c r="U3">
-        <v>0.9955117299807449</v>
+        <v>0.9870345771689445</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9969635476418582</v>
+        <v>0.9958361577048487</v>
       </c>
       <c r="Y3">
-        <v>0.9995667048606002</v>
+        <v>0.9996813680637163</v>
       </c>
       <c r="Z3">
-        <v>0.002603157218741936</v>
+        <v>0.003845210358867646</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>11.32491668756644</v>
+        <v>19.48638135698798</v>
       </c>
       <c r="AC3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AD3">
-        <v>0.9805293531091277</v>
+        <v>0.9427208070692576</v>
       </c>
       <c r="AE3">
-        <v>0.1963725736741146</v>
+        <v>0.3335827931993607</v>
       </c>
       <c r="AF3">
-        <v>2.099045165750148</v>
+        <v>2.410681128242724</v>
       </c>
       <c r="AG3">
-        <v>2.098135659682447</v>
+        <v>2.40991300824707</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.9801044945063867</v>
+        <v>0.9424204261131263</v>
       </c>
       <c r="AM3">
-        <v>0.9884276915057459</v>
+        <v>0.9770942979932045</v>
       </c>
       <c r="AN3">
-        <v>2.064471096028702</v>
+        <v>2.291777580912676</v>
       </c>
       <c r="AO3">
-        <v>0.3423932881954153</v>
+        <v>0.714733802331325</v>
       </c>
       <c r="AP3">
-        <v>2.836125209226585</v>
+        <v>3.196126880711641</v>
       </c>
       <c r="AQ3">
-        <v>-3.832640055995153</v>
+        <v>-4.219988204615172</v>
       </c>
       <c r="AR3">
-        <v>2.513968953375532</v>
+        <v>2.835316583281092</v>
       </c>
       <c r="AS3">
-        <v>0.0371964075213495</v>
+        <v>0.03740281966582361</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C4" s="2">
         <v>46273</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46272</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.01657963019459711</v>
+        <v>0.003428391748841053</v>
       </c>
       <c r="H4">
-        <v>2.078603444657875</v>
+        <v>2.078852150666709</v>
       </c>
       <c r="I4">
-        <v>0.4924786608804972</v>
+        <v>0.4925204832609791</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1094,19 +1094,19 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4">
-        <v>-0.2402355136844739</v>
+        <v>-0.244171066094964</v>
       </c>
       <c r="O4">
-        <v>-8.506062700006634</v>
+        <v>-9.559269925418015</v>
       </c>
       <c r="P4">
-        <v>0.6284577328223165</v>
+        <v>0.508850383125106</v>
       </c>
       <c r="Q4">
-        <v>0.04462380638558195</v>
+        <v>0.006980340879944809</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>0.6496908965436862</v>
+        <v>0.6218300357302415</v>
       </c>
       <c r="U4">
-        <v>0.6422283636159762</v>
+        <v>0.6289619180383681</v>
       </c>
       <c r="V4" t="s">
         <v>68</v>
@@ -1127,34 +1127,34 @@
         <v>68</v>
       </c>
       <c r="X4">
-        <v>0.9838826395771607</v>
+        <v>0.9738334343429886</v>
       </c>
       <c r="Y4">
-        <v>0.9994698406852699</v>
+        <v>0.9965536078390376</v>
       </c>
       <c r="Z4">
-        <v>0.01558720110810918</v>
+        <v>0.02272017349604893</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-85.2836487829335</v>
+        <v>-89.57386343343255</v>
       </c>
       <c r="AC4">
-        <v>-44</v>
+        <v>-58.99999999999999</v>
       </c>
       <c r="AD4">
-        <v>0.0822229282328244</v>
+        <v>0.007437417581023465</v>
       </c>
       <c r="AE4">
-        <v>-0.9966139624111333</v>
+        <v>-0.9999723420273811</v>
       </c>
       <c r="AF4">
-        <v>0.8118185826057236</v>
+        <v>0.6976709108203109</v>
       </c>
       <c r="AG4">
-        <v>0.8113881894222842</v>
+        <v>0.6952664632623282</v>
       </c>
       <c r="AH4" t="s">
         <v>70</v>
@@ -1169,28 +1169,28 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>0.04108966849076869</v>
+        <v>0.003705892661687211</v>
       </c>
       <c r="AM4">
-        <v>0.4967065775528007</v>
+        <v>0.4715908125182166</v>
       </c>
       <c r="AN4">
-        <v>0.1601042929883315</v>
+        <v>0.1311248043795806</v>
       </c>
       <c r="AO4">
-        <v>-0.7825234523324572</v>
+        <v>-0.66664186787868</v>
       </c>
       <c r="AP4">
-        <v>-0.5227757194932624</v>
+        <v>-0.5699903874016419</v>
       </c>
       <c r="AQ4">
-        <v>-1.26713315497497</v>
+        <v>-1.180169988254712</v>
       </c>
       <c r="AR4">
-        <v>0.6065858699962972</v>
+        <v>0.6360865082059438</v>
       </c>
       <c r="AS4">
-        <v>0.1851649677126074</v>
+        <v>0.1962278366650238</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C5" s="2">
         <v>46273</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46272</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.1096653187544404</v>
+        <v>0.6416158443203563</v>
       </c>
       <c r="G5">
-        <v>1.230944690076117</v>
+        <v>1.592148382521257</v>
       </c>
       <c r="H5">
-        <v>1.492457133107204</v>
+        <v>1.496707011662919</v>
       </c>
       <c r="I5">
-        <v>0.3349848932159966</v>
+        <v>0.336972784776947</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,31 +1234,31 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N5">
-        <v>-0.1048678555225676</v>
+        <v>-0.1088156461493224</v>
       </c>
       <c r="O5">
-        <v>-29.46613100483611</v>
+        <v>-35.27657858262192</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.230944690076117</v>
+        <v>1.592148382521257</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T5">
-        <v>0.9392227807266568</v>
+        <v>0.9999063779159618</v>
       </c>
       <c r="U5">
-        <v>0.8381969984093558</v>
+        <v>0.944930317589195</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9926628797477552</v>
+        <v>0.9603702114923992</v>
       </c>
       <c r="Y5">
-        <v>0.9963877970767767</v>
+        <v>0.9949202835158347</v>
       </c>
       <c r="Z5">
-        <v>0.003724917329021471</v>
+        <v>0.03455007202343552</v>
       </c>
       <c r="AA5">
-        <v>0.2813168943633795</v>
+        <v>0.3940351668400586</v>
       </c>
       <c r="AB5">
-        <v>-30.92133310190683</v>
+        <v>-1.230986268728187</v>
       </c>
       <c r="AC5">
-        <v>22.00000000000001</v>
+        <v>58.00000000000001</v>
       </c>
       <c r="AD5">
-        <v>0.857873637963354</v>
+        <v>0.9997692113478265</v>
       </c>
       <c r="AE5">
-        <v>-0.5138607022214484</v>
+        <v>-0.02148311059751658</v>
       </c>
       <c r="AF5">
-        <v>1.312452426908651</v>
+        <v>1.393143136775112</v>
       </c>
       <c r="AG5">
-        <v>1.30771158241558</v>
+        <v>1.386066364618434</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1309,28 +1309,28 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>0.5476187116263899</v>
+        <v>0.6933168851053944</v>
       </c>
       <c r="AM5">
-        <v>0.8059770240761885</v>
+        <v>0.8711177658960196</v>
       </c>
       <c r="AN5">
-        <v>1.073903918500121</v>
+        <v>1.32061768692522</v>
       </c>
       <c r="AO5">
-        <v>-0.7376161852156446</v>
+        <v>-0.2145555625788086</v>
       </c>
       <c r="AP5">
-        <v>0.8950066191053321</v>
+        <v>1.453872140759293</v>
       </c>
       <c r="AQ5">
-        <v>-2.700938541313292</v>
+        <v>-2.480284097118669</v>
       </c>
       <c r="AR5">
-        <v>0.7179606737755675</v>
+        <v>1.29164197434492</v>
       </c>
       <c r="AS5">
-        <v>0.04256116774910201</v>
+        <v>0.03894753404588104</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,136 +1341,136 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C6" s="2">
         <v>46273</v>
       </c>
-      <c r="C6" s="2">
-        <v>46272</v>
-      </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1227504124957605</v>
+        <v>0.1709770580259295</v>
       </c>
       <c r="H6">
-        <v>0.9433001337824681</v>
+        <v>0.9433119231496286</v>
       </c>
       <c r="I6">
-        <v>0.257051643633687</v>
+        <v>0.2569583223870474</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>159</v>
       </c>
       <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0.00385184952603078</v>
+      </c>
+      <c r="O6">
+        <v>0.07544721002368804</v>
+      </c>
+      <c r="P6">
+        <v>0.04564211363881277</v>
+      </c>
+      <c r="Q6">
+        <v>0.1791540264604901</v>
+      </c>
+      <c r="R6" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" t="s">
+        <v>66</v>
+      </c>
+      <c r="T6">
+        <v>-0.7294718844236066</v>
+      </c>
+      <c r="U6">
+        <v>0.7281208447294604</v>
+      </c>
+      <c r="V6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W6" t="s">
+        <v>69</v>
+      </c>
+      <c r="X6">
+        <v>0.9928866482122811</v>
+      </c>
+      <c r="Y6">
+        <v>0.9994339869553498</v>
+      </c>
+      <c r="Z6">
+        <v>0.006547338743068676</v>
+      </c>
+      <c r="AA6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0.1137245349241522</v>
-      </c>
-      <c r="Q6">
-        <v>0.1385014223374168</v>
-      </c>
-      <c r="R6" t="s">
-        <v>59</v>
-      </c>
-      <c r="S6" t="s">
-        <v>64</v>
-      </c>
-      <c r="T6">
-        <v>0.3969018922560495</v>
-      </c>
-      <c r="U6">
-        <v>0.4535576362848359</v>
-      </c>
-      <c r="V6" t="s">
-        <v>68</v>
-      </c>
-      <c r="W6" t="s">
-        <v>68</v>
-      </c>
-      <c r="X6">
-        <v>0.9955663368490487</v>
-      </c>
-      <c r="Y6">
-        <v>0.9998071390784544</v>
-      </c>
-      <c r="Z6">
-        <v>0.004240802229405705</v>
-      </c>
-      <c r="AA6">
-        <v>0.1880285614085631</v>
-      </c>
       <c r="AB6">
-        <v>-96.85647803352097</v>
+        <v>-101.9725834939739</v>
       </c>
       <c r="AC6">
-        <v>-21.99999999999999</v>
+        <v>-29</v>
       </c>
       <c r="AD6">
-        <v>-0.119382704170757</v>
+        <v>-0.2074436152876978</v>
       </c>
       <c r="AE6">
-        <v>-0.992848311649306</v>
+        <v>-0.9782469762163181</v>
       </c>
       <c r="AF6">
-        <v>0.7873767214187826</v>
+        <v>0.7011631957402866</v>
       </c>
       <c r="AG6">
-        <v>0.7872248672186862</v>
+        <v>0.700766328225069</v>
       </c>
       <c r="AH6" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AK6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AL6">
-        <v>-0.07090135440826592</v>
+        <v>-0.1036630997477078</v>
       </c>
       <c r="AM6">
-        <v>0.5380106563305191</v>
+        <v>0.536036785176411</v>
       </c>
       <c r="AN6">
-        <v>-0.05377530696909347</v>
+        <v>-0.0919466019147635</v>
       </c>
       <c r="AO6">
-        <v>-0.7820390644770328</v>
+        <v>-0.6900769913542941</v>
       </c>
       <c r="AP6">
-        <v>-0.4085404372394565</v>
+        <v>-0.4284720386196494</v>
       </c>
       <c r="AQ6">
-        <v>-0.2464802607138144</v>
+        <v>-0.07415299124684954</v>
       </c>
       <c r="AR6">
-        <v>0.3924626088054131</v>
+        <v>0.4001715686241753</v>
       </c>
       <c r="AS6">
-        <v>0.2356157725325308</v>
+        <v>0.1733212989618051</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C7" s="2">
         <v>46273</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46272</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1493,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.05901926764080149</v>
       </c>
       <c r="G7">
-        <v>0.9145432411443594</v>
+        <v>1.138358467706816</v>
       </c>
       <c r="H7">
-        <v>1.450610255804733</v>
+        <v>1.455206670760353</v>
       </c>
       <c r="I7">
-        <v>0.3569679572850659</v>
+        <v>0.3592540215515024</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7">
-        <v>-0.1463876586164193</v>
+        <v>-0.1497761042917866</v>
       </c>
       <c r="O7">
-        <v>-33.97309938880834</v>
+        <v>-39.21940447180414</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.9145432411443594</v>
+        <v>1.138358467706816</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>0.720610870143059</v>
+        <v>0.9438699622389386</v>
       </c>
       <c r="U7">
-        <v>0.7238971039999447</v>
+        <v>0.8305876903728253</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9981268018448028</v>
+        <v>0.9526862952903115</v>
       </c>
       <c r="Y7">
-        <v>0.9984888497422726</v>
+        <v>0.987973268876731</v>
       </c>
       <c r="Z7">
-        <v>0.0003620478974697416</v>
+        <v>0.03528697358641952</v>
       </c>
       <c r="AA7">
-        <v>0.8360836497435948</v>
+        <v>0.3009372436950627</v>
       </c>
       <c r="AB7">
-        <v>-59.38848286026088</v>
+        <v>-29.35651878186547</v>
       </c>
       <c r="AC7">
-        <v>6.999999999999997</v>
+        <v>65</v>
       </c>
       <c r="AD7">
-        <v>0.5092144249490446</v>
+        <v>0.8715861023674165</v>
       </c>
       <c r="AE7">
-        <v>-0.8606396861775628</v>
+        <v>-0.4902424565049169</v>
       </c>
       <c r="AF7">
-        <v>1.561370507760722</v>
+        <v>1.244058323880343</v>
       </c>
       <c r="AG7">
-        <v>1.559011042315512</v>
+        <v>1.229096368917369</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1583,34 +1583,34 @@
         <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AL7">
-        <v>0.4667737071973243</v>
+        <v>0.5601209829711771</v>
       </c>
       <c r="AM7">
-        <v>0.812129388705314</v>
+        <v>0.8116297563197563</v>
       </c>
       <c r="AN7">
-        <v>0.7685281417255759</v>
+        <v>0.9074164174822598</v>
       </c>
       <c r="AO7">
-        <v>-1.355771977675915</v>
+        <v>-0.7624225353650035</v>
       </c>
       <c r="AP7">
-        <v>0.7897851815310688</v>
+        <v>1.199043329782393</v>
       </c>
       <c r="AQ7">
-        <v>-1.350891593156276</v>
+        <v>-1.070579516087418</v>
       </c>
       <c r="AR7">
-        <v>0.737424183407118</v>
+        <v>1.158870645631176</v>
       </c>
       <c r="AS7">
-        <v>0.04881844091942383</v>
+        <v>0.03882778157557992</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C8" s="2">
         <v>46273</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46272</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.5257793442834557</v>
+        <v>0.4791918109621205</v>
       </c>
       <c r="H8">
-        <v>1.437771778200543</v>
+        <v>1.438027335608234</v>
       </c>
       <c r="I8">
-        <v>0.3564998446067633</v>
+        <v>0.3566594213178618</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>-0.003080145647887595</v>
+        <v>-0.004283397136889295</v>
       </c>
       <c r="O8">
-        <v>-0.7089525535622916</v>
+        <v>-1.206226690464652</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.5257793442834557</v>
+        <v>0.4791918109621205</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.8345605825612374</v>
+        <v>0.9926047311091624</v>
       </c>
       <c r="U8">
-        <v>0.775395298077429</v>
+        <v>0.8380318182616666</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9810981667059494</v>
+        <v>0.7681153578384311</v>
       </c>
       <c r="Y8">
-        <v>0.9993721436994882</v>
+        <v>0.9654387570501746</v>
       </c>
       <c r="Z8">
-        <v>0.01827397699353883</v>
+        <v>0.1973233992117435</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>58.98259758085585</v>
+        <v>12.08670299803667</v>
       </c>
       <c r="AC8">
-        <v>-44</v>
+        <v>-90</v>
       </c>
       <c r="AD8">
-        <v>0.5152983981553437</v>
+        <v>0.9778318579617756</v>
       </c>
       <c r="AE8">
-        <v>0.8570108289038925</v>
+        <v>0.2093916367838551</v>
       </c>
       <c r="AF8">
-        <v>0.7236538951625455</v>
+        <v>0.4075810245071754</v>
       </c>
       <c r="AG8">
-        <v>0.7231995445050778</v>
+        <v>0.3934945176974441</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1723,34 +1723,34 @@
         <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AL8">
-        <v>0.2574874324047091</v>
+        <v>0.4720183867773398</v>
       </c>
       <c r="AM8">
-        <v>0.6404964866540324</v>
+        <v>0.7699726661680064</v>
       </c>
       <c r="AN8">
-        <v>0.3106804279234047</v>
+        <v>0.2975742665917043</v>
       </c>
       <c r="AO8">
-        <v>0.6383908648513057</v>
+        <v>0.09727233782722064</v>
       </c>
       <c r="AP8">
-        <v>1.063794997024615</v>
+        <v>0.922849257509929</v>
       </c>
       <c r="AQ8">
-        <v>0.1748740564399984</v>
+        <v>-0.3984701105700039</v>
       </c>
       <c r="AR8">
-        <v>1.032793010352023</v>
+        <v>0.8391839145740082</v>
       </c>
       <c r="AS8">
-        <v>0.09248855391594409</v>
+        <v>0.07520304125391587</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C9" s="2">
         <v>46273</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46272</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.9038475664035587</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3.53105594817804</v>
+        <v>4.165795617825229</v>
       </c>
       <c r="H9">
-        <v>3.020945889670893</v>
+        <v>3.026918270058355</v>
       </c>
       <c r="I9">
-        <v>0.6315626252869405</v>
+        <v>0.6345722416700066</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,31 +1794,31 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N9">
-        <v>0.5820695800011771</v>
+        <v>0.6027280476141204</v>
       </c>
       <c r="O9">
-        <v>75.91386762323701</v>
+        <v>90.19017386273447</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.53105594817804</v>
+        <v>4.165795617825229</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T9">
-        <v>-0.9917129125256611</v>
+        <v>-0.9851604609161748</v>
       </c>
       <c r="U9">
-        <v>0.9817957314688525</v>
+        <v>0.993286050618328</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9980136378313611</v>
+        <v>0.9985799160352148</v>
       </c>
       <c r="Y9">
-        <v>0.9997911434870851</v>
+        <v>0.999855372824197</v>
       </c>
       <c r="Z9">
-        <v>0.001777505655723988</v>
+        <v>0.001275456788982221</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-169.6354953647062</v>
+        <v>-166.0054598837859</v>
       </c>
       <c r="AC9">
-        <v>13.00000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD9">
-        <v>-0.9836831156550757</v>
+        <v>-0.9703187753212777</v>
       </c>
       <c r="AE9">
-        <v>-0.1799097773194191</v>
+        <v>-0.2418294321603881</v>
       </c>
       <c r="AF9">
-        <v>2.697889675278914</v>
+        <v>3.216423687621671</v>
       </c>
       <c r="AG9">
-        <v>2.697326203449106</v>
+        <v>3.215958505347544</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1863,34 +1863,34 @@
         <v>73</v>
       </c>
       <c r="AJ9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL9">
-        <v>-0.9834776670297267</v>
+        <v>-0.9701784408571744</v>
       </c>
       <c r="AM9">
-        <v>0.9893743134434058</v>
+        <v>0.9852935984492057</v>
       </c>
       <c r="AN9">
-        <v>-2.659346103125017</v>
+        <v>-3.131355127430962</v>
       </c>
       <c r="AO9">
-        <v>-0.4214259324925717</v>
+        <v>-0.7145870463445099</v>
       </c>
       <c r="AP9">
-        <v>-4.492511969630058</v>
+        <v>-5.327837454877005</v>
       </c>
       <c r="AQ9">
-        <v>3.605115645282452</v>
+        <v>4.218171759738232</v>
       </c>
       <c r="AR9">
-        <v>4.162264000732653</v>
+        <v>4.934981558661325</v>
       </c>
       <c r="AS9">
-        <v>0.03771680982397817</v>
+        <v>0.03834276423764264</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C10" s="2">
         <v>46273</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46272</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.6713171198624325</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>2.202363507106859</v>
+        <v>2.673427082224345</v>
       </c>
       <c r="H10">
-        <v>2.046652624782537</v>
+        <v>2.04811628411588</v>
       </c>
       <c r="I10">
-        <v>0.4544521949976669</v>
+        <v>0.4534642697187833</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,31 +1934,31 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10">
-        <v>22.08762140444414</v>
+        <v>23.9021198807701</v>
       </c>
       <c r="O10">
-        <v>21.41459138935036</v>
+        <v>22.82992859155941</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.202363507106859</v>
+        <v>2.673427082224345</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T10">
-        <v>-0.7474814155486789</v>
+        <v>-0.7516003784162759</v>
       </c>
       <c r="U10">
-        <v>0.8370417231215145</v>
+        <v>0.8882102736206549</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9987133226783429</v>
+        <v>0.999537423507436</v>
       </c>
       <c r="Y10">
-        <v>0.9999100725809763</v>
+        <v>0.9999604133333229</v>
       </c>
       <c r="Z10">
-        <v>0.001196749902633409</v>
+        <v>0.0004229898258868436</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-121.4609328829015</v>
+        <v>-120.2113352789085</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AD10">
-        <v>-0.5219170707563664</v>
+        <v>-0.5031909231302459</v>
       </c>
       <c r="AE10">
-        <v>-0.8529962316757876</v>
+        <v>-0.8641752686112528</v>
       </c>
       <c r="AF10">
-        <v>2.955774704857857</v>
+        <v>3.759698778017272</v>
       </c>
       <c r="AG10">
-        <v>2.955508899667434</v>
+        <v>3.75954994407494</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2003,34 +2003,34 @@
         <v>73</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AK10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AL10">
-        <v>-0.5218701361012489</v>
+        <v>-0.503171003478897</v>
       </c>
       <c r="AM10">
-        <v>0.8464482310779792</v>
+        <v>0.8410872634518578</v>
       </c>
       <c r="AN10">
-        <v>-1.571460909393736</v>
+        <v>-1.918066642025004</v>
       </c>
       <c r="AO10">
-        <v>-2.4989291304811</v>
+        <v>-3.231606556425515</v>
       </c>
       <c r="AP10">
-        <v>-3.155973934756926</v>
+        <v>-3.797562043692175</v>
       </c>
       <c r="AQ10">
-        <v>0.7191873413693028</v>
+        <v>1.316207346677813</v>
       </c>
       <c r="AR10">
-        <v>3.025631969106124</v>
+        <v>3.592251439094361</v>
       </c>
       <c r="AS10">
-        <v>0.06730277034848185</v>
+        <v>0.06570772102586056</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C11" s="2">
         <v>46273</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46272</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9012724993344023</v>
+        <v>0.8562544998741403</v>
       </c>
       <c r="H11">
-        <v>2.47131790628759</v>
+        <v>2.450562493686923</v>
       </c>
       <c r="I11">
-        <v>0.5876186061208492</v>
+        <v>0.582203009848217</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N11">
-        <v>-2012.452748643014</v>
+        <v>-2079.393854391359</v>
       </c>
       <c r="O11">
-        <v>-24.21193436284993</v>
+        <v>-27.11819130928961</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.9012724993344023</v>
+        <v>0.8562544998741403</v>
       </c>
       <c r="R11" t="s">
         <v>59</v>
@@ -2095,10 +2095,10 @@
         <v>64</v>
       </c>
       <c r="T11">
-        <v>0.8396326438744856</v>
+        <v>0.9065486428219646</v>
       </c>
       <c r="U11">
-        <v>0.7775815498610414</v>
+        <v>0.8059623723914771</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9980060588095965</v>
+        <v>0.9904423352852886</v>
       </c>
       <c r="Y11">
-        <v>0.9989874404700918</v>
+        <v>0.992061932486372</v>
       </c>
       <c r="Z11">
-        <v>0.0009813816604953285</v>
+        <v>0.0016195972010834</v>
       </c>
       <c r="AA11">
-        <v>0.05544383545829693</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>-56.01739052334261</v>
+        <v>-43.54122375681116</v>
       </c>
       <c r="AC11">
-        <v>-11</v>
+        <v>16</v>
       </c>
       <c r="AD11">
-        <v>0.5589412466649271</v>
+        <v>0.7248789188732947</v>
       </c>
       <c r="AE11">
-        <v>-0.8292072616521501</v>
+        <v>-0.6888762972937039</v>
       </c>
       <c r="AF11">
-        <v>1.466833979433798</v>
+        <v>1.202131108686866</v>
       </c>
       <c r="AG11">
-        <v>1.465348722709129</v>
+        <v>1.192588510785877</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2143,34 +2143,34 @@
         <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AL11">
-        <v>0.2946668764127441</v>
+        <v>0.3595623905380364</v>
       </c>
       <c r="AM11">
-        <v>0.669243529618861</v>
+        <v>0.7051231573892797</v>
       </c>
       <c r="AN11">
-        <v>0.8545968567970055</v>
+        <v>0.8196469094764647</v>
       </c>
       <c r="AO11">
-        <v>-1.188568195147521</v>
+        <v>-0.8636007334220179</v>
       </c>
       <c r="AP11">
-        <v>0.3498533311468189</v>
+        <v>0.2949296292788891</v>
       </c>
       <c r="AQ11">
-        <v>-2.763163284504506</v>
+        <v>-2.642194266982881</v>
       </c>
       <c r="AR11">
-        <v>0.3955920105007742</v>
+        <v>0.3626478390434086</v>
       </c>
       <c r="AS11">
-        <v>0.06115477091205695</v>
+        <v>0.06374796428625953</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -193,12 +193,12 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>多头加速</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
@@ -259,10 +259,10 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
     <t>地形转换区</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C2" s="2">
         <v>46274</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46273</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.5193430657141522</v>
+        <v>0.5692800216481988</v>
       </c>
       <c r="G2">
-        <v>1.082279446828884</v>
+        <v>1.109282431255643</v>
       </c>
       <c r="H2">
-        <v>1.072283951301478</v>
+        <v>1.07346016977262</v>
       </c>
       <c r="I2">
-        <v>0.258374129393889</v>
+        <v>0.2585324068237655</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2">
-        <v>-0.3953015137842225</v>
+        <v>-0.4260524205199425</v>
       </c>
       <c r="O2">
-        <v>-11.36974050945886</v>
+        <v>-12.42497580985538</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.082279446828884</v>
+        <v>1.109282431255643</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.9760507447377137</v>
+        <v>0.9724499547242961</v>
       </c>
       <c r="U2">
-        <v>0.9170497758265125</v>
+        <v>0.9229624934160302</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9963782815092849</v>
+        <v>0.9972992558815378</v>
       </c>
       <c r="Y2">
-        <v>0.9997019233496741</v>
+        <v>0.9998720421714683</v>
       </c>
       <c r="Z2">
-        <v>0.003323641840389246</v>
+        <v>0.002572786289930518</v>
       </c>
       <c r="AA2">
-        <v>0.395486038893807</v>
+        <v>0.4630903664045969</v>
       </c>
       <c r="AB2">
-        <v>19.48089570545192</v>
+        <v>20.60150864564121</v>
       </c>
       <c r="AC2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD2">
-        <v>0.9427527408593379</v>
+        <v>0.9360502711305557</v>
       </c>
       <c r="AE2">
-        <v>0.3334925330531495</v>
+        <v>0.3518662955106855</v>
       </c>
       <c r="AF2">
-        <v>0.9241680174369504</v>
+        <v>0.9544972080568478</v>
       </c>
       <c r="AG2">
-        <v>0.9238925445299745</v>
+        <v>0.9543750726667652</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.6576030694336081</v>
+        <v>0.6846754462856411</v>
       </c>
       <c r="AM2">
-        <v>0.8561915320118576</v>
+        <v>0.8678659499928586</v>
       </c>
       <c r="AN2">
-        <v>0.879279519383606</v>
+        <v>0.9020457495733645</v>
       </c>
       <c r="AO2">
-        <v>0.2734570025611356</v>
+        <v>0.3040788133693674</v>
       </c>
       <c r="AP2">
-        <v>1.085511373077254</v>
+        <v>1.110409765564364</v>
       </c>
       <c r="AQ2">
-        <v>-1.886107645787611</v>
+        <v>-1.973152759960435</v>
       </c>
       <c r="AR2">
-        <v>0.9265917411423564</v>
+        <v>0.9435296817973353</v>
       </c>
       <c r="AS2">
-        <v>0.03751447464727287</v>
+        <v>0.03681612924827607</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C3" s="2">
         <v>46274</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46273</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2.899548383439985</v>
+        <v>2.80948747210962</v>
       </c>
       <c r="H3">
-        <v>1.951434324331175</v>
+        <v>1.962805776838827</v>
       </c>
       <c r="I3">
-        <v>0.4368697577802059</v>
+        <v>0.4391778308274965</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,31 +954,31 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3">
-        <v>-0.1084789628855116</v>
+        <v>-0.1149480421046835</v>
       </c>
       <c r="O3">
-        <v>-37.31921563821525</v>
+        <v>-41.62629564059953</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.899548383439985</v>
+        <v>2.80948747210962</v>
       </c>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T3">
-        <v>0.9713649670067009</v>
+        <v>0.995854994680618</v>
       </c>
       <c r="U3">
-        <v>0.9870345771689445</v>
+        <v>0.9981218429706541</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9958361577048487</v>
+        <v>0.9998373602272229</v>
       </c>
       <c r="Y3">
-        <v>0.9996813680637163</v>
+        <v>0.9999483814575042</v>
       </c>
       <c r="Z3">
-        <v>0.003845210358867646</v>
+        <v>0.000111021230281283</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>19.48638135698798</v>
+        <v>7.382802814430751</v>
       </c>
       <c r="AC3">
-        <v>19</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AD3">
-        <v>0.9427208070692576</v>
+        <v>0.9917097753910579</v>
       </c>
       <c r="AE3">
-        <v>0.3335827931993607</v>
+        <v>0.1284979431501433</v>
       </c>
       <c r="AF3">
-        <v>2.410681128242724</v>
+        <v>2.290341953709482</v>
       </c>
       <c r="AG3">
-        <v>2.40991300824707</v>
+        <v>2.290223729596014</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1023,34 +1023,34 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL3">
-        <v>0.9424204261131263</v>
+        <v>0.9916585847778734</v>
       </c>
       <c r="AM3">
-        <v>0.9770942979932045</v>
+        <v>0.9924783265735199</v>
       </c>
       <c r="AN3">
-        <v>2.291777580912676</v>
+        <v>2.272900400454537</v>
       </c>
       <c r="AO3">
-        <v>0.714733802331325</v>
+        <v>0.2790768090568564</v>
       </c>
       <c r="AP3">
-        <v>3.196126880711641</v>
+        <v>2.881898475879362</v>
       </c>
       <c r="AQ3">
-        <v>-4.219988204615172</v>
+        <v>-5.135591575188919</v>
       </c>
       <c r="AR3">
-        <v>2.835316583281092</v>
+        <v>2.443644714065337</v>
       </c>
       <c r="AS3">
-        <v>0.03740281966582361</v>
+        <v>0.0334435970261589</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C4" s="2">
         <v>46274</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46273</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.003428391748841053</v>
+        <v>0.01403701514849852</v>
       </c>
       <c r="H4">
-        <v>2.078852150666709</v>
+        <v>2.079077170388987</v>
       </c>
       <c r="I4">
-        <v>0.4925204832609791</v>
+        <v>0.4926789713552525</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1094,31 +1094,31 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4">
-        <v>-0.244171066094964</v>
+        <v>-0.2474658915567291</v>
       </c>
       <c r="O4">
-        <v>-9.559269925418015</v>
+        <v>-9.873247312038155</v>
       </c>
       <c r="P4">
-        <v>0.508850383125106</v>
+        <v>0.5285570140969089</v>
       </c>
       <c r="Q4">
-        <v>0.006980340879944809</v>
+        <v>0.02977457628648216</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T4">
-        <v>0.6218300357302415</v>
+        <v>0.6038783655477967</v>
       </c>
       <c r="U4">
-        <v>0.6289619180383681</v>
+        <v>0.6069459207557859</v>
       </c>
       <c r="V4" t="s">
         <v>68</v>
@@ -1127,34 +1127,34 @@
         <v>68</v>
       </c>
       <c r="X4">
-        <v>0.9738334343429886</v>
+        <v>0.8934936223121174</v>
       </c>
       <c r="Y4">
-        <v>0.9965536078390376</v>
+        <v>0.9408026250371093</v>
       </c>
       <c r="Z4">
-        <v>0.02272017349604893</v>
+        <v>0.04730900272499194</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-89.57386343343255</v>
+        <v>-94.46303669474203</v>
       </c>
       <c r="AC4">
-        <v>-58.99999999999999</v>
+        <v>-90</v>
       </c>
       <c r="AD4">
-        <v>0.007437417581023465</v>
+        <v>-0.07781593679090455</v>
       </c>
       <c r="AE4">
-        <v>-0.9999723420273811</v>
+        <v>-0.9969677426985057</v>
       </c>
       <c r="AF4">
-        <v>0.6976709108203109</v>
+        <v>0.4431683733027507</v>
       </c>
       <c r="AG4">
-        <v>0.6952664632623282</v>
+        <v>0.4169339689366535</v>
       </c>
       <c r="AH4" t="s">
         <v>70</v>
@@ -1163,34 +1163,34 @@
         <v>72</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL4">
-        <v>0.003705892661687211</v>
+        <v>-0.03660471880130239</v>
       </c>
       <c r="AM4">
-        <v>0.4715908125182166</v>
+        <v>0.4759844382618538</v>
       </c>
       <c r="AN4">
-        <v>0.1311248043795806</v>
+        <v>0.1292815129190201</v>
       </c>
       <c r="AO4">
-        <v>-0.66664186787868</v>
+        <v>-0.3742686717291679</v>
       </c>
       <c r="AP4">
-        <v>-0.5699903874016419</v>
+        <v>-0.4592823010889686</v>
       </c>
       <c r="AQ4">
-        <v>-1.180169988254712</v>
+        <v>-0.9123482222380772</v>
       </c>
       <c r="AR4">
-        <v>0.6360865082059438</v>
+        <v>0.5084784036395883</v>
       </c>
       <c r="AS4">
-        <v>0.1962278366650238</v>
+        <v>0.1776084102560392</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C5" s="2">
         <v>46274</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46273</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.6416158443203563</v>
+        <v>0.4266819783946858</v>
       </c>
       <c r="G5">
-        <v>1.592148382521257</v>
+        <v>1.450868759022682</v>
       </c>
       <c r="H5">
-        <v>1.496707011662919</v>
+        <v>1.500552139879995</v>
       </c>
       <c r="I5">
-        <v>0.336972784776947</v>
+        <v>0.3388210686096281</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,31 +1234,31 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5">
-        <v>-0.1088156461493224</v>
+        <v>-0.1127442842491932</v>
       </c>
       <c r="O5">
-        <v>-35.27657858262192</v>
+        <v>-36.52481729697374</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.592148382521257</v>
+        <v>1.450868759022682</v>
       </c>
       <c r="R5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T5">
-        <v>0.9999063779159618</v>
+        <v>0.9965186387595244</v>
       </c>
       <c r="U5">
-        <v>0.944930317589195</v>
+        <v>0.9119427220414751</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9603702114923992</v>
+        <v>0.9827021318240701</v>
       </c>
       <c r="Y5">
-        <v>0.9949202835158347</v>
+        <v>0.9980281513619448</v>
       </c>
       <c r="Z5">
-        <v>0.03455007202343552</v>
+        <v>0.01532601953787471</v>
       </c>
       <c r="AA5">
-        <v>0.3940351668400586</v>
+        <v>0.2329782802410662</v>
       </c>
       <c r="AB5">
-        <v>-1.230986268728187</v>
+        <v>-7.753214303499411</v>
       </c>
       <c r="AC5">
-        <v>58.00000000000001</v>
+        <v>40.99999999999999</v>
       </c>
       <c r="AD5">
-        <v>0.9997692113478265</v>
+        <v>0.990858330666288</v>
       </c>
       <c r="AE5">
-        <v>-0.02148311059751658</v>
+        <v>-0.1349065178159199</v>
       </c>
       <c r="AF5">
-        <v>1.393143136775112</v>
+        <v>1.284540762135069</v>
       </c>
       <c r="AG5">
-        <v>1.386066364618434</v>
+        <v>1.282007842182727</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1303,34 +1303,34 @@
         <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL5">
-        <v>0.6933168851053944</v>
+        <v>0.6096488898083851</v>
       </c>
       <c r="AM5">
-        <v>0.8711177658960196</v>
+        <v>0.837692027098163</v>
       </c>
       <c r="AN5">
-        <v>1.32061768692522</v>
+        <v>1.225754760766346</v>
       </c>
       <c r="AO5">
-        <v>-0.2145555625788086</v>
+        <v>-0.3016279754365427</v>
       </c>
       <c r="AP5">
-        <v>1.453872140759293</v>
+        <v>1.236600414817661</v>
       </c>
       <c r="AQ5">
-        <v>-2.480284097118669</v>
+        <v>-2.808461627930354</v>
       </c>
       <c r="AR5">
-        <v>1.29164197434492</v>
+        <v>1.03317886421508</v>
       </c>
       <c r="AS5">
-        <v>0.03894753404588104</v>
+        <v>0.03647320751078251</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C6" s="2">
         <v>46274</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46273</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1356,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1709770580259295</v>
+        <v>0.1899500130054068</v>
       </c>
       <c r="H6">
-        <v>0.9433119231496286</v>
+        <v>0.9433225897199168</v>
       </c>
       <c r="I6">
-        <v>0.2569583223870474</v>
+        <v>0.2568699422799828</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1371,22 +1371,22 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>0.00385184952603078</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0.07544721002368804</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.04564211363881277</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.1791540264604901</v>
+        <v>0.1899500130054068</v>
       </c>
       <c r="R6" t="s">
         <v>61</v>
@@ -1395,10 +1395,10 @@
         <v>66</v>
       </c>
       <c r="T6">
-        <v>-0.7294718844236066</v>
+        <v>-0.8280617309978223</v>
       </c>
       <c r="U6">
-        <v>0.7281208447294604</v>
+        <v>0.7686373726648043</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,34 +1407,34 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9928866482122811</v>
+        <v>0.9494089524131439</v>
       </c>
       <c r="Y6">
-        <v>0.9994339869553498</v>
+        <v>0.9840383748631368</v>
       </c>
       <c r="Z6">
-        <v>0.006547338743068676</v>
+        <v>0.0346294224499929</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-101.9725834939739</v>
+        <v>-119.4121077146081</v>
       </c>
       <c r="AC6">
-        <v>-29</v>
+        <v>-77</v>
       </c>
       <c r="AD6">
-        <v>-0.2074436152876978</v>
+        <v>-0.4910878471066095</v>
       </c>
       <c r="AE6">
-        <v>-0.9782469762163181</v>
+        <v>-0.8711100541402305</v>
       </c>
       <c r="AF6">
-        <v>0.7011631957402866</v>
+        <v>0.467147505623246</v>
       </c>
       <c r="AG6">
-        <v>0.700766328225069</v>
+        <v>0.4596910722548671</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>83</v>
       </c>
       <c r="AL6">
-        <v>-0.1036630997477078</v>
+        <v>-0.2416246434909123</v>
       </c>
       <c r="AM6">
-        <v>0.536036785176411</v>
+        <v>0.6221468121514782</v>
       </c>
       <c r="AN6">
-        <v>-0.0919466019147635</v>
+        <v>-0.1118580393334388</v>
       </c>
       <c r="AO6">
-        <v>-0.6900769913542941</v>
+        <v>-0.4291765003638253</v>
       </c>
       <c r="AP6">
-        <v>-0.4284720386196494</v>
+        <v>-0.3912646910892517</v>
       </c>
       <c r="AQ6">
-        <v>-0.07415299124684954</v>
+        <v>0.1062995051137328</v>
       </c>
       <c r="AR6">
-        <v>0.4001715686241753</v>
+        <v>0.3528146985862998</v>
       </c>
       <c r="AS6">
-        <v>0.1733212989618051</v>
+        <v>0.1306198212173499</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C7" s="2">
         <v>46274</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46273</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1493,16 +1493,16 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0.05901926764080149</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.138358467706816</v>
+        <v>1.016772576813987</v>
       </c>
       <c r="H7">
-        <v>1.455206670760353</v>
+        <v>1.459365331910676</v>
       </c>
       <c r="I7">
-        <v>0.3592540215515024</v>
+        <v>0.3612908735759212</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,31 +1514,31 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N7">
-        <v>-0.1497761042917866</v>
+        <v>-0.1530436213969156</v>
       </c>
       <c r="O7">
-        <v>-39.21940447180414</v>
+        <v>-41.19216955795083</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.138358467706816</v>
+        <v>1.016772576813987</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T7">
-        <v>0.9438699622389386</v>
+        <v>0.9805254827859041</v>
       </c>
       <c r="U7">
-        <v>0.8305876903728253</v>
+        <v>0.8386678405219214</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9526862952903115</v>
+        <v>0.9397788366431039</v>
       </c>
       <c r="Y7">
-        <v>0.987973268876731</v>
+        <v>0.9897254930730585</v>
       </c>
       <c r="Z7">
-        <v>0.03528697358641952</v>
+        <v>0.04994665642995455</v>
       </c>
       <c r="AA7">
-        <v>0.3009372436950627</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>-29.35651878186547</v>
+        <v>-19.51096534603836</v>
       </c>
       <c r="AC7">
-        <v>65</v>
+        <v>74.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>0.8715861023674165</v>
+        <v>0.9425775894082042</v>
       </c>
       <c r="AE7">
-        <v>-0.4902424565049169</v>
+        <v>-0.3339872571602375</v>
       </c>
       <c r="AF7">
-        <v>1.244058323880343</v>
+        <v>1.032186602686159</v>
       </c>
       <c r="AG7">
-        <v>1.229096368917369</v>
+        <v>1.021581394286964</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1589,28 +1589,28 @@
         <v>84</v>
       </c>
       <c r="AL7">
-        <v>0.5601209829711771</v>
+        <v>0.4664465347183249</v>
       </c>
       <c r="AM7">
-        <v>0.8116297563197563</v>
+        <v>0.7739317707643107</v>
       </c>
       <c r="AN7">
-        <v>0.9074164174822598</v>
+        <v>0.8262128267408263</v>
       </c>
       <c r="AO7">
-        <v>-0.7624225353650035</v>
+        <v>-0.5082568125725563</v>
       </c>
       <c r="AP7">
-        <v>1.199043329782393</v>
+        <v>1.011677001301629</v>
       </c>
       <c r="AQ7">
-        <v>-1.070579516087418</v>
+        <v>-1.407178365885063</v>
       </c>
       <c r="AR7">
-        <v>1.158870645631176</v>
+        <v>0.9269730964381281</v>
       </c>
       <c r="AS7">
-        <v>0.03882778157557992</v>
+        <v>0.03496952422480668</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C8" s="2">
         <v>46274</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46273</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.4791918109621205</v>
+        <v>0.6005909781916019</v>
       </c>
       <c r="H8">
-        <v>1.438027335608234</v>
+        <v>1.438258554215193</v>
       </c>
       <c r="I8">
-        <v>0.3566594213178618</v>
+        <v>0.3567845500354639</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,31 +1654,31 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-0.004283397136889295</v>
+        <v>-0.005498960418972647</v>
       </c>
       <c r="O8">
-        <v>-1.206226690464652</v>
+        <v>-1.501129879411469</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.4791918109621205</v>
+        <v>0.6005909781916019</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T8">
-        <v>0.9926047311091624</v>
+        <v>0.9556874599152398</v>
       </c>
       <c r="U8">
-        <v>0.8380318182616666</v>
+        <v>0.8292741833208217</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.7681153578384311</v>
+        <v>0.9431289083829874</v>
       </c>
       <c r="Y8">
-        <v>0.9654387570501746</v>
+        <v>0.9968593054358549</v>
       </c>
       <c r="Z8">
-        <v>0.1973233992117435</v>
+        <v>0.05373039705286753</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>12.08670299803667</v>
+        <v>29.54620453941579</v>
       </c>
       <c r="AC8">
-        <v>-90</v>
+        <v>-70</v>
       </c>
       <c r="AD8">
-        <v>0.9778318579617756</v>
+        <v>0.8699583121118509</v>
       </c>
       <c r="AE8">
-        <v>0.2093916367838551</v>
+        <v>0.4931252733205828</v>
       </c>
       <c r="AF8">
-        <v>0.4075810245071754</v>
+        <v>0.4946063292364956</v>
       </c>
       <c r="AG8">
-        <v>0.3934945176974441</v>
+        <v>0.4930529218268708</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1723,34 +1723,34 @@
         <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL8">
-        <v>0.4720183867773398</v>
+        <v>0.4336130193849842</v>
       </c>
       <c r="AM8">
-        <v>0.7699726661680064</v>
+        <v>0.7493466694651054</v>
       </c>
       <c r="AN8">
-        <v>0.2975742665917043</v>
+        <v>0.3751948373740336</v>
       </c>
       <c r="AO8">
-        <v>0.09727233782722064</v>
+        <v>0.2771824625604786</v>
       </c>
       <c r="AP8">
-        <v>0.922849257509929</v>
+        <v>1.126869207941201</v>
       </c>
       <c r="AQ8">
-        <v>-0.3984701105700039</v>
+        <v>-0.06969369288327512</v>
       </c>
       <c r="AR8">
-        <v>0.8391839145740082</v>
+        <v>1.081140949300065</v>
       </c>
       <c r="AS8">
-        <v>0.07520304125391587</v>
+        <v>0.07027720713999359</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C9" s="2">
         <v>46274</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46273</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1776,13 +1776,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.165795617825229</v>
+        <v>4.168882434469204</v>
       </c>
       <c r="H9">
-        <v>3.026918270058355</v>
+        <v>3.033388003049883</v>
       </c>
       <c r="I9">
-        <v>0.6345722416700066</v>
+        <v>0.6378528057457957</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N9">
-        <v>0.6027280476141204</v>
+        <v>0.623426079803278</v>
       </c>
       <c r="O9">
-        <v>90.19017386273447</v>
+        <v>96.43627553445329</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.165795617825229</v>
+        <v>4.168882434469204</v>
       </c>
       <c r="R9" t="s">
         <v>62</v>
@@ -1815,10 +1815,10 @@
         <v>67</v>
       </c>
       <c r="T9">
-        <v>-0.9851604609161748</v>
+        <v>-0.9897352629795897</v>
       </c>
       <c r="U9">
-        <v>0.993286050618328</v>
+        <v>0.9953623838234893</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9985799160352148</v>
+        <v>0.999637629439567</v>
       </c>
       <c r="Y9">
-        <v>0.999855372824197</v>
+        <v>0.9999260619306957</v>
       </c>
       <c r="Z9">
-        <v>0.001275456788982221</v>
+        <v>0.0002884324911286429</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-166.0054598837859</v>
+        <v>-168.3699817462219</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AD9">
-        <v>-0.9703187753212777</v>
+        <v>-0.9794697669482223</v>
       </c>
       <c r="AE9">
-        <v>-0.2418294321603881</v>
+        <v>-0.201591110008341</v>
       </c>
       <c r="AF9">
-        <v>3.216423687621671</v>
+        <v>3.227806295906887</v>
       </c>
       <c r="AG9">
-        <v>3.215958505347544</v>
+        <v>3.227567638141279</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>85</v>
       </c>
       <c r="AL9">
-        <v>-0.9701784408571744</v>
+        <v>-0.9793973468447121</v>
       </c>
       <c r="AM9">
-        <v>0.9852935984492057</v>
+        <v>0.988449476258463</v>
       </c>
       <c r="AN9">
-        <v>-3.131355127430962</v>
+        <v>-3.166403133240801</v>
       </c>
       <c r="AO9">
-        <v>-0.7145870463445099</v>
+        <v>-0.6205442492079006</v>
       </c>
       <c r="AP9">
-        <v>-5.327837454877005</v>
+        <v>-5.201157229962569</v>
       </c>
       <c r="AQ9">
-        <v>4.218171759738232</v>
+        <v>4.963366596708446</v>
       </c>
       <c r="AR9">
-        <v>4.934981558661325</v>
+        <v>4.741587371836053</v>
       </c>
       <c r="AS9">
-        <v>0.03834276423764264</v>
+        <v>0.0357705033449802</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C10" s="2">
         <v>46274</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46273</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1916,13 +1916,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.673427082224345</v>
+        <v>2.770835826498998</v>
       </c>
       <c r="H10">
-        <v>2.04811628411588</v>
+        <v>2.051034809298019</v>
       </c>
       <c r="I10">
-        <v>0.4534642697187833</v>
+        <v>0.4526917807004999</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N10">
-        <v>23.9021198807701</v>
+        <v>25.98764264140891</v>
       </c>
       <c r="O10">
-        <v>22.82992859155941</v>
+        <v>24.58622766453071</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.673427082224345</v>
+        <v>2.770835826498998</v>
       </c>
       <c r="R10" t="s">
         <v>61</v>
@@ -1955,10 +1955,10 @@
         <v>66</v>
       </c>
       <c r="T10">
-        <v>-0.7516003784162759</v>
+        <v>-0.8021105853176919</v>
       </c>
       <c r="U10">
-        <v>0.8882102736206549</v>
+        <v>0.9109192273751268</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.999537423507436</v>
+        <v>0.9998778559286617</v>
       </c>
       <c r="Y10">
-        <v>0.9999604133333229</v>
+        <v>0.9998778559286617</v>
       </c>
       <c r="Z10">
-        <v>0.0004229898258868436</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-120.2113352789085</v>
+        <v>-127.1710804786239</v>
       </c>
       <c r="AC10">
-        <v>6.000000000000009</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>-0.5031909231302459</v>
+        <v>-0.6041969966638925</v>
       </c>
       <c r="AE10">
-        <v>-0.8641752686112528</v>
+        <v>-0.7968349824288165</v>
       </c>
       <c r="AF10">
-        <v>3.759698778017272</v>
+        <v>3.387159043982499</v>
       </c>
       <c r="AG10">
-        <v>3.75954994407494</v>
+        <v>3.386745322586596</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>83</v>
       </c>
       <c r="AL10">
-        <v>-0.503171003478897</v>
+        <v>-0.6041231975828296</v>
       </c>
       <c r="AM10">
-        <v>0.8410872634518578</v>
+        <v>0.8725029968446851</v>
       </c>
       <c r="AN10">
-        <v>-1.918066642025004</v>
+        <v>-2.046261352372307</v>
       </c>
       <c r="AO10">
-        <v>-3.231606556425515</v>
+        <v>-2.698677149614167</v>
       </c>
       <c r="AP10">
-        <v>-3.797562043692175</v>
+        <v>-3.704382662691871</v>
       </c>
       <c r="AQ10">
-        <v>1.316207346677813</v>
+        <v>2.745353844411959</v>
       </c>
       <c r="AR10">
-        <v>3.592251439094361</v>
+        <v>3.36365172865137</v>
       </c>
       <c r="AS10">
-        <v>0.06570772102586056</v>
+        <v>0.05808901153009509</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C11" s="2">
         <v>46274</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46273</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.8562544998741403</v>
+        <v>0.7303045623762349</v>
       </c>
       <c r="H11">
-        <v>2.450562493686923</v>
+        <v>2.431345099254925</v>
       </c>
       <c r="I11">
-        <v>0.582203009848217</v>
+        <v>0.5766718786152386</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,31 +2074,31 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N11">
-        <v>-2079.393854391359</v>
+        <v>-2136.779488307108</v>
       </c>
       <c r="O11">
-        <v>-27.11819130928961</v>
+        <v>-30.12306320303241</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.8562544998741403</v>
+        <v>0.7303045623762349</v>
       </c>
       <c r="R11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T11">
-        <v>0.9065486428219646</v>
+        <v>0.8375578481369297</v>
       </c>
       <c r="U11">
-        <v>0.8059623723914771</v>
+        <v>0.7768735799681212</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9904423352852886</v>
+        <v>0.9985492495152208</v>
       </c>
       <c r="Y11">
-        <v>0.992061932486372</v>
+        <v>0.9998901932260111</v>
       </c>
       <c r="Z11">
-        <v>0.0016195972010834</v>
+        <v>0.001340943710790299</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-43.54122375681116</v>
+        <v>-58.38276076350893</v>
       </c>
       <c r="AC11">
-        <v>16</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD11">
-        <v>0.7248789188732947</v>
+        <v>0.5242421510722166</v>
       </c>
       <c r="AE11">
-        <v>-0.6888762972937039</v>
+        <v>-0.8515692379596478</v>
       </c>
       <c r="AF11">
-        <v>1.202131108686866</v>
+        <v>1.318002023260689</v>
       </c>
       <c r="AG11">
-        <v>1.192588510785877</v>
+        <v>1.317857297710404</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2149,28 +2149,28 @@
         <v>84</v>
       </c>
       <c r="AL11">
-        <v>0.3595623905380364</v>
+        <v>0.2620922928664092</v>
       </c>
       <c r="AM11">
-        <v>0.7051231573892797</v>
+        <v>0.6461128338479821</v>
       </c>
       <c r="AN11">
-        <v>0.8196469094764647</v>
+        <v>0.7319605414246987</v>
       </c>
       <c r="AO11">
-        <v>-0.8636007334220179</v>
+        <v>-1.09376710170299</v>
       </c>
       <c r="AP11">
-        <v>0.2949296292788891</v>
+        <v>0.1047188308951358</v>
       </c>
       <c r="AQ11">
-        <v>-2.642194266982881</v>
+        <v>-2.629511894418323</v>
       </c>
       <c r="AR11">
-        <v>0.3626478390434086</v>
+        <v>0.3324834843152654</v>
       </c>
       <c r="AS11">
-        <v>0.06374796428625953</v>
+        <v>0.07414252735191168</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -190,33 +190,33 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_ACCELERATING</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>空头加速</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
@@ -238,37 +238,37 @@
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>下降坡延续</t>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C2" s="2">
         <v>46275</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46274</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.5692800216481988</v>
+        <v>0.1466153677489054</v>
       </c>
       <c r="G2">
-        <v>1.109282431255643</v>
+        <v>0.8916981049182402</v>
       </c>
       <c r="H2">
-        <v>1.07346016977262</v>
+        <v>1.074524367436986</v>
       </c>
       <c r="I2">
-        <v>0.2585324068237655</v>
+        <v>0.2586788527759752</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2">
-        <v>-0.4260524205199425</v>
+        <v>-0.4546807671936381</v>
       </c>
       <c r="O2">
-        <v>-12.42497580985538</v>
+        <v>-13.33598160712083</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.109282431255643</v>
+        <v>0.8916981049182402</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.9724499547242961</v>
+        <v>0.9937501621635167</v>
       </c>
       <c r="U2">
-        <v>0.9229624934160302</v>
+        <v>0.8687640725410471</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -847,34 +847,34 @@
         <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9972992558815378</v>
+        <v>0.9927174271705089</v>
       </c>
       <c r="Y2">
-        <v>0.9998720421714683</v>
+        <v>0.9983367776205151</v>
       </c>
       <c r="Z2">
-        <v>0.002572786289930518</v>
+        <v>0.005619350450006166</v>
       </c>
       <c r="AA2">
-        <v>0.4630903664045969</v>
+        <v>0.0861904706490934</v>
       </c>
       <c r="AB2">
-        <v>20.60150864564121</v>
+        <v>-10.70146987287008</v>
       </c>
       <c r="AC2">
-        <v>16</v>
+        <v>-25</v>
       </c>
       <c r="AD2">
-        <v>0.9360502711305557</v>
+        <v>0.9826080331064223</v>
       </c>
       <c r="AE2">
-        <v>0.3518662955106855</v>
+        <v>-0.185691823392222</v>
       </c>
       <c r="AF2">
-        <v>0.9544972080568478</v>
+        <v>0.7839688006626742</v>
       </c>
       <c r="AG2">
-        <v>0.9543750726667652</v>
+        <v>0.7826648862085941</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.6846754462856411</v>
+        <v>0.532762162779732</v>
       </c>
       <c r="AM2">
-        <v>0.8678659499928586</v>
+        <v>0.8065536943702535</v>
       </c>
       <c r="AN2">
-        <v>0.9020457495733645</v>
+        <v>0.7721394961939267</v>
       </c>
       <c r="AO2">
-        <v>0.3040788133693674</v>
+        <v>-0.09740858997026673</v>
       </c>
       <c r="AP2">
-        <v>1.110409765564364</v>
+        <v>0.6952620954468656</v>
       </c>
       <c r="AQ2">
-        <v>-1.973152759960435</v>
+        <v>-2.436636701598483</v>
       </c>
       <c r="AR2">
-        <v>0.9435296817973353</v>
+        <v>0.5520612450243971</v>
       </c>
       <c r="AS2">
-        <v>0.03681612924827607</v>
+        <v>0.0325645457244813</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C3" s="2">
         <v>46275</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46274</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -933,16 +933,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0.9831164404353598</v>
       </c>
       <c r="G3">
-        <v>2.80948747210962</v>
+        <v>2.401175662286452</v>
       </c>
       <c r="H3">
-        <v>1.962805776838827</v>
+        <v>1.974588821290828</v>
       </c>
       <c r="I3">
-        <v>0.4391778308274965</v>
+        <v>0.441494850197197</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,31 +954,31 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>-0.1149480421046835</v>
+        <v>-0.1209826998982565</v>
       </c>
       <c r="O3">
-        <v>-41.62629564059953</v>
+        <v>-41.41723434590048</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.80948747210962</v>
+        <v>2.401175662286452</v>
       </c>
       <c r="R3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.995854994680618</v>
+        <v>0.9928059095650883</v>
       </c>
       <c r="U3">
-        <v>0.9981218429706541</v>
+        <v>0.9940720574079374</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9998373602272229</v>
+        <v>0.9971460318026678</v>
       </c>
       <c r="Y3">
-        <v>0.9999483814575042</v>
+        <v>0.9993677281533742</v>
       </c>
       <c r="Z3">
-        <v>0.000111021230281283</v>
+        <v>0.002221696350706348</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>7.382802814430751</v>
+        <v>-9.719262686398665</v>
       </c>
       <c r="AC3">
-        <v>3.000000000000004</v>
+        <v>-15</v>
       </c>
       <c r="AD3">
-        <v>0.9917097753910579</v>
+        <v>0.9856467677090055</v>
       </c>
       <c r="AE3">
-        <v>0.1284979431501433</v>
+        <v>-0.1688207608820363</v>
       </c>
       <c r="AF3">
-        <v>2.290341953709482</v>
+        <v>2.007202716349008</v>
       </c>
       <c r="AG3">
-        <v>2.290223729596014</v>
+        <v>2.00593361858099</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1023,34 +1023,34 @@
         <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.9916585847778734</v>
+        <v>0.9850235710070653</v>
       </c>
       <c r="AM3">
-        <v>0.9924783265735199</v>
+        <v>0.9907626449903175</v>
       </c>
       <c r="AN3">
-        <v>2.272900400454537</v>
+        <v>1.983129691611978</v>
       </c>
       <c r="AO3">
-        <v>0.2790768090568564</v>
+        <v>-0.2703621536126906</v>
       </c>
       <c r="AP3">
-        <v>2.881898475879362</v>
+        <v>2.291754641934131</v>
       </c>
       <c r="AQ3">
-        <v>-5.135591575188919</v>
+        <v>-5.059268123616951</v>
       </c>
       <c r="AR3">
-        <v>2.443644714065337</v>
+        <v>1.871991524109026</v>
       </c>
       <c r="AS3">
-        <v>0.0334435970261589</v>
+        <v>0.03140060117376767</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C4" s="2">
         <v>46275</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46274</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.01403701514849852</v>
+        <v>0.007077295597485317</v>
       </c>
       <c r="H4">
-        <v>2.079077170388987</v>
+        <v>2.079280759661525</v>
       </c>
       <c r="I4">
-        <v>0.4926789713552525</v>
+        <v>0.4929587606991727</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1094,31 +1094,31 @@
         <v>146</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4">
-        <v>-0.2474658915567291</v>
+        <v>-0.2502181443567891</v>
       </c>
       <c r="O4">
-        <v>-9.873247312038155</v>
+        <v>-9.991597321719969</v>
       </c>
       <c r="P4">
-        <v>0.5285570140969089</v>
+        <v>0.4593543508125868</v>
       </c>
       <c r="Q4">
-        <v>0.02977457628648216</v>
+        <v>0.01309045140402488</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T4">
-        <v>0.6038783655477967</v>
+        <v>0.6039828205957997</v>
       </c>
       <c r="U4">
-        <v>0.6069459207557859</v>
+        <v>0.6206553275968192</v>
       </c>
       <c r="V4" t="s">
         <v>68</v>
@@ -1127,34 +1127,34 @@
         <v>68</v>
       </c>
       <c r="X4">
-        <v>0.8934936223121174</v>
+        <v>0.9655065205278323</v>
       </c>
       <c r="Y4">
-        <v>0.9408026250371093</v>
+        <v>0.9954522333148373</v>
       </c>
       <c r="Z4">
-        <v>0.04730900272499194</v>
+        <v>0.02994571278700509</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-94.46303669474203</v>
+        <v>-92.29915559941685</v>
       </c>
       <c r="AC4">
-        <v>-90</v>
+        <v>-68</v>
       </c>
       <c r="AD4">
-        <v>-0.07781593679090455</v>
+        <v>-0.040117066830479</v>
       </c>
       <c r="AE4">
-        <v>-0.9969677426985057</v>
+        <v>-0.9991949864510524</v>
       </c>
       <c r="AF4">
-        <v>0.4431683733027507</v>
+        <v>0.4841383908154071</v>
       </c>
       <c r="AG4">
-        <v>0.4169339689366535</v>
+        <v>0.4819366423706485</v>
       </c>
       <c r="AH4" t="s">
         <v>70</v>
@@ -1163,34 +1163,34 @@
         <v>72</v>
       </c>
       <c r="AJ4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL4">
-        <v>-0.03660471880130239</v>
+        <v>-0.01996731188522045</v>
       </c>
       <c r="AM4">
-        <v>0.4759844382618538</v>
+        <v>0.4827768605672526</v>
       </c>
       <c r="AN4">
-        <v>0.1292815129190201</v>
+        <v>0.09041128214031938</v>
       </c>
       <c r="AO4">
-        <v>-0.3742686717291679</v>
+        <v>-0.4586118257574019</v>
       </c>
       <c r="AP4">
-        <v>-0.4592823010889686</v>
+        <v>-0.4808385627583562</v>
       </c>
       <c r="AQ4">
-        <v>-0.9123482222380772</v>
+        <v>-0.8782450330104122</v>
       </c>
       <c r="AR4">
-        <v>0.5084784036395883</v>
+        <v>0.5245460561227651</v>
       </c>
       <c r="AS4">
-        <v>0.1776084102560392</v>
+        <v>0.1844436076138944</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C5" s="2">
         <v>46275</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46274</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1213,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.4266819783946858</v>
+        <v>0.06213464408790158</v>
       </c>
       <c r="G5">
-        <v>1.450868759022682</v>
+        <v>1.205848195906553</v>
       </c>
       <c r="H5">
-        <v>1.500552139879995</v>
+        <v>1.50403106540973</v>
       </c>
       <c r="I5">
-        <v>0.3388210686096281</v>
+        <v>0.3404960742806936</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,19 +1234,19 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>-0.1127442842491932</v>
+        <v>-0.1162676288228979</v>
       </c>
       <c r="O5">
-        <v>-36.52481729697374</v>
+        <v>-37.79744115919171</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.450868759022682</v>
+        <v>1.205848195906553</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>0.9965186387595244</v>
+        <v>0.9404449150584619</v>
       </c>
       <c r="U5">
-        <v>0.9119427220414751</v>
+        <v>0.8324109017031668</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9827021318240701</v>
+        <v>0.9995537443848532</v>
       </c>
       <c r="Y5">
-        <v>0.9980281513619448</v>
+        <v>0.9995619732546944</v>
       </c>
       <c r="Z5">
-        <v>0.01532601953787471</v>
+        <v>8.228869841198083E-06</v>
       </c>
       <c r="AA5">
-        <v>0.2329782802410662</v>
+        <v>0.1778889054644588</v>
       </c>
       <c r="AB5">
-        <v>-7.753214303499411</v>
+        <v>-31.62603587327359</v>
       </c>
       <c r="AC5">
-        <v>40.99999999999999</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AD5">
-        <v>0.990858330666288</v>
+        <v>0.8514887408819645</v>
       </c>
       <c r="AE5">
-        <v>-0.1349065178159199</v>
+        <v>-0.5243728865523529</v>
       </c>
       <c r="AF5">
-        <v>1.284540762135069</v>
+        <v>1.248398427799492</v>
       </c>
       <c r="AG5">
-        <v>1.282007842182727</v>
+        <v>1.247851595899319</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1303,34 +1303,34 @@
         <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL5">
-        <v>0.6096488898083851</v>
+        <v>0.5012599090422775</v>
       </c>
       <c r="AM5">
-        <v>0.837692027098163</v>
+        <v>0.7852230296161203</v>
       </c>
       <c r="AN5">
-        <v>1.225754760766346</v>
+        <v>1.060783840176871</v>
       </c>
       <c r="AO5">
-        <v>-0.3016279754365427</v>
+        <v>-0.6571496114157754</v>
       </c>
       <c r="AP5">
-        <v>1.236600414817661</v>
+        <v>0.8512635793615695</v>
       </c>
       <c r="AQ5">
-        <v>-2.808461627930354</v>
+        <v>-3.082724975108901</v>
       </c>
       <c r="AR5">
-        <v>1.03317886421508</v>
+        <v>0.6491904612606465</v>
       </c>
       <c r="AS5">
-        <v>0.03647320751078251</v>
+        <v>0.03765376253669189</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C6" s="2">
         <v>46275</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46274</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1356,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.1899500130054068</v>
+        <v>0.2384300129785058</v>
       </c>
       <c r="H6">
-        <v>0.9433225897199168</v>
+        <v>0.943332240426368</v>
       </c>
       <c r="I6">
-        <v>0.2568699422799828</v>
+        <v>0.2567822908950231</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,31 +1374,31 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>0.006499294950282595</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.1310058733049552</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.1899500130054068</v>
+        <v>0.2384300129785058</v>
       </c>
       <c r="R6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T6">
-        <v>-0.8280617309978223</v>
+        <v>-0.8386833152190706</v>
       </c>
       <c r="U6">
-        <v>0.7686373726648043</v>
+        <v>0.7762214031496457</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,34 +1407,34 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9494089524131439</v>
+        <v>0.9676997054779294</v>
       </c>
       <c r="Y6">
-        <v>0.9840383748631368</v>
+        <v>0.9952556452042558</v>
       </c>
       <c r="Z6">
-        <v>0.0346294224499929</v>
+        <v>0.02755593972632642</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-119.4121077146081</v>
+        <v>-121.7416175324508</v>
       </c>
       <c r="AC6">
-        <v>-77</v>
+        <v>-61</v>
       </c>
       <c r="AD6">
-        <v>-0.4910878471066095</v>
+        <v>-0.526089510080176</v>
       </c>
       <c r="AE6">
-        <v>-0.8711100541402305</v>
+        <v>-0.8504292018643294</v>
       </c>
       <c r="AF6">
-        <v>0.467147505623246</v>
+        <v>0.4342834274981694</v>
       </c>
       <c r="AG6">
-        <v>0.4596910722548671</v>
+        <v>0.4322230328362062</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>83</v>
       </c>
       <c r="AL6">
-        <v>-0.2416246434909123</v>
+        <v>-0.2617967773950182</v>
       </c>
       <c r="AM6">
-        <v>0.6221468121514782</v>
+        <v>0.6417163165867966</v>
       </c>
       <c r="AN6">
-        <v>-0.1118580393334388</v>
+        <v>-0.1519236588311104</v>
       </c>
       <c r="AO6">
-        <v>-0.4291765003638253</v>
+        <v>-0.3918344817619402</v>
       </c>
       <c r="AP6">
-        <v>-0.3912646910892517</v>
+        <v>-0.4339082491779432</v>
       </c>
       <c r="AQ6">
-        <v>0.1062995051137328</v>
+        <v>0.1170630111252183</v>
       </c>
       <c r="AR6">
-        <v>0.3528146985862998</v>
+        <v>0.4009972801686971</v>
       </c>
       <c r="AS6">
-        <v>0.1306198212173499</v>
+        <v>0.09633341505830399</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C7" s="2">
         <v>46275</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46274</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1.016772576813987</v>
+        <v>0.8139260349039491</v>
       </c>
       <c r="H7">
-        <v>1.459365331910676</v>
+        <v>1.463127930094301</v>
       </c>
       <c r="I7">
-        <v>0.3612908735759212</v>
+        <v>0.3630944913655973</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,31 +1514,31 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7">
-        <v>-0.1530436213969156</v>
+        <v>-0.1558491165953869</v>
       </c>
       <c r="O7">
-        <v>-41.19216955795083</v>
+        <v>-41.8427007831127</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.016772576813987</v>
+        <v>0.8139260349039491</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T7">
-        <v>0.9805254827859041</v>
+        <v>0.9316469936104604</v>
       </c>
       <c r="U7">
-        <v>0.8386678405219214</v>
+        <v>0.818771331126668</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9397788366431039</v>
+        <v>0.9872732673098995</v>
       </c>
       <c r="Y7">
-        <v>0.9897254930730585</v>
+        <v>0.9981207360078433</v>
       </c>
       <c r="Z7">
-        <v>0.04994665642995455</v>
+        <v>0.01084746869794384</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>-19.51096534603836</v>
+        <v>-36.91044960373866</v>
       </c>
       <c r="AC7">
-        <v>74.99999999999999</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="AD7">
-        <v>0.9425775894082042</v>
+        <v>0.7995751405528057</v>
       </c>
       <c r="AE7">
-        <v>-0.3339872571602375</v>
+        <v>-0.6005660618199808</v>
       </c>
       <c r="AF7">
-        <v>1.032186602686159</v>
+        <v>0.9466815060356877</v>
       </c>
       <c r="AG7">
-        <v>1.021581394286964</v>
+        <v>0.9449024415693542</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1583,34 +1583,34 @@
         <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AL7">
-        <v>0.4664465347183249</v>
+        <v>0.3990362638910706</v>
       </c>
       <c r="AM7">
-        <v>0.7739317707643107</v>
+        <v>0.7338323803457383</v>
       </c>
       <c r="AN7">
-        <v>0.8262128267408263</v>
+        <v>0.6822975428952236</v>
       </c>
       <c r="AO7">
-        <v>-0.5082568125725563</v>
+        <v>-0.6387562523090935</v>
       </c>
       <c r="AP7">
-        <v>1.011677001301629</v>
+        <v>0.7250910476433676</v>
       </c>
       <c r="AQ7">
-        <v>-1.407178365885063</v>
+        <v>-1.550986721546837</v>
       </c>
       <c r="AR7">
-        <v>0.9269730964381281</v>
+        <v>0.6218725144078714</v>
       </c>
       <c r="AS7">
-        <v>0.03496952422480668</v>
+        <v>0.03588279615232357</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C8" s="2">
         <v>46275</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46274</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.6005909781916019</v>
+        <v>0.842535182301704</v>
       </c>
       <c r="H8">
-        <v>1.438258554215193</v>
+        <v>1.438467752002441</v>
       </c>
       <c r="I8">
-        <v>0.3567845500354639</v>
+        <v>0.356871774222388</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,31 +1654,31 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-0.005498960418972647</v>
+        <v>-0.007191542852915994</v>
       </c>
       <c r="O8">
-        <v>-1.501129879411469</v>
+        <v>-1.91119210214169</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.6005909781916019</v>
+        <v>0.842535182301704</v>
       </c>
       <c r="R8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T8">
-        <v>0.9556874599152398</v>
+        <v>0.8990306146348624</v>
       </c>
       <c r="U8">
-        <v>0.8292741833208217</v>
+        <v>0.8043107252188452</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9431289083829874</v>
+        <v>0.9911835175935791</v>
       </c>
       <c r="Y8">
-        <v>0.9968593054358549</v>
+        <v>0.9989877945326281</v>
       </c>
       <c r="Z8">
-        <v>0.05373039705286753</v>
+        <v>0.007804276939048949</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>29.54620453941579</v>
+        <v>45.24258405442502</v>
       </c>
       <c r="AC8">
-        <v>-70</v>
+        <v>-26</v>
       </c>
       <c r="AD8">
-        <v>0.8699583121118509</v>
+        <v>0.7041066397461356</v>
       </c>
       <c r="AE8">
-        <v>0.4931252733205828</v>
+        <v>0.7100942471710396</v>
       </c>
       <c r="AF8">
-        <v>0.4946063292364956</v>
+        <v>0.798085888289748</v>
       </c>
       <c r="AG8">
-        <v>0.4930529218268708</v>
+        <v>0.7972780613901888</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1723,34 +1723,34 @@
         <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL8">
-        <v>0.4336130193849842</v>
+        <v>0.3516969695778859</v>
       </c>
       <c r="AM8">
-        <v>0.7493466694651054</v>
+        <v>0.6998346222889451</v>
       </c>
       <c r="AN8">
-        <v>0.3751948373740336</v>
+        <v>0.5343667599788634</v>
       </c>
       <c r="AO8">
-        <v>0.2771824625604786</v>
+        <v>0.583276607482987</v>
       </c>
       <c r="AP8">
-        <v>1.126869207941201</v>
+        <v>1.524969502733192</v>
       </c>
       <c r="AQ8">
-        <v>-0.06969369288327512</v>
+        <v>0.2222349447075852</v>
       </c>
       <c r="AR8">
-        <v>1.081140949300065</v>
+        <v>1.503406852245616</v>
       </c>
       <c r="AS8">
-        <v>0.07027720713999359</v>
+        <v>0.07362065147543613</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C9" s="2">
         <v>46275</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46274</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1776,13 +1776,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4.168882434469204</v>
+        <v>3.856630204854587</v>
       </c>
       <c r="H9">
-        <v>3.033388003049883</v>
+        <v>3.041329146300729</v>
       </c>
       <c r="I9">
-        <v>0.6378528057457957</v>
+        <v>0.6412326289402306</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9">
-        <v>0.623426079803278</v>
+        <v>0.6436543616434559</v>
       </c>
       <c r="O9">
-        <v>96.43627553445329</v>
+        <v>94.8992792692152</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.168882434469204</v>
+        <v>3.856630204854587</v>
       </c>
       <c r="R9" t="s">
         <v>62</v>
@@ -1815,10 +1815,10 @@
         <v>67</v>
       </c>
       <c r="T9">
-        <v>-0.9897352629795897</v>
+        <v>-0.9995502225675734</v>
       </c>
       <c r="U9">
-        <v>0.9953623838234893</v>
+        <v>0.9997581877229801</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.999637629439567</v>
+        <v>0.9996242397568611</v>
       </c>
       <c r="Y9">
-        <v>0.9999260619306957</v>
+        <v>0.999842350270288</v>
       </c>
       <c r="Z9">
-        <v>0.0002884324911286429</v>
+        <v>0.0002181105134269057</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-168.3699817462219</v>
+        <v>-177.5694691317406</v>
       </c>
       <c r="AC9">
-        <v>5.000000000000007</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD9">
-        <v>-0.9794697669482223</v>
+        <v>-0.9991003742166761</v>
       </c>
       <c r="AE9">
-        <v>-0.201591110008341</v>
+        <v>-0.0424080445210326</v>
       </c>
       <c r="AF9">
-        <v>3.227806295906887</v>
+        <v>2.951953715387135</v>
       </c>
       <c r="AG9">
-        <v>3.227567638141279</v>
+        <v>2.951488340681782</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>85</v>
       </c>
       <c r="AL9">
-        <v>-0.9793973468447121</v>
+        <v>-0.9989428663127257</v>
       </c>
       <c r="AM9">
-        <v>0.988449476258463</v>
+        <v>0.9945802336410562</v>
       </c>
       <c r="AN9">
-        <v>-3.166403133240801</v>
+        <v>-2.946833510094436</v>
       </c>
       <c r="AO9">
-        <v>-0.6205442492079006</v>
+        <v>-0.1538033138105544</v>
       </c>
       <c r="AP9">
-        <v>-5.201157229962569</v>
+        <v>-4.73947218000892</v>
       </c>
       <c r="AQ9">
-        <v>4.963366596708446</v>
+        <v>4.920456880994661</v>
       </c>
       <c r="AR9">
-        <v>4.741587371836053</v>
+        <v>4.291788192979363</v>
       </c>
       <c r="AS9">
-        <v>0.0357705033449802</v>
+        <v>0.03396467479031572</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C10" s="2">
         <v>46275</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46274</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1916,13 +1916,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.770835826498998</v>
+        <v>2.798196837805659</v>
       </c>
       <c r="H10">
-        <v>2.051034809298019</v>
+        <v>2.0555522779808</v>
       </c>
       <c r="I10">
-        <v>0.4526917807004999</v>
+        <v>0.4521184617969376</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,31 +1934,31 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N10">
-        <v>25.98764264140891</v>
+        <v>28.21222100906685</v>
       </c>
       <c r="O10">
-        <v>24.58622766453071</v>
+        <v>26.02089031734215</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.770835826498998</v>
+        <v>2.798196837805659</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.8021105853176919</v>
+        <v>-0.8377920202772901</v>
       </c>
       <c r="U10">
-        <v>0.9109192273751268</v>
+        <v>0.9269575719191055</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9998778559286617</v>
+        <v>0.9995805755066395</v>
       </c>
       <c r="Y10">
-        <v>0.9998778559286617</v>
+        <v>0.9998046511773003</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>0.0002240756706608504</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-127.1710804786239</v>
+        <v>-132.4970578377665</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD10">
-        <v>-0.6041969966638925</v>
+        <v>-0.6755523472254542</v>
       </c>
       <c r="AE10">
-        <v>-0.7968349824288165</v>
+        <v>-0.737312027677685</v>
       </c>
       <c r="AF10">
-        <v>3.387159043982499</v>
+        <v>3.156771008977966</v>
       </c>
       <c r="AG10">
-        <v>3.386745322586596</v>
+        <v>3.15615433747783</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>83</v>
       </c>
       <c r="AL10">
-        <v>-0.6041231975828296</v>
+        <v>-0.6754203788697517</v>
       </c>
       <c r="AM10">
-        <v>0.8725029968446851</v>
+        <v>0.8948797732391993</v>
       </c>
       <c r="AN10">
-        <v>-2.046261352372307</v>
+        <v>-2.10867769958606</v>
       </c>
       <c r="AO10">
-        <v>-2.698677149614167</v>
+        <v>-2.347407935325795</v>
       </c>
       <c r="AP10">
-        <v>-3.704382662691871</v>
+        <v>-3.568394250874231</v>
       </c>
       <c r="AQ10">
-        <v>2.745353844411959</v>
+        <v>3.619139089034123</v>
       </c>
       <c r="AR10">
-        <v>3.36365172865137</v>
+        <v>3.158217086892496</v>
       </c>
       <c r="AS10">
-        <v>0.05808901153009509</v>
+        <v>0.05145039226994787</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46276</v>
+      </c>
+      <c r="C11" s="2">
         <v>46275</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46274</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.7303045623762349</v>
+        <v>0.322878077889677</v>
       </c>
       <c r="H11">
-        <v>2.431345099254925</v>
+        <v>2.411917296847714</v>
       </c>
       <c r="I11">
-        <v>0.5766718786152386</v>
+        <v>0.5711207913118737</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,31 +2074,31 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11">
-        <v>-2136.779488307108</v>
+        <v>-2182.06575823985</v>
       </c>
       <c r="O11">
-        <v>-30.12306320303241</v>
+        <v>-29.06182693128404</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>0.2969488778001208</v>
       </c>
       <c r="Q11">
-        <v>0.7303045623762349</v>
+        <v>0.4592526314151618</v>
       </c>
       <c r="R11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T11">
-        <v>0.8375578481369297</v>
+        <v>0.7568632986052749</v>
       </c>
       <c r="U11">
-        <v>0.7768735799681212</v>
+        <v>0.740508961547742</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9985492495152208</v>
+        <v>0.9941113304981589</v>
       </c>
       <c r="Y11">
-        <v>0.9998901932260111</v>
+        <v>0.9996819087014734</v>
       </c>
       <c r="Z11">
-        <v>0.001340943710790299</v>
+        <v>0.005570578203314525</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.02142553806564812</v>
       </c>
       <c r="AB11">
-        <v>-58.38276076350893</v>
+        <v>-72.19627297879811</v>
       </c>
       <c r="AC11">
-        <v>-12.99999999999999</v>
+        <v>-24</v>
       </c>
       <c r="AD11">
-        <v>0.5242421510722166</v>
+        <v>0.3057572391824364</v>
       </c>
       <c r="AE11">
-        <v>-0.8515692379596478</v>
+        <v>-0.9521095056176755</v>
       </c>
       <c r="AF11">
-        <v>1.318002023260689</v>
+        <v>1.435111442888528</v>
       </c>
       <c r="AG11">
-        <v>1.317857297710404</v>
+        <v>1.434654946426129</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2143,34 +2143,34 @@
         <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AK11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AL11">
-        <v>0.2620922928664092</v>
+        <v>0.1561044550058966</v>
       </c>
       <c r="AM11">
-        <v>0.6461128338479821</v>
+        <v>0.5807521591084351</v>
       </c>
       <c r="AN11">
-        <v>0.7319605414246987</v>
+        <v>0.5147719817282685</v>
       </c>
       <c r="AO11">
-        <v>-1.09376710170299</v>
+        <v>-1.330552561932046</v>
       </c>
       <c r="AP11">
-        <v>0.1047188308951358</v>
+        <v>-0.1771006120820895</v>
       </c>
       <c r="AQ11">
-        <v>-2.629511894418323</v>
+        <v>-2.280037637543915</v>
       </c>
       <c r="AR11">
-        <v>0.3324834843152654</v>
+        <v>0.481562497732405</v>
       </c>
       <c r="AS11">
-        <v>0.07414252735191168</v>
+        <v>0.1009919220329404</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -190,10 +190,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
+    <t>UP_REVERSAL_WATCH</t>
   </si>
   <si>
     <t>DOWN_ACCELERATING</t>
@@ -205,10 +208,13 @@
     <t>DOWN_STEADY</t>
   </si>
   <si>
+    <t>多头减速</t>
+  </si>
+  <si>
     <t>多头稳态</t>
   </si>
   <si>
-    <t>多头减速</t>
+    <t>多头反转预警</t>
   </si>
   <si>
     <t>空头加速</t>
@@ -220,31 +226,25 @@
     <t>空头稳态</t>
   </si>
   <si>
-    <t>NEUTRAL</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>TRANSITION</t>
+    <t>CONFLICT</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
+    <t>TURNING_DOWN</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
@@ -256,13 +256,13 @@
     <t>DOWN_SLOPE</t>
   </si>
   <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
     <t>上升坡延续</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
+    <t>向下转折带</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46277</v>
+      </c>
+      <c r="C2" s="2">
         <v>46276</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46275</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -793,16 +793,16 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0.1466153677489054</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.8916981049182402</v>
+        <v>0.7627340899366188</v>
       </c>
       <c r="H2">
-        <v>1.074524367436986</v>
+        <v>1.075487212942842</v>
       </c>
       <c r="I2">
-        <v>0.2586788527759752</v>
+        <v>0.2587974643150144</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -814,73 +814,73 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2">
-        <v>-0.4546807671936381</v>
+        <v>-0.4794678796074124</v>
       </c>
       <c r="O2">
-        <v>-13.33598160712083</v>
+        <v>-14.01455271625312</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.8916981049182402</v>
+        <v>0.7627340899366188</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2">
-        <v>0.9937501621635167</v>
+        <v>0.9519909109868182</v>
       </c>
       <c r="U2">
-        <v>0.8687640725410471</v>
+        <v>0.8279369155102769</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X2">
-        <v>0.9927174271705089</v>
+        <v>0.9847295311363554</v>
       </c>
       <c r="Y2">
-        <v>0.9983367776205151</v>
+        <v>0.9981640222648349</v>
       </c>
       <c r="Z2">
-        <v>0.005619350450006166</v>
+        <v>0.0134344911284795</v>
       </c>
       <c r="AA2">
-        <v>0.0861904706490934</v>
+        <v>0.04010881987763081</v>
       </c>
       <c r="AB2">
-        <v>-10.70146987287008</v>
+        <v>-30.04160606895899</v>
       </c>
       <c r="AC2">
-        <v>-25</v>
+        <v>-37</v>
       </c>
       <c r="AD2">
-        <v>0.9826080331064223</v>
+        <v>0.8656620940372549</v>
       </c>
       <c r="AE2">
-        <v>-0.185691823392222</v>
+        <v>-0.5006287436284845</v>
       </c>
       <c r="AF2">
-        <v>0.7839688006626742</v>
+        <v>0.7629811261465481</v>
       </c>
       <c r="AG2">
-        <v>0.7826648862085941</v>
+        <v>0.7615803097865919</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="s">
         <v>74</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.532762162779732</v>
+        <v>0.4493648481532204</v>
       </c>
       <c r="AM2">
-        <v>0.8065536943702535</v>
+        <v>0.7614545481235691</v>
       </c>
       <c r="AN2">
-        <v>0.7721394961939267</v>
+        <v>0.6795446964577995</v>
       </c>
       <c r="AO2">
-        <v>-0.09740858997026673</v>
+        <v>-0.32049312701577</v>
       </c>
       <c r="AP2">
-        <v>0.6952620954468656</v>
+        <v>0.5106168384412557</v>
       </c>
       <c r="AQ2">
-        <v>-2.436636701598483</v>
+        <v>-2.309988956264086</v>
       </c>
       <c r="AR2">
-        <v>0.5520612450243971</v>
+        <v>0.4159035631018527</v>
       </c>
       <c r="AS2">
-        <v>0.0325645457244813</v>
+        <v>0.03748834570550436</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C3" s="2">
         <v>46275</v>
@@ -969,10 +969,10 @@
         <v>2.401175662286452</v>
       </c>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T3">
         <v>0.9928059095650883</v>
@@ -984,7 +984,7 @@
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X3">
         <v>0.9971460318026678</v>
@@ -1020,13 +1020,13 @@
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL3">
         <v>0.9850235710070653</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46277</v>
+      </c>
+      <c r="C4" s="2">
         <v>46276</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46275</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1076,121 +1076,121 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.007077295597485317</v>
+        <v>0.138907574804795</v>
       </c>
       <c r="H4">
-        <v>2.079280759661525</v>
+        <v>2.079464959479535</v>
       </c>
       <c r="I4">
-        <v>0.4929587606991727</v>
+        <v>0.4932988478904669</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4">
-        <v>-0.2502181443567891</v>
+        <v>-0.2511252061252907</v>
       </c>
       <c r="O4">
-        <v>-9.991597321719969</v>
+        <v>-9.624289312220228</v>
       </c>
       <c r="P4">
-        <v>0.4593543508125868</v>
+        <v>0.1448209490283399</v>
       </c>
       <c r="Q4">
-        <v>0.01309045140402488</v>
+        <v>0.1624309840693213</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T4">
-        <v>0.6039828205957997</v>
+        <v>0.4648788460450831</v>
       </c>
       <c r="U4">
-        <v>0.6206553275968192</v>
+        <v>0.5085445576424406</v>
       </c>
       <c r="V4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X4">
-        <v>0.9655065205278323</v>
+        <v>0.952695096459136</v>
       </c>
       <c r="Y4">
-        <v>0.9954522333148373</v>
+        <v>0.9973963076886128</v>
       </c>
       <c r="Z4">
-        <v>0.02994571278700509</v>
+        <v>0.04470121122947679</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-92.29915559941685</v>
+        <v>-103.7510891352802</v>
       </c>
       <c r="AC4">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="AD4">
-        <v>-0.040117066830479</v>
+        <v>-0.2377043565213686</v>
       </c>
       <c r="AE4">
-        <v>-0.9991949864510524</v>
+        <v>-0.9713375514674402</v>
       </c>
       <c r="AF4">
-        <v>0.4841383908154071</v>
+        <v>0.4832250112247069</v>
       </c>
       <c r="AG4">
-        <v>0.4819366423706485</v>
+        <v>0.4819668419783111</v>
       </c>
       <c r="AH4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="AI4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL4">
-        <v>-0.01996731188522045</v>
+        <v>-0.1185427237579554</v>
       </c>
       <c r="AM4">
-        <v>0.4827768605672526</v>
+        <v>0.5419526672058479</v>
       </c>
       <c r="AN4">
-        <v>0.09041128214031938</v>
+        <v>-0.01724737476143526</v>
       </c>
       <c r="AO4">
-        <v>-0.4586118257574019</v>
+        <v>-0.4600429033012642</v>
       </c>
       <c r="AP4">
-        <v>-0.4808385627583562</v>
+        <v>-0.6831301709401844</v>
       </c>
       <c r="AQ4">
-        <v>-0.8782450330104122</v>
+        <v>-0.9812357988182752</v>
       </c>
       <c r="AR4">
-        <v>0.5245460561227651</v>
+        <v>0.7337126753893859</v>
       </c>
       <c r="AS4">
-        <v>0.1844436076138944</v>
+        <v>0.1896489829438474</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,7 +1201,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C5" s="2">
         <v>46275</v>
@@ -1249,7 +1249,7 @@
         <v>1.205848195906553</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S5" t="s">
         <v>64</v>
@@ -1264,7 +1264,7 @@
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X5">
         <v>0.9995537443848532</v>
@@ -1300,13 +1300,13 @@
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL5">
         <v>0.5012599090422775</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46277</v>
+      </c>
+      <c r="C6" s="2">
         <v>46276</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46275</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1356,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.2384300129785058</v>
+        <v>0.281499877920296</v>
       </c>
       <c r="H6">
-        <v>0.943332240426368</v>
+        <v>0.943340972017919</v>
       </c>
       <c r="I6">
-        <v>0.2567822908950231</v>
+        <v>0.2566980963193565</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,67 +1374,67 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <v>0.006499294950282595</v>
+        <v>0.01499112816820195</v>
       </c>
       <c r="O6">
-        <v>0.1310058733049552</v>
+        <v>0.2996941230256008</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.2384300129785058</v>
+        <v>0.281499877920296</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T6">
-        <v>-0.8386833152190706</v>
+        <v>-0.8897938918869088</v>
       </c>
       <c r="U6">
-        <v>0.7762214031496457</v>
+        <v>0.7992171690588966</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
       </c>
       <c r="W6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X6">
-        <v>0.9676997054779294</v>
+        <v>0.9569406621468657</v>
       </c>
       <c r="Y6">
-        <v>0.9952556452042558</v>
+        <v>0.9952396708391507</v>
       </c>
       <c r="Z6">
-        <v>0.02755593972632642</v>
+        <v>0.03829900869228497</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-121.7416175324508</v>
+        <v>-132.5502794454923</v>
       </c>
       <c r="AC6">
-        <v>-61</v>
+        <v>-68</v>
       </c>
       <c r="AD6">
-        <v>-0.526089510080176</v>
+        <v>-0.6762369391362666</v>
       </c>
       <c r="AE6">
-        <v>-0.8504292018643294</v>
+        <v>-0.736684194310977</v>
       </c>
       <c r="AF6">
-        <v>0.4342834274981694</v>
+        <v>0.3785972529747204</v>
       </c>
       <c r="AG6">
-        <v>0.4322230328362062</v>
+        <v>0.3767950054311673</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>83</v>
       </c>
       <c r="AL6">
-        <v>-0.2617967773950182</v>
+        <v>-0.3365089143576264</v>
       </c>
       <c r="AM6">
-        <v>0.6417163165867966</v>
+        <v>0.6894951858989864</v>
       </c>
       <c r="AN6">
-        <v>-0.1519236588311104</v>
+        <v>-0.1888515677004071</v>
       </c>
       <c r="AO6">
-        <v>-0.3918344817619402</v>
+        <v>-0.3091809003988046</v>
       </c>
       <c r="AP6">
-        <v>-0.4339082491779432</v>
+        <v>-0.4667626019016398</v>
       </c>
       <c r="AQ6">
-        <v>0.1170630111252183</v>
+        <v>0.1693803799238007</v>
       </c>
       <c r="AR6">
-        <v>0.4009972801686971</v>
+        <v>0.4334020959173555</v>
       </c>
       <c r="AS6">
-        <v>0.09633341505830399</v>
+        <v>0.07806520423730776</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C7" s="2">
         <v>46275</v>
@@ -1529,7 +1529,7 @@
         <v>0.8139260349039491</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S7" t="s">
         <v>64</v>
@@ -1544,7 +1544,7 @@
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X7">
         <v>0.9872732673098995</v>
@@ -1580,13 +1580,13 @@
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL7">
         <v>0.3990362638910706</v>
@@ -1621,7 +1621,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C8" s="2">
         <v>46275</v>
@@ -1669,10 +1669,10 @@
         <v>0.842535182301704</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T8">
         <v>0.8990306146348624</v>
@@ -1684,7 +1684,7 @@
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X8">
         <v>0.9911835175935791</v>
@@ -1720,7 +1720,7 @@
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s">
         <v>78</v>
@@ -1761,7 +1761,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C9" s="2">
         <v>46275</v>
@@ -1809,10 +1809,10 @@
         <v>3.856630204854587</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T9">
         <v>-0.9995502225675734</v>
@@ -1824,7 +1824,7 @@
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X9">
         <v>0.9996242397568611</v>
@@ -1901,7 +1901,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C10" s="2">
         <v>46275</v>
@@ -1949,10 +1949,10 @@
         <v>2.798196837805659</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T10">
         <v>-0.8377920202772901</v>
@@ -1964,7 +1964,7 @@
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X10">
         <v>0.9995805755066395</v>
@@ -2041,7 +2041,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C11" s="2">
         <v>46275</v>
@@ -2089,7 +2089,7 @@
         <v>0.4592526314151618</v>
       </c>
       <c r="R11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S11" t="s">
         <v>64</v>
@@ -2104,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X11">
         <v>0.9941113304981589</v>
@@ -2140,13 +2140,13 @@
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL11">
         <v>0.1561044550058966</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>Pair</t>
   </si>
@@ -193,9 +193,6 @@
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>UP_REVERSAL_WATCH</t>
   </si>
   <si>
@@ -211,9 +208,6 @@
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
     <t>多头反转预警</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>TURNING_DOWN</t>
   </si>
   <si>
@@ -257,9 +248,6 @@
   </si>
   <si>
     <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
   </si>
   <si>
     <t>向下转折带</t>
@@ -781,7 +769,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C2" s="2">
         <v>46276</v>
@@ -832,7 +820,7 @@
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T2">
         <v>0.9519909109868182</v>
@@ -844,7 +832,7 @@
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X2">
         <v>0.9847295311363554</v>
@@ -880,13 +868,13 @@
         <v>56</v>
       </c>
       <c r="AI2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>72</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>74</v>
-      </c>
       <c r="AK2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL2">
         <v>0.4493648481532204</v>
@@ -921,10 +909,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C3" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -933,16 +921,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.9831164404353598</v>
+        <v>0.703221216942846</v>
       </c>
       <c r="G3">
-        <v>2.401175662286452</v>
+        <v>2.167902143529543</v>
       </c>
       <c r="H3">
-        <v>1.974588821290828</v>
+        <v>1.987551891302176</v>
       </c>
       <c r="I3">
-        <v>0.441494850197197</v>
+        <v>0.4437288953891284</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,103 +942,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3">
-        <v>-0.1209826998982565</v>
+        <v>-0.1265021697956313</v>
       </c>
       <c r="O3">
-        <v>-41.41723434590048</v>
+        <v>-44.00075471152392</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.401175662286452</v>
+        <v>2.167902143529543</v>
       </c>
       <c r="R3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.9928059095650883</v>
+        <v>0.9502927037673258</v>
       </c>
       <c r="U3">
-        <v>0.9940720574079374</v>
+        <v>0.9328738465763199</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X3">
-        <v>0.9971460318026678</v>
+        <v>0.9929004085374168</v>
       </c>
       <c r="Y3">
-        <v>0.9993677281533742</v>
+        <v>0.9990357893583854</v>
       </c>
       <c r="Z3">
-        <v>0.002221696350706348</v>
+        <v>0.00613538082096865</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.992041590135873</v>
       </c>
       <c r="AB3">
-        <v>-9.719262686398665</v>
+        <v>-25.1628791310978</v>
       </c>
       <c r="AC3">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="AD3">
-        <v>0.9856467677090055</v>
+        <v>0.9051027170225241</v>
       </c>
       <c r="AE3">
-        <v>-0.1688207608820363</v>
+        <v>-0.4251929816429767</v>
       </c>
       <c r="AF3">
-        <v>2.007202716349008</v>
+        <v>1.982549504892468</v>
       </c>
       <c r="AG3">
-        <v>2.00593361858099</v>
+        <v>1.980637909562323</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>72</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>75</v>
-      </c>
       <c r="AK3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AL3">
-        <v>0.9850235710070653</v>
+        <v>0.9006318908460458</v>
       </c>
       <c r="AM3">
-        <v>0.9907626449903175</v>
+        <v>0.9647992452175191</v>
       </c>
       <c r="AN3">
-        <v>1.983129691611978</v>
+        <v>1.82472219597571</v>
       </c>
       <c r="AO3">
-        <v>-0.2703621536126906</v>
+        <v>-0.7384305222231893</v>
       </c>
       <c r="AP3">
-        <v>2.291754641934131</v>
+        <v>1.921060464331321</v>
       </c>
       <c r="AQ3">
-        <v>-5.059268123616951</v>
+        <v>-5.034163411394008</v>
       </c>
       <c r="AR3">
-        <v>1.871991524109026</v>
+        <v>1.519758685396873</v>
       </c>
       <c r="AS3">
-        <v>0.03140060117376767</v>
+        <v>0.03201609461231736</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,7 +1049,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C4" s="2">
         <v>46276</v>
@@ -1109,10 +1097,10 @@
         <v>0.1624309840693213</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T4">
         <v>0.4648788460450831</v>
@@ -1124,7 +1112,7 @@
         <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="X4">
         <v>0.952695096459136</v>
@@ -1160,13 +1148,13 @@
         <v>57</v>
       </c>
       <c r="AI4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>73</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>76</v>
-      </c>
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AL4">
         <v>-0.1185427237579554</v>
@@ -1201,10 +1189,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C5" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1213,16 +1201,16 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0.06213464408790158</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1.205848195906553</v>
+        <v>1.103416729551548</v>
       </c>
       <c r="H5">
-        <v>1.50403106540973</v>
+        <v>1.507178664698538</v>
       </c>
       <c r="I5">
-        <v>0.3404960742806936</v>
+        <v>0.3420183545496275</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,103 +1222,103 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5">
-        <v>-0.1162676288228979</v>
+        <v>-0.11935622638572</v>
       </c>
       <c r="O5">
-        <v>-37.79744115919171</v>
+        <v>-40.15830736361693</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.205848195906553</v>
+        <v>1.103416729551548</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T5">
-        <v>0.9404449150584619</v>
+        <v>0.9115597468132107</v>
       </c>
       <c r="U5">
-        <v>0.8324109017031668</v>
+        <v>0.8101149323188382</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X5">
-        <v>0.9995537443848532</v>
+        <v>0.9994484109535479</v>
       </c>
       <c r="Y5">
-        <v>0.9995619732546944</v>
+        <v>0.9996521850115739</v>
       </c>
       <c r="Z5">
-        <v>8.228869841198083E-06</v>
+        <v>0.0002037740580260738</v>
       </c>
       <c r="AA5">
-        <v>0.1778889054644588</v>
+        <v>0.1663286017293179</v>
       </c>
       <c r="AB5">
-        <v>-31.62603587327359</v>
+        <v>-38.62909547814716</v>
       </c>
       <c r="AC5">
-        <v>1.000000000000001</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD5">
-        <v>0.8514887408819645</v>
+        <v>0.7812035581881254</v>
       </c>
       <c r="AE5">
-        <v>-0.5243728865523529</v>
+        <v>-0.6242763816405457</v>
       </c>
       <c r="AF5">
-        <v>1.248398427799492</v>
+        <v>1.242898479668008</v>
       </c>
       <c r="AG5">
-        <v>1.247851595899319</v>
+        <v>1.242466180947688</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>72</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>74</v>
-      </c>
       <c r="AK5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL5">
-        <v>0.5012599090422775</v>
+        <v>0.4554115727601482</v>
       </c>
       <c r="AM5">
-        <v>0.7852230296161203</v>
+        <v>0.761421320401063</v>
       </c>
       <c r="AN5">
-        <v>1.060783840176871</v>
+        <v>0.9804872790627667</v>
       </c>
       <c r="AO5">
-        <v>-0.6571496114157754</v>
+        <v>-0.7627172546633524</v>
       </c>
       <c r="AP5">
-        <v>0.8512635793615695</v>
+        <v>0.7356685751804637</v>
       </c>
       <c r="AQ5">
-        <v>-3.082724975108901</v>
+        <v>-2.91952979581337</v>
       </c>
       <c r="AR5">
-        <v>0.6491904612606465</v>
+        <v>0.5659491287338677</v>
       </c>
       <c r="AS5">
-        <v>0.03765376253669189</v>
+        <v>0.04055821436859326</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,7 +1329,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C6" s="2">
         <v>46276</v>
@@ -1389,10 +1377,10 @@
         <v>0.281499877920296</v>
       </c>
       <c r="R6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T6">
         <v>-0.8897938918869088</v>
@@ -1404,7 +1392,7 @@
         <v>57</v>
       </c>
       <c r="W6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X6">
         <v>0.9569406621468657</v>
@@ -1440,13 +1428,13 @@
         <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AL6">
         <v>-0.3365089143576264</v>
@@ -1481,10 +1469,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C7" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1496,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8139260349039491</v>
+        <v>0.7795846339819062</v>
       </c>
       <c r="H7">
-        <v>1.463127930094301</v>
+        <v>1.466532185593772</v>
       </c>
       <c r="I7">
-        <v>0.3630944913655973</v>
+        <v>0.3646107957045758</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,103 +1502,103 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N7">
-        <v>-0.1558491165953869</v>
+        <v>-0.1582914631175507</v>
       </c>
       <c r="O7">
-        <v>-41.8427007831127</v>
+        <v>-43.02651167159895</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0.8139260349039491</v>
+        <v>0.7795846339819062</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T7">
-        <v>0.9316469936104604</v>
+        <v>0.9451365324997493</v>
       </c>
       <c r="U7">
-        <v>0.818771331126668</v>
+        <v>0.8248317097822648</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X7">
-        <v>0.9872732673098995</v>
+        <v>0.9827923773749249</v>
       </c>
       <c r="Y7">
-        <v>0.9981207360078433</v>
+        <v>0.9980810806295107</v>
       </c>
       <c r="Z7">
-        <v>0.01084746869794384</v>
+        <v>0.01528870325458587</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>-36.91044960373866</v>
+        <v>-32.95216435618324</v>
       </c>
       <c r="AC7">
-        <v>37.00000000000001</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="AD7">
-        <v>0.7995751405528057</v>
+        <v>0.8391249890020952</v>
       </c>
       <c r="AE7">
-        <v>-0.6005660618199808</v>
+        <v>-0.5439386480405981</v>
       </c>
       <c r="AF7">
-        <v>0.9466815060356877</v>
+        <v>0.8435190262788987</v>
       </c>
       <c r="AG7">
-        <v>0.9449024415693542</v>
+        <v>0.8419003812799959</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>72</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>74</v>
-      </c>
       <c r="AK7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL7">
-        <v>0.3990362638910706</v>
+        <v>0.4187573879032188</v>
       </c>
       <c r="AM7">
-        <v>0.7338323803457383</v>
+        <v>0.7460396725337519</v>
       </c>
       <c r="AN7">
-        <v>0.6822975428952236</v>
+        <v>0.636973055942427</v>
       </c>
       <c r="AO7">
-        <v>-0.6387562523090935</v>
+        <v>-0.5305780552845913</v>
       </c>
       <c r="AP7">
-        <v>0.7250910476433676</v>
+        <v>0.7658837827235925</v>
       </c>
       <c r="AQ7">
-        <v>-1.550986721546837</v>
+        <v>-1.21489278594029</v>
       </c>
       <c r="AR7">
-        <v>0.6218725144078714</v>
+        <v>0.6890771073644926</v>
       </c>
       <c r="AS7">
-        <v>0.03588279615232357</v>
+        <v>0.03350801591470254</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1609,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C8" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1633,16 +1621,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.009441760357892058</v>
       </c>
       <c r="G8">
-        <v>0.842535182301704</v>
+        <v>1.088462135949222</v>
       </c>
       <c r="H8">
-        <v>1.438467752002441</v>
+        <v>1.438657026190904</v>
       </c>
       <c r="I8">
-        <v>0.356871774222388</v>
+        <v>0.3569350812425149</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,103 +1642,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-0.007191542852915994</v>
+        <v>-0.009508135974423161</v>
       </c>
       <c r="O8">
-        <v>-1.91119210214169</v>
+        <v>-2.573243836109119</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0.842535182301704</v>
+        <v>1.088462135949222</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="T8">
-        <v>0.8990306146348624</v>
+        <v>0.875180513618772</v>
       </c>
       <c r="U8">
-        <v>0.8043107252188452</v>
+        <v>0.7951338869404498</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X8">
-        <v>0.9911835175935791</v>
+        <v>0.9965675985595633</v>
       </c>
       <c r="Y8">
-        <v>0.9989877945326281</v>
+        <v>0.9995455670332747</v>
       </c>
       <c r="Z8">
-        <v>0.007804276939048949</v>
+        <v>0.002977968473711345</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.06857142533282168</v>
       </c>
       <c r="AB8">
-        <v>45.24258405442502</v>
+        <v>48.65576573871741</v>
       </c>
       <c r="AC8">
-        <v>-26</v>
+        <v>-16</v>
       </c>
       <c r="AD8">
-        <v>0.7041066397461356</v>
+        <v>0.6605814722906341</v>
       </c>
       <c r="AE8">
-        <v>0.7100942471710396</v>
+        <v>0.7507543662652507</v>
       </c>
       <c r="AF8">
-        <v>0.798085888289748</v>
+        <v>1.108465476693037</v>
       </c>
       <c r="AG8">
-        <v>0.7972780613901888</v>
+        <v>1.107961753437951</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AL8">
-        <v>0.3516969695778859</v>
+        <v>0.3527788554698958</v>
       </c>
       <c r="AM8">
-        <v>0.6998346222889451</v>
+        <v>0.7008202970272939</v>
       </c>
       <c r="AN8">
-        <v>0.5343667599788634</v>
+        <v>0.7097267830372</v>
       </c>
       <c r="AO8">
-        <v>0.583276607482987</v>
+        <v>0.8465006369284063</v>
       </c>
       <c r="AP8">
-        <v>1.524969502733192</v>
+        <v>1.878834130420117</v>
       </c>
       <c r="AQ8">
-        <v>0.2222349447075852</v>
+        <v>0.1147461191625324</v>
       </c>
       <c r="AR8">
-        <v>1.503406852245616</v>
+        <v>1.838899944721231</v>
       </c>
       <c r="AS8">
-        <v>0.07362065147543613</v>
+        <v>0.07272918792071138</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1749,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C9" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1776,13 +1764,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>3.856630204854587</v>
+        <v>4.018325932385717</v>
       </c>
       <c r="H9">
-        <v>3.041329146300729</v>
+        <v>3.04958083432183</v>
       </c>
       <c r="I9">
-        <v>0.6412326289402306</v>
+        <v>0.6447388313743558</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,103 +1782,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N9">
-        <v>0.6436543616434559</v>
+        <v>0.6634365550158924</v>
       </c>
       <c r="O9">
-        <v>94.8992792692152</v>
+        <v>104.2612310739463</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.856630204854587</v>
+        <v>4.018325932385717</v>
       </c>
       <c r="R9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="T9">
-        <v>-0.9995502225675734</v>
+        <v>-0.9982527805535222</v>
       </c>
       <c r="U9">
-        <v>0.9997581877229801</v>
+        <v>0.9991612286773894</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X9">
-        <v>0.9996242397568611</v>
+        <v>0.9989579236675291</v>
       </c>
       <c r="Y9">
-        <v>0.999842350270288</v>
+        <v>0.9997899097132181</v>
       </c>
       <c r="Z9">
-        <v>0.0002181105134269057</v>
+        <v>0.0008319860456890149</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>-177.5694691317406</v>
+        <v>175.2084532296269</v>
       </c>
       <c r="AC9">
-        <v>-4.999999999999995</v>
+        <v>-9</v>
       </c>
       <c r="AD9">
-        <v>-0.9991003742166761</v>
+        <v>-0.9965051939560751</v>
       </c>
       <c r="AE9">
-        <v>-0.0424080445210326</v>
+        <v>0.08353082316465722</v>
       </c>
       <c r="AF9">
-        <v>2.951953715387135</v>
+        <v>3.086639271220491</v>
       </c>
       <c r="AG9">
-        <v>2.951488340681782</v>
+        <v>3.085990798290808</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AK9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AL9">
-        <v>-0.9989428663127257</v>
+        <v>-0.9962958378940973</v>
       </c>
       <c r="AM9">
-        <v>0.9945802336410562</v>
+        <v>0.9939200917282511</v>
       </c>
       <c r="AN9">
-        <v>-2.946833510094436</v>
+        <v>-3.076666537320581</v>
       </c>
       <c r="AO9">
-        <v>-0.1538033138105544</v>
+        <v>0.2040071555934416</v>
       </c>
       <c r="AP9">
-        <v>-4.73947218000892</v>
+        <v>-4.911067845256198</v>
       </c>
       <c r="AQ9">
-        <v>4.920456880994661</v>
+        <v>5.187757736561392</v>
       </c>
       <c r="AR9">
-        <v>4.291788192979363</v>
+        <v>4.447543961691609</v>
       </c>
       <c r="AS9">
-        <v>0.03396467479031572</v>
+        <v>0.03305289905465125</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1889,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C10" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1916,13 +1904,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2.798196837805659</v>
+        <v>2.931110464579591</v>
       </c>
       <c r="H10">
-        <v>2.0555522779808</v>
+        <v>2.060742825669897</v>
       </c>
       <c r="I10">
-        <v>0.4521184617969376</v>
+        <v>0.451850052161358</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,103 +1922,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10">
-        <v>28.21222100906685</v>
+        <v>30.56647684723054</v>
       </c>
       <c r="O10">
-        <v>26.02089031734215</v>
+        <v>28.17465028549412</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.798196837805659</v>
+        <v>2.931110464579591</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.8377920202772901</v>
+        <v>-0.8628123004240695</v>
       </c>
       <c r="U10">
-        <v>0.9269575719191055</v>
+        <v>0.9382192925622748</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X10">
-        <v>0.9995805755066395</v>
+        <v>0.999345160101522</v>
       </c>
       <c r="Y10">
-        <v>0.9998046511773003</v>
+        <v>0.9998150294857738</v>
       </c>
       <c r="Z10">
-        <v>0.0002240756706608504</v>
+        <v>0.0004698693842518642</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-132.4970578377665</v>
+        <v>-136.5187187590342</v>
       </c>
       <c r="AC10">
-        <v>-4.999999999999995</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD10">
-        <v>-0.6755523472254542</v>
+        <v>-0.725599220474182</v>
       </c>
       <c r="AE10">
-        <v>-0.737312027677685</v>
+        <v>-0.6881175562701909</v>
       </c>
       <c r="AF10">
-        <v>3.156771008977966</v>
+        <v>3.121834074522203</v>
       </c>
       <c r="AG10">
-        <v>3.15615433747783</v>
+        <v>3.12125662726811</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AK10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AL10">
-        <v>-0.6754203788697517</v>
+        <v>-0.7254650060132488</v>
       </c>
       <c r="AM10">
-        <v>0.8948797732391993</v>
+        <v>0.9105481239043232</v>
       </c>
       <c r="AN10">
-        <v>-2.10867769958606</v>
+        <v>-2.232711898249784</v>
       </c>
       <c r="AO10">
-        <v>-2.347407935325795</v>
+        <v>-2.179010281576294</v>
       </c>
       <c r="AP10">
-        <v>-3.568394250874231</v>
+        <v>-3.63642016197765</v>
       </c>
       <c r="AQ10">
-        <v>3.619139089034123</v>
+        <v>4.150513773132973</v>
       </c>
       <c r="AR10">
-        <v>3.158217086892496</v>
+        <v>3.190145770786708</v>
       </c>
       <c r="AS10">
-        <v>0.05145039226994787</v>
+        <v>0.04711268371968138</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2029,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C11" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2044,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.322878077889677</v>
+        <v>0.1968159997324024</v>
       </c>
       <c r="H11">
-        <v>2.411917296847714</v>
+        <v>2.392961920492562</v>
       </c>
       <c r="I11">
-        <v>0.5711207913118737</v>
+        <v>0.56558464236321</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,103 +2062,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11">
-        <v>-2182.06575823985</v>
+        <v>-2216.301867657914</v>
       </c>
       <c r="O11">
-        <v>-29.06182693128404</v>
+        <v>-31.84962805474257</v>
       </c>
       <c r="P11">
-        <v>0.2969488778001208</v>
+        <v>0.4516653036347984</v>
       </c>
       <c r="Q11">
-        <v>0.4592526314151618</v>
+        <v>0.3589340616908894</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T11">
-        <v>0.7568632986052749</v>
+        <v>0.6949642886995006</v>
       </c>
       <c r="U11">
-        <v>0.740508961547742</v>
+        <v>0.7126617526412041</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9941113304981589</v>
+        <v>0.995018626213148</v>
       </c>
       <c r="Y11">
-        <v>0.9996819087014734</v>
+        <v>0.9997112909057156</v>
       </c>
       <c r="Z11">
-        <v>0.005570578203314525</v>
+        <v>0.004692664692567683</v>
       </c>
       <c r="AA11">
-        <v>0.02142553806564812</v>
+        <v>0.1406307919426623</v>
       </c>
       <c r="AB11">
-        <v>-72.19627297879811</v>
+        <v>-76.798764247509</v>
       </c>
       <c r="AC11">
-        <v>-24</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD11">
-        <v>0.3057572391824364</v>
+        <v>0.228371868158356</v>
       </c>
       <c r="AE11">
-        <v>-0.9521095056176755</v>
+        <v>-0.9735739775866354</v>
       </c>
       <c r="AF11">
-        <v>1.435111442888528</v>
+        <v>1.538559395412338</v>
       </c>
       <c r="AG11">
-        <v>1.434654946426129</v>
+        <v>1.538115199322786</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>72</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>74</v>
-      </c>
       <c r="AK11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AL11">
-        <v>0.1561044550058966</v>
+        <v>0.1302063897923587</v>
       </c>
       <c r="AM11">
-        <v>0.5807521591084351</v>
+        <v>0.5783253456726923</v>
       </c>
       <c r="AN11">
-        <v>0.5147719817282685</v>
+        <v>0.4285505175192901</v>
       </c>
       <c r="AO11">
-        <v>-1.330552561932046</v>
+        <v>-1.46968865365661</v>
       </c>
       <c r="AP11">
-        <v>-0.1771006120820895</v>
+        <v>-0.2616187175915644</v>
       </c>
       <c r="AQ11">
-        <v>-2.280037637543915</v>
+        <v>-1.91773203214572</v>
       </c>
       <c r="AR11">
-        <v>0.481562497732405</v>
+        <v>0.4823579895471006</v>
       </c>
       <c r="AS11">
-        <v>0.1009919220329404</v>
+        <v>0.1214088332023164</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -193,9 +193,6 @@
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_REVERSAL_WATCH</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头反转预警</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -220,10 +214,13 @@
     <t>空头稳态</t>
   </si>
   <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>TRANSITION</t>
   </si>
   <si>
     <t>上涨</t>
@@ -232,12 +229,12 @@
     <t>下跌</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>TURNING_DOWN</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
@@ -247,12 +244,12 @@
     <t>DOWN_SLOPE</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
-    <t>向下转折带</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
@@ -260,6 +257,9 @@
   </si>
   <si>
     <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
   </si>
 </sst>
 </file>
@@ -769,10 +769,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C2" s="2">
         <v>46279</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46276</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -784,13 +784,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.7627340899366188</v>
+        <v>0.5322898086271723</v>
       </c>
       <c r="H2">
-        <v>1.075487212942842</v>
+        <v>1.076358358876711</v>
       </c>
       <c r="I2">
-        <v>0.2587974643150144</v>
+        <v>0.2588448654001832</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -802,73 +802,73 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2">
-        <v>-0.4794678796074124</v>
+        <v>-0.5002233026953614</v>
       </c>
       <c r="O2">
-        <v>-14.01455271625312</v>
+        <v>-14.07974876401826</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.7627340899366188</v>
+        <v>0.5322898086271723</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T2">
-        <v>0.9519909109868182</v>
+        <v>0.8040328903044585</v>
       </c>
       <c r="U2">
-        <v>0.8279369155102769</v>
+        <v>0.7614848539166132</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X2">
-        <v>0.9847295311363554</v>
+        <v>0.9806151748731429</v>
       </c>
       <c r="Y2">
-        <v>0.9981640222648349</v>
+        <v>0.9986802131184278</v>
       </c>
       <c r="Z2">
-        <v>0.0134344911284795</v>
+        <v>0.01806503824528494</v>
       </c>
       <c r="AA2">
-        <v>0.04010881987763081</v>
+        <v>0.2633578518385805</v>
       </c>
       <c r="AB2">
-        <v>-30.04160606895899</v>
+        <v>-56.64023767166175</v>
       </c>
       <c r="AC2">
-        <v>-37</v>
+        <v>-40</v>
       </c>
       <c r="AD2">
-        <v>0.8656620940372549</v>
+        <v>0.5498943075500854</v>
       </c>
       <c r="AE2">
-        <v>-0.5006287436284845</v>
+        <v>-0.8352342488930947</v>
       </c>
       <c r="AF2">
-        <v>0.7629811261465481</v>
+        <v>0.8640199279568578</v>
       </c>
       <c r="AG2">
-        <v>0.7615803097865919</v>
+        <v>0.8628796057905234</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AJ2" t="s">
         <v>72</v>
@@ -877,28 +877,28 @@
         <v>77</v>
       </c>
       <c r="AL2">
-        <v>0.4493648481532204</v>
+        <v>0.3468982088183297</v>
       </c>
       <c r="AM2">
-        <v>0.7614545481235691</v>
+        <v>0.7087548104940669</v>
       </c>
       <c r="AN2">
-        <v>0.6795446964577995</v>
+        <v>0.5140238509020666</v>
       </c>
       <c r="AO2">
-        <v>-0.32049312701577</v>
+        <v>-0.6735337538144014</v>
       </c>
       <c r="AP2">
-        <v>0.5106168384412557</v>
+        <v>0.1840277826922503</v>
       </c>
       <c r="AQ2">
-        <v>-2.309988956264086</v>
+        <v>-2.183203764413147</v>
       </c>
       <c r="AR2">
-        <v>0.4159035631018527</v>
+        <v>0.2761722435110276</v>
       </c>
       <c r="AS2">
-        <v>0.03748834570550436</v>
+        <v>0.05615417820083014</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -909,10 +909,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C3" s="2">
         <v>46279</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46276</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -921,16 +921,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.703221216942846</v>
+        <v>0.1070399265804761</v>
       </c>
       <c r="G3">
-        <v>2.167902143529543</v>
+        <v>1.648978363959246</v>
       </c>
       <c r="H3">
-        <v>1.987551891302176</v>
+        <v>1.999280383217206</v>
       </c>
       <c r="I3">
-        <v>0.4437288953891284</v>
+        <v>0.4457221521383132</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -942,73 +942,73 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3">
-        <v>-0.1265021697956313</v>
+        <v>-0.1312925567490325</v>
       </c>
       <c r="O3">
-        <v>-44.00075471152392</v>
+        <v>-44.13725043790246</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.167902143529543</v>
+        <v>1.648978363959246</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T3">
-        <v>0.9502927037673258</v>
+        <v>0.8040844093871631</v>
       </c>
       <c r="U3">
-        <v>0.9328738465763199</v>
+        <v>0.7776074934517428</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X3">
-        <v>0.9929004085374168</v>
+        <v>0.9870907508187853</v>
       </c>
       <c r="Y3">
-        <v>0.9990357893583854</v>
+        <v>0.9988540809617921</v>
       </c>
       <c r="Z3">
-        <v>0.00613538082096865</v>
+        <v>0.01176333014300679</v>
       </c>
       <c r="AA3">
-        <v>0.992041590135873</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>-25.1628791310978</v>
+        <v>-48.32792734363106</v>
       </c>
       <c r="AC3">
-        <v>-25</v>
+        <v>-32.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>0.9051027170225241</v>
+        <v>0.6648663462030032</v>
       </c>
       <c r="AE3">
-        <v>-0.4251929816429767</v>
+        <v>-0.7469623428839424</v>
       </c>
       <c r="AF3">
-        <v>1.982549504892468</v>
+        <v>2.080466297191172</v>
       </c>
       <c r="AG3">
-        <v>1.980637909562323</v>
+        <v>2.078082251252871</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AJ3" t="s">
         <v>72</v>
@@ -1017,28 +1017,28 @@
         <v>77</v>
       </c>
       <c r="AL3">
-        <v>0.9006318908460458</v>
+        <v>0.6641044631990255</v>
       </c>
       <c r="AM3">
-        <v>0.9647992452175191</v>
+        <v>0.8931011357392076</v>
       </c>
       <c r="AN3">
-        <v>1.82472219597571</v>
+        <v>1.457216143767806</v>
       </c>
       <c r="AO3">
-        <v>-0.7384305222231893</v>
+        <v>-1.447007669928777</v>
       </c>
       <c r="AP3">
-        <v>1.921060464331321</v>
+        <v>1.164795403623578</v>
       </c>
       <c r="AQ3">
-        <v>-5.034163411394008</v>
+        <v>-4.882106732060211</v>
       </c>
       <c r="AR3">
-        <v>1.519758685396873</v>
+        <v>0.9319104903366719</v>
       </c>
       <c r="AS3">
-        <v>0.03201609461231736</v>
+        <v>0.03971797638880459</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1049,106 +1049,106 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C4" s="2">
         <v>46279</v>
       </c>
-      <c r="C4" s="2">
-        <v>46276</v>
-      </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.138907574804795</v>
+        <v>0.4644705373884119</v>
       </c>
       <c r="H4">
-        <v>2.079464959479535</v>
+        <v>2.079631616457734</v>
       </c>
       <c r="I4">
-        <v>0.4932988478904669</v>
+        <v>0.493581089309781</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>146</v>
       </c>
       <c r="M4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N4">
-        <v>-0.2511252061252907</v>
+        <v>-0.2476995568903617</v>
       </c>
       <c r="O4">
-        <v>-9.624289312220228</v>
+        <v>-8.741602713549383</v>
       </c>
       <c r="P4">
-        <v>0.1448209490283399</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.1624309840693213</v>
+        <v>0.4644705373884119</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T4">
-        <v>0.4648788460450831</v>
+        <v>-0.7737186465331317</v>
       </c>
       <c r="U4">
-        <v>0.5085445576424406</v>
+        <v>0.7479743913347484</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="X4">
-        <v>0.952695096459136</v>
+        <v>0.9856952087081511</v>
       </c>
       <c r="Y4">
-        <v>0.9973963076886128</v>
+        <v>0.9992040015793563</v>
       </c>
       <c r="Z4">
-        <v>0.04470121122947679</v>
+        <v>0.01350879287120521</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-103.7510891352802</v>
+        <v>-109.6924528889363</v>
       </c>
       <c r="AC4">
-        <v>-71</v>
+        <v>-34</v>
       </c>
       <c r="AD4">
-        <v>-0.2377043565213686</v>
+        <v>-0.3369712431751639</v>
       </c>
       <c r="AE4">
-        <v>-0.9713375514674402</v>
+        <v>-0.9415149394847564</v>
       </c>
       <c r="AF4">
-        <v>0.4832250112247069</v>
+        <v>0.8150502755325302</v>
       </c>
       <c r="AG4">
-        <v>0.4819668419783111</v>
+        <v>0.814401496800461</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
       </c>
       <c r="AI4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="s">
         <v>73</v>
@@ -1157,28 +1157,28 @@
         <v>78</v>
       </c>
       <c r="AL4">
-        <v>-0.1185427237579554</v>
+        <v>-0.168351507298897</v>
       </c>
       <c r="AM4">
-        <v>0.5419526672058479</v>
+        <v>0.5809853472856928</v>
       </c>
       <c r="AN4">
-        <v>-0.01724737476143526</v>
+        <v>-0.2259080226308482</v>
       </c>
       <c r="AO4">
-        <v>-0.4600429033012642</v>
+        <v>-0.7709752963208648</v>
       </c>
       <c r="AP4">
-        <v>-0.6831301709401844</v>
+        <v>-1.137502229099049</v>
       </c>
       <c r="AQ4">
-        <v>-0.9812357988182752</v>
+        <v>-1.173432794323517</v>
       </c>
       <c r="AR4">
-        <v>0.7337126753893859</v>
+        <v>1.202387605559851</v>
       </c>
       <c r="AS4">
-        <v>0.1896489829438474</v>
+        <v>0.1321828414642066</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1189,10 +1189,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C5" s="2">
         <v>46279</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46276</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1204,13 +1204,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1.103416729551548</v>
+        <v>0.3284909043607342</v>
       </c>
       <c r="H5">
-        <v>1.507178664698538</v>
+        <v>1.510026492626507</v>
       </c>
       <c r="I5">
-        <v>0.3420183545496275</v>
+        <v>0.3434459197385207</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1222,73 +1222,73 @@
         <v>226</v>
       </c>
       <c r="M5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N5">
-        <v>-0.11935622638572</v>
+        <v>-0.1217660477721098</v>
       </c>
       <c r="O5">
-        <v>-40.15830736361693</v>
+        <v>-36.28617856129333</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>0.3803248458818078</v>
       </c>
       <c r="Q5">
-        <v>1.103416729551548</v>
+        <v>0.5301017834548847</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T5">
-        <v>0.9115597468132107</v>
+        <v>0.740562428887295</v>
       </c>
       <c r="U5">
-        <v>0.8101149323188382</v>
+        <v>0.7330167150300032</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X5">
-        <v>0.9994484109535479</v>
+        <v>0.9900455463104854</v>
       </c>
       <c r="Y5">
-        <v>0.9996521850115739</v>
+        <v>0.9990544881228819</v>
       </c>
       <c r="Z5">
-        <v>0.0002037740580260738</v>
+        <v>0.009008941812396531</v>
       </c>
       <c r="AA5">
-        <v>0.1663286017293179</v>
+        <v>0.2295652278539875</v>
       </c>
       <c r="AB5">
-        <v>-38.62909547814716</v>
+        <v>-67.08029985022648</v>
       </c>
       <c r="AC5">
-        <v>-4.999999999999995</v>
+        <v>-29</v>
       </c>
       <c r="AD5">
-        <v>0.7812035581881254</v>
+        <v>0.3894406605921795</v>
       </c>
       <c r="AE5">
-        <v>-0.6242763816405457</v>
+        <v>-0.9210515576652193</v>
       </c>
       <c r="AF5">
-        <v>1.242898479668008</v>
+        <v>1.288389504537526</v>
       </c>
       <c r="AG5">
-        <v>1.242466180947688</v>
+        <v>1.287171316958632</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
         <v>72</v>
@@ -1297,28 +1297,28 @@
         <v>77</v>
       </c>
       <c r="AL5">
-        <v>0.4554115727601482</v>
+        <v>0.2391949715608186</v>
       </c>
       <c r="AM5">
-        <v>0.761421320401063</v>
+        <v>0.6501215412376978</v>
       </c>
       <c r="AN5">
-        <v>0.9804872790627667</v>
+        <v>0.5678357415307461</v>
       </c>
       <c r="AO5">
-        <v>-0.7627172546633524</v>
+        <v>-1.14220262248422</v>
       </c>
       <c r="AP5">
-        <v>0.7356685751804637</v>
+        <v>-0.06179268083553235</v>
       </c>
       <c r="AQ5">
-        <v>-2.91952979581337</v>
+        <v>-2.900968096772592</v>
       </c>
       <c r="AR5">
-        <v>0.5659491287338677</v>
+        <v>0.5133339514840164</v>
       </c>
       <c r="AS5">
-        <v>0.04055821436859326</v>
+        <v>0.0819518223584141</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1329,10 +1329,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C6" s="2">
         <v>46279</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46276</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1344,13 +1344,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.281499877920296</v>
+        <v>0.3541415674016754</v>
       </c>
       <c r="H6">
-        <v>0.943340972017919</v>
+        <v>0.9433488720293223</v>
       </c>
       <c r="I6">
-        <v>0.2566980963193565</v>
+        <v>0.2566284989526173</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1362,103 +1362,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>0.01499112816820195</v>
+        <v>0.02595949721692993</v>
       </c>
       <c r="O6">
-        <v>0.2996941230256008</v>
+        <v>0.505069640253235</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.281499877920296</v>
+        <v>0.3541415674016754</v>
       </c>
       <c r="R6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T6">
-        <v>-0.8897938918869088</v>
+        <v>-0.8686042979154364</v>
       </c>
       <c r="U6">
-        <v>0.7992171690588966</v>
+        <v>0.790585254275402</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
       </c>
       <c r="W6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X6">
-        <v>0.9569406621468657</v>
+        <v>0.9872155901835044</v>
       </c>
       <c r="Y6">
-        <v>0.9952396708391507</v>
+        <v>0.998853280853823</v>
       </c>
       <c r="Z6">
-        <v>0.03829900869228497</v>
+        <v>0.01163769067031861</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-132.5502794454923</v>
+        <v>-127.9451908038636</v>
       </c>
       <c r="AC6">
-        <v>-68</v>
+        <v>-34</v>
       </c>
       <c r="AD6">
-        <v>-0.6762369391362666</v>
+        <v>-0.6149073819271738</v>
       </c>
       <c r="AE6">
-        <v>-0.736684194310977</v>
+        <v>-0.7885993353100602</v>
       </c>
       <c r="AF6">
-        <v>0.3785972529747204</v>
+        <v>0.4474767583701829</v>
       </c>
       <c r="AG6">
-        <v>0.3767950054311673</v>
+        <v>0.4469636282038905</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AL6">
-        <v>-0.3365089143576264</v>
+        <v>-0.3071011279295962</v>
       </c>
       <c r="AM6">
-        <v>0.6894951858989864</v>
+        <v>0.673461485962789</v>
       </c>
       <c r="AN6">
-        <v>-0.1888515677004071</v>
+        <v>-0.2430084362936052</v>
       </c>
       <c r="AO6">
-        <v>-0.3091809003988046</v>
+        <v>-0.368910953746</v>
       </c>
       <c r="AP6">
-        <v>-0.4667626019016398</v>
+        <v>-0.5581255149946011</v>
       </c>
       <c r="AQ6">
-        <v>0.1693803799238007</v>
+        <v>0.1596279715553374</v>
       </c>
       <c r="AR6">
-        <v>0.4334020959173555</v>
+        <v>0.5280506619945343</v>
       </c>
       <c r="AS6">
-        <v>0.07806520423730776</v>
+        <v>0.07072917942800762</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C7" s="2">
         <v>46279</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46276</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1484,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.7795846339819062</v>
+        <v>0.3272372832527371</v>
       </c>
       <c r="H7">
-        <v>1.466532185593772</v>
+        <v>1.469612226283769</v>
       </c>
       <c r="I7">
-        <v>0.3646107957045758</v>
+        <v>0.3659522585114973</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1502,73 +1502,73 @@
         <v>239</v>
       </c>
       <c r="M7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N7">
-        <v>-0.1582914631175507</v>
+        <v>-0.1602673140814661</v>
       </c>
       <c r="O7">
-        <v>-43.02651167159895</v>
+        <v>-41.60471717301159</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>0.2991550707415915</v>
       </c>
       <c r="Q7">
-        <v>0.7795846339819062</v>
+        <v>0.4669182433823124</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T7">
-        <v>0.9451365324997493</v>
+        <v>0.7986004666080007</v>
       </c>
       <c r="U7">
-        <v>0.8248317097822648</v>
+        <v>0.7592379857681434</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X7">
-        <v>0.9827923773749249</v>
+        <v>0.9988155075451334</v>
       </c>
       <c r="Y7">
-        <v>0.9980810806295107</v>
+        <v>0.9994711031781724</v>
       </c>
       <c r="Z7">
-        <v>0.01528870325458587</v>
+        <v>0.0006555956330390744</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>-32.95216435618324</v>
+        <v>-65.79632472936247</v>
       </c>
       <c r="AC7">
-        <v>42.00000000000001</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD7">
-        <v>0.8391249890020952</v>
+        <v>0.409981541466164</v>
       </c>
       <c r="AE7">
-        <v>-0.5439386480405981</v>
+        <v>-0.9120938195476538</v>
       </c>
       <c r="AF7">
-        <v>0.8435190262788987</v>
+        <v>0.9790605313600033</v>
       </c>
       <c r="AG7">
-        <v>0.8419003812799959</v>
+        <v>0.9785427093565902</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
         <v>72</v>
@@ -1577,28 +1577,28 @@
         <v>77</v>
       </c>
       <c r="AL7">
-        <v>0.4187573879032188</v>
+        <v>0.2048823517659373</v>
       </c>
       <c r="AM7">
-        <v>0.7460396725337519</v>
+        <v>0.6144344292101485</v>
       </c>
       <c r="AN7">
-        <v>0.636973055942427</v>
+        <v>0.417513994869618</v>
       </c>
       <c r="AO7">
-        <v>-0.5305780552845913</v>
+        <v>-0.8842918748851024</v>
       </c>
       <c r="AP7">
-        <v>0.7658837827235925</v>
+        <v>0.3092411070603037</v>
       </c>
       <c r="AQ7">
-        <v>-1.21489278594029</v>
+        <v>-1.358901367601592</v>
       </c>
       <c r="AR7">
-        <v>0.6890771073644926</v>
+        <v>0.2652449766801828</v>
       </c>
       <c r="AS7">
-        <v>0.03350801591470254</v>
+        <v>0.0558327956137401</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1609,10 +1609,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C8" s="2">
         <v>46279</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46276</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1621,16 +1621,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.009441760357892058</v>
+        <v>0.4085139427329589</v>
       </c>
       <c r="G8">
-        <v>1.088462135949222</v>
+        <v>1.373498749861369</v>
       </c>
       <c r="H8">
-        <v>1.438657026190904</v>
+        <v>1.43882827426618</v>
       </c>
       <c r="I8">
-        <v>0.3569350812425149</v>
+        <v>0.3570463432155477</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1642,103 +1642,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>-0.009508135974423161</v>
+        <v>-0.01246644480791922</v>
       </c>
       <c r="O8">
-        <v>-2.573243836109119</v>
+        <v>-3.473238354445169</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.088462135949222</v>
+        <v>1.373498749861369</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T8">
-        <v>0.875180513618772</v>
+        <v>0.8398296143974808</v>
       </c>
       <c r="U8">
-        <v>0.7951338869404498</v>
+        <v>0.8391478778747419</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X8">
-        <v>0.9965675985595633</v>
+        <v>0.9979708824706606</v>
       </c>
       <c r="Y8">
-        <v>0.9995455670332747</v>
+        <v>0.9997898399437267</v>
       </c>
       <c r="Z8">
-        <v>0.002977968473711345</v>
+        <v>0.001818957473066152</v>
       </c>
       <c r="AA8">
-        <v>0.06857142533282168</v>
+        <v>0.577851014516473</v>
       </c>
       <c r="AB8">
-        <v>48.65576573871741</v>
+        <v>48.58678857679728</v>
       </c>
       <c r="AC8">
-        <v>-16</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.6605814722906341</v>
+        <v>0.6614848104777297</v>
       </c>
       <c r="AE8">
-        <v>0.7507543662652507</v>
+        <v>0.7499585625267853</v>
       </c>
       <c r="AF8">
-        <v>1.108465476693037</v>
+        <v>1.4228011970436</v>
       </c>
       <c r="AG8">
-        <v>1.107961753437951</v>
+        <v>1.422502181063964</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AJ8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL8">
-        <v>0.3527788554698958</v>
+        <v>0.5217525650521097</v>
       </c>
       <c r="AM8">
-        <v>0.7008202970272939</v>
+        <v>0.8033716330019459</v>
       </c>
       <c r="AN8">
-        <v>0.7097267830372</v>
+        <v>0.9177807134602085</v>
       </c>
       <c r="AO8">
-        <v>0.8465006369284063</v>
+        <v>1.083436570067038</v>
       </c>
       <c r="AP8">
-        <v>1.878834130420117</v>
+        <v>2.270108714869733</v>
       </c>
       <c r="AQ8">
-        <v>0.1147461191625324</v>
+        <v>-0.1250406182136466</v>
       </c>
       <c r="AR8">
-        <v>1.838899944721231</v>
+        <v>2.198550716678369</v>
       </c>
       <c r="AS8">
-        <v>0.07272918792071138</v>
+        <v>0.07046971349981229</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1749,10 +1749,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C9" s="2">
         <v>46279</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46276</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1761,16 +1761,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.9407221123010578</v>
       </c>
       <c r="G9">
-        <v>4.018325932385717</v>
+        <v>3.62860109327589</v>
       </c>
       <c r="H9">
-        <v>3.04958083432183</v>
+        <v>3.057294646908424</v>
       </c>
       <c r="I9">
-        <v>0.6447388313743558</v>
+        <v>0.6481481532485552</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1782,103 +1782,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N9">
-        <v>0.6634365550158924</v>
+        <v>0.6824528451040284</v>
       </c>
       <c r="O9">
-        <v>104.2612310739463</v>
+        <v>103.8063866955301</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.018325932385717</v>
+        <v>3.62860109327589</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="T9">
-        <v>-0.9982527805535222</v>
+        <v>-0.9867058542560161</v>
       </c>
       <c r="U9">
-        <v>0.9991612286773894</v>
+        <v>0.9850481836537166</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X9">
-        <v>0.9989579236675291</v>
+        <v>0.998053511027817</v>
       </c>
       <c r="Y9">
-        <v>0.9997899097132181</v>
+        <v>0.9996889295734031</v>
       </c>
       <c r="Z9">
-        <v>0.0008319860456890149</v>
+        <v>0.00163541854558602</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>175.2084532296269</v>
+        <v>166.8213103505525</v>
       </c>
       <c r="AC9">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="AD9">
-        <v>-0.9965051939560751</v>
+        <v>-0.9736637673900084</v>
       </c>
       <c r="AE9">
-        <v>0.08353082316465722</v>
+        <v>0.2279887454939294</v>
       </c>
       <c r="AF9">
-        <v>3.086639271220491</v>
+        <v>2.873840858389804</v>
       </c>
       <c r="AG9">
-        <v>3.085990798290808</v>
+        <v>2.872946891488013</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AL9">
-        <v>-0.9962958378940973</v>
+        <v>-0.9733608893865243</v>
       </c>
       <c r="AM9">
-        <v>0.9939200917282511</v>
+        <v>0.9874202203026983</v>
       </c>
       <c r="AN9">
-        <v>-3.076666537320581</v>
+        <v>-2.80716301597792</v>
       </c>
       <c r="AO9">
-        <v>0.2040071555934416</v>
+        <v>0.5887923391863664</v>
       </c>
       <c r="AP9">
-        <v>-4.911067845256198</v>
+        <v>-4.315599903873433</v>
       </c>
       <c r="AQ9">
-        <v>5.187757736561392</v>
+        <v>5.207316204213797</v>
       </c>
       <c r="AR9">
-        <v>4.447543961691609</v>
+        <v>3.861539043783517</v>
       </c>
       <c r="AS9">
-        <v>0.03305289905465125</v>
+        <v>0.03046690176663491</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1889,10 +1889,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C10" s="2">
         <v>46279</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46276</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1901,16 +1901,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.9854140213095479</v>
       </c>
       <c r="G10">
-        <v>2.931110464579591</v>
+        <v>2.506061488315238</v>
       </c>
       <c r="H10">
-        <v>2.060742825669897</v>
+        <v>2.067488987913405</v>
       </c>
       <c r="I10">
-        <v>0.451850052161358</v>
+        <v>0.4517509601583548</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1922,103 +1922,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N10">
-        <v>30.56647684723054</v>
+        <v>32.94041438557652</v>
       </c>
       <c r="O10">
-        <v>28.17465028549412</v>
+        <v>27.92405700260799</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.931110464579591</v>
+        <v>2.506061488315238</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.8628123004240695</v>
+        <v>-0.941786007256101</v>
       </c>
       <c r="U10">
-        <v>0.9382192925622748</v>
+        <v>0.9712317342149173</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X10">
-        <v>0.999345160101522</v>
+        <v>0.9925590473473577</v>
       </c>
       <c r="Y10">
-        <v>0.9998150294857738</v>
+        <v>0.9984637110129587</v>
       </c>
       <c r="Z10">
-        <v>0.0004698693842518642</v>
+        <v>0.005904663665601051</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>-136.5187187590342</v>
+        <v>-152.0991671420752</v>
       </c>
       <c r="AC10">
-        <v>-6.999999999999997</v>
+        <v>-25</v>
       </c>
       <c r="AD10">
-        <v>-0.725599220474182</v>
+        <v>-0.8837588281146735</v>
       </c>
       <c r="AE10">
-        <v>-0.6881175562701909</v>
+        <v>-0.4679426607281911</v>
       </c>
       <c r="AF10">
-        <v>3.121834074522203</v>
+        <v>2.322586839197069</v>
       </c>
       <c r="AG10">
-        <v>3.12125662726811</v>
+        <v>2.319018674614564</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AK10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AL10">
-        <v>-0.7254650060132488</v>
+        <v>-0.8824011191598404</v>
       </c>
       <c r="AM10">
-        <v>0.9105481239043232</v>
+        <v>0.9588462785035203</v>
       </c>
       <c r="AN10">
-        <v>-2.232711898249784</v>
+        <v>-1.971462694951287</v>
       </c>
       <c r="AO10">
-        <v>-2.179010281576294</v>
+        <v>-1.194890811441123</v>
       </c>
       <c r="AP10">
-        <v>-3.63642016197765</v>
+        <v>-2.849982399328737</v>
       </c>
       <c r="AQ10">
-        <v>4.150513773132973</v>
+        <v>4.732644937606127</v>
       </c>
       <c r="AR10">
-        <v>3.190145770786708</v>
+        <v>2.376526241075518</v>
       </c>
       <c r="AS10">
-        <v>0.04711268371968138</v>
+        <v>0.03829112523611434</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2029,10 +2029,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C11" s="2">
         <v>46279</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46276</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2044,121 +2044,121 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1968159997324024</v>
+        <v>0.04729329014570197</v>
       </c>
       <c r="H11">
-        <v>2.392961920492562</v>
+        <v>2.373993695812118</v>
       </c>
       <c r="I11">
-        <v>0.56558464236321</v>
+        <v>0.5601619226630118</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L11">
         <v>212</v>
       </c>
       <c r="M11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11">
-        <v>-2216.301867657914</v>
+        <v>-2238.626186388778</v>
       </c>
       <c r="O11">
-        <v>-31.84962805474257</v>
+        <v>-31.38093420522555</v>
       </c>
       <c r="P11">
-        <v>0.4516653036347984</v>
+        <v>0.3264748705041146</v>
       </c>
       <c r="Q11">
-        <v>0.3589340616908894</v>
+        <v>0.07021755844670512</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T11">
-        <v>0.6949642886995006</v>
+        <v>0.5729881006925248</v>
       </c>
       <c r="U11">
-        <v>0.7126617526412041</v>
+        <v>0.6077600739464163</v>
       </c>
       <c r="V11" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9939980577034802</v>
+      </c>
+      <c r="Y11">
+        <v>0.9996617145391203</v>
+      </c>
+      <c r="Z11">
+        <v>0.005663656835640185</v>
+      </c>
+      <c r="AA11">
+        <v>0.2117179824501232</v>
+      </c>
+      <c r="AB11">
+        <v>-85.60780292807019</v>
+      </c>
+      <c r="AC11">
+        <v>-24</v>
+      </c>
+      <c r="AD11">
+        <v>0.07658324200587172</v>
+      </c>
+      <c r="AE11">
+        <v>-0.9970631910986736</v>
+      </c>
+      <c r="AF11">
+        <v>1.599009383588538</v>
+      </c>
+      <c r="AG11">
+        <v>1.59846846196226</v>
+      </c>
+      <c r="AH11" t="s">
         <v>68</v>
       </c>
-      <c r="X11">
-        <v>0.995018626213148</v>
-      </c>
-      <c r="Y11">
-        <v>0.9997112909057156</v>
-      </c>
-      <c r="Z11">
-        <v>0.004692664692567683</v>
-      </c>
-      <c r="AA11">
-        <v>0.1406307919426623</v>
-      </c>
-      <c r="AB11">
-        <v>-76.798764247509</v>
-      </c>
-      <c r="AC11">
-        <v>-21.99999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>0.228371868158356</v>
-      </c>
-      <c r="AE11">
-        <v>-0.9735739775866354</v>
-      </c>
-      <c r="AF11">
-        <v>1.538559395412338</v>
-      </c>
-      <c r="AG11">
-        <v>1.538115199322786</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>56</v>
-      </c>
       <c r="AI11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AL11">
-        <v>0.1302063897923587</v>
+        <v>0.04638294975916168</v>
       </c>
       <c r="AM11">
-        <v>0.5783253456726923</v>
+        <v>0.5320886528497983</v>
       </c>
       <c r="AN11">
-        <v>0.4285505175192901</v>
+        <v>0.2078487712189059</v>
       </c>
       <c r="AO11">
-        <v>-1.46968865365661</v>
+        <v>-1.57576333828175</v>
       </c>
       <c r="AP11">
-        <v>-0.2616187175915644</v>
+        <v>-0.6075882353552399</v>
       </c>
       <c r="AQ11">
-        <v>-1.91773203214572</v>
+        <v>-1.713534707069807</v>
       </c>
       <c r="AR11">
-        <v>0.4823579895471006</v>
+        <v>0.7187090165714427</v>
       </c>
       <c r="AS11">
-        <v>0.1214088332023164</v>
+        <v>0.2207434422045328</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
   <si>
     <t>Pair</t>
   </si>
@@ -199,6 +199,9 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
@@ -211,6 +214,9 @@
     <t>多头加速</t>
   </si>
   <si>
+    <t>空头减速</t>
+  </si>
+  <si>
     <t>空头稳态</t>
   </si>
   <si>
@@ -238,28 +244,34 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
     <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
   </si>
 </sst>
 </file>
@@ -769,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C2" s="2">
         <v>46280</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46279</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -784,13 +796,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.5322898086271723</v>
+        <v>0.3022150780607559</v>
       </c>
       <c r="H2">
-        <v>1.076358358876711</v>
+        <v>1.077146538531164</v>
       </c>
       <c r="I2">
-        <v>0.2588448654001832</v>
+        <v>0.2588262425116752</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -802,103 +814,103 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2">
-        <v>-0.5002233026953614</v>
+        <v>-0.5163274007280384</v>
       </c>
       <c r="O2">
-        <v>-14.07974876401826</v>
+        <v>-14.64135547222565</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.1970187147800589</v>
       </c>
       <c r="Q2">
-        <v>0.5322898086271723</v>
+        <v>0.376366278546551</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T2">
-        <v>0.8040328903044585</v>
+        <v>0.6492674853593453</v>
       </c>
       <c r="U2">
-        <v>0.7614848539166132</v>
+        <v>0.6919866239514849</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X2">
-        <v>0.9806151748731429</v>
+        <v>0.9885406449942716</v>
       </c>
       <c r="Y2">
-        <v>0.9986802131184278</v>
+        <v>0.9992650221591181</v>
       </c>
       <c r="Z2">
-        <v>0.01806503824528494</v>
+        <v>0.01072437716484642</v>
       </c>
       <c r="AA2">
-        <v>0.2633578518385805</v>
+        <v>0.6388297233188638</v>
       </c>
       <c r="AB2">
-        <v>-56.64023767166175</v>
+        <v>-70.14342172803055</v>
       </c>
       <c r="AC2">
-        <v>-40</v>
+        <v>-30.99999999999999</v>
       </c>
       <c r="AD2">
-        <v>0.5498943075500854</v>
+        <v>0.3396668531830572</v>
       </c>
       <c r="AE2">
-        <v>-0.8352342488930947</v>
+        <v>-0.9405458143273614</v>
       </c>
       <c r="AF2">
-        <v>0.8640199279568578</v>
+        <v>1.034270654404251</v>
       </c>
       <c r="AG2">
-        <v>0.8628796057905234</v>
+        <v>1.033510488391789</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.3468982088183297</v>
+        <v>0.2781235025491731</v>
       </c>
       <c r="AM2">
-        <v>0.7087548104940669</v>
+        <v>0.7167910906636098</v>
       </c>
       <c r="AN2">
-        <v>0.5140238509020666</v>
+        <v>0.3954637777536929</v>
       </c>
       <c r="AO2">
-        <v>-0.6735337538144014</v>
+        <v>-0.9428404704996661</v>
       </c>
       <c r="AP2">
-        <v>0.1840277826922503</v>
+        <v>-0.01195494673094893</v>
       </c>
       <c r="AQ2">
-        <v>-2.183203764413147</v>
+        <v>-1.908957297092834</v>
       </c>
       <c r="AR2">
-        <v>0.2761722435110276</v>
+        <v>0.3148565047003864</v>
       </c>
       <c r="AS2">
-        <v>0.05615417820083014</v>
+        <v>0.08411778473847624</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -909,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C3" s="2">
         <v>46280</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46279</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -921,16 +933,16 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0.1070399265804761</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.648978363959246</v>
+        <v>1.387655313461933</v>
       </c>
       <c r="H3">
-        <v>1.999280383217206</v>
+        <v>2.009891875902233</v>
       </c>
       <c r="I3">
-        <v>0.4457221521383132</v>
+        <v>0.4474215071285371</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -942,103 +954,103 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3">
-        <v>-0.1312925567490325</v>
+        <v>-0.1352919102675332</v>
       </c>
       <c r="O3">
-        <v>-44.13725043790246</v>
+        <v>-46.26494244615194</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.648978363959246</v>
+        <v>1.387655313461933</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.8040844093871631</v>
+        <v>0.6911000426247549</v>
       </c>
       <c r="U3">
-        <v>0.7776074934517428</v>
+        <v>0.7108173139027903</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9870907508187853</v>
+        <v>0.9914516392699743</v>
       </c>
       <c r="Y3">
-        <v>0.9988540809617921</v>
+        <v>0.9992891788866024</v>
       </c>
       <c r="Z3">
-        <v>0.01176333014300679</v>
+        <v>0.007837539616628142</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-48.32792734363106</v>
+        <v>-61.15483782159379</v>
       </c>
       <c r="AC3">
-        <v>-32.99999999999999</v>
+        <v>-26</v>
       </c>
       <c r="AD3">
-        <v>0.6648663462030032</v>
+        <v>0.4824442544568019</v>
       </c>
       <c r="AE3">
-        <v>-0.7469623428839424</v>
+        <v>-0.8759266757792119</v>
       </c>
       <c r="AF3">
-        <v>2.080466297191172</v>
+        <v>2.423477310066249</v>
       </c>
       <c r="AG3">
-        <v>2.078082251252871</v>
+        <v>2.421754651226414</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AL3">
-        <v>0.6641044631990255</v>
+        <v>0.4821013228946967</v>
       </c>
       <c r="AM3">
-        <v>0.8931011357392076</v>
+        <v>0.8369788651536564</v>
       </c>
       <c r="AN3">
-        <v>1.457216143767806</v>
+        <v>1.252958774079383</v>
       </c>
       <c r="AO3">
-        <v>-1.447007669928777</v>
+        <v>-2.050207935731843</v>
       </c>
       <c r="AP3">
-        <v>1.164795403623578</v>
+        <v>0.8579562417671847</v>
       </c>
       <c r="AQ3">
-        <v>-4.882106732060211</v>
+        <v>-4.270417556524586</v>
       </c>
       <c r="AR3">
-        <v>0.9319104903366719</v>
+        <v>0.7591683021197938</v>
       </c>
       <c r="AS3">
-        <v>0.03971797638880459</v>
+        <v>0.05003749195796645</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1049,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C4" s="2">
         <v>46280</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46279</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -1064,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.4644705373884119</v>
+        <v>0.672766288446513</v>
       </c>
       <c r="H4">
-        <v>2.079631616457734</v>
+        <v>2.079782401342772</v>
       </c>
       <c r="I4">
-        <v>0.493581089309781</v>
+        <v>0.4937642073307707</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1079,106 +1091,106 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>-0.2476995568903617</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>-8.741602713549383</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.4644705373884119</v>
+        <v>0.672766288446513</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
       </c>
       <c r="S4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.7737186465331317</v>
+        <v>-0.7923531373068823</v>
       </c>
       <c r="U4">
-        <v>0.7479743913347484</v>
+        <v>0.7564604566596984</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9856952087081511</v>
+        <v>0.9932415841150277</v>
       </c>
       <c r="Y4">
-        <v>0.9992040015793563</v>
+        <v>0.9996061794864057</v>
       </c>
       <c r="Z4">
-        <v>0.01350879287120521</v>
+        <v>0.006364595371378012</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>-109.6924528889363</v>
+        <v>-113.0624095566154</v>
       </c>
       <c r="AC4">
-        <v>-34</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AD4">
-        <v>-0.3369712431751639</v>
+        <v>-0.3917335584761495</v>
       </c>
       <c r="AE4">
-        <v>-0.9415149394847564</v>
+        <v>-0.9200787027008142</v>
       </c>
       <c r="AF4">
-        <v>0.8150502755325302</v>
+        <v>1.086435141160702</v>
       </c>
       <c r="AG4">
-        <v>0.814401496800461</v>
+        <v>1.086007280715424</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
       </c>
       <c r="AI4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AL4">
-        <v>-0.168351507298897</v>
+        <v>-0.1957896428824792</v>
       </c>
       <c r="AM4">
-        <v>0.5809853472856928</v>
+        <v>0.6009195802152922</v>
       </c>
       <c r="AN4">
-        <v>-0.2259080226308482</v>
+        <v>-0.3849972177905258</v>
       </c>
       <c r="AO4">
-        <v>-0.7709752963208648</v>
+        <v>-1.00807633477444</v>
       </c>
       <c r="AP4">
-        <v>-1.137502229099049</v>
+        <v>-1.393443476071012</v>
       </c>
       <c r="AQ4">
-        <v>-1.173432794323517</v>
+        <v>-0.8654607001560514</v>
       </c>
       <c r="AR4">
-        <v>1.202387605559851</v>
+        <v>1.421876780670325</v>
       </c>
       <c r="AS4">
-        <v>0.1321828414642066</v>
+        <v>0.1097510009852973</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1189,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C5" s="2">
         <v>46280</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46279</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1204,121 +1216,121 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.3284909043607342</v>
+        <v>0.113902919212323</v>
       </c>
       <c r="H5">
-        <v>1.510026492626507</v>
+        <v>1.51260309884705</v>
       </c>
       <c r="I5">
-        <v>0.3434459197385207</v>
+        <v>0.3448241377382673</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L5">
         <v>226</v>
       </c>
       <c r="M5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5">
-        <v>-0.1217660477721098</v>
+        <v>-0.1232632685450506</v>
       </c>
       <c r="O5">
-        <v>-36.28617856129333</v>
+        <v>-37.26780606048443</v>
       </c>
       <c r="P5">
-        <v>0.3803248458818078</v>
+        <v>0.4624982528334107</v>
       </c>
       <c r="Q5">
-        <v>0.5301017834548847</v>
+        <v>0.2119117190088329</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T5">
-        <v>0.740562428887295</v>
+        <v>0.4711543821923891</v>
       </c>
       <c r="U5">
-        <v>0.7330167150300032</v>
+        <v>0.5869151630352247</v>
       </c>
       <c r="V5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="W5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X5">
-        <v>0.9900455463104854</v>
+        <v>0.9938664709178598</v>
       </c>
       <c r="Y5">
-        <v>0.9990544881228819</v>
+        <v>0.9995827641945983</v>
       </c>
       <c r="Z5">
-        <v>0.009008941812396531</v>
+        <v>0.005716293276738504</v>
       </c>
       <c r="AA5">
-        <v>0.2295652278539875</v>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>-67.08029985022648</v>
+        <v>-81.79632906096435</v>
       </c>
       <c r="AC5">
-        <v>-29</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD5">
-        <v>0.3894406605921795</v>
+        <v>0.1426923483489294</v>
       </c>
       <c r="AE5">
-        <v>-0.9210515576652193</v>
+        <v>-0.9897670906443938</v>
       </c>
       <c r="AF5">
-        <v>1.288389504537526</v>
+        <v>1.845905445364723</v>
       </c>
       <c r="AG5">
-        <v>1.287171316958632</v>
+        <v>1.845135267519531</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AI5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AL5">
-        <v>0.2391949715608186</v>
+        <v>0.1426328119920414</v>
       </c>
       <c r="AM5">
-        <v>0.6501215412376978</v>
+        <v>0.7178144135710045</v>
       </c>
       <c r="AN5">
-        <v>0.5678357415307461</v>
+        <v>0.3292356874036996</v>
       </c>
       <c r="AO5">
-        <v>-1.14220262248422</v>
+        <v>-1.80479932208779</v>
       </c>
       <c r="AP5">
-        <v>-0.06179268083553235</v>
+        <v>-0.471504674148112</v>
       </c>
       <c r="AQ5">
-        <v>-2.900968096772592</v>
+        <v>-2.50829722002397</v>
       </c>
       <c r="AR5">
-        <v>0.5133339514840164</v>
+        <v>0.7362429268641191</v>
       </c>
       <c r="AS5">
-        <v>0.0819518223584141</v>
+        <v>0.1656483893452242</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1329,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C6" s="2">
         <v>46280</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46279</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1344,13 +1356,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.3541415674016754</v>
+        <v>0.457979184325273</v>
       </c>
       <c r="H6">
-        <v>0.9433488720293223</v>
+        <v>0.9433560196586872</v>
       </c>
       <c r="I6">
-        <v>0.2566284989526173</v>
+        <v>0.2565659272722934</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1362,103 +1374,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>0.02595949721692993</v>
+        <v>0.0401998095575697</v>
       </c>
       <c r="O6">
-        <v>0.505069640253235</v>
+        <v>0.8037895024222023</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.3541415674016754</v>
+        <v>0.457979184325273</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.8686042979154364</v>
+        <v>-0.8677601508868771</v>
       </c>
       <c r="U6">
-        <v>0.790585254275402</v>
+        <v>0.7903499084832597</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
       </c>
       <c r="W6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9872155901835044</v>
+        <v>0.9949659016343844</v>
       </c>
       <c r="Y6">
-        <v>0.998853280853823</v>
+        <v>0.9994313623366604</v>
       </c>
       <c r="Z6">
-        <v>0.01163769067031861</v>
+        <v>0.004465460702276047</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>-127.9451908038636</v>
+        <v>-127.7763647042577</v>
       </c>
       <c r="AC6">
-        <v>-34</v>
+        <v>-21</v>
       </c>
       <c r="AD6">
-        <v>-0.6149073819271738</v>
+        <v>-0.612581051722029</v>
       </c>
       <c r="AE6">
-        <v>-0.7885993353100602</v>
+        <v>-0.7904077777142207</v>
       </c>
       <c r="AF6">
-        <v>0.4474767583701829</v>
+        <v>0.5562363364492732</v>
       </c>
       <c r="AG6">
-        <v>0.4469636282038905</v>
+        <v>0.5559200395186501</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AL6">
-        <v>-0.3071011279295962</v>
+        <v>-0.3061163575320859</v>
       </c>
       <c r="AM6">
-        <v>0.673461485962789</v>
+        <v>0.6735269321142432</v>
       </c>
       <c r="AN6">
-        <v>-0.2430084362936052</v>
+        <v>-0.3197280199864684</v>
       </c>
       <c r="AO6">
-        <v>-0.368910953746</v>
+        <v>-0.4517362144464229</v>
       </c>
       <c r="AP6">
-        <v>-0.5581255149946011</v>
+        <v>-0.6943676706362006</v>
       </c>
       <c r="AQ6">
-        <v>0.1596279715553374</v>
+        <v>0.2027265347920631</v>
       </c>
       <c r="AR6">
-        <v>0.5280506619945343</v>
+        <v>0.6599940573354511</v>
       </c>
       <c r="AS6">
-        <v>0.07072917942800762</v>
+        <v>0.06698906813464363</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1469,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C7" s="2">
         <v>46280</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46279</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1484,121 +1496,121 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.3272372832527371</v>
+        <v>0.03416955490130145</v>
       </c>
       <c r="H7">
-        <v>1.469612226283769</v>
+        <v>1.472398929765195</v>
       </c>
       <c r="I7">
-        <v>0.3659522585114973</v>
+        <v>0.3672315487624704</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L7">
         <v>239</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N7">
-        <v>-0.1602673140814661</v>
+        <v>-0.1614386454849679</v>
       </c>
       <c r="O7">
-        <v>-41.60471717301159</v>
+        <v>-43.05030546265794</v>
       </c>
       <c r="P7">
-        <v>0.2991550707415915</v>
+        <v>0.7755232343606417</v>
       </c>
       <c r="Q7">
-        <v>0.4669182433823124</v>
+        <v>0.1522186708454177</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T7">
-        <v>0.7986004666080007</v>
+        <v>0.5036694739926805</v>
       </c>
       <c r="U7">
-        <v>0.7592379857681434</v>
+        <v>0.6015757688088759</v>
       </c>
       <c r="V7" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="W7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X7">
-        <v>0.9988155075451334</v>
+        <v>0.9978595574241531</v>
       </c>
       <c r="Y7">
-        <v>0.9994711031781724</v>
+        <v>0.9996980220486789</v>
       </c>
       <c r="Z7">
-        <v>0.0006555956330390744</v>
+        <v>0.001838464624525749</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.6668888251877514</v>
       </c>
       <c r="AB7">
-        <v>-65.79632472936247</v>
+        <v>-83.66999434434932</v>
       </c>
       <c r="AC7">
-        <v>-7.999999999999998</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>0.409981541466164</v>
+        <v>0.11025483087232</v>
       </c>
       <c r="AE7">
-        <v>-0.9120938195476538</v>
+        <v>-0.9939033515736407</v>
       </c>
       <c r="AF7">
-        <v>0.9790605313600033</v>
+        <v>1.472800766366187</v>
       </c>
       <c r="AG7">
-        <v>0.9785427093565902</v>
+        <v>1.472356013008056</v>
       </c>
       <c r="AH7" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AI7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AJ7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AL7">
-        <v>0.2048823517659373</v>
+        <v>0.09186352361372788</v>
       </c>
       <c r="AM7">
-        <v>0.6144344292101485</v>
+        <v>0.6392194039758973</v>
       </c>
       <c r="AN7">
-        <v>0.417513994869618</v>
+        <v>0.1958238010424785</v>
       </c>
       <c r="AO7">
-        <v>-0.8842918748851024</v>
+        <v>-1.45654358879843</v>
       </c>
       <c r="AP7">
-        <v>0.3092411070603037</v>
+        <v>-0.1512775050486639</v>
       </c>
       <c r="AQ7">
-        <v>-1.358901367601592</v>
+        <v>-1.358708286649757</v>
       </c>
       <c r="AR7">
-        <v>0.2652449766801828</v>
+        <v>0.3236101391705627</v>
       </c>
       <c r="AS7">
-        <v>0.0558327956137401</v>
+        <v>0.1808607869359098</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1609,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C8" s="2">
         <v>46280</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46279</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1621,16 +1633,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.4085139427329589</v>
+        <v>0.6827852171250517</v>
       </c>
       <c r="G8">
-        <v>1.373498749861369</v>
+        <v>1.570696400134309</v>
       </c>
       <c r="H8">
-        <v>1.43882827426618</v>
+        <v>1.440090492348078</v>
       </c>
       <c r="I8">
-        <v>0.3570463432155477</v>
+        <v>0.3572660575085722</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1642,103 +1654,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-0.01246644480791922</v>
+        <v>-0.01602976123212788</v>
       </c>
       <c r="O8">
-        <v>-3.473238354445169</v>
+        <v>-4.507263652335626</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.373498749861369</v>
+        <v>1.570696400134309</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T8">
-        <v>0.8398296143974808</v>
+        <v>0.7763367086703723</v>
       </c>
       <c r="U8">
-        <v>0.8391478778747419</v>
+        <v>0.8517324938063381</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9979708824706606</v>
+        <v>0.9994599426143425</v>
       </c>
       <c r="Y8">
-        <v>0.9997898399437267</v>
+        <v>0.9998527693436513</v>
       </c>
       <c r="Z8">
-        <v>0.001818957473066152</v>
+        <v>0.0003928267293088483</v>
       </c>
       <c r="AA8">
-        <v>0.577851014516473</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>48.58678857679728</v>
+        <v>54.85116337480898</v>
       </c>
       <c r="AC8">
-        <v>-12.99999999999999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD8">
-        <v>0.6614848104777297</v>
+        <v>0.5757024010987276</v>
       </c>
       <c r="AE8">
-        <v>0.7499585625267853</v>
+        <v>0.8176593088622912</v>
       </c>
       <c r="AF8">
-        <v>1.4228011970436</v>
+        <v>1.897836514770312</v>
       </c>
       <c r="AG8">
-        <v>1.422502181063964</v>
+        <v>1.8975570950546</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.5217525650521097</v>
+        <v>0.5756176400563523</v>
       </c>
       <c r="AM8">
-        <v>0.8033716330019459</v>
+        <v>0.8627898672340636</v>
       </c>
       <c r="AN8">
-        <v>0.9177807134602085</v>
+        <v>1.077613557470728</v>
       </c>
       <c r="AO8">
-        <v>1.083436570067038</v>
+        <v>1.560975069807629</v>
       </c>
       <c r="AP8">
-        <v>2.270108714869733</v>
+        <v>2.475284634128603</v>
       </c>
       <c r="AQ8">
-        <v>-0.1250406182136466</v>
+        <v>-0.6124997590557972</v>
       </c>
       <c r="AR8">
-        <v>2.198550716678369</v>
+        <v>2.353697948581886</v>
       </c>
       <c r="AS8">
-        <v>0.07046971349981229</v>
+        <v>0.06579548243888363</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1749,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C9" s="2">
         <v>46280</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46279</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1761,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.9407221123010578</v>
+        <v>0.7971463881552604</v>
       </c>
       <c r="G9">
-        <v>3.62860109327589</v>
+        <v>3.451571604623169</v>
       </c>
       <c r="H9">
-        <v>3.057294646908424</v>
+        <v>3.064476262182454</v>
       </c>
       <c r="I9">
-        <v>0.6481481532485552</v>
+        <v>0.6513546148816989</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1782,103 +1794,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N9">
-        <v>0.6824528451040284</v>
+        <v>0.7007155479481726</v>
       </c>
       <c r="O9">
-        <v>103.8063866955301</v>
+        <v>102.9923115094455</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.62860109327589</v>
+        <v>3.451571604623169</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9867058542560161</v>
+        <v>-0.9725963678079926</v>
       </c>
       <c r="U9">
-        <v>0.9850481836537166</v>
+        <v>0.9571777461701203</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X9">
-        <v>0.998053511027817</v>
+        <v>0.9984336364738039</v>
       </c>
       <c r="Y9">
-        <v>0.9996889295734031</v>
+        <v>0.9997496897329385</v>
       </c>
       <c r="Z9">
-        <v>0.00163541854558602</v>
+        <v>0.001316053259134642</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>166.8213103505525</v>
+        <v>161.2612057631207</v>
       </c>
       <c r="AC9">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="AD9">
-        <v>-0.9736637673900084</v>
+        <v>-0.9469929776991087</v>
       </c>
       <c r="AE9">
-        <v>0.2279887454939294</v>
+        <v>0.3212542609656335</v>
       </c>
       <c r="AF9">
-        <v>2.873840858389804</v>
+        <v>2.789914748591813</v>
       </c>
       <c r="AG9">
-        <v>2.872946891488013</v>
+        <v>2.789216404286015</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9733608893865243</v>
+        <v>-0.9467559356339555</v>
       </c>
       <c r="AM9">
-        <v>0.9874202203026983</v>
+        <v>0.9793602774739623</v>
       </c>
       <c r="AN9">
-        <v>-2.80716301597792</v>
+        <v>-2.656004153757917</v>
       </c>
       <c r="AO9">
-        <v>0.5887923391863664</v>
+        <v>0.8395840436118809</v>
       </c>
       <c r="AP9">
-        <v>-4.315599903873433</v>
+        <v>-4.160384258272138</v>
       </c>
       <c r="AQ9">
-        <v>5.207316204213797</v>
+        <v>4.559363097133033</v>
       </c>
       <c r="AR9">
-        <v>3.861539043783517</v>
+        <v>3.772165455730732</v>
       </c>
       <c r="AS9">
-        <v>0.03046690176663491</v>
+        <v>0.03100004828199295</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1889,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C10" s="2">
         <v>46280</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46279</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1901,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.9854140213095479</v>
+        <v>0.7767584709530562</v>
       </c>
       <c r="G10">
-        <v>2.506061488315238</v>
+        <v>2.324637152564254</v>
       </c>
       <c r="H10">
-        <v>2.067488987913405</v>
+        <v>2.074573598265138</v>
       </c>
       <c r="I10">
-        <v>0.4517509601583548</v>
+        <v>0.451772177809026</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1922,103 +1934,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N10">
-        <v>32.94041438557652</v>
+        <v>35.21481058082014</v>
       </c>
       <c r="O10">
-        <v>27.92405700260799</v>
+        <v>29.59050165845274</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.506061488315238</v>
+        <v>2.324637152564254</v>
       </c>
       <c r="R10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.941786007256101</v>
+        <v>-0.9982818662459734</v>
       </c>
       <c r="U10">
-        <v>0.9712317342149173</v>
+        <v>0.9648302177448576</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
       </c>
       <c r="W10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9925590473473577</v>
+        <v>0.9740167224373539</v>
       </c>
       <c r="Y10">
-        <v>0.9984637110129587</v>
+        <v>0.9963584291648447</v>
       </c>
       <c r="Z10">
-        <v>0.005904663665601051</v>
+        <v>0.02234170672749081</v>
       </c>
       <c r="AA10">
-        <v>1</v>
+        <v>0.8446382050838273</v>
       </c>
       <c r="AB10">
-        <v>-152.0991671420752</v>
+        <v>-175.2068921605852</v>
       </c>
       <c r="AC10">
-        <v>-25</v>
+        <v>-48</v>
       </c>
       <c r="AD10">
-        <v>-0.8837588281146735</v>
+        <v>-0.9965029177225527</v>
       </c>
       <c r="AE10">
-        <v>-0.4679426607281911</v>
+        <v>-0.08355797370951025</v>
       </c>
       <c r="AF10">
-        <v>2.322586839197069</v>
+        <v>1.953486001143956</v>
       </c>
       <c r="AG10">
-        <v>2.319018674614564</v>
+        <v>1.946372243495306</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AJ10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.8824011191598404</v>
+        <v>-0.9157467320262193</v>
       </c>
       <c r="AM10">
-        <v>0.9588462785035203</v>
+        <v>0.961691872397425</v>
       </c>
       <c r="AN10">
-        <v>-1.971462694951287</v>
+        <v>-1.868098377030235</v>
       </c>
       <c r="AO10">
-        <v>-1.194890811441123</v>
+        <v>-0.3613618935501299</v>
       </c>
       <c r="AP10">
-        <v>-2.849982399328737</v>
+        <v>-2.474844600796342</v>
       </c>
       <c r="AQ10">
-        <v>4.732644937606127</v>
+        <v>4.966267091630977</v>
       </c>
       <c r="AR10">
-        <v>2.376526241075518</v>
+        <v>2.005753682561695</v>
       </c>
       <c r="AS10">
-        <v>0.03829112523611434</v>
+        <v>0.03274729429201255</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2029,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C11" s="2">
         <v>46280</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46279</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2044,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.04729329014570197</v>
+        <v>0.03165600104598355</v>
       </c>
       <c r="H11">
-        <v>2.373993695812118</v>
+        <v>2.355280680267783</v>
       </c>
       <c r="I11">
-        <v>0.5601619226630118</v>
+        <v>0.5546648246847962</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2062,103 +2074,103 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N11">
-        <v>-2238.626186388778</v>
+        <v>-2251.467465141096</v>
       </c>
       <c r="O11">
-        <v>-31.38093420522555</v>
+        <v>-31.4221930477359</v>
       </c>
       <c r="P11">
-        <v>0.3264748705041146</v>
+        <v>0.3996038728836551</v>
       </c>
       <c r="Q11">
-        <v>0.07021755844670512</v>
+        <v>0.05272519194623192</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T11">
-        <v>0.5729881006925248</v>
+        <v>0.6158939918839855</v>
       </c>
       <c r="U11">
-        <v>0.6077600739464163</v>
+        <v>0.6270906499783299</v>
       </c>
       <c r="V11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9939980577034802</v>
+        <v>0.9961087547886562</v>
       </c>
       <c r="Y11">
-        <v>0.9996617145391203</v>
+        <v>0.9997534145221455</v>
       </c>
       <c r="Z11">
-        <v>0.005663656835640185</v>
+        <v>0.003644659733489264</v>
       </c>
       <c r="AA11">
-        <v>0.2117179824501232</v>
+        <v>0.05871282590859755</v>
       </c>
       <c r="AB11">
-        <v>-85.60780292807019</v>
+        <v>-86.84644237015766</v>
       </c>
       <c r="AC11">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="AD11">
-        <v>0.07658324200587172</v>
+        <v>0.05501217834529652</v>
       </c>
       <c r="AE11">
-        <v>-0.9970631910986736</v>
+        <v>-0.9984856835396817</v>
       </c>
       <c r="AF11">
-        <v>1.599009383588538</v>
+        <v>1.464887545020026</v>
       </c>
       <c r="AG11">
-        <v>1.59846846196226</v>
+        <v>1.464526325024735</v>
       </c>
       <c r="AH11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AI11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AJ11" t="s">
         <v>76</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11">
-        <v>0.04638294975916168</v>
+        <v>0.02911386856978697</v>
       </c>
       <c r="AM11">
-        <v>0.5320886528497983</v>
+        <v>0.4914746051588749</v>
       </c>
       <c r="AN11">
-        <v>0.2078487712189059</v>
+        <v>0.1514988887513829</v>
       </c>
       <c r="AO11">
-        <v>-1.57576333828175</v>
+        <v>-1.4513013772579</v>
       </c>
       <c r="AP11">
-        <v>-0.6075882353552399</v>
+        <v>-0.4478905679736006</v>
       </c>
       <c r="AQ11">
-        <v>-1.713534707069807</v>
+        <v>-0.9173147340484979</v>
       </c>
       <c r="AR11">
-        <v>0.7187090165714427</v>
+        <v>0.4763741290751481</v>
       </c>
       <c r="AS11">
-        <v>0.2207434422045328</v>
+        <v>0.2445687240612294</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -229,13 +229,16 @@
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>转换</t>
+    <t>TRANSITION_ZONE</t>
   </si>
   <si>
     <t>UP_CREST_FLATTENING</t>
@@ -244,9 +247,6 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
@@ -256,13 +256,13 @@
     <t>DOWN_SLOPE</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -784,7 +784,7 @@
         <v>46282</v>
       </c>
       <c r="C2" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -796,37 +796,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.3022150780607559</v>
+        <v>0.06524719674745511</v>
       </c>
       <c r="H2">
-        <v>1.077146538531164</v>
+        <v>1.077859653456621</v>
       </c>
       <c r="I2">
-        <v>0.2588262425116752</v>
+        <v>0.2588123111577922</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L2">
         <v>149</v>
       </c>
       <c r="M2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2">
-        <v>-0.5163274007280384</v>
+        <v>-0.5268384415653199</v>
       </c>
       <c r="O2">
-        <v>-14.64135547222565</v>
+        <v>-14.22679226509235</v>
       </c>
       <c r="P2">
-        <v>0.1970187147800589</v>
+        <v>0.3329888744503931</v>
       </c>
       <c r="Q2">
-        <v>0.376366278546551</v>
+        <v>0.09782025253880498</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,49 +835,49 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.6492674853593453</v>
+        <v>0.4344034749202256</v>
       </c>
       <c r="U2">
-        <v>0.6919866239514849</v>
+        <v>0.545387314894983</v>
       </c>
       <c r="V2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="W2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X2">
-        <v>0.9885406449942716</v>
+        <v>0.9937912919980996</v>
       </c>
       <c r="Y2">
-        <v>0.9992650221591181</v>
+        <v>0.9996230047235263</v>
       </c>
       <c r="Z2">
-        <v>0.01072437716484642</v>
+        <v>0.005831712725426708</v>
       </c>
       <c r="AA2">
-        <v>0.6388297233188638</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>-70.14342172803055</v>
+        <v>-83.46685860511681</v>
       </c>
       <c r="AC2">
-        <v>-30.99999999999999</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD2">
-        <v>0.3396668531830572</v>
+        <v>0.1137779030489081</v>
       </c>
       <c r="AE2">
-        <v>-0.9405458143273614</v>
+        <v>-0.99350620973288</v>
       </c>
       <c r="AF2">
-        <v>1.034270654404251</v>
+        <v>1.310600417491263</v>
       </c>
       <c r="AG2">
-        <v>1.033510488391789</v>
+        <v>1.310106327324525</v>
       </c>
       <c r="AH2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AI2" t="s">
         <v>71</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.2781235025491731</v>
+        <v>0.1137350093168916</v>
       </c>
       <c r="AM2">
-        <v>0.7167910906636098</v>
+        <v>0.7051261272952865</v>
       </c>
       <c r="AN2">
-        <v>0.3954637777536929</v>
+        <v>0.1910823272299699</v>
       </c>
       <c r="AO2">
-        <v>-0.9428404704996661</v>
+        <v>-1.28837034492356</v>
       </c>
       <c r="AP2">
-        <v>-0.01195494673094893</v>
+        <v>-0.3878254263067406</v>
       </c>
       <c r="AQ2">
-        <v>-1.908957297092834</v>
+        <v>-1.709134775113346</v>
       </c>
       <c r="AR2">
-        <v>0.3148565047003864</v>
+        <v>0.5484235748821181</v>
       </c>
       <c r="AS2">
-        <v>0.08411778473847624</v>
+        <v>0.1925019684841343</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -924,7 +924,7 @@
         <v>46282</v>
       </c>
       <c r="C3" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1.387655313461933</v>
+        <v>0.8577256191889026</v>
       </c>
       <c r="H3">
-        <v>2.009891875902233</v>
+        <v>2.019492750236305</v>
       </c>
       <c r="I3">
-        <v>0.4474215071285371</v>
+        <v>0.4488829291088468</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3">
-        <v>-0.1352919102675332</v>
+        <v>-0.1385722051860541</v>
       </c>
       <c r="O3">
-        <v>-46.26494244615194</v>
+        <v>-43.92643207528037</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>0.1173467262048713</v>
       </c>
       <c r="Q3">
-        <v>1.387655313461933</v>
+        <v>0.9717582709470446</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.6911000426247549</v>
+        <v>0.6159994718469458</v>
       </c>
       <c r="U3">
-        <v>0.7108173139027903</v>
+        <v>0.677076930841619</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,70 +987,70 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9914516392699743</v>
+        <v>0.9944536752619145</v>
       </c>
       <c r="Y3">
-        <v>0.9992891788866024</v>
+        <v>0.9995086740419734</v>
       </c>
       <c r="Z3">
-        <v>0.007837539616628142</v>
+        <v>0.005054998780058884</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-61.15483782159379</v>
+        <v>-69.10406610064956</v>
       </c>
       <c r="AC3">
-        <v>-26</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>0.4824442544568019</v>
+        <v>0.3566717008781201</v>
       </c>
       <c r="AE3">
-        <v>-0.8759266757792119</v>
+        <v>-0.9342297885385098</v>
       </c>
       <c r="AF3">
-        <v>2.423477310066249</v>
+        <v>2.344233603329397</v>
       </c>
       <c r="AG3">
-        <v>2.421754651226414</v>
+        <v>2.343081820508403</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL3">
-        <v>0.4821013228946967</v>
+        <v>0.3564964588129852</v>
       </c>
       <c r="AM3">
-        <v>0.8369788651536564</v>
+        <v>0.7966078738714228</v>
       </c>
       <c r="AN3">
-        <v>1.252958774079383</v>
+        <v>0.9181959811564773</v>
       </c>
       <c r="AO3">
-        <v>-2.050207935731843</v>
+        <v>-2.142791983416557</v>
       </c>
       <c r="AP3">
-        <v>0.8579562417671847</v>
+        <v>0.4198628180733306</v>
       </c>
       <c r="AQ3">
-        <v>-4.270417556524586</v>
+        <v>-3.418587270096519</v>
       </c>
       <c r="AR3">
-        <v>0.7591683021197938</v>
+        <v>0.5071495902468289</v>
       </c>
       <c r="AS3">
-        <v>0.05003749195796645</v>
+        <v>0.06814448204469208</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1064,7 +1064,7 @@
         <v>46282</v>
       </c>
       <c r="C4" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.672766288446513</v>
+        <v>1.070761368424196</v>
       </c>
       <c r="H4">
-        <v>2.079782401342772</v>
+        <v>2.079918825762568</v>
       </c>
       <c r="I4">
-        <v>0.4937642073307707</v>
+        <v>0.493827798664462</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1094,19 +1094,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>0.01567112774911642</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.5066877332277786</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.672766288446513</v>
+        <v>1.070761368424196</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.7923531373068823</v>
+        <v>-0.714030007035483</v>
       </c>
       <c r="U4">
-        <v>0.7564604566596984</v>
+        <v>0.7212776062636812</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
@@ -1127,70 +1127,70 @@
         <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9932415841150277</v>
+        <v>0.998179359265844</v>
       </c>
       <c r="Y4">
-        <v>0.9996061794864057</v>
+        <v>0.9998564123908554</v>
       </c>
       <c r="Z4">
-        <v>0.006364595371378012</v>
+        <v>0.00167705312501143</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.4451120696948463</v>
       </c>
       <c r="AB4">
-        <v>-113.0624095566154</v>
+        <v>-114.3341943260237</v>
       </c>
       <c r="AC4">
-        <v>-22.99999999999999</v>
+        <v>-12</v>
       </c>
       <c r="AD4">
-        <v>-0.3917335584761495</v>
+        <v>-0.4120582140207711</v>
       </c>
       <c r="AE4">
-        <v>-0.9200787027008142</v>
+        <v>-0.9111575211005023</v>
       </c>
       <c r="AF4">
-        <v>1.086435141160702</v>
+        <v>1.675928138923994</v>
       </c>
       <c r="AG4">
-        <v>1.086007280715424</v>
+        <v>1.675687496409428</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
       </c>
       <c r="AI4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL4">
-        <v>-0.1957896428824792</v>
+        <v>-0.2976923981709202</v>
       </c>
       <c r="AM4">
-        <v>0.6009195802152922</v>
+        <v>0.6982067874420025</v>
       </c>
       <c r="AN4">
-        <v>-0.3849972177905258</v>
+        <v>-0.663143586345423</v>
       </c>
       <c r="AO4">
-        <v>-1.00807633477444</v>
+        <v>-1.535824737971604</v>
       </c>
       <c r="AP4">
-        <v>-1.393443476071012</v>
+        <v>-1.983768835891844</v>
       </c>
       <c r="AQ4">
-        <v>-0.8654607001560514</v>
+        <v>-0.943282125898916</v>
       </c>
       <c r="AR4">
-        <v>1.421876780670325</v>
+        <v>2.010883721962682</v>
       </c>
       <c r="AS4">
-        <v>0.1097510009852973</v>
+        <v>0.09588556693331662</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1204,7 +1204,7 @@
         <v>46282</v>
       </c>
       <c r="C5" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1216,37 +1216,37 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.113902919212323</v>
+        <v>0.2823585839149488</v>
       </c>
       <c r="H5">
-        <v>1.51260309884705</v>
+        <v>1.51493431399897</v>
       </c>
       <c r="I5">
-        <v>0.3448241377382673</v>
+        <v>0.3461160908997283</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5">
         <v>226</v>
       </c>
       <c r="M5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N5">
-        <v>-0.1232632685450506</v>
+        <v>-0.1236343070421374</v>
       </c>
       <c r="O5">
-        <v>-37.26780606048443</v>
+        <v>-32.71057920419423</v>
       </c>
       <c r="P5">
-        <v>0.4624982528334107</v>
+        <v>0.2128031532417952</v>
       </c>
       <c r="Q5">
-        <v>0.2119117190088329</v>
+        <v>0.3586886622802721</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1255,10 +1255,10 @@
         <v>63</v>
       </c>
       <c r="T5">
-        <v>0.4711543821923891</v>
+        <v>0.2673946141720625</v>
       </c>
       <c r="U5">
-        <v>0.5869151630352247</v>
+        <v>0.420269735781742</v>
       </c>
       <c r="V5" t="s">
         <v>68</v>
@@ -1267,70 +1267,70 @@
         <v>68</v>
       </c>
       <c r="X5">
-        <v>0.9938664709178598</v>
+        <v>0.9962987772528413</v>
       </c>
       <c r="Y5">
-        <v>0.9995827641945983</v>
+        <v>0.9997686376172555</v>
       </c>
       <c r="Z5">
-        <v>0.005716293276738504</v>
+        <v>0.003469860364414212</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-81.79632906096435</v>
+        <v>-93.92557157819374</v>
       </c>
       <c r="AC5">
-        <v>-21.99999999999999</v>
+        <v>-17</v>
       </c>
       <c r="AD5">
-        <v>0.1426923483489294</v>
+        <v>-0.06846055858543516</v>
       </c>
       <c r="AE5">
-        <v>-0.9897670906443938</v>
+        <v>-0.9976538236874403</v>
       </c>
       <c r="AF5">
-        <v>1.845905445364723</v>
+        <v>2.19571546869809</v>
       </c>
       <c r="AG5">
-        <v>1.845135267519531</v>
+        <v>2.195207462735423</v>
       </c>
       <c r="AH5" t="s">
         <v>70</v>
       </c>
       <c r="AI5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL5">
-        <v>0.1426328119920414</v>
+        <v>-0.06844471938747682</v>
       </c>
       <c r="AM5">
-        <v>0.7178144135710045</v>
+        <v>0.6812703624360725</v>
       </c>
       <c r="AN5">
-        <v>0.3292356874036996</v>
+        <v>-0.09177323229322928</v>
       </c>
       <c r="AO5">
-        <v>-1.80479932208779</v>
+        <v>-2.185662763802843</v>
       </c>
       <c r="AP5">
-        <v>-0.471504674148112</v>
+        <v>-1.226663472154302</v>
       </c>
       <c r="AQ5">
-        <v>-2.50829722002397</v>
+        <v>-2.187890960935691</v>
       </c>
       <c r="AR5">
-        <v>0.7362429268641191</v>
+        <v>1.346423448110695</v>
       </c>
       <c r="AS5">
-        <v>0.1656483893452242</v>
+        <v>0.2612455220373168</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>46282</v>
       </c>
       <c r="C6" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1353,16 +1353,16 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.01880191757619046</v>
       </c>
       <c r="G6">
-        <v>0.457979184325273</v>
+        <v>0.6964939566289734</v>
       </c>
       <c r="H6">
-        <v>0.9433560196586872</v>
+        <v>0.9433624865614459</v>
       </c>
       <c r="I6">
-        <v>0.2565659272722934</v>
+        <v>0.2565144572989445</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,19 +1374,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>0.0401998095575697</v>
+        <v>0.06122746988876236</v>
       </c>
       <c r="O6">
-        <v>0.8037895024222023</v>
+        <v>1.116983852754948</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.457979184325273</v>
+        <v>0.6964939566289734</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.8677601508868771</v>
+        <v>-0.7794743312517826</v>
       </c>
       <c r="U6">
-        <v>0.7903499084832597</v>
+        <v>0.7535444680721862</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,70 +1407,70 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9949659016343844</v>
+        <v>0.9994589915775443</v>
       </c>
       <c r="Y6">
-        <v>0.9994313623366604</v>
+        <v>0.9998429254898222</v>
       </c>
       <c r="Z6">
-        <v>0.004465460702276047</v>
+        <v>0.0003839339122779784</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.4370428318113841</v>
       </c>
       <c r="AB6">
-        <v>-127.7763647042577</v>
+        <v>-122.8576661840473</v>
       </c>
       <c r="AC6">
-        <v>-21</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD6">
-        <v>-0.612581051722029</v>
+        <v>-0.5425539364530436</v>
       </c>
       <c r="AE6">
-        <v>-0.7904077777142207</v>
+        <v>-0.8400209676188486</v>
       </c>
       <c r="AF6">
-        <v>0.5562363364492732</v>
+        <v>0.8899842257649391</v>
       </c>
       <c r="AG6">
-        <v>0.5559200395186501</v>
+        <v>0.8898444319286111</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
       </c>
       <c r="AI6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL6">
-        <v>-0.3061163575320859</v>
+        <v>-0.3897753892288995</v>
       </c>
       <c r="AM6">
-        <v>0.6735269321142432</v>
+        <v>0.7390183193719653</v>
       </c>
       <c r="AN6">
-        <v>-0.3197280199864684</v>
+        <v>-0.4755050419453364</v>
       </c>
       <c r="AO6">
-        <v>-0.4517362144464229</v>
+        <v>-0.7517380353983013</v>
       </c>
       <c r="AP6">
-        <v>-0.6943676706362006</v>
+        <v>-1.093101510666785</v>
       </c>
       <c r="AQ6">
-        <v>0.2027265347920631</v>
+        <v>-0.07158285209649816</v>
       </c>
       <c r="AR6">
-        <v>0.6599940573354511</v>
+        <v>1.078841554071325</v>
       </c>
       <c r="AS6">
-        <v>0.06698906813464363</v>
+        <v>0.07400967898441663</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1484,61 +1484,61 @@
         <v>46282</v>
       </c>
       <c r="C7" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.03416955490130145</v>
+        <v>0.3223109922322406</v>
       </c>
       <c r="H7">
-        <v>1.472398929765195</v>
+        <v>1.474920232915057</v>
       </c>
       <c r="I7">
-        <v>0.3672315487624704</v>
+        <v>0.3683907238792796</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>239</v>
       </c>
       <c r="M7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N7">
-        <v>-0.1614386454849679</v>
+        <v>-0.1613152092741409</v>
       </c>
       <c r="O7">
-        <v>-43.05030546265794</v>
+        <v>-36.94442875573316</v>
       </c>
       <c r="P7">
-        <v>0.7755232343606417</v>
+        <v>0.2855119160367274</v>
       </c>
       <c r="Q7">
-        <v>0.1522186708454177</v>
+        <v>0.451107582430736</v>
       </c>
       <c r="R7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T7">
-        <v>0.5036694739926805</v>
+        <v>-0.4848709250354737</v>
       </c>
       <c r="U7">
-        <v>0.6015757688088759</v>
+        <v>0.6181497420822262</v>
       </c>
       <c r="V7" t="s">
         <v>68</v>
@@ -1547,70 +1547,70 @@
         <v>68</v>
       </c>
       <c r="X7">
-        <v>0.9978595574241531</v>
+        <v>0.9983590367213651</v>
       </c>
       <c r="Y7">
-        <v>0.9996980220486789</v>
+        <v>0.9998313032650523</v>
       </c>
       <c r="Z7">
-        <v>0.001838464624525749</v>
+        <v>0.001472266543687262</v>
       </c>
       <c r="AA7">
-        <v>0.6668888251877514</v>
+        <v>1</v>
       </c>
       <c r="AB7">
-        <v>-83.66999434434932</v>
+        <v>-97.88007791281441</v>
       </c>
       <c r="AC7">
-        <v>-12.99999999999999</v>
+        <v>-11</v>
       </c>
       <c r="AD7">
-        <v>0.11025483087232</v>
+        <v>-0.1371001316370621</v>
       </c>
       <c r="AE7">
-        <v>-0.9939033515736407</v>
+        <v>-0.9905571936567319</v>
       </c>
       <c r="AF7">
-        <v>1.472800766366187</v>
+        <v>1.87209978768258</v>
       </c>
       <c r="AG7">
-        <v>1.472356013008056</v>
+        <v>1.871783970560902</v>
       </c>
       <c r="AH7" t="s">
         <v>70</v>
       </c>
       <c r="AI7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL7">
-        <v>0.09186352361372788</v>
+        <v>-0.137077003292494</v>
       </c>
       <c r="AM7">
-        <v>0.6392194039758973</v>
+        <v>0.7112252278539652</v>
       </c>
       <c r="AN7">
-        <v>0.1958238010424785</v>
+        <v>-0.2247172167165957</v>
       </c>
       <c r="AO7">
-        <v>-1.45654358879843</v>
+        <v>-1.855469446779309</v>
       </c>
       <c r="AP7">
-        <v>-0.1512775050486639</v>
+        <v>-1.054361149087296</v>
       </c>
       <c r="AQ7">
-        <v>-1.358708286649757</v>
+        <v>-1.453125711083343</v>
       </c>
       <c r="AR7">
-        <v>0.3236101391705627</v>
+        <v>1.134914451439164</v>
       </c>
       <c r="AS7">
-        <v>0.1808607869359098</v>
+        <v>0.1989717851994777</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1624,7 +1624,7 @@
         <v>46282</v>
       </c>
       <c r="C8" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1633,16 +1633,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0.6827852171250517</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1.570696400134309</v>
+        <v>1.833137795769725</v>
       </c>
       <c r="H8">
-        <v>1.440090492348078</v>
+        <v>1.441320106386858</v>
       </c>
       <c r="I8">
-        <v>0.3572660575085722</v>
+        <v>0.3576741495903446</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-0.01602976123212788</v>
+        <v>-0.02042125102779525</v>
       </c>
       <c r="O8">
-        <v>-4.507263652335626</v>
+        <v>-5.206182543733658</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.570696400134309</v>
+        <v>1.833137795769725</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7763367086703723</v>
+        <v>0.7877561267150857</v>
       </c>
       <c r="U8">
-        <v>0.8517324938063381</v>
+        <v>0.9044774195220939</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,40 +1687,40 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9994599426143425</v>
+        <v>0.9996346529403842</v>
       </c>
       <c r="Y8">
-        <v>0.9998527693436513</v>
+        <v>0.9999486500012214</v>
       </c>
       <c r="Z8">
-        <v>0.0003928267293088483</v>
+        <v>0.0003139970608371234</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>54.85116337480898</v>
+        <v>54.86525010363052</v>
       </c>
       <c r="AC8">
-        <v>-5.999999999999996</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD8">
-        <v>0.5757024010987276</v>
+        <v>0.5755013541478592</v>
       </c>
       <c r="AE8">
-        <v>0.8176593088622912</v>
+        <v>0.817800826224809</v>
       </c>
       <c r="AF8">
-        <v>1.897836514770312</v>
+        <v>2.218370360949344</v>
       </c>
       <c r="AG8">
-        <v>1.8975570950546</v>
+        <v>2.218256447634019</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s">
         <v>77</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.5756176400563523</v>
+        <v>0.5754718021540266</v>
       </c>
       <c r="AM8">
-        <v>0.8627898672340636</v>
+        <v>0.8626418778182841</v>
       </c>
       <c r="AN8">
-        <v>1.077613557470728</v>
+        <v>1.262083861462606</v>
       </c>
       <c r="AO8">
-        <v>1.560975069807629</v>
+        <v>1.823380424929133</v>
       </c>
       <c r="AP8">
-        <v>2.475284634128603</v>
+        <v>2.857590311835407</v>
       </c>
       <c r="AQ8">
-        <v>-0.6124997590557972</v>
+        <v>-0.5195046719087689</v>
       </c>
       <c r="AR8">
-        <v>2.353697948581886</v>
+        <v>2.742310406239305</v>
       </c>
       <c r="AS8">
-        <v>0.06579548243888363</v>
+        <v>0.0666037061766743</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>46282</v>
       </c>
       <c r="C9" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.7971463881552604</v>
+        <v>0.6838933934311553</v>
       </c>
       <c r="G9">
-        <v>3.451571604623169</v>
+        <v>3.312044073047681</v>
       </c>
       <c r="H9">
-        <v>3.064476262182454</v>
+        <v>3.071386625738303</v>
       </c>
       <c r="I9">
-        <v>0.6513546148816989</v>
+        <v>0.6543395682114969</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N9">
-        <v>0.7007155479481726</v>
+        <v>0.7186796791223328</v>
       </c>
       <c r="O9">
-        <v>102.9923115094455</v>
+        <v>101.9197275902848</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.451571604623169</v>
+        <v>3.312044073047681</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9725963678079926</v>
+        <v>-0.9776490232765577</v>
       </c>
       <c r="U9">
-        <v>0.9571777461701203</v>
+        <v>0.9425015538993265</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,40 +1827,40 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9984336364738039</v>
+        <v>0.9997638097801202</v>
       </c>
       <c r="Y9">
-        <v>0.9997496897329385</v>
+        <v>0.9999019376408095</v>
       </c>
       <c r="Z9">
-        <v>0.001316053259134642</v>
+        <v>0.00013812786068923</v>
       </c>
       <c r="AA9">
         <v>1</v>
       </c>
       <c r="AB9">
-        <v>161.2612057631207</v>
+        <v>163.2541632768595</v>
       </c>
       <c r="AC9">
-        <v>-11</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD9">
-        <v>-0.9469929776991087</v>
+        <v>-0.9575922994502618</v>
       </c>
       <c r="AE9">
-        <v>0.3212542609656335</v>
+        <v>0.2881266874719525</v>
       </c>
       <c r="AF9">
-        <v>2.789914748591813</v>
+        <v>2.639265632067036</v>
       </c>
       <c r="AG9">
-        <v>2.789216404286015</v>
+        <v>2.639006819452625</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
       </c>
       <c r="AI9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ9" t="s">
         <v>78</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9467559356339555</v>
+        <v>-0.9574983956902351</v>
       </c>
       <c r="AM9">
-        <v>0.9793602774739623</v>
+        <v>0.982465254189971</v>
       </c>
       <c r="AN9">
-        <v>-2.656004153757917</v>
+        <v>-2.532529145371306</v>
       </c>
       <c r="AO9">
-        <v>0.8395840436118809</v>
+        <v>0.7407625272065881</v>
       </c>
       <c r="AP9">
-        <v>-4.160384258272138</v>
+        <v>-4.057636880023013</v>
       </c>
       <c r="AQ9">
-        <v>4.559363097133033</v>
+        <v>4.020113645045003</v>
       </c>
       <c r="AR9">
-        <v>3.772165455730732</v>
+        <v>3.718235628769614</v>
       </c>
       <c r="AS9">
-        <v>0.03100004828199295</v>
+        <v>0.03185409212927249</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1904,7 +1904,7 @@
         <v>46282</v>
       </c>
       <c r="C10" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.7767584709530562</v>
+        <v>0.3707565925524526</v>
       </c>
       <c r="G10">
-        <v>2.324637152564254</v>
+        <v>1.964198137243035</v>
       </c>
       <c r="H10">
-        <v>2.074573598265138</v>
+        <v>2.080983483821467</v>
       </c>
       <c r="I10">
-        <v>0.451772177809026</v>
+        <v>0.4518038826306425</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N10">
-        <v>35.21481058082014</v>
+        <v>37.34299974151758</v>
       </c>
       <c r="O10">
-        <v>29.59050165845274</v>
+        <v>29.81137003941638</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.324637152564254</v>
+        <v>1.964198137243035</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.9982818662459734</v>
+        <v>-0.9875211525167262</v>
       </c>
       <c r="U10">
-        <v>0.9648302177448576</v>
+        <v>0.8991693313402891</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,40 +1967,40 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9740167224373539</v>
+        <v>0.9674499444213529</v>
       </c>
       <c r="Y10">
-        <v>0.9963584291648447</v>
+        <v>0.9966852952995774</v>
       </c>
       <c r="Z10">
-        <v>0.02234170672749081</v>
+        <v>0.02923535087822449</v>
       </c>
       <c r="AA10">
-        <v>0.8446382050838273</v>
+        <v>0.4866481629492806</v>
       </c>
       <c r="AB10">
-        <v>-175.2068921605852</v>
+        <v>166.5500764688677</v>
       </c>
       <c r="AC10">
-        <v>-48</v>
+        <v>-53</v>
       </c>
       <c r="AD10">
-        <v>-0.9965029177225527</v>
+        <v>-0.9725735800624781</v>
       </c>
       <c r="AE10">
-        <v>-0.08355797370951025</v>
+        <v>0.2325954242122029</v>
       </c>
       <c r="AF10">
-        <v>1.953486001143956</v>
+        <v>1.691342461870851</v>
       </c>
       <c r="AG10">
-        <v>1.946372243495306</v>
+        <v>1.685736161062463</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ10" t="s">
         <v>79</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.9157467320262193</v>
+        <v>-0.7205410391909765</v>
       </c>
       <c r="AM10">
-        <v>0.961691872397425</v>
+        <v>0.8836085414058914</v>
       </c>
       <c r="AN10">
-        <v>-1.868098377030235</v>
+        <v>-1.623134483653261</v>
       </c>
       <c r="AO10">
-        <v>-0.3613618935501299</v>
+        <v>0.2070668931491191</v>
       </c>
       <c r="AP10">
-        <v>-2.474844600796342</v>
+        <v>-1.899610962887603</v>
       </c>
       <c r="AQ10">
-        <v>4.966267091630977</v>
+        <v>4.86306506272691</v>
       </c>
       <c r="AR10">
-        <v>2.005753682561695</v>
+        <v>1.465803668699609</v>
       </c>
       <c r="AS10">
-        <v>0.03274729429201255</v>
+        <v>0.02888679038373533</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2044,7 +2044,7 @@
         <v>46282</v>
       </c>
       <c r="C11" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.03165600104598355</v>
+        <v>0.02492614749915493</v>
       </c>
       <c r="H11">
-        <v>2.355280680267783</v>
+        <v>2.336800016269269</v>
       </c>
       <c r="I11">
-        <v>0.5546648246847962</v>
+        <v>0.548902863999148</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11">
-        <v>-2251.467465141096</v>
+        <v>-2261.128916439387</v>
       </c>
       <c r="O11">
-        <v>-31.4221930477359</v>
+        <v>-29.97652017021589</v>
       </c>
       <c r="P11">
-        <v>0.3996038728836551</v>
+        <v>0.5030297814625151</v>
       </c>
       <c r="Q11">
-        <v>0.05272519194623192</v>
+        <v>0.05015621976807617</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2095,10 +2095,10 @@
         <v>63</v>
       </c>
       <c r="T11">
-        <v>0.6158939918839855</v>
+        <v>0.6373752912759435</v>
       </c>
       <c r="U11">
-        <v>0.6270906499783299</v>
+        <v>0.6367709655424278</v>
       </c>
       <c r="V11" t="s">
         <v>68</v>
@@ -2107,70 +2107,70 @@
         <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9961087547886562</v>
+        <v>0.9973218236095097</v>
       </c>
       <c r="Y11">
-        <v>0.9997534145221455</v>
+        <v>0.9998083378730133</v>
       </c>
       <c r="Z11">
-        <v>0.003644659733489264</v>
+        <v>0.002486514263503548</v>
       </c>
       <c r="AA11">
-        <v>0.05871282590859755</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>-86.84644237015766</v>
+        <v>-87.12506249802411</v>
       </c>
       <c r="AC11">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="AD11">
-        <v>0.05501217834529652</v>
+        <v>0.05015607232391142</v>
       </c>
       <c r="AE11">
-        <v>-0.9984856835396817</v>
+        <v>-0.9987413921576689</v>
       </c>
       <c r="AF11">
-        <v>1.464887545020026</v>
+        <v>1.160730511712819</v>
       </c>
       <c r="AG11">
-        <v>1.464526325024735</v>
+        <v>1.160508043634086</v>
       </c>
       <c r="AH11" t="s">
         <v>70</v>
       </c>
       <c r="AI11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AJ11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL11">
-        <v>0.02911386856978697</v>
+        <v>0.02507322965220426</v>
       </c>
       <c r="AM11">
-        <v>0.4914746051588749</v>
+        <v>0.4781089601370971</v>
       </c>
       <c r="AN11">
-        <v>0.1514988887513829</v>
+        <v>0.1122588171426417</v>
       </c>
       <c r="AO11">
-        <v>-1.4513013772579</v>
+        <v>-1.152165940047503</v>
       </c>
       <c r="AP11">
-        <v>-0.4478905679736006</v>
+        <v>-0.2881312433733745</v>
       </c>
       <c r="AQ11">
-        <v>-0.9173147340484979</v>
+        <v>-0.4037334404284169</v>
       </c>
       <c r="AR11">
-        <v>0.4763741290751481</v>
+        <v>0.2766360853880414</v>
       </c>
       <c r="AS11">
-        <v>0.2445687240612294</v>
+        <v>0.2458051987708726</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -199,12 +199,12 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
-  </si>
-  <si>
     <t>多头减速</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>多头加速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
@@ -250,12 +250,12 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
     <t>地形转换区</t>
   </si>
   <si>
@@ -268,10 +268,10 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
   </si>
 </sst>
 </file>
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C2" s="2">
         <v>46282</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46281</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -796,13 +796,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.06524719674745511</v>
+        <v>0.01655556595978891</v>
       </c>
       <c r="H2">
-        <v>1.077859653456621</v>
+        <v>1.078504852674892</v>
       </c>
       <c r="I2">
-        <v>0.2588123111577922</v>
+        <v>0.2588574614349974</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -814,19 +814,19 @@
         <v>149</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2">
-        <v>-0.5268384415653199</v>
+        <v>-0.5319112687934471</v>
       </c>
       <c r="O2">
-        <v>-14.22679226509235</v>
+        <v>-14.6092201030119</v>
       </c>
       <c r="P2">
-        <v>0.3329888744503931</v>
+        <v>0.289481274266952</v>
       </c>
       <c r="Q2">
-        <v>0.09782025253880498</v>
+        <v>0.02330067507046827</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.4344034749202256</v>
+        <v>0.3807338069966937</v>
       </c>
       <c r="U2">
-        <v>0.545387314894983</v>
+        <v>0.5212641397611941</v>
       </c>
       <c r="V2" t="s">
         <v>68</v>
@@ -847,34 +847,34 @@
         <v>68</v>
       </c>
       <c r="X2">
-        <v>0.9937912919980996</v>
+        <v>0.9955332722745112</v>
       </c>
       <c r="Y2">
-        <v>0.9996230047235263</v>
+        <v>0.9997357064507278</v>
       </c>
       <c r="Z2">
-        <v>0.005831712725426708</v>
+        <v>0.004202434176216685</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-83.46685860511681</v>
+        <v>-88.29671643254534</v>
       </c>
       <c r="AC2">
-        <v>-21.99999999999999</v>
+        <v>-20</v>
       </c>
       <c r="AD2">
-        <v>0.1137779030489081</v>
+        <v>0.02972352787565342</v>
       </c>
       <c r="AE2">
-        <v>-0.99350620973288</v>
+        <v>-0.9995581583332834</v>
       </c>
       <c r="AF2">
-        <v>1.310600417491263</v>
+        <v>1.285996288196794</v>
       </c>
       <c r="AG2">
-        <v>1.310106327324525</v>
+        <v>1.285656407673436</v>
       </c>
       <c r="AH2" t="s">
         <v>70</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.1137350093168916</v>
+        <v>0.02971567213897427</v>
       </c>
       <c r="AM2">
-        <v>0.7051261272952865</v>
+        <v>0.6640602090769308</v>
       </c>
       <c r="AN2">
-        <v>0.1910823272299699</v>
+        <v>0.08430824290988428</v>
       </c>
       <c r="AO2">
-        <v>-1.28837034492356</v>
+        <v>-1.27747310797807</v>
       </c>
       <c r="AP2">
-        <v>-0.3878254263067406</v>
+        <v>-0.480242505338311</v>
       </c>
       <c r="AQ2">
-        <v>-1.709134775113346</v>
+        <v>-1.185912524583119</v>
       </c>
       <c r="AR2">
-        <v>0.5484235748821181</v>
+        <v>0.5444737846546214</v>
       </c>
       <c r="AS2">
-        <v>0.1925019684841343</v>
+        <v>0.2984289769568</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C3" s="2">
         <v>46282</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46281</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.8577256191889026</v>
+        <v>0.6920440496369997</v>
       </c>
       <c r="H3">
-        <v>2.019492750236305</v>
+        <v>2.028179255586179</v>
       </c>
       <c r="I3">
-        <v>0.4488829291088468</v>
+        <v>0.4501857391479409</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3">
-        <v>-0.1385722051860541</v>
+        <v>-0.1412231228378537</v>
       </c>
       <c r="O3">
-        <v>-43.92643207528037</v>
+        <v>-45.99566638897197</v>
       </c>
       <c r="P3">
-        <v>0.1173467262048713</v>
+        <v>0.1658865067430869</v>
       </c>
       <c r="Q3">
-        <v>0.9717582709470446</v>
+        <v>0.8296761234910811</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.6159994718469458</v>
+        <v>0.5846718301826457</v>
       </c>
       <c r="U3">
-        <v>0.677076930841619</v>
+        <v>0.6630150633925173</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9944536752619145</v>
+        <v>0.9969090269506007</v>
       </c>
       <c r="Y3">
-        <v>0.9995086740419734</v>
+        <v>0.9996509592413069</v>
       </c>
       <c r="Z3">
-        <v>0.005054998780058884</v>
+        <v>0.002741932290706184</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-69.10406610064956</v>
+        <v>-72.2883097669946</v>
       </c>
       <c r="AC3">
-        <v>-21.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AD3">
-        <v>0.3566717008781201</v>
+        <v>0.3042274290293818</v>
       </c>
       <c r="AE3">
-        <v>-0.9342297885385098</v>
+        <v>-0.9525994286299843</v>
       </c>
       <c r="AF3">
-        <v>2.344233603329397</v>
+        <v>2.348842404123014</v>
       </c>
       <c r="AG3">
-        <v>2.343081820508403</v>
+        <v>2.348022562388228</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>0.3564964588129852</v>
+        <v>0.3041212412567381</v>
       </c>
       <c r="AM3">
-        <v>0.7966078738714228</v>
+        <v>0.7795386901863116</v>
       </c>
       <c r="AN3">
-        <v>0.9181959811564773</v>
+        <v>0.7833795217544304</v>
       </c>
       <c r="AO3">
-        <v>-2.142791983416557</v>
+        <v>-2.206654414137842</v>
       </c>
       <c r="AP3">
-        <v>0.4198628180733306</v>
+        <v>0.3515149772265023</v>
       </c>
       <c r="AQ3">
-        <v>-3.418587270096519</v>
+        <v>-2.62818533186247</v>
       </c>
       <c r="AR3">
-        <v>0.5071495902468289</v>
+        <v>0.4103625275900591</v>
       </c>
       <c r="AS3">
-        <v>0.06814448204469208</v>
+        <v>0.07738249504640238</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C4" s="2">
         <v>46282</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46281</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1.070761368424196</v>
+        <v>1.44161677324608</v>
       </c>
       <c r="H4">
-        <v>2.079918825762568</v>
+        <v>2.080042257380478</v>
       </c>
       <c r="I4">
-        <v>0.493827798664462</v>
+        <v>0.4937976080082358</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1094,19 +1094,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>0.01567112774911642</v>
+        <v>0.03986260345418973</v>
       </c>
       <c r="O4">
-        <v>0.5066877332277786</v>
+        <v>1.348988272561402</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.070761368424196</v>
+        <v>1.44161677324608</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.714030007035483</v>
+        <v>-0.6609764876253195</v>
       </c>
       <c r="U4">
-        <v>0.7212776062636812</v>
+        <v>0.6974245382524717</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
@@ -1127,34 +1127,34 @@
         <v>69</v>
       </c>
       <c r="X4">
-        <v>0.998179359265844</v>
+        <v>0.9990962369745683</v>
       </c>
       <c r="Y4">
-        <v>0.9998564123908554</v>
+        <v>0.999940475284312</v>
       </c>
       <c r="Z4">
-        <v>0.00167705312501143</v>
+        <v>0.0008442383097436723</v>
       </c>
       <c r="AA4">
-        <v>0.4451120696948463</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>-114.3341943260237</v>
+        <v>-115.6023027918092</v>
       </c>
       <c r="AC4">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="AD4">
-        <v>-0.4120582140207711</v>
+        <v>-0.4321219942737594</v>
       </c>
       <c r="AE4">
-        <v>-0.9111575211005023</v>
+        <v>-0.901815159589186</v>
       </c>
       <c r="AF4">
-        <v>1.675928138923994</v>
+        <v>2.249300503378939</v>
       </c>
       <c r="AG4">
-        <v>1.675687496409428</v>
+        <v>2.249166614405978</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
@@ -1169,28 +1169,28 @@
         <v>82</v>
       </c>
       <c r="AL4">
-        <v>-0.2976923981709202</v>
+        <v>-0.4320962723349077</v>
       </c>
       <c r="AM4">
-        <v>0.6982067874420025</v>
+        <v>0.8168070767963024</v>
       </c>
       <c r="AN4">
-        <v>-0.663143586345423</v>
+        <v>-0.9432442515215841</v>
       </c>
       <c r="AO4">
-        <v>-1.535824737971604</v>
+        <v>-2.039730927594273</v>
       </c>
       <c r="AP4">
-        <v>-1.983768835891844</v>
+        <v>-2.45604809939681</v>
       </c>
       <c r="AQ4">
-        <v>-0.943282125898916</v>
+        <v>-0.3859727635142868</v>
       </c>
       <c r="AR4">
-        <v>2.010883721962682</v>
+        <v>2.416353699652829</v>
       </c>
       <c r="AS4">
-        <v>0.09588556693331662</v>
+        <v>0.08539125223556419</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,136 +1201,136 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C5" s="2">
         <v>46282</v>
       </c>
-      <c r="C5" s="2">
-        <v>46281</v>
-      </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.2823585839149488</v>
+        <v>0.7772118913444507</v>
       </c>
       <c r="H5">
-        <v>1.51493431399897</v>
+        <v>1.517043508660231</v>
       </c>
       <c r="I5">
-        <v>0.3461160908997283</v>
+        <v>0.3472574132864043</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>226</v>
       </c>
       <c r="M5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5">
-        <v>-0.1236343070421374</v>
+        <v>-0.1226770417380635</v>
       </c>
       <c r="O5">
-        <v>-32.71057920419423</v>
+        <v>-34.45984318484954</v>
       </c>
       <c r="P5">
-        <v>0.2128031532417952</v>
+        <v>0.05987444796614516</v>
       </c>
       <c r="Q5">
-        <v>0.3586886622802721</v>
+        <v>0.8267107405633652</v>
       </c>
       <c r="R5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T5">
-        <v>0.2673946141720625</v>
+        <v>-0.5121842826309468</v>
       </c>
       <c r="U5">
-        <v>0.420269735781742</v>
+        <v>0.6304485710096058</v>
       </c>
       <c r="V5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="W5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9962987772528413</v>
+        <v>0.9977537483377563</v>
       </c>
       <c r="Y5">
-        <v>0.9997686376172555</v>
+        <v>0.999862575302719</v>
       </c>
       <c r="Z5">
-        <v>0.003469860364414212</v>
+        <v>0.002108826964962729</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-93.92557157819374</v>
+        <v>-100.5365903501272</v>
       </c>
       <c r="AC5">
-        <v>-17</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AD5">
-        <v>-0.06846055858543516</v>
+        <v>-0.1828634165865115</v>
       </c>
       <c r="AE5">
-        <v>-0.9976538236874403</v>
+        <v>-0.9831383274363318</v>
       </c>
       <c r="AF5">
-        <v>2.19571546869809</v>
+        <v>2.755564077013055</v>
       </c>
       <c r="AG5">
-        <v>2.195207462735423</v>
+        <v>2.755185394453934</v>
       </c>
       <c r="AH5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AL5">
-        <v>-0.06844471938747682</v>
+        <v>-0.1828382866368433</v>
       </c>
       <c r="AM5">
-        <v>0.6812703624360725</v>
+        <v>0.7300549854365139</v>
       </c>
       <c r="AN5">
-        <v>-0.09177323229322928</v>
+        <v>-0.4403540916387163</v>
       </c>
       <c r="AO5">
-        <v>-2.185662763802843</v>
+        <v>-2.713880578029307</v>
       </c>
       <c r="AP5">
-        <v>-1.226663472154302</v>
+        <v>-1.842430185426691</v>
       </c>
       <c r="AQ5">
-        <v>-2.187890960935691</v>
+        <v>-1.588397178922474</v>
       </c>
       <c r="AR5">
-        <v>1.346423448110695</v>
+        <v>1.886683180913546</v>
       </c>
       <c r="AS5">
-        <v>0.2612455220373168</v>
+        <v>0.1650396059692746</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C6" s="2">
         <v>46282</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46281</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1353,16 +1353,16 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>0.01880191757619046</v>
+        <v>0.5795383327517757</v>
       </c>
       <c r="G6">
-        <v>0.6964939566289734</v>
+        <v>0.9852090534858458</v>
       </c>
       <c r="H6">
-        <v>0.9433624865614459</v>
+        <v>0.9444030349288555</v>
       </c>
       <c r="I6">
-        <v>0.2565144572989445</v>
+        <v>0.2565179401254128</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,19 +1374,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>0.06122746988876236</v>
+        <v>0.09269805156042499</v>
       </c>
       <c r="O6">
-        <v>1.116983852754948</v>
+        <v>1.706652536553422</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.6964939566289734</v>
+        <v>0.9852090534858458</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.7794743312517826</v>
+        <v>-0.750971043846107</v>
       </c>
       <c r="U6">
-        <v>0.7535444680721862</v>
+        <v>0.8248566478294365</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,34 +1407,34 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9994589915775443</v>
+        <v>0.9998577701251513</v>
       </c>
       <c r="Y6">
-        <v>0.9998429254898222</v>
+        <v>0.9999557127436877</v>
       </c>
       <c r="Z6">
-        <v>0.0003839339122779784</v>
+        <v>9.794261853635078E-05</v>
       </c>
       <c r="AA6">
-        <v>0.4370428318113841</v>
+        <v>1</v>
       </c>
       <c r="AB6">
-        <v>-122.8576661840473</v>
+        <v>-122.4092014101674</v>
       </c>
       <c r="AC6">
-        <v>-5.999999999999996</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AD6">
-        <v>-0.5425539364530436</v>
+        <v>-0.5359623828302383</v>
       </c>
       <c r="AE6">
-        <v>-0.8400209676188486</v>
+        <v>-0.8442418635621743</v>
       </c>
       <c r="AF6">
-        <v>0.8899842257649391</v>
+        <v>1.276129312965184</v>
       </c>
       <c r="AG6">
-        <v>0.8898444319286111</v>
+        <v>1.276072796699213</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>-0.3897753892288995</v>
+        <v>-0.5359386465268161</v>
       </c>
       <c r="AM6">
-        <v>0.7390183193719653</v>
+        <v>0.8497017684473732</v>
       </c>
       <c r="AN6">
-        <v>-0.4755050419453364</v>
+        <v>-0.678926070549545</v>
       </c>
       <c r="AO6">
-        <v>-0.7517380353983013</v>
+        <v>-1.080325044912384</v>
       </c>
       <c r="AP6">
-        <v>-1.093101510666785</v>
+        <v>-1.518876694813364</v>
       </c>
       <c r="AQ6">
-        <v>-0.07158285209649816</v>
+        <v>0.01055656208299138</v>
       </c>
       <c r="AR6">
-        <v>1.078841554071325</v>
+        <v>1.486091757780796</v>
       </c>
       <c r="AS6">
-        <v>0.07400967898441663</v>
+        <v>0.07380963907992617</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C7" s="2">
         <v>46282</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46281</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.3223109922322406</v>
+        <v>0.924936610197405</v>
       </c>
       <c r="H7">
-        <v>1.474920232915057</v>
+        <v>1.477201411955408</v>
       </c>
       <c r="I7">
-        <v>0.3683907238792796</v>
+        <v>0.3693898933233874</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1511,22 +1511,22 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>-0.1613152092741409</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>-36.94442875573316</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>0.2855119160367274</v>
+        <v>0.06516524549527072</v>
       </c>
       <c r="Q7">
-        <v>0.451107582430736</v>
+        <v>0.9894118781318006</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,82 +1535,82 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>-0.4848709250354737</v>
+        <v>-0.5561168204200569</v>
       </c>
       <c r="U7">
-        <v>0.6181497420822262</v>
+        <v>0.6502308918462194</v>
       </c>
       <c r="V7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="W7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9983590367213651</v>
+        <v>0.9991597310797949</v>
       </c>
       <c r="Y7">
-        <v>0.9998313032650523</v>
+        <v>0.999913290628775</v>
       </c>
       <c r="Z7">
-        <v>0.001472266543687262</v>
+        <v>0.0007535595489800428</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-97.88007791281441</v>
+        <v>-104.8606887688172</v>
       </c>
       <c r="AC7">
-        <v>-11</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD7">
-        <v>-0.1371001316370621</v>
+        <v>-0.2564696919894996</v>
       </c>
       <c r="AE7">
-        <v>-0.9905571936567319</v>
+        <v>-0.9665522733359077</v>
       </c>
       <c r="AF7">
-        <v>1.87209978768258</v>
+        <v>2.520267106113173</v>
       </c>
       <c r="AG7">
-        <v>1.871783970560902</v>
+        <v>2.520048575337083</v>
       </c>
       <c r="AH7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="AI7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AJ7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AL7">
-        <v>-0.137077003292494</v>
+        <v>-0.256447453663769</v>
       </c>
       <c r="AM7">
-        <v>0.7112252278539652</v>
+        <v>0.7577298228538096</v>
       </c>
       <c r="AN7">
-        <v>-0.2247172167165957</v>
+        <v>-0.6151802809032</v>
       </c>
       <c r="AO7">
-        <v>-1.855469446779309</v>
+        <v>-2.441849635587668</v>
       </c>
       <c r="AP7">
-        <v>-1.054361149087296</v>
+        <v>-1.80377892824894</v>
       </c>
       <c r="AQ7">
-        <v>-1.453125711083343</v>
+        <v>-1.023166154625297</v>
       </c>
       <c r="AR7">
-        <v>1.134914451439164</v>
+        <v>1.822018625129852</v>
       </c>
       <c r="AS7">
-        <v>0.1989717851994777</v>
+        <v>0.1278715764207432</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C8" s="2">
         <v>46282</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46281</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1.833137795769725</v>
+        <v>2.219972358040653</v>
       </c>
       <c r="H8">
-        <v>1.441320106386858</v>
+        <v>1.442633975126879</v>
       </c>
       <c r="I8">
-        <v>0.3576741495903446</v>
+        <v>0.358427533503214</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8">
-        <v>-0.02042125102779525</v>
+        <v>-0.02581088272300217</v>
       </c>
       <c r="O8">
-        <v>-5.206182543733658</v>
+        <v>-6.894063877173174</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.833137795769725</v>
+        <v>2.219972358040653</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.7877561267150857</v>
+        <v>0.8080428531121724</v>
       </c>
       <c r="U8">
-        <v>0.9044774195220939</v>
+        <v>0.913616507569292</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9996346529403842</v>
+        <v>0.9994384568176362</v>
       </c>
       <c r="Y8">
-        <v>0.9999486500012214</v>
+        <v>0.9999888946752581</v>
       </c>
       <c r="Z8">
-        <v>0.0003139970608371234</v>
+        <v>0.0005504378576218771</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>54.86525010363052</v>
+        <v>51.96930300464032</v>
       </c>
       <c r="AC8">
-        <v>-4.999999999999995</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD8">
-        <v>0.5755013541478592</v>
+        <v>0.6160835744542178</v>
       </c>
       <c r="AE8">
-        <v>0.817800826224809</v>
+        <v>0.7876807914934287</v>
       </c>
       <c r="AF8">
-        <v>2.218370360949344</v>
+        <v>2.567296796592367</v>
       </c>
       <c r="AG8">
-        <v>2.218256447634019</v>
+        <v>2.567268285927732</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.5754718021540266</v>
+        <v>0.6160767326460553</v>
       </c>
       <c r="AM8">
-        <v>0.8626418778182841</v>
+        <v>0.8753104062886309</v>
       </c>
       <c r="AN8">
-        <v>1.262083861462606</v>
+        <v>1.556851134476295</v>
       </c>
       <c r="AO8">
-        <v>1.823380424929133</v>
+        <v>2.039565441109928</v>
       </c>
       <c r="AP8">
-        <v>2.857590311835407</v>
+        <v>3.338512226818299</v>
       </c>
       <c r="AQ8">
-        <v>-0.5195046719087689</v>
+        <v>-1.112094145329638</v>
       </c>
       <c r="AR8">
-        <v>2.742310406239305</v>
+        <v>3.157360108686769</v>
       </c>
       <c r="AS8">
-        <v>0.0666037061766743</v>
+        <v>0.06340519455983201</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C9" s="2">
         <v>46282</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46281</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.6838933934311553</v>
+        <v>0.7348033142862079</v>
       </c>
       <c r="G9">
-        <v>3.312044073047681</v>
+        <v>3.387701679821335</v>
       </c>
       <c r="H9">
-        <v>3.071386625738303</v>
+        <v>3.079102139160119</v>
       </c>
       <c r="I9">
-        <v>0.6543395682114969</v>
+        <v>0.6571447715705065</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N9">
-        <v>0.7186796791223328</v>
+        <v>0.736848348978105</v>
       </c>
       <c r="O9">
-        <v>101.9197275902848</v>
+        <v>101.7244540547648</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.312044073047681</v>
+        <v>3.387701679821335</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9776490232765577</v>
+        <v>-0.9942167738971054</v>
       </c>
       <c r="U9">
-        <v>0.9425015538993265</v>
+        <v>0.9575949453430195</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.9997638097801202</v>
+        <v>0.999475908596434</v>
       </c>
       <c r="Y9">
-        <v>0.9999019376408095</v>
+        <v>0.9999075997855635</v>
       </c>
       <c r="Z9">
-        <v>0.00013812786068923</v>
+        <v>0.0004316911891295572</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>0.9405409251419504</v>
       </c>
       <c r="AB9">
-        <v>163.2541632768595</v>
+        <v>171.3857006022782</v>
       </c>
       <c r="AC9">
-        <v>-3.999999999999993</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AD9">
-        <v>-0.9575922994502618</v>
+        <v>-0.9887190304839409</v>
       </c>
       <c r="AE9">
-        <v>0.2881266874719525</v>
+        <v>0.149782104267819</v>
       </c>
       <c r="AF9">
-        <v>2.639265632067036</v>
+        <v>2.586231422806371</v>
       </c>
       <c r="AG9">
-        <v>2.639006819452625</v>
+        <v>2.585992454468321</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9574983956902351</v>
+        <v>-0.9592362292365794</v>
       </c>
       <c r="AM9">
-        <v>0.982465254189971</v>
+        <v>0.9794401315396966</v>
       </c>
       <c r="AN9">
-        <v>-2.532529145371306</v>
+        <v>-2.551143661676161</v>
       </c>
       <c r="AO9">
-        <v>0.7407625272065881</v>
+        <v>0.4162330582870611</v>
       </c>
       <c r="AP9">
-        <v>-4.057636880023013</v>
+        <v>-4.312108478118331</v>
       </c>
       <c r="AQ9">
-        <v>4.020113645045003</v>
+        <v>3.358595373306814</v>
       </c>
       <c r="AR9">
-        <v>3.718235628769614</v>
+        <v>4.024164510598976</v>
       </c>
       <c r="AS9">
-        <v>0.03185409212927249</v>
+        <v>0.03500948372548682</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C10" s="2">
         <v>46282</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46281</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1913,16 +1913,16 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>0.3707565925524526</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1.964198137243035</v>
+        <v>1.326215123079677</v>
       </c>
       <c r="H10">
-        <v>2.080983483821467</v>
+        <v>2.086782904086717</v>
       </c>
       <c r="I10">
-        <v>0.4518038826306425</v>
+        <v>0.4517473824866979</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10">
-        <v>37.34299974151758</v>
+        <v>39.17135216588338</v>
       </c>
       <c r="O10">
-        <v>29.81137003941638</v>
+        <v>28.45573528032201</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.964198137243035</v>
+        <v>1.326215123079677</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.9875211525167262</v>
+        <v>-0.8738735230020797</v>
       </c>
       <c r="U10">
-        <v>0.8991693313402891</v>
+        <v>0.7925867707208032</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9674499444213529</v>
+        <v>0.9641876238970215</v>
       </c>
       <c r="Y10">
-        <v>0.9966852952995774</v>
+        <v>0.9973747414794695</v>
       </c>
       <c r="Z10">
-        <v>0.02923535087822449</v>
+        <v>0.03318711758244797</v>
       </c>
       <c r="AA10">
-        <v>0.4866481629492806</v>
+        <v>0.3315673733474611</v>
       </c>
       <c r="AB10">
-        <v>166.5500764688677</v>
+        <v>136.2972034583038</v>
       </c>
       <c r="AC10">
         <v>-53</v>
       </c>
       <c r="AD10">
-        <v>-0.9725735800624781</v>
+        <v>-0.7229334238653541</v>
       </c>
       <c r="AE10">
-        <v>0.2325954242122029</v>
+        <v>0.6909176974563007</v>
       </c>
       <c r="AF10">
-        <v>1.691342461870851</v>
+        <v>1.579094487018609</v>
       </c>
       <c r="AG10">
-        <v>1.685736161062463</v>
+        <v>1.57494895576184</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.7205410391909765</v>
+        <v>-0.4800536978699176</v>
       </c>
       <c r="AM10">
-        <v>0.8836085414058914</v>
+        <v>0.7770164922437377</v>
       </c>
       <c r="AN10">
-        <v>-1.623134483653261</v>
+        <v>-1.179377254172649</v>
       </c>
       <c r="AO10">
-        <v>0.2070668931491191</v>
+        <v>0.9629161850976939</v>
       </c>
       <c r="AP10">
-        <v>-1.899610962887603</v>
+        <v>-0.9306409438947538</v>
       </c>
       <c r="AQ10">
-        <v>4.86306506272691</v>
+        <v>4.69785617985081</v>
       </c>
       <c r="AR10">
-        <v>1.465803668699609</v>
+        <v>0.8121045632290568</v>
       </c>
       <c r="AS10">
-        <v>0.02888679038373533</v>
+        <v>0.03505446068783412</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C11" s="2">
         <v>46282</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46281</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,37 +2056,37 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.02492614749915493</v>
+        <v>0.04969460202241648</v>
       </c>
       <c r="H11">
-        <v>2.336800016269269</v>
+        <v>2.318175294854195</v>
       </c>
       <c r="I11">
-        <v>0.548902863999148</v>
+        <v>0.5432049885695118</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>212</v>
       </c>
       <c r="M11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11">
-        <v>-2261.128916439387</v>
+        <v>-2269.994565806371</v>
       </c>
       <c r="O11">
-        <v>-29.97652017021589</v>
+        <v>-32.29929661079068</v>
       </c>
       <c r="P11">
-        <v>0.5030297814625151</v>
+        <v>0.5595016330430923</v>
       </c>
       <c r="Q11">
-        <v>0.05015621976807617</v>
+        <v>0.1128144977374636</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2095,10 +2095,10 @@
         <v>63</v>
       </c>
       <c r="T11">
-        <v>0.6373752912759435</v>
+        <v>0.7023511159933751</v>
       </c>
       <c r="U11">
-        <v>0.6367709655424278</v>
+        <v>0.7158272077718091</v>
       </c>
       <c r="V11" t="s">
         <v>68</v>
@@ -2107,34 +2107,34 @@
         <v>68</v>
       </c>
       <c r="X11">
-        <v>0.9973218236095097</v>
+        <v>0.9987294164417612</v>
       </c>
       <c r="Y11">
-        <v>0.9998083378730133</v>
+        <v>0.9990768222991612</v>
       </c>
       <c r="Z11">
-        <v>0.002486514263503548</v>
+        <v>0.0003474058574000072</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-87.12506249802411</v>
+        <v>-82.65846887999095</v>
       </c>
       <c r="AC11">
-        <v>-17</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD11">
-        <v>0.05015607232391142</v>
+        <v>0.1277835545917157</v>
       </c>
       <c r="AE11">
-        <v>-0.9987413921576689</v>
+        <v>-0.9918020786305632</v>
       </c>
       <c r="AF11">
-        <v>1.160730511712819</v>
+        <v>0.847692861307589</v>
       </c>
       <c r="AG11">
-        <v>1.160508043634086</v>
+        <v>0.8469102901608696</v>
       </c>
       <c r="AH11" t="s">
         <v>70</v>
@@ -2149,28 +2149,28 @@
         <v>80</v>
       </c>
       <c r="AL11">
-        <v>0.02507322965220426</v>
+        <v>0.06383279383179137</v>
       </c>
       <c r="AM11">
-        <v>0.4781089601370971</v>
+        <v>0.5135323923098526</v>
       </c>
       <c r="AN11">
-        <v>0.1122588171426417</v>
+        <v>0.1318101331374104</v>
       </c>
       <c r="AO11">
-        <v>-1.152165940047503</v>
+        <v>-0.836292051867517</v>
       </c>
       <c r="AP11">
-        <v>-0.2881312433733745</v>
+        <v>-0.08946860949674705</v>
       </c>
       <c r="AQ11">
-        <v>-0.4037334404284169</v>
+        <v>-0.05403530635355595</v>
       </c>
       <c r="AR11">
-        <v>0.2766360853880414</v>
+        <v>0.1139465447500654</v>
       </c>
       <c r="AS11">
-        <v>0.2458051987708726</v>
+        <v>0.1631970791491234</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C2" s="2">
         <v>46283</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46282</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -796,37 +796,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.01655556595978891</v>
+        <v>0.08554759762750143</v>
       </c>
       <c r="H2">
-        <v>1.078504852674892</v>
+        <v>1.079088604348566</v>
       </c>
       <c r="I2">
-        <v>0.2588574614349974</v>
+        <v>0.2589482565137322</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L2">
         <v>149</v>
       </c>
       <c r="M2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2">
-        <v>-0.5319112687934471</v>
+        <v>-0.5333555537414959</v>
       </c>
       <c r="O2">
-        <v>-14.6092201030119</v>
+        <v>-14.48857665828617</v>
       </c>
       <c r="P2">
-        <v>0.289481274266952</v>
+        <v>0.2587742305873376</v>
       </c>
       <c r="Q2">
-        <v>0.02330067507046827</v>
+        <v>0.1154136852194011</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.3807338069966937</v>
+        <v>0.3142695571397605</v>
       </c>
       <c r="U2">
-        <v>0.5212641397611941</v>
+        <v>0.4663733985142371</v>
       </c>
       <c r="V2" t="s">
         <v>68</v>
@@ -847,34 +847,34 @@
         <v>68</v>
       </c>
       <c r="X2">
-        <v>0.9955332722745112</v>
+        <v>0.9968562986243207</v>
       </c>
       <c r="Y2">
-        <v>0.9997357064507278</v>
+        <v>0.9998083912053797</v>
       </c>
       <c r="Z2">
-        <v>0.004202434176216685</v>
+        <v>0.002952092581058996</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-88.29671643254534</v>
+        <v>-92.13388134388816</v>
       </c>
       <c r="AC2">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="AD2">
-        <v>0.02972352787565342</v>
+        <v>-0.03723464612280344</v>
       </c>
       <c r="AE2">
-        <v>-0.9995581583332834</v>
+        <v>-0.9993065501276921</v>
       </c>
       <c r="AF2">
-        <v>1.285996288196794</v>
+        <v>1.276957825287862</v>
       </c>
       <c r="AG2">
-        <v>1.285656407673436</v>
+        <v>1.276713148938177</v>
       </c>
       <c r="AH2" t="s">
         <v>70</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>0.02971567213897427</v>
+        <v>-0.03722751163714174</v>
       </c>
       <c r="AM2">
-        <v>0.6640602090769308</v>
+        <v>0.6615956465052489</v>
       </c>
       <c r="AN2">
-        <v>0.08430824290988428</v>
+        <v>-0.00491775251390192</v>
       </c>
       <c r="AO2">
-        <v>-1.27747310797807</v>
+        <v>-1.272933951822895</v>
       </c>
       <c r="AP2">
-        <v>-0.480242505338311</v>
+        <v>-0.51507400972078</v>
       </c>
       <c r="AQ2">
-        <v>-1.185912524583119</v>
+        <v>-0.6963759476103385</v>
       </c>
       <c r="AR2">
-        <v>0.5444737846546214</v>
+        <v>0.522262883478808</v>
       </c>
       <c r="AS2">
-        <v>0.2984289769568</v>
+        <v>0.3300512283564994</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C3" s="2">
         <v>46282</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C4" s="2">
         <v>46283</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46282</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -1073,16 +1073,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.07896167182858867</v>
       </c>
       <c r="G4">
-        <v>1.44161677324608</v>
+        <v>1.664419904478783</v>
       </c>
       <c r="H4">
-        <v>2.080042257380478</v>
+        <v>2.080153933606207</v>
       </c>
       <c r="I4">
-        <v>0.4937976080082358</v>
+        <v>0.4937009309021533</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1094,19 +1094,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>0.03986260345418973</v>
+        <v>0.07057724691827695</v>
       </c>
       <c r="O4">
-        <v>1.348988272561402</v>
+        <v>2.388978377311101</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.44161677324608</v>
+        <v>1.664419904478783</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.6609764876253195</v>
+        <v>-0.684818444315218</v>
       </c>
       <c r="U4">
-        <v>0.6974245382524717</v>
+        <v>0.7200068284780117</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
@@ -1127,34 +1127,34 @@
         <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9990962369745683</v>
+        <v>0.9992701306473631</v>
       </c>
       <c r="Y4">
-        <v>0.999940475284312</v>
+        <v>0.9999771110475011</v>
       </c>
       <c r="Z4">
-        <v>0.0008442383097436723</v>
+        <v>0.0007069804001379465</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-115.6023027918092</v>
+        <v>-117.644066305188</v>
       </c>
       <c r="AC4">
-        <v>-9</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD4">
-        <v>-0.4321219942737594</v>
+        <v>-0.4639774790755453</v>
       </c>
       <c r="AE4">
-        <v>-0.901815159589186</v>
+        <v>-0.8858469952032925</v>
       </c>
       <c r="AF4">
-        <v>2.249300503378939</v>
+        <v>2.514472440617667</v>
       </c>
       <c r="AG4">
-        <v>2.249166614405978</v>
+        <v>2.514414886977414</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
@@ -1169,28 +1169,28 @@
         <v>82</v>
       </c>
       <c r="AL4">
-        <v>-0.4320962723349077</v>
+        <v>-0.4639668591170661</v>
       </c>
       <c r="AM4">
-        <v>0.8168070767963024</v>
+        <v>0.8278743507134645</v>
       </c>
       <c r="AN4">
-        <v>-0.9432442515215841</v>
+        <v>-1.13585558544477</v>
       </c>
       <c r="AO4">
-        <v>-2.039730927594273</v>
+        <v>-2.241244700868494</v>
       </c>
       <c r="AP4">
-        <v>-2.45604809939681</v>
+        <v>-2.638569280296996</v>
       </c>
       <c r="AQ4">
-        <v>-0.3859727635142868</v>
+        <v>0.412048627952475</v>
       </c>
       <c r="AR4">
-        <v>2.416353699652829</v>
+        <v>2.52065545207872</v>
       </c>
       <c r="AS4">
-        <v>0.08539125223556419</v>
+        <v>0.0754058791721629</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,7 +1201,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C5" s="2">
         <v>46282</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C6" s="2">
         <v>46283</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46282</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1353,16 +1353,16 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>0.5795383327517757</v>
+        <v>0.7961295937276529</v>
       </c>
       <c r="G6">
-        <v>0.9852090534858458</v>
+        <v>1.099162256042905</v>
       </c>
       <c r="H6">
-        <v>0.9444030349288555</v>
+        <v>0.947191304232047</v>
       </c>
       <c r="I6">
-        <v>0.2565179401254128</v>
+        <v>0.2565953471550433</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,19 +1374,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>0.09269805156042499</v>
+        <v>0.1325969633483026</v>
       </c>
       <c r="O6">
-        <v>1.706652536553422</v>
+        <v>2.417761769830995</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.9852090534858458</v>
+        <v>1.099162256042905</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.750971043846107</v>
+        <v>-0.7634159909761071</v>
       </c>
       <c r="U6">
-        <v>0.8248566478294365</v>
+        <v>0.8629527559013159</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,34 +1407,34 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9998577701251513</v>
+        <v>0.9999260044652175</v>
       </c>
       <c r="Y6">
-        <v>0.9999557127436877</v>
+        <v>0.9999844836116794</v>
       </c>
       <c r="Z6">
-        <v>9.794261853635078E-05</v>
+        <v>5.847914646184282E-05</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-122.4092014101674</v>
+        <v>-122.8542676783943</v>
       </c>
       <c r="AC6">
-        <v>-3.000000000000004</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AD6">
-        <v>-0.5359623828302383</v>
+        <v>-0.5425041095597809</v>
       </c>
       <c r="AE6">
-        <v>-0.8442418635621743</v>
+        <v>-0.8400531477893224</v>
       </c>
       <c r="AF6">
-        <v>1.276129312965184</v>
+        <v>1.450192373498942</v>
       </c>
       <c r="AG6">
-        <v>1.276072796699213</v>
+        <v>1.450169871750935</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>-0.5359386465268161</v>
+        <v>-0.5424956918553514</v>
       </c>
       <c r="AM6">
-        <v>0.8497017684473732</v>
+        <v>0.8527255077304319</v>
       </c>
       <c r="AN6">
-        <v>-0.678926070549545</v>
+        <v>-0.782626422887848</v>
       </c>
       <c r="AO6">
-        <v>-1.080325044912384</v>
+        <v>-1.2207549222003</v>
       </c>
       <c r="AP6">
-        <v>-1.518876694813364</v>
+        <v>-1.592488924166868</v>
       </c>
       <c r="AQ6">
-        <v>0.01055656208299138</v>
+        <v>0.5709083704187535</v>
       </c>
       <c r="AR6">
-        <v>1.486091757780796</v>
+        <v>1.502624010295105</v>
       </c>
       <c r="AS6">
-        <v>0.07380963907992617</v>
+        <v>0.06680196267726835</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C7" s="2">
         <v>46282</v>
@@ -1621,7 +1621,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C8" s="2">
         <v>46282</v>
@@ -1761,7 +1761,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C9" s="2">
         <v>46282</v>
@@ -1901,7 +1901,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C10" s="2">
         <v>46282</v>
@@ -2041,7 +2041,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C11" s="2">
         <v>46282</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,7 +781,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C2" s="2">
         <v>46283</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C3" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.6920440496369997</v>
+        <v>0.6714888821016466</v>
       </c>
       <c r="H3">
-        <v>2.028179255586179</v>
+        <v>2.036038474712256</v>
       </c>
       <c r="I3">
-        <v>0.4501857391479409</v>
+        <v>0.4513666636251979</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3">
-        <v>-0.1412231228378537</v>
+        <v>-0.1434528520964091</v>
       </c>
       <c r="O3">
-        <v>-45.99566638897197</v>
+        <v>-51.25931417431683</v>
       </c>
       <c r="P3">
-        <v>0.1658865067430869</v>
+        <v>0.1564557820823254</v>
       </c>
       <c r="Q3">
-        <v>0.8296761234910811</v>
+        <v>0.7960328194285368</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.5846718301826457</v>
+        <v>0.5721566250061204</v>
       </c>
       <c r="U3">
-        <v>0.6630150633925173</v>
+        <v>0.6574023218762785</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.9969090269506007</v>
+        <v>0.998485614933011</v>
       </c>
       <c r="Y3">
-        <v>0.9996509592413069</v>
+        <v>0.9997273624940969</v>
       </c>
       <c r="Z3">
-        <v>0.002741932290706184</v>
+        <v>0.00124174756108586</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-72.2883097669946</v>
+        <v>-73.54372225878554</v>
       </c>
       <c r="AC3">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="AD3">
-        <v>0.3042274290293818</v>
+        <v>0.2832835892612633</v>
       </c>
       <c r="AE3">
-        <v>-0.9525994286299843</v>
+        <v>-0.9590361870415818</v>
       </c>
       <c r="AF3">
-        <v>2.348842404123014</v>
+        <v>2.399897479370515</v>
       </c>
       <c r="AG3">
-        <v>2.348022562388228</v>
+        <v>2.399243177307317</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>0.3041212412567381</v>
+        <v>0.2832063555300239</v>
       </c>
       <c r="AM3">
-        <v>0.7795386901863116</v>
+        <v>0.7731312137537724</v>
       </c>
       <c r="AN3">
-        <v>0.7833795217544304</v>
+        <v>0.7340186446384928</v>
       </c>
       <c r="AO3">
-        <v>-2.206654414137842</v>
+        <v>-2.281072888774191</v>
       </c>
       <c r="AP3">
-        <v>0.3515149772265023</v>
+        <v>0.405411182059805</v>
       </c>
       <c r="AQ3">
-        <v>-2.62818533186247</v>
+        <v>-2.033462601656284</v>
       </c>
       <c r="AR3">
-        <v>0.4103625275900591</v>
+        <v>0.3800632544046766</v>
       </c>
       <c r="AS3">
-        <v>0.07738249504640238</v>
+        <v>0.07838959931693661</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,7 +1061,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C4" s="2">
         <v>46283</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C5" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.7772118913444507</v>
+        <v>1.000167377653249</v>
       </c>
       <c r="H5">
-        <v>1.517043508660231</v>
+        <v>1.518951827639467</v>
       </c>
       <c r="I5">
-        <v>0.3472574132864043</v>
+        <v>0.348257771719839</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1231,22 +1231,22 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>-0.1226770417380635</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>-34.45984318484954</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.05987444796614516</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>0.8267107405633652</v>
+        <v>1.000167377653249</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>-0.5121842826309468</v>
+        <v>-0.5386034294224616</v>
       </c>
       <c r="U5">
-        <v>0.6304485710096058</v>
+        <v>0.6423493220989157</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9977537483377563</v>
+        <v>0.9987268036452234</v>
       </c>
       <c r="Y5">
-        <v>0.999862575302719</v>
+        <v>0.9999111154352319</v>
       </c>
       <c r="Z5">
-        <v>0.002108826964962729</v>
+        <v>0.001184311790008552</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-100.5365903501272</v>
+        <v>-103.1283415028481</v>
       </c>
       <c r="AC5">
-        <v>-13.99999999999999</v>
+        <v>-11</v>
       </c>
       <c r="AD5">
-        <v>-0.1828634165865115</v>
+        <v>-0.2271330593743433</v>
       </c>
       <c r="AE5">
-        <v>-0.9831383274363318</v>
+        <v>-0.9738637344820121</v>
       </c>
       <c r="AF5">
-        <v>2.755564077013055</v>
+        <v>3.002443979585842</v>
       </c>
       <c r="AG5">
-        <v>2.755185394453934</v>
+        <v>3.002177108659476</v>
       </c>
       <c r="AH5" t="s">
         <v>57</v>
@@ -1309,28 +1309,28 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>-0.1828382866368433</v>
+        <v>-0.2271128707512164</v>
       </c>
       <c r="AM5">
-        <v>0.7300549854365139</v>
+        <v>0.7491375611531098</v>
       </c>
       <c r="AN5">
-        <v>-0.4403540916387163</v>
+        <v>-0.622650177525401</v>
       </c>
       <c r="AO5">
-        <v>-2.713880578029307</v>
+        <v>-2.933263767620166</v>
       </c>
       <c r="AP5">
-        <v>-1.842430185426691</v>
+        <v>-1.853504669552984</v>
       </c>
       <c r="AQ5">
-        <v>-1.588397178922474</v>
+        <v>-0.2526973252355096</v>
       </c>
       <c r="AR5">
-        <v>1.886683180913546</v>
+        <v>1.770934123438676</v>
       </c>
       <c r="AS5">
-        <v>0.1650396059692746</v>
+        <v>0.1264749804101626</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C6" s="2">
         <v>46283</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C7" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.924936610197405</v>
+        <v>1.061797745320032</v>
       </c>
       <c r="H7">
-        <v>1.477201411955408</v>
+        <v>1.479265335849058</v>
       </c>
       <c r="I7">
-        <v>0.3693898933233874</v>
+        <v>0.3702292902507237</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>240</v>
       </c>
       <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0.002880202844561708</v>
+      </c>
+      <c r="O7">
+        <v>0.6623875125069998</v>
+      </c>
+      <c r="P7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0.06516524549527072</v>
-      </c>
       <c r="Q7">
-        <v>0.9894118781318006</v>
+        <v>1.061797745320032</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>-0.5561168204200569</v>
+        <v>-0.5731410801839203</v>
       </c>
       <c r="U7">
-        <v>0.6502308918462194</v>
+        <v>0.6579014605262827</v>
       </c>
       <c r="V7" t="s">
         <v>57</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9991597310797949</v>
+        <v>0.9997085450990938</v>
       </c>
       <c r="Y7">
-        <v>0.999913290628775</v>
+        <v>0.9999518977740743</v>
       </c>
       <c r="Z7">
-        <v>0.0007535595489800428</v>
+        <v>0.0002433526749805459</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-104.8606887688172</v>
+        <v>-106.558696098558</v>
       </c>
       <c r="AC7">
-        <v>-7.999999999999998</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD7">
-        <v>-0.2564696919894996</v>
+        <v>-0.2849974489580183</v>
       </c>
       <c r="AE7">
-        <v>-0.9665522733359077</v>
+        <v>-0.9585282750589165</v>
       </c>
       <c r="AF7">
-        <v>2.520267106113173</v>
+        <v>2.644216320757104</v>
       </c>
       <c r="AG7">
-        <v>2.520048575337083</v>
+        <v>2.644089128066246</v>
       </c>
       <c r="AH7" t="s">
         <v>57</v>
@@ -1589,28 +1589,28 @@
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>-0.256447453663769</v>
+        <v>-0.2849837399463402</v>
       </c>
       <c r="AM7">
-        <v>0.7577298228538096</v>
+        <v>0.7703955525319746</v>
       </c>
       <c r="AN7">
-        <v>-0.6151802809032</v>
+        <v>-0.7312207942320805</v>
       </c>
       <c r="AO7">
-        <v>-2.441849635587668</v>
+        <v>-2.54029940353815</v>
       </c>
       <c r="AP7">
-        <v>-1.80377892824894</v>
+        <v>-1.646490000985853</v>
       </c>
       <c r="AQ7">
-        <v>-1.023166154625297</v>
+        <v>0.4093169905058616</v>
       </c>
       <c r="AR7">
-        <v>1.822018625129852</v>
+        <v>1.531132693320519</v>
       </c>
       <c r="AS7">
-        <v>0.1278715764207432</v>
+        <v>0.1005789758423803</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C8" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.219972358040653</v>
+        <v>2.204458390183103</v>
       </c>
       <c r="H8">
-        <v>1.442633975126879</v>
+        <v>1.444885106128493</v>
       </c>
       <c r="I8">
-        <v>0.358427533503214</v>
+        <v>0.3594763537499774</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N8">
-        <v>-0.02581088272300217</v>
+        <v>-0.03171816718976128</v>
       </c>
       <c r="O8">
-        <v>-6.894063877173174</v>
+        <v>-8.485655277214963</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.219972358040653</v>
+        <v>2.204458390183103</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.8080428531121724</v>
+        <v>0.8401908892389828</v>
       </c>
       <c r="U8">
-        <v>0.913616507569292</v>
+        <v>0.9280799837310828</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9994384568176362</v>
+        <v>0.9986291358859761</v>
       </c>
       <c r="Y8">
-        <v>0.9999888946752581</v>
+        <v>0.9999763342941623</v>
       </c>
       <c r="Z8">
-        <v>0.0005504378576218771</v>
+        <v>0.001347198408186201</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>51.96930300464032</v>
+        <v>47.12681191947653</v>
       </c>
       <c r="AC8">
-        <v>-6.999999999999997</v>
+        <v>-11</v>
       </c>
       <c r="AD8">
-        <v>0.6160835744542178</v>
+        <v>0.6803779963930544</v>
       </c>
       <c r="AE8">
-        <v>0.7876807914934287</v>
+        <v>0.7328613661697366</v>
       </c>
       <c r="AF8">
-        <v>2.567296796592367</v>
+        <v>2.412287844146139</v>
       </c>
       <c r="AG8">
-        <v>2.567268285927732</v>
+        <v>2.412230755651624</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.6160767326460553</v>
+        <v>0.6803618947675334</v>
       </c>
       <c r="AM8">
-        <v>0.8753104062886309</v>
+        <v>0.8959369865154437</v>
       </c>
       <c r="AN8">
-        <v>1.556851134476295</v>
+        <v>1.60140670467573</v>
       </c>
       <c r="AO8">
-        <v>2.039565441109928</v>
+        <v>1.799634869832472</v>
       </c>
       <c r="AP8">
-        <v>3.338512226818299</v>
+        <v>3.088340235516783</v>
       </c>
       <c r="AQ8">
-        <v>-1.112094145329638</v>
+        <v>-2.258449850764255</v>
       </c>
       <c r="AR8">
-        <v>3.157360108686769</v>
+        <v>2.806959672095708</v>
       </c>
       <c r="AS8">
-        <v>0.06340519455983201</v>
+        <v>0.05445419603619626</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C9" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.7348033142862079</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>3.387701679821335</v>
+        <v>3.810434383610249</v>
       </c>
       <c r="H9">
-        <v>3.079102139160119</v>
+        <v>3.08861352250222</v>
       </c>
       <c r="I9">
-        <v>0.6571447715705065</v>
+        <v>0.6599208872269491</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N9">
-        <v>0.736848348978105</v>
+        <v>0.7555566622281711</v>
       </c>
       <c r="O9">
-        <v>101.7244540547648</v>
+        <v>113.8192636917698</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.387701679821335</v>
+        <v>3.810434383610249</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9942167738971054</v>
+        <v>-0.9994010773607538</v>
       </c>
       <c r="U9">
-        <v>0.9575949453430195</v>
+        <v>0.9997053321694902</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.999475908596434</v>
+        <v>0.99880060076487</v>
       </c>
       <c r="Y9">
-        <v>0.9999075997855635</v>
+        <v>0.9998993894286041</v>
       </c>
       <c r="Z9">
-        <v>0.0004316911891295572</v>
+        <v>0.00109878866373414</v>
       </c>
       <c r="AA9">
-        <v>0.9405409251419504</v>
+        <v>1</v>
       </c>
       <c r="AB9">
-        <v>171.3857006022782</v>
+        <v>177.1952621162782</v>
       </c>
       <c r="AC9">
-        <v>6.000000000000009</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>-0.9887190304839409</v>
+        <v>-0.9988020944574952</v>
       </c>
       <c r="AE9">
-        <v>0.149782104267819</v>
+        <v>0.0489323625765286</v>
       </c>
       <c r="AF9">
-        <v>2.586231422806371</v>
+        <v>2.862708315683091</v>
       </c>
       <c r="AG9">
-        <v>2.585992454468321</v>
+        <v>2.86242029696371</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9592362292365794</v>
+        <v>-0.9987016044080604</v>
       </c>
       <c r="AM9">
-        <v>0.9794401315396966</v>
+        <v>0.9941049421684818</v>
       </c>
       <c r="AN9">
-        <v>-2.551143661676161</v>
+        <v>-2.852760448391738</v>
       </c>
       <c r="AO9">
-        <v>0.4162330582870611</v>
+        <v>0.1928992565970481</v>
       </c>
       <c r="AP9">
-        <v>-4.312108478118331</v>
+        <v>-4.923376570422746</v>
       </c>
       <c r="AQ9">
-        <v>3.358595373306814</v>
+        <v>3.583576937470743</v>
       </c>
       <c r="AR9">
-        <v>4.024164510598976</v>
+        <v>4.603722682386502</v>
       </c>
       <c r="AS9">
-        <v>0.03500948372548682</v>
+        <v>0.03666981645852199</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C10" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.326215123079677</v>
+        <v>1.129510121686975</v>
       </c>
       <c r="H10">
-        <v>2.086782904086717</v>
+        <v>2.09202999861242</v>
       </c>
       <c r="I10">
-        <v>0.4517473824866979</v>
+        <v>0.4515199270056686</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10">
-        <v>39.17135216588338</v>
+        <v>40.69593768772194</v>
       </c>
       <c r="O10">
-        <v>28.45573528032201</v>
+        <v>28.90996461388335</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.326215123079677</v>
+        <v>1.129510121686975</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.8738735230020797</v>
+        <v>-0.7604381919198788</v>
       </c>
       <c r="U10">
-        <v>0.7925867707208032</v>
+        <v>0.7418676067757343</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9641876238970215</v>
+        <v>0.9827698792456987</v>
       </c>
       <c r="Y10">
-        <v>0.9973747414794695</v>
+        <v>0.9986816816471552</v>
       </c>
       <c r="Z10">
-        <v>0.03318711758244797</v>
+        <v>0.01591180240145651</v>
       </c>
       <c r="AA10">
-        <v>0.3315673733474611</v>
+        <v>0.5832446989296391</v>
       </c>
       <c r="AB10">
-        <v>136.2972034583038</v>
+        <v>122.5722102741784</v>
       </c>
       <c r="AC10">
-        <v>-53</v>
+        <v>-37</v>
       </c>
       <c r="AD10">
-        <v>-0.7229334238653541</v>
+        <v>-0.538362113524273</v>
       </c>
       <c r="AE10">
-        <v>0.6909176974563007</v>
+        <v>0.8427136137037765</v>
       </c>
       <c r="AF10">
-        <v>1.579094487018609</v>
+        <v>1.771370320416987</v>
       </c>
       <c r="AG10">
-        <v>1.57494895576184</v>
+        <v>1.769035090413897</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.4800536978699176</v>
+        <v>-0.4256176409392974</v>
       </c>
       <c r="AM10">
-        <v>0.7770164922437377</v>
+        <v>0.7710242745176157</v>
       </c>
       <c r="AN10">
-        <v>-1.179377254172649</v>
+        <v>-1.012783771105633</v>
       </c>
       <c r="AO10">
-        <v>0.9629161850976939</v>
+        <v>1.41591866015502</v>
       </c>
       <c r="AP10">
-        <v>-0.9306409438947538</v>
+        <v>-0.7463860614320315</v>
       </c>
       <c r="AQ10">
-        <v>4.69785617985081</v>
+        <v>3.819793183395782</v>
       </c>
       <c r="AR10">
-        <v>0.8121045632290568</v>
+        <v>0.6643473352406452</v>
       </c>
       <c r="AS10">
-        <v>0.03505446068783412</v>
+        <v>0.04447925268065549</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C11" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.04969460202241648</v>
+        <v>0.1315860881573243</v>
       </c>
       <c r="H11">
-        <v>2.318175294854195</v>
+        <v>2.300199799121176</v>
       </c>
       <c r="I11">
-        <v>0.5432049885695118</v>
+        <v>0.5374577966827665</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>212</v>
       </c>
       <c r="M11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N11">
-        <v>-2269.994565806371</v>
+        <v>-2279.910090518671</v>
       </c>
       <c r="O11">
-        <v>-32.29929661079068</v>
+        <v>-35.6709706722783</v>
       </c>
       <c r="P11">
-        <v>0.5595016330430923</v>
+        <v>0.2843215795379294</v>
       </c>
       <c r="Q11">
-        <v>0.1128144977374636</v>
+        <v>0.1838620313189925</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2095,82 +2095,82 @@
         <v>63</v>
       </c>
       <c r="T11">
-        <v>0.7023511159933751</v>
+        <v>0.8263005543277491</v>
       </c>
       <c r="U11">
-        <v>0.7158272077718091</v>
+        <v>0.7633635218447925</v>
       </c>
       <c r="V11" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9987294164417612</v>
+        <v>0.9555700489337118</v>
       </c>
       <c r="Y11">
-        <v>0.9990768222991612</v>
+        <v>0.9661130895892217</v>
       </c>
       <c r="Z11">
-        <v>0.0003474058574000072</v>
+        <v>0.01054304065550993</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-82.65846887999095</v>
+        <v>-61.34341222524586</v>
       </c>
       <c r="AC11">
-        <v>-7.999999999999998</v>
+        <v>56</v>
       </c>
       <c r="AD11">
-        <v>0.1277835545917157</v>
+        <v>0.4795587580597446</v>
       </c>
       <c r="AE11">
-        <v>-0.9918020786305632</v>
+        <v>-0.8775097706397321</v>
       </c>
       <c r="AF11">
-        <v>0.847692861307589</v>
+        <v>0.6538063630104698</v>
       </c>
       <c r="AG11">
-        <v>0.8469102901608696</v>
+        <v>0.6316508853611372</v>
       </c>
       <c r="AH11" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL11">
-        <v>0.06383279383179137</v>
+        <v>0.231653996694335</v>
       </c>
       <c r="AM11">
-        <v>0.5135323923098526</v>
+        <v>0.6198718889289074</v>
       </c>
       <c r="AN11">
-        <v>0.1318101331374104</v>
+        <v>0.1653357313260205</v>
       </c>
       <c r="AO11">
-        <v>-0.836292051867517</v>
+        <v>-0.6024835080623392</v>
       </c>
       <c r="AP11">
-        <v>-0.08946860949674705</v>
+        <v>0.08968126878286138</v>
       </c>
       <c r="AQ11">
-        <v>-0.05403530635355595</v>
+        <v>0.09596656650477405</v>
       </c>
       <c r="AR11">
-        <v>0.1139465447500654</v>
+        <v>0.1290642195994172</v>
       </c>
       <c r="AS11">
-        <v>0.1631970791491234</v>
+        <v>0.08090213230162374</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -781,10 +781,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C2" s="2">
         <v>46286</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46283</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -796,37 +796,37 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.08554759762750143</v>
+        <v>0.1526537623190971</v>
       </c>
       <c r="H2">
-        <v>1.079088604348566</v>
+        <v>1.079616760624747</v>
       </c>
       <c r="I2">
-        <v>0.2589482565137322</v>
+        <v>0.2590612061110446</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L2">
         <v>149</v>
       </c>
       <c r="M2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2">
-        <v>-0.5333555537414959</v>
+        <v>-0.5317589157285457</v>
       </c>
       <c r="O2">
-        <v>-14.48857665828617</v>
+        <v>-14.5815783374785</v>
       </c>
       <c r="P2">
-        <v>0.2587742305873376</v>
+        <v>0.2246474935261928</v>
       </c>
       <c r="Q2">
-        <v>0.1154136852194011</v>
+        <v>0.1968830448660632</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -835,10 +835,10 @@
         <v>63</v>
       </c>
       <c r="T2">
-        <v>0.3142695571397605</v>
+        <v>0.2186794537827037</v>
       </c>
       <c r="U2">
-        <v>0.4663733985142371</v>
+        <v>0.3733611123269195</v>
       </c>
       <c r="V2" t="s">
         <v>68</v>
@@ -847,34 +847,34 @@
         <v>68</v>
       </c>
       <c r="X2">
-        <v>0.9968562986243207</v>
+        <v>0.9969099425123716</v>
       </c>
       <c r="Y2">
-        <v>0.9998083912053797</v>
+        <v>0.9998214324988115</v>
       </c>
       <c r="Z2">
-        <v>0.002952092581058996</v>
+        <v>0.002911489986439864</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>0.9400710092179918</v>
       </c>
       <c r="AB2">
-        <v>-92.13388134388816</v>
+        <v>-96.31315585318613</v>
       </c>
       <c r="AC2">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="AD2">
-        <v>-0.03723464612280344</v>
+        <v>-0.1099625345074773</v>
       </c>
       <c r="AE2">
-        <v>-0.9993065501276921</v>
+        <v>-0.993935732834217</v>
       </c>
       <c r="AF2">
-        <v>1.276957825287862</v>
+        <v>1.173294231587521</v>
       </c>
       <c r="AG2">
-        <v>1.276713148938177</v>
+        <v>1.173084719368428</v>
       </c>
       <c r="AH2" t="s">
         <v>70</v>
@@ -889,28 +889,28 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>-0.03722751163714174</v>
+        <v>-0.1066485152889248</v>
       </c>
       <c r="AM2">
-        <v>0.6615956465052489</v>
+        <v>0.6844906202511921</v>
       </c>
       <c r="AN2">
-        <v>-0.00491775251390192</v>
+        <v>-0.08259994564590215</v>
       </c>
       <c r="AO2">
-        <v>-1.272933951822895</v>
+        <v>-1.166748508274195</v>
       </c>
       <c r="AP2">
-        <v>-0.51507400972078</v>
+        <v>-0.5497611236473408</v>
       </c>
       <c r="AQ2">
-        <v>-0.6963759476103385</v>
+        <v>-0.3231161013929401</v>
       </c>
       <c r="AR2">
-        <v>0.522262883478808</v>
+        <v>0.5269346290651268</v>
       </c>
       <c r="AS2">
-        <v>0.3300512283564994</v>
+        <v>0.2429989554615568</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C3" s="2">
         <v>46286</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46283</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.6714888821016466</v>
+        <v>0.4181638738972803</v>
       </c>
       <c r="H3">
-        <v>2.036038474712256</v>
+        <v>2.043149196778707</v>
       </c>
       <c r="I3">
-        <v>0.4513666636251979</v>
+        <v>0.4524779691394357</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>225</v>
       </c>
       <c r="M3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3">
-        <v>-0.1434528520964091</v>
+        <v>-0.1452732506889644</v>
       </c>
       <c r="O3">
-        <v>-51.25931417431683</v>
+        <v>-51.67896098705403</v>
       </c>
       <c r="P3">
-        <v>0.1564557820823254</v>
+        <v>0.2991629577577173</v>
       </c>
       <c r="Q3">
-        <v>0.7960328194285368</v>
+        <v>0.59666348764813</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -975,10 +975,10 @@
         <v>63</v>
       </c>
       <c r="T3">
-        <v>0.5721566250061204</v>
+        <v>0.5558378967449604</v>
       </c>
       <c r="U3">
-        <v>0.6574023218762785</v>
+        <v>0.6500641347383993</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -987,34 +987,34 @@
         <v>69</v>
       </c>
       <c r="X3">
-        <v>0.998485614933011</v>
+        <v>0.9990959954248881</v>
       </c>
       <c r="Y3">
-        <v>0.9997273624940969</v>
+        <v>0.9997483248126688</v>
       </c>
       <c r="Z3">
-        <v>0.00124174756108586</v>
+        <v>0.0006523293877807035</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-73.54372225878554</v>
+        <v>-75.16993758728142</v>
       </c>
       <c r="AC3">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="AD3">
-        <v>0.2832835892612633</v>
+        <v>0.2559530034611136</v>
       </c>
       <c r="AE3">
-        <v>-0.9590361870415818</v>
+        <v>-0.9666892261834903</v>
       </c>
       <c r="AF3">
-        <v>2.399897479370515</v>
+        <v>2.036875992672758</v>
       </c>
       <c r="AG3">
-        <v>2.399243177307317</v>
+        <v>2.036363361525732</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1029,28 +1029,28 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>0.2832063555300239</v>
+        <v>0.2558885864410196</v>
       </c>
       <c r="AM3">
-        <v>0.7731312137537724</v>
+        <v>0.7628201312597849</v>
       </c>
       <c r="AN3">
-        <v>0.7340186446384928</v>
+        <v>0.5644088449907517</v>
       </c>
       <c r="AO3">
-        <v>-2.281072888774191</v>
+        <v>-1.955200417359916</v>
       </c>
       <c r="AP3">
-        <v>0.405411182059805</v>
+        <v>0.238370532503597</v>
       </c>
       <c r="AQ3">
-        <v>-2.033462601656284</v>
+        <v>-1.590173488013066</v>
       </c>
       <c r="AR3">
-        <v>0.3800632544046766</v>
+        <v>0.2705967320131298</v>
       </c>
       <c r="AS3">
-        <v>0.07838959931693661</v>
+        <v>0.09251788975322217</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,10 +1061,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C4" s="2">
         <v>46286</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46283</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -1073,16 +1073,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.07896167182858867</v>
+        <v>0.3438626324877645</v>
       </c>
       <c r="G4">
-        <v>1.664419904478783</v>
+        <v>1.926125894897982</v>
       </c>
       <c r="H4">
-        <v>2.080153933606207</v>
+        <v>2.080254974000914</v>
       </c>
       <c r="I4">
-        <v>0.4937009309021533</v>
+        <v>0.4935688412027747</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1094,19 +1094,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>0.07057724691827695</v>
+        <v>0.1072367568082447</v>
       </c>
       <c r="O4">
-        <v>2.388978377311101</v>
+        <v>3.638668432659754</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.664419904478783</v>
+        <v>1.926125894897982</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1115,10 +1115,10 @@
         <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.684818444315218</v>
+        <v>-0.7355337437864559</v>
       </c>
       <c r="U4">
-        <v>0.7200068284780117</v>
+        <v>0.7825647886622367</v>
       </c>
       <c r="V4" t="s">
         <v>57</v>
@@ -1127,34 +1127,34 @@
         <v>69</v>
       </c>
       <c r="X4">
-        <v>0.9992701306473631</v>
+        <v>0.9989758169455758</v>
       </c>
       <c r="Y4">
-        <v>0.9999771110475011</v>
+        <v>0.9999808363406676</v>
       </c>
       <c r="Z4">
-        <v>0.0007069804001379465</v>
+        <v>0.001005019395091789</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-117.644066305188</v>
+        <v>-121.8339645075535</v>
       </c>
       <c r="AC4">
-        <v>-7.999999999999998</v>
+        <v>-10</v>
       </c>
       <c r="AD4">
-        <v>-0.4639774790755453</v>
+        <v>-0.5274595128822603</v>
       </c>
       <c r="AE4">
-        <v>-0.8858469952032925</v>
+        <v>-0.8495801682419433</v>
       </c>
       <c r="AF4">
-        <v>2.514472440617667</v>
+        <v>2.638212355389538</v>
       </c>
       <c r="AG4">
-        <v>2.514414886977414</v>
+        <v>2.638161797586712</v>
       </c>
       <c r="AH4" t="s">
         <v>57</v>
@@ -1169,28 +1169,28 @@
         <v>82</v>
       </c>
       <c r="AL4">
-        <v>-0.4639668591170661</v>
+        <v>-0.5274494048278439</v>
       </c>
       <c r="AM4">
-        <v>0.8278743507134645</v>
+        <v>0.8480274956895379</v>
       </c>
       <c r="AN4">
-        <v>-1.13585558544477</v>
+        <v>-1.349191485165129</v>
       </c>
       <c r="AO4">
-        <v>-2.241244700868494</v>
+        <v>-2.263978158998908</v>
       </c>
       <c r="AP4">
-        <v>-2.638569280296996</v>
+        <v>-2.903115257756255</v>
       </c>
       <c r="AQ4">
-        <v>0.412048627952475</v>
+        <v>0.9980947323278444</v>
       </c>
       <c r="AR4">
-        <v>2.52065545207872</v>
+        <v>2.731178806381457</v>
       </c>
       <c r="AS4">
-        <v>0.0754058791721629</v>
+        <v>0.06802433929582494</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C5" s="2">
         <v>46286</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46283</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1.000167377653249</v>
+        <v>1.16554786331072</v>
       </c>
       <c r="H5">
-        <v>1.518951827639467</v>
+        <v>1.520678401954014</v>
       </c>
       <c r="I5">
-        <v>0.348257771719839</v>
+        <v>0.3491269889852451</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,19 +1234,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>0.002489337482335389</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.6902500446166696</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.000167377653249</v>
+        <v>1.16554786331072</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1255,10 +1255,10 @@
         <v>64</v>
       </c>
       <c r="T5">
-        <v>-0.5386034294224616</v>
+        <v>-0.58775016694939</v>
       </c>
       <c r="U5">
-        <v>0.6423493220989157</v>
+        <v>0.6644663500040134</v>
       </c>
       <c r="V5" t="s">
         <v>57</v>
@@ -1267,34 +1267,34 @@
         <v>69</v>
       </c>
       <c r="X5">
-        <v>0.9987268036452234</v>
+        <v>0.9984729621537499</v>
       </c>
       <c r="Y5">
-        <v>0.9999111154352319</v>
+        <v>0.9999150995071521</v>
       </c>
       <c r="Z5">
-        <v>0.001184311790008552</v>
+        <v>0.001442137353402151</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-103.1283415028481</v>
+        <v>-108.0265642236214</v>
       </c>
       <c r="AC5">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="AD5">
-        <v>-0.2271330593743433</v>
+        <v>-0.3094579024898199</v>
       </c>
       <c r="AE5">
-        <v>-0.9738637344820121</v>
+        <v>-0.9509131435554991</v>
       </c>
       <c r="AF5">
-        <v>3.002443979585842</v>
+        <v>2.744301968280822</v>
       </c>
       <c r="AG5">
-        <v>3.002177108659476</v>
+        <v>2.744068975691192</v>
       </c>
       <c r="AH5" t="s">
         <v>57</v>
@@ -1309,28 +1309,28 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>-0.2271128707512164</v>
+        <v>-0.3094316293613829</v>
       </c>
       <c r="AM5">
-        <v>0.7491375611531098</v>
+        <v>0.7781174576414135</v>
       </c>
       <c r="AN5">
-        <v>-0.622650177525401</v>
+        <v>-0.7843640309727368</v>
       </c>
       <c r="AO5">
-        <v>-2.933263767620166</v>
+        <v>-2.625449121050811</v>
       </c>
       <c r="AP5">
-        <v>-1.853504669552984</v>
+        <v>-1.904919545246617</v>
       </c>
       <c r="AQ5">
-        <v>-0.2526973252355096</v>
+        <v>0.516566091981597</v>
       </c>
       <c r="AR5">
-        <v>1.770934123438676</v>
+        <v>1.764158597753124</v>
       </c>
       <c r="AS5">
-        <v>0.1264749804101626</v>
+        <v>0.09793465288690467</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C6" s="2">
         <v>46286</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46283</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -1353,16 +1353,16 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>0.7961295937276529</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1.099162256042905</v>
+        <v>1.284619702940228</v>
       </c>
       <c r="H6">
-        <v>0.947191304232047</v>
+        <v>0.9509634698023387</v>
       </c>
       <c r="I6">
-        <v>0.2565953471550433</v>
+        <v>0.2568013710638661</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,19 +1374,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>0.1325969633483026</v>
+        <v>0.179037581131401</v>
       </c>
       <c r="O6">
-        <v>2.417761769830995</v>
+        <v>3.334432342046298</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.099162256042905</v>
+        <v>1.284619702940228</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1395,10 +1395,10 @@
         <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.7634159909761071</v>
+        <v>-0.7787999376878065</v>
       </c>
       <c r="U6">
-        <v>0.8629527559013159</v>
+        <v>0.9004588682205338</v>
       </c>
       <c r="V6" t="s">
         <v>57</v>
@@ -1407,34 +1407,34 @@
         <v>69</v>
       </c>
       <c r="X6">
-        <v>0.9999260044652175</v>
+        <v>0.9999395331854015</v>
       </c>
       <c r="Y6">
-        <v>0.9999844836116794</v>
+        <v>0.9999955850440831</v>
       </c>
       <c r="Z6">
-        <v>5.847914646184282E-05</v>
+        <v>5.605185868162721E-05</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-122.8542676783943</v>
+        <v>-123.8899077017919</v>
       </c>
       <c r="AC6">
         <v>-2.000000000000003</v>
       </c>
       <c r="AD6">
-        <v>-0.5425041095597809</v>
+        <v>-0.5575988987827774</v>
       </c>
       <c r="AE6">
-        <v>-0.8400531477893224</v>
+        <v>-0.8301105155798437</v>
       </c>
       <c r="AF6">
-        <v>1.450192373498942</v>
+        <v>1.677508289183937</v>
       </c>
       <c r="AG6">
-        <v>1.450169871750935</v>
+        <v>1.67750088305879</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -1449,28 +1449,28 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>-0.5424956918553514</v>
+        <v>-0.5575964370082199</v>
       </c>
       <c r="AM6">
-        <v>0.8527255077304319</v>
+        <v>0.8579998559087119</v>
       </c>
       <c r="AN6">
-        <v>-0.782626422887848</v>
+        <v>-0.9304608564918229</v>
       </c>
       <c r="AO6">
-        <v>-1.2207549222003</v>
+        <v>-1.395684904895981</v>
       </c>
       <c r="AP6">
-        <v>-1.592488924166868</v>
+        <v>-1.794984205749615</v>
       </c>
       <c r="AQ6">
-        <v>0.5709083704187535</v>
+        <v>0.9515974066848344</v>
       </c>
       <c r="AR6">
-        <v>1.502624010295105</v>
+        <v>1.667567034891542</v>
       </c>
       <c r="AS6">
-        <v>0.06680196267726835</v>
+        <v>0.06185512327700235</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,10 +1481,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C7" s="2">
         <v>46286</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46283</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -1493,16 +1493,16 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.1910502009538229</v>
       </c>
       <c r="G7">
-        <v>1.061797745320032</v>
+        <v>1.251921697359182</v>
       </c>
       <c r="H7">
-        <v>1.479265335849058</v>
+        <v>1.481132695562362</v>
       </c>
       <c r="I7">
-        <v>0.3702292902507237</v>
+        <v>0.3709518486673632</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>0.002880202844561708</v>
+        <v>0.006457383772562279</v>
       </c>
       <c r="O7">
-        <v>0.6623875125069998</v>
+        <v>1.465327381730629</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.061797745320032</v>
+        <v>1.251921697359182</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1535,10 +1535,10 @@
         <v>64</v>
       </c>
       <c r="T7">
-        <v>-0.5731410801839203</v>
+        <v>-0.6225277707030407</v>
       </c>
       <c r="U7">
-        <v>0.6579014605262827</v>
+        <v>0.7087856933245674</v>
       </c>
       <c r="V7" t="s">
         <v>57</v>
@@ -1547,34 +1547,34 @@
         <v>69</v>
       </c>
       <c r="X7">
-        <v>0.9997085450990938</v>
+        <v>0.9997436562537549</v>
       </c>
       <c r="Y7">
-        <v>0.9999518977740743</v>
+        <v>0.9999626654605028</v>
       </c>
       <c r="Z7">
-        <v>0.0002433526749805459</v>
+        <v>0.0002190092067478888</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-106.558696098558</v>
+        <v>-110.1382093721169</v>
       </c>
       <c r="AC7">
         <v>-4.999999999999995</v>
       </c>
       <c r="AD7">
-        <v>-0.2849974489580183</v>
+        <v>-0.3442858806847173</v>
       </c>
       <c r="AE7">
-        <v>-0.9585282750589165</v>
+        <v>-0.9388648637376673</v>
       </c>
       <c r="AF7">
-        <v>2.644216320757104</v>
+        <v>2.690343039808895</v>
       </c>
       <c r="AG7">
-        <v>2.644089128066246</v>
+        <v>2.690242597090414</v>
       </c>
       <c r="AH7" t="s">
         <v>57</v>
@@ -1589,28 +1589,28 @@
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>-0.2849837399463402</v>
+        <v>-0.3442730269299066</v>
       </c>
       <c r="AM7">
-        <v>0.7703955525319746</v>
+        <v>0.7910621921093854</v>
       </c>
       <c r="AN7">
-        <v>-0.7312207942320805</v>
+        <v>-0.9019855763860494</v>
       </c>
       <c r="AO7">
-        <v>-2.54029940353815</v>
+        <v>-2.533901608832344</v>
       </c>
       <c r="AP7">
-        <v>-1.646490000985853</v>
+        <v>-1.772215587384921</v>
       </c>
       <c r="AQ7">
-        <v>0.4093169905058616</v>
+        <v>1.10061735100406</v>
       </c>
       <c r="AR7">
-        <v>1.531132693320519</v>
+        <v>1.599572967380154</v>
       </c>
       <c r="AS7">
-        <v>0.1005789758423803</v>
+        <v>0.08140336671470533</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,10 +1621,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C8" s="2">
         <v>46286</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46283</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1636,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.204458390183103</v>
+        <v>2.05651322737015</v>
       </c>
       <c r="H8">
-        <v>1.444885106128493</v>
+        <v>1.449316163320201</v>
       </c>
       <c r="I8">
-        <v>0.3594763537499774</v>
+        <v>0.3607095589230885</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,19 +1654,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N8">
-        <v>-0.03171816718976128</v>
+        <v>-0.03754752240651413</v>
       </c>
       <c r="O8">
-        <v>-8.485655277214963</v>
+        <v>-10.28497972395226</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.204458390183103</v>
+        <v>2.05651322737015</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1675,10 +1675,10 @@
         <v>65</v>
       </c>
       <c r="T8">
-        <v>0.8401908892389828</v>
+        <v>0.8988917203478006</v>
       </c>
       <c r="U8">
-        <v>0.9280799837310828</v>
+        <v>0.9544023477634401</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
@@ -1687,34 +1687,34 @@
         <v>69</v>
       </c>
       <c r="X8">
-        <v>0.9986291358859761</v>
+        <v>0.9943957645662223</v>
       </c>
       <c r="Y8">
-        <v>0.9999763342941623</v>
+        <v>0.9996042944277196</v>
       </c>
       <c r="Z8">
-        <v>0.001347198408186201</v>
+        <v>0.005208529861497335</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>47.12681191947653</v>
+        <v>37.08484846736302</v>
       </c>
       <c r="AC8">
-        <v>-11</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.6803779963930544</v>
+        <v>0.7977434157478444</v>
       </c>
       <c r="AE8">
-        <v>0.7328613661697366</v>
+        <v>0.6029970502672148</v>
       </c>
       <c r="AF8">
-        <v>2.412287844146139</v>
+        <v>2.039438594875659</v>
       </c>
       <c r="AG8">
-        <v>2.412230755651624</v>
+        <v>2.038631577659344</v>
       </c>
       <c r="AH8" t="s">
         <v>56</v>
@@ -1729,28 +1729,28 @@
         <v>83</v>
       </c>
       <c r="AL8">
-        <v>0.6803618947675334</v>
+        <v>0.7974277442329829</v>
       </c>
       <c r="AM8">
-        <v>0.8959369865154437</v>
+        <v>0.9327697977437558</v>
       </c>
       <c r="AN8">
-        <v>1.60140670467573</v>
+        <v>1.553909865259229</v>
       </c>
       <c r="AO8">
-        <v>1.799634869832472</v>
+        <v>1.303144291215953</v>
       </c>
       <c r="AP8">
-        <v>3.088340235516783</v>
+        <v>2.634002089849427</v>
       </c>
       <c r="AQ8">
-        <v>-2.258449850764255</v>
+        <v>-3.278751439118282</v>
       </c>
       <c r="AR8">
-        <v>2.806959672095708</v>
+        <v>2.277861118416645</v>
       </c>
       <c r="AS8">
-        <v>0.05445419603619626</v>
+        <v>0.04276486686866134</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,10 +1761,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C9" s="2">
         <v>46286</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46283</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -1773,16 +1773,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.8246640972210072</v>
       </c>
       <c r="G9">
-        <v>3.810434383610249</v>
+        <v>3.528177455506283</v>
       </c>
       <c r="H9">
-        <v>3.08861352250222</v>
+        <v>3.09796169046018</v>
       </c>
       <c r="I9">
-        <v>0.6599208872269491</v>
+        <v>0.6625551897000239</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,19 +1794,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N9">
-        <v>0.7555566622281711</v>
+        <v>0.7744388995905783</v>
       </c>
       <c r="O9">
-        <v>113.8192636917698</v>
+        <v>109.0594436882606</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.810434383610249</v>
+        <v>3.528177455506283</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
@@ -1815,10 +1815,10 @@
         <v>66</v>
       </c>
       <c r="T9">
-        <v>-0.9994010773607538</v>
+        <v>-0.998965934647524</v>
       </c>
       <c r="U9">
-        <v>0.9997053321694902</v>
+        <v>0.9731981751687198</v>
       </c>
       <c r="V9" t="s">
         <v>57</v>
@@ -1827,34 +1827,34 @@
         <v>69</v>
       </c>
       <c r="X9">
-        <v>0.99880060076487</v>
+        <v>0.9981177889678176</v>
       </c>
       <c r="Y9">
-        <v>0.9998993894286041</v>
+        <v>0.9998555599767319</v>
       </c>
       <c r="Z9">
-        <v>0.00109878866373414</v>
+        <v>0.001737771008914368</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>0.9928258762532932</v>
       </c>
       <c r="AB9">
-        <v>177.1952621162782</v>
+        <v>-176.3631016843742</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AD9">
-        <v>-0.9988020944574952</v>
+        <v>-0.9979860845618934</v>
       </c>
       <c r="AE9">
-        <v>0.0489323625765286</v>
+        <v>-0.06343323277920872</v>
       </c>
       <c r="AF9">
-        <v>2.862708315683091</v>
+        <v>2.65839845364152</v>
       </c>
       <c r="AG9">
-        <v>2.86242029696371</v>
+        <v>2.65801447450702</v>
       </c>
       <c r="AH9" t="s">
         <v>57</v>
@@ -1869,28 +1869,28 @@
         <v>84</v>
       </c>
       <c r="AL9">
-        <v>-0.9987016044080604</v>
+        <v>-0.994262614666409</v>
       </c>
       <c r="AM9">
-        <v>0.9941049421684818</v>
+        <v>0.9925208284367179</v>
       </c>
       <c r="AN9">
-        <v>-2.852760448391738</v>
+        <v>-2.651323782891174</v>
       </c>
       <c r="AO9">
-        <v>0.1928992565970481</v>
+        <v>-0.1048145629032953</v>
       </c>
       <c r="AP9">
-        <v>-4.923376570422746</v>
+        <v>-4.52315797129816</v>
       </c>
       <c r="AQ9">
-        <v>3.583576937470743</v>
+        <v>3.65213557072818</v>
       </c>
       <c r="AR9">
-        <v>4.603722682386502</v>
+        <v>4.189749352804028</v>
       </c>
       <c r="AS9">
-        <v>0.03666981645852199</v>
+        <v>0.03593078782909975</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,10 +1901,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C10" s="2">
         <v>46286</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46283</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1.129510121686975</v>
+        <v>0.9655620847251117</v>
       </c>
       <c r="H10">
-        <v>2.09202999861242</v>
+        <v>2.096777369849961</v>
       </c>
       <c r="I10">
-        <v>0.4515199270056686</v>
+        <v>0.4510764324801304</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,19 +1934,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N10">
-        <v>40.69593768772194</v>
+        <v>42.02481681485907</v>
       </c>
       <c r="O10">
-        <v>28.90996461388335</v>
+        <v>29.86156251277891</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>1.129510121686975</v>
+        <v>0.9655620847251117</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
@@ -1955,10 +1955,10 @@
         <v>67</v>
       </c>
       <c r="T10">
-        <v>-0.7604381919198788</v>
+        <v>-0.7109343538734294</v>
       </c>
       <c r="U10">
-        <v>0.7418676067757343</v>
+        <v>0.7197202381217118</v>
       </c>
       <c r="V10" t="s">
         <v>57</v>
@@ -1967,34 +1967,34 @@
         <v>69</v>
       </c>
       <c r="X10">
-        <v>0.9827698792456987</v>
+        <v>0.9908280140512149</v>
       </c>
       <c r="Y10">
-        <v>0.9986816816471552</v>
+        <v>0.9991991155146743</v>
       </c>
       <c r="Z10">
-        <v>0.01591180240145651</v>
+        <v>0.008371101463459429</v>
       </c>
       <c r="AA10">
-        <v>0.5832446989296391</v>
+        <v>0.6144610582570272</v>
       </c>
       <c r="AB10">
-        <v>122.5722102741784</v>
+        <v>116.7666666385041</v>
       </c>
       <c r="AC10">
-        <v>-37</v>
+        <v>-28</v>
       </c>
       <c r="AD10">
-        <v>-0.538362113524273</v>
+        <v>-0.4503581785973821</v>
       </c>
       <c r="AE10">
-        <v>0.8427136137037765</v>
+        <v>0.8928479775249807</v>
       </c>
       <c r="AF10">
-        <v>1.771370320416987</v>
+        <v>1.800215641900121</v>
       </c>
       <c r="AG10">
-        <v>1.769035090413897</v>
+        <v>1.798773877122283</v>
       </c>
       <c r="AH10" t="s">
         <v>57</v>
@@ -2009,28 +2009,28 @@
         <v>85</v>
       </c>
       <c r="AL10">
-        <v>-0.4256176409392974</v>
+        <v>-0.3632517149615387</v>
       </c>
       <c r="AM10">
-        <v>0.7710242745176157</v>
+        <v>0.7497097212193088</v>
       </c>
       <c r="AN10">
-        <v>-1.012783771105633</v>
+        <v>-0.8754817607296135</v>
       </c>
       <c r="AO10">
-        <v>1.41591866015502</v>
+        <v>1.554069485227286</v>
       </c>
       <c r="AP10">
-        <v>-0.7463860614320315</v>
+        <v>-0.5886128695847785</v>
       </c>
       <c r="AQ10">
-        <v>3.819793183395782</v>
+        <v>3.189245913176564</v>
       </c>
       <c r="AR10">
-        <v>0.6643473352406452</v>
+        <v>0.5463548806730636</v>
       </c>
       <c r="AS10">
-        <v>0.04447925268065549</v>
+        <v>0.05339756294298168</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,10 +2041,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C11" s="2">
         <v>46286</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46283</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2056,37 +2056,37 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1315860881573243</v>
+        <v>0.01093802734210199</v>
       </c>
       <c r="H11">
-        <v>2.300199799121176</v>
+        <v>2.281221815650924</v>
       </c>
       <c r="I11">
-        <v>0.5374577966827665</v>
+        <v>0.5317631192489489</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L11">
         <v>212</v>
       </c>
       <c r="M11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11">
-        <v>-2279.910090518671</v>
+        <v>-2287.199610175742</v>
       </c>
       <c r="O11">
-        <v>-35.6709706722783</v>
+        <v>-35.79982395963997</v>
       </c>
       <c r="P11">
-        <v>0.2843215795379294</v>
+        <v>0.643534845564956</v>
       </c>
       <c r="Q11">
-        <v>0.1838620313189925</v>
+        <v>0.03068470285528328</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2095,10 +2095,10 @@
         <v>63</v>
       </c>
       <c r="T11">
-        <v>0.8263005543277491</v>
+        <v>0.8747428227636473</v>
       </c>
       <c r="U11">
-        <v>0.7633635218447925</v>
+        <v>0.7044609170831502</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2107,34 +2107,34 @@
         <v>69</v>
       </c>
       <c r="X11">
-        <v>0.9555700489337118</v>
+        <v>0.8032307277164809</v>
       </c>
       <c r="Y11">
-        <v>0.9661130895892217</v>
+        <v>0.8433065873580352</v>
       </c>
       <c r="Z11">
-        <v>0.01054304065550993</v>
+        <v>0.04007585964155436</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-61.34341222524586</v>
+        <v>-50.63457834155941</v>
       </c>
       <c r="AC11">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="AD11">
-        <v>0.4795587580597446</v>
+        <v>0.6342640483614705</v>
       </c>
       <c r="AE11">
-        <v>-0.8775097706397321</v>
+        <v>-0.7731164963678618</v>
       </c>
       <c r="AF11">
-        <v>0.6538063630104698</v>
+        <v>0.4287114648084668</v>
       </c>
       <c r="AG11">
-        <v>0.6316508853611372</v>
+        <v>0.3615352023488925</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2149,28 +2149,28 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>0.231653996694335</v>
+        <v>0.2674395250538018</v>
       </c>
       <c r="AM11">
-        <v>0.6198718889289074</v>
+        <v>0.6070657455659292</v>
       </c>
       <c r="AN11">
-        <v>0.1653357313260205</v>
+        <v>0.0627906675128186</v>
       </c>
       <c r="AO11">
-        <v>-0.6024835080623392</v>
+        <v>-0.3385811013406831</v>
       </c>
       <c r="AP11">
-        <v>0.08968126878286138</v>
+        <v>-0.1469459846318279</v>
       </c>
       <c r="AQ11">
-        <v>0.09596656650477405</v>
+        <v>-0.2679331550601287</v>
       </c>
       <c r="AR11">
-        <v>0.1290642195994172</v>
+        <v>0.151127139077636</v>
       </c>
       <c r="AS11">
-        <v>0.08090213230162374</v>
+        <v>0.189138496785495</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
   <si>
     <t>Pair</t>
   </si>
@@ -184,18 +184,18 @@
     <t>XAUUSD</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
-  </si>
-  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
@@ -205,12 +205,15 @@
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
+    <t>UP_REVERSAL_WATCH</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
@@ -220,33 +223,36 @@
     <t>空头减速</t>
   </si>
   <si>
+    <t>多头反转预警</t>
+  </si>
+  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>转换</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>下跌</t>
+    <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
@@ -256,15 +262,15 @@
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
+    <t>TURNING_DOWN</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
     <t>地形转换区</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
@@ -272,6 +278,9 @@
   </si>
   <si>
     <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>向下转折带</t>
   </si>
 </sst>
 </file>
@@ -781,136 +790,136 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C2" s="2">
         <v>46287</v>
       </c>
-      <c r="C2" s="2">
-        <v>46286</v>
-      </c>
       <c r="D2" t="s">
         <v>56</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.1526537623190971</v>
+        <v>0.2093737509907309</v>
       </c>
       <c r="H2">
-        <v>1.079616760624747</v>
+        <v>1.080094616303197</v>
       </c>
       <c r="I2">
-        <v>0.2590612061110446</v>
+        <v>0.2591860924200768</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>149</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2">
-        <v>-0.5317589157285457</v>
+        <v>-0.5278195790061191</v>
       </c>
       <c r="O2">
-        <v>-14.5815783374785</v>
+        <v>-14.84873727737504</v>
       </c>
       <c r="P2">
-        <v>0.2246474935261928</v>
+        <v>0.1457252795510106</v>
       </c>
       <c r="Q2">
-        <v>0.1968830448660632</v>
+        <v>0.2450894846574511</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2">
-        <v>0.2186794537827037</v>
+        <v>-0.5472059317582344</v>
       </c>
       <c r="U2">
-        <v>0.3733611123269195</v>
+        <v>0.6461936102511192</v>
       </c>
       <c r="V2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X2">
-        <v>0.9969099425123716</v>
+        <v>0.9968306442832696</v>
       </c>
       <c r="Y2">
-        <v>0.9998214324988115</v>
+        <v>0.999803763839655</v>
       </c>
       <c r="Z2">
-        <v>0.002911489986439864</v>
+        <v>0.002973119556385351</v>
       </c>
       <c r="AA2">
-        <v>0.9400710092179918</v>
+        <v>0.7115228263201009</v>
       </c>
       <c r="AB2">
-        <v>-96.31315585318613</v>
+        <v>-99.84364096212249</v>
       </c>
       <c r="AC2">
         <v>-18</v>
       </c>
       <c r="AD2">
-        <v>-0.1099625345074773</v>
+        <v>-0.1709600137076963</v>
       </c>
       <c r="AE2">
-        <v>-0.993935732834217</v>
+        <v>-0.985277967739594</v>
       </c>
       <c r="AF2">
-        <v>1.173294231587521</v>
+        <v>1.070682856807244</v>
       </c>
       <c r="AG2">
-        <v>1.173084719368428</v>
+        <v>1.070472750114476</v>
       </c>
       <c r="AH2" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AJ2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AL2">
-        <v>-0.1066485152889248</v>
+        <v>-0.146272273381216</v>
       </c>
       <c r="AM2">
-        <v>0.6844906202511921</v>
+        <v>0.6674818814331507</v>
       </c>
       <c r="AN2">
-        <v>-0.08259994564590215</v>
+        <v>-0.1369034983993388</v>
       </c>
       <c r="AO2">
-        <v>-1.166748508274195</v>
+        <v>-1.058472612049463</v>
       </c>
       <c r="AP2">
-        <v>-0.5497611236473408</v>
+        <v>-0.5346054176647519</v>
       </c>
       <c r="AQ2">
-        <v>-0.3231161013929401</v>
+        <v>0.0283605067527304</v>
       </c>
       <c r="AR2">
-        <v>0.5269346290651268</v>
+        <v>0.4856165403755571</v>
       </c>
       <c r="AS2">
-        <v>0.2429989554615568</v>
+        <v>0.173613368580384</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -921,13 +930,13 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C3" s="2">
         <v>46287</v>
       </c>
-      <c r="C3" s="2">
-        <v>46286</v>
-      </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -936,121 +945,121 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.4181638738972803</v>
+        <v>0.04694163332292873</v>
       </c>
       <c r="H3">
-        <v>2.043149196778707</v>
+        <v>2.049582707219781</v>
       </c>
       <c r="I3">
-        <v>0.4524779691394357</v>
+        <v>0.4536305434427991</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L3">
         <v>225</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N3">
-        <v>-0.1452732506889644</v>
+        <v>-0.1464096065507443</v>
       </c>
       <c r="O3">
-        <v>-51.67896098705403</v>
+        <v>-51.42334399674927</v>
       </c>
       <c r="P3">
-        <v>0.2991629577577173</v>
+        <v>0.6774098120205421</v>
       </c>
       <c r="Q3">
-        <v>0.59666348764813</v>
+        <v>0.1455147585763455</v>
       </c>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T3">
-        <v>0.5558378967449604</v>
+        <v>0.4129561684468722</v>
       </c>
       <c r="U3">
-        <v>0.6500641347383993</v>
+        <v>0.5357659834023484</v>
       </c>
       <c r="V3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="W3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="X3">
-        <v>0.9990959954248881</v>
+        <v>0.9976334296172309</v>
       </c>
       <c r="Y3">
-        <v>0.9997483248126688</v>
+        <v>0.9997428304050235</v>
       </c>
       <c r="Z3">
-        <v>0.0006523293877807035</v>
+        <v>0.002109400787792648</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-75.16993758728142</v>
+        <v>-85.39922393047949</v>
       </c>
       <c r="AC3">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="AD3">
-        <v>0.2559530034611136</v>
+        <v>0.08021242565986955</v>
       </c>
       <c r="AE3">
-        <v>-0.9666892261834903</v>
+        <v>-0.9967777920729173</v>
       </c>
       <c r="AF3">
-        <v>2.036875992672758</v>
+        <v>2.110675644730364</v>
       </c>
       <c r="AG3">
-        <v>2.036363361525732</v>
+        <v>2.110132843129682</v>
       </c>
       <c r="AH3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="AI3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AL3">
-        <v>0.2558885864410196</v>
+        <v>0.08019179746285052</v>
       </c>
       <c r="AM3">
-        <v>0.7628201312597849</v>
+        <v>0.6883379886469313</v>
       </c>
       <c r="AN3">
-        <v>0.5644088449907517</v>
+        <v>0.240984797672557</v>
       </c>
       <c r="AO3">
-        <v>-1.955200417359916</v>
+        <v>-2.091845367565583</v>
       </c>
       <c r="AP3">
-        <v>0.238370532503597</v>
+        <v>-0.3948136949341936</v>
       </c>
       <c r="AQ3">
-        <v>-1.590173488013066</v>
+        <v>-1.616098126748459</v>
       </c>
       <c r="AR3">
-        <v>0.2705967320131298</v>
+        <v>0.5286548680489591</v>
       </c>
       <c r="AS3">
-        <v>0.09251788975322217</v>
+        <v>0.2375715312852523</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1061,28 +1070,28 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C4" s="2">
         <v>46287</v>
       </c>
-      <c r="C4" s="2">
-        <v>46286</v>
-      </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.3438626324877645</v>
+        <v>0.4926462336262687</v>
       </c>
       <c r="G4">
-        <v>1.926125894897982</v>
+        <v>2.073088797280267</v>
       </c>
       <c r="H4">
-        <v>2.080254974000914</v>
+        <v>2.080346391500886</v>
       </c>
       <c r="I4">
-        <v>0.4935688412027747</v>
+        <v>0.4934610274365089</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1094,103 +1103,103 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4">
-        <v>0.1072367568082447</v>
+        <v>0.1493523087924303</v>
       </c>
       <c r="O4">
-        <v>3.638668432659754</v>
+        <v>4.999838170956509</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.926125894897982</v>
+        <v>2.073088797280267</v>
       </c>
       <c r="R4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S4" t="s">
         <v>64</v>
       </c>
       <c r="T4">
-        <v>-0.7355337437864559</v>
+        <v>-0.7642070699045426</v>
       </c>
       <c r="U4">
-        <v>0.7825647886622367</v>
+        <v>0.8177839062277842</v>
       </c>
       <c r="V4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X4">
-        <v>0.9989758169455758</v>
+        <v>0.998967183058051</v>
       </c>
       <c r="Y4">
-        <v>0.9999808363406676</v>
+        <v>0.9999751589071989</v>
       </c>
       <c r="Z4">
-        <v>0.001005019395091789</v>
+        <v>0.001007975849147913</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-121.8339645075535</v>
+        <v>-124.5614046355496</v>
       </c>
       <c r="AC4">
         <v>-10</v>
       </c>
       <c r="AD4">
-        <v>-0.5274595128822603</v>
+        <v>-0.5672891382821459</v>
       </c>
       <c r="AE4">
-        <v>-0.8495801682419433</v>
+        <v>-0.8235186904904468</v>
       </c>
       <c r="AF4">
-        <v>2.638212355389538</v>
+        <v>2.702412461124234</v>
       </c>
       <c r="AG4">
-        <v>2.638161797586712</v>
+        <v>2.7023453302455</v>
       </c>
       <c r="AH4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL4">
-        <v>-0.5274494048278439</v>
+        <v>-0.5672750462000168</v>
       </c>
       <c r="AM4">
-        <v>0.8480274956895379</v>
+        <v>0.8610512426607231</v>
       </c>
       <c r="AN4">
-        <v>-1.349191485165129</v>
+        <v>-1.488663435624243</v>
       </c>
       <c r="AO4">
-        <v>-2.263978158998908</v>
+        <v>-2.252073862699043</v>
       </c>
       <c r="AP4">
-        <v>-2.903115257756255</v>
+        <v>-2.96861681290742</v>
       </c>
       <c r="AQ4">
-        <v>0.9980947323278444</v>
+        <v>1.667210972507485</v>
       </c>
       <c r="AR4">
-        <v>2.731178806381457</v>
+        <v>2.740950933643604</v>
       </c>
       <c r="AS4">
-        <v>0.06802433929582494</v>
+        <v>0.0608453629429361</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1201,28 +1210,28 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C5" s="2">
         <v>46287</v>
       </c>
-      <c r="C5" s="2">
-        <v>46286</v>
-      </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>0.5129785038932553</v>
       </c>
       <c r="G5">
-        <v>1.16554786331072</v>
+        <v>1.531323994638813</v>
       </c>
       <c r="H5">
-        <v>1.520678401954014</v>
+        <v>1.522240540619557</v>
       </c>
       <c r="I5">
-        <v>0.3491269889852451</v>
+        <v>0.3499422619881554</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1234,103 +1243,103 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>0.002489337482335389</v>
+        <v>0.005905830908348682</v>
       </c>
       <c r="O5">
-        <v>0.6902500446166696</v>
+        <v>1.560030805978906</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.16554786331072</v>
+        <v>1.531323994638813</v>
       </c>
       <c r="R5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S5" t="s">
         <v>64</v>
       </c>
       <c r="T5">
-        <v>-0.58775016694939</v>
+        <v>-0.6666080153865663</v>
       </c>
       <c r="U5">
-        <v>0.6644663500040134</v>
+        <v>0.7769005430959033</v>
       </c>
       <c r="V5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X5">
-        <v>0.9984729621537499</v>
+        <v>0.9986505370245441</v>
       </c>
       <c r="Y5">
-        <v>0.9999150995071521</v>
+        <v>0.9999206423518406</v>
       </c>
       <c r="Z5">
-        <v>0.001442137353402151</v>
+        <v>0.001270105327296545</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-108.0265642236214</v>
+        <v>-112.7035812855123</v>
       </c>
       <c r="AC5">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="AD5">
-        <v>-0.3094579024898199</v>
+        <v>-0.3859637050200329</v>
       </c>
       <c r="AE5">
-        <v>-0.9509131435554991</v>
+        <v>-0.9225139665106481</v>
       </c>
       <c r="AF5">
-        <v>2.744301968280822</v>
+        <v>2.895073106386351</v>
       </c>
       <c r="AG5">
-        <v>2.744068975691192</v>
+        <v>2.894843360193379</v>
       </c>
       <c r="AH5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL5">
-        <v>-0.3094316293613829</v>
+        <v>-0.3859330758481276</v>
       </c>
       <c r="AM5">
-        <v>0.7781174576414135</v>
+        <v>0.8033281115250186</v>
       </c>
       <c r="AN5">
-        <v>-0.7843640309727368</v>
+        <v>-1.057722188765269</v>
       </c>
       <c r="AO5">
-        <v>-2.625449121050811</v>
+        <v>-2.690737151312734</v>
       </c>
       <c r="AP5">
-        <v>-1.904919545246617</v>
+        <v>-2.370579042741876</v>
       </c>
       <c r="AQ5">
-        <v>0.516566091981597</v>
+        <v>0.6611776113723781</v>
       </c>
       <c r="AR5">
-        <v>1.764158597753124</v>
+        <v>2.224121156604697</v>
       </c>
       <c r="AS5">
-        <v>0.09793465288690467</v>
+        <v>0.0828881653609035</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1341,13 +1350,13 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C6" s="2">
         <v>46287</v>
       </c>
-      <c r="C6" s="2">
-        <v>46286</v>
-      </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -1356,13 +1365,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.284619702940228</v>
+        <v>1.381248909600365</v>
       </c>
       <c r="H6">
-        <v>0.9509634698023387</v>
+        <v>0.9546996021780038</v>
       </c>
       <c r="I6">
-        <v>0.2568013710638661</v>
+        <v>0.2571520464602783</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1374,103 +1383,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>0.179037581131401</v>
+        <v>0.2319109096253461</v>
       </c>
       <c r="O6">
-        <v>3.334432342046298</v>
+        <v>4.231013376539168</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.284619702940228</v>
+        <v>1.381248909600365</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S6" t="s">
         <v>64</v>
       </c>
       <c r="T6">
-        <v>-0.7787999376878065</v>
+        <v>-0.789229280077872</v>
       </c>
       <c r="U6">
-        <v>0.9004588682205338</v>
+        <v>0.9051524404477519</v>
       </c>
       <c r="V6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X6">
-        <v>0.9999395331854015</v>
+        <v>0.9999249365275449</v>
       </c>
       <c r="Y6">
-        <v>0.9999955850440831</v>
+        <v>0.9999970576508379</v>
       </c>
       <c r="Z6">
-        <v>5.605185868162721E-05</v>
+        <v>7.2121123293023E-05</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-123.8899077017919</v>
+        <v>-125.3421552880807</v>
       </c>
       <c r="AC6">
-        <v>-2.000000000000003</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AD6">
-        <v>-0.5575988987827774</v>
+        <v>-0.5784579399928681</v>
       </c>
       <c r="AE6">
-        <v>-0.8301105155798437</v>
+        <v>-0.8157122112971017</v>
       </c>
       <c r="AF6">
-        <v>1.677508289183937</v>
+        <v>1.773401255129343</v>
       </c>
       <c r="AG6">
-        <v>1.67750088305879</v>
+        <v>1.773396037163646</v>
       </c>
       <c r="AH6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL6">
-        <v>-0.5575964370082199</v>
+        <v>-0.578456237967633</v>
       </c>
       <c r="AM6">
-        <v>0.8579998559087119</v>
+        <v>0.8650299022740746</v>
       </c>
       <c r="AN6">
-        <v>-0.9304608564918229</v>
+        <v>-1.017783425722924</v>
       </c>
       <c r="AO6">
-        <v>-1.395684904895981</v>
+        <v>-1.452100818022269</v>
       </c>
       <c r="AP6">
-        <v>-1.794984205749615</v>
+        <v>-1.857171237747023</v>
       </c>
       <c r="AQ6">
-        <v>0.9515974066848344</v>
+        <v>1.329157897606892</v>
       </c>
       <c r="AR6">
-        <v>1.667567034891542</v>
+        <v>1.697031421034574</v>
       </c>
       <c r="AS6">
-        <v>0.06185512327700235</v>
+        <v>0.05670966601052702</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1481,28 +1490,28 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C7" s="2">
         <v>46287</v>
       </c>
-      <c r="C7" s="2">
-        <v>46286</v>
-      </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0.1910502009538229</v>
+        <v>0.6832713888004702</v>
       </c>
       <c r="G7">
-        <v>1.251921697359182</v>
+        <v>1.619095300778423</v>
       </c>
       <c r="H7">
-        <v>1.481132695562362</v>
+        <v>1.482878494007738</v>
       </c>
       <c r="I7">
-        <v>0.3709518486673632</v>
+        <v>0.3716259468055488</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1514,103 +1523,103 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>0.006457383772562279</v>
+        <v>0.0112485953468672</v>
       </c>
       <c r="O7">
-        <v>1.465327381730629</v>
+        <v>2.329418458045107</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.251921697359182</v>
+        <v>1.619095300778423</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S7" t="s">
         <v>64</v>
       </c>
       <c r="T7">
-        <v>-0.6225277707030407</v>
+        <v>-0.6904655038694207</v>
       </c>
       <c r="U7">
-        <v>0.7087856933245674</v>
+        <v>0.8131919886960746</v>
       </c>
       <c r="V7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X7">
-        <v>0.9997436562537549</v>
+        <v>0.9997339323084558</v>
       </c>
       <c r="Y7">
-        <v>0.9999626654605028</v>
+        <v>0.999967214539059</v>
       </c>
       <c r="Z7">
-        <v>0.0002190092067478888</v>
+        <v>0.00023328223060326</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-110.1382093721169</v>
+        <v>-114.3798665051813</v>
       </c>
       <c r="AC7">
         <v>-4.999999999999995</v>
       </c>
       <c r="AD7">
-        <v>-0.3442858806847173</v>
+        <v>-0.4127843939359378</v>
       </c>
       <c r="AE7">
-        <v>-0.9388648637376673</v>
+        <v>-0.9108287677291164</v>
       </c>
       <c r="AF7">
-        <v>2.690343039808895</v>
+        <v>2.872640984650549</v>
       </c>
       <c r="AG7">
-        <v>2.690242597090414</v>
+        <v>2.872546803791749</v>
       </c>
       <c r="AH7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL7">
-        <v>-0.3442730269299066</v>
+        <v>-0.4127708606093133</v>
       </c>
       <c r="AM7">
-        <v>0.7910621921093854</v>
+        <v>0.8126213546059401</v>
       </c>
       <c r="AN7">
-        <v>-0.9019855763860494</v>
+        <v>-1.161244345024767</v>
       </c>
       <c r="AO7">
-        <v>-2.533901608832344</v>
+        <v>-2.626630382371999</v>
       </c>
       <c r="AP7">
-        <v>-1.772215587384921</v>
+        <v>-2.304505260688903</v>
       </c>
       <c r="AQ7">
-        <v>1.10061735100406</v>
+        <v>0.9905931590872408</v>
       </c>
       <c r="AR7">
-        <v>1.599572967380154</v>
+        <v>2.146520531148934</v>
       </c>
       <c r="AS7">
-        <v>0.08140336671470533</v>
+        <v>0.07468325775674514</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1621,13 +1630,13 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C8" s="2">
         <v>46287</v>
       </c>
-      <c r="C8" s="2">
-        <v>46286</v>
-      </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1636,13 +1645,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.05651322737015</v>
+        <v>2.192273573372067</v>
       </c>
       <c r="H8">
-        <v>1.449316163320201</v>
+        <v>1.454573538347879</v>
       </c>
       <c r="I8">
-        <v>0.3607095589230885</v>
+        <v>0.3621618433489849</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1654,103 +1663,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N8">
-        <v>-0.03754752240651413</v>
+        <v>-0.04332863059197604</v>
       </c>
       <c r="O8">
-        <v>-10.28497972395226</v>
+        <v>-12.21261985680828</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.05651322737015</v>
+        <v>2.192273573372067</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T8">
-        <v>0.8988917203478006</v>
+        <v>0.9242740106740395</v>
       </c>
       <c r="U8">
-        <v>0.9544023477634401</v>
+        <v>0.9658409170466475</v>
       </c>
       <c r="V8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X8">
-        <v>0.9943957645662223</v>
+        <v>0.9942339104021372</v>
       </c>
       <c r="Y8">
-        <v>0.9996042944277196</v>
+        <v>0.999670448973319</v>
       </c>
       <c r="Z8">
-        <v>0.005208529861497335</v>
+        <v>0.00543653857118187</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>37.08484846736302</v>
+        <v>31.94860947065497</v>
       </c>
       <c r="AC8">
-        <v>-22.99999999999999</v>
+        <v>-24</v>
       </c>
       <c r="AD8">
-        <v>0.7977434157478444</v>
+        <v>0.8485230575437027</v>
       </c>
       <c r="AE8">
-        <v>0.6029970502672148</v>
+        <v>0.5291584080563081</v>
       </c>
       <c r="AF8">
-        <v>2.039438594875659</v>
+        <v>2.036576973604223</v>
       </c>
       <c r="AG8">
-        <v>2.038631577659344</v>
+        <v>2.035905817571657</v>
       </c>
       <c r="AH8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AK8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AL8">
-        <v>0.7974277442329829</v>
+        <v>0.8482434258989268</v>
       </c>
       <c r="AM8">
-        <v>0.9327697977437558</v>
+        <v>0.9483751407441491</v>
       </c>
       <c r="AN8">
-        <v>1.553909865259229</v>
+        <v>1.659969719740997</v>
       </c>
       <c r="AO8">
-        <v>1.303144291215953</v>
+        <v>1.159505413854145</v>
       </c>
       <c r="AP8">
-        <v>2.634002089849427</v>
+        <v>2.781852845213402</v>
       </c>
       <c r="AQ8">
-        <v>-3.278751439118282</v>
+        <v>-3.240957977731926</v>
       </c>
       <c r="AR8">
-        <v>2.277861118416645</v>
+        <v>2.446842755826611</v>
       </c>
       <c r="AS8">
-        <v>0.04276486686866134</v>
+        <v>0.040442891064156</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1761,28 +1770,28 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C9" s="2">
         <v>46287</v>
       </c>
-      <c r="C9" s="2">
-        <v>46286</v>
-      </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.8246640972210072</v>
+        <v>0.4030843275967169</v>
       </c>
       <c r="G9">
-        <v>3.528177455506283</v>
+        <v>2.977543930371167</v>
       </c>
       <c r="H9">
-        <v>3.09796169046018</v>
+        <v>3.106419556707859</v>
       </c>
       <c r="I9">
-        <v>0.6625551897000239</v>
+        <v>0.6648853747844725</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1794,103 +1803,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N9">
-        <v>0.7744388995905783</v>
+        <v>0.7926158758419788</v>
       </c>
       <c r="O9">
-        <v>109.0594436882606</v>
+        <v>102.9753365050853</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.528177455506283</v>
+        <v>2.977543930371167</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T9">
-        <v>-0.998965934647524</v>
+        <v>-0.999306556385563</v>
       </c>
       <c r="U9">
-        <v>0.9731981751687198</v>
+        <v>0.9101417880330798</v>
       </c>
       <c r="V9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X9">
-        <v>0.9981177889678176</v>
+        <v>0.999823504546148</v>
       </c>
       <c r="Y9">
-        <v>0.9998555599767319</v>
+        <v>0.9999647540802756</v>
       </c>
       <c r="Z9">
-        <v>0.001737771008914368</v>
+        <v>0.000141249534127641</v>
       </c>
       <c r="AA9">
-        <v>0.9928258762532932</v>
+        <v>0.5735485146995495</v>
       </c>
       <c r="AB9">
-        <v>-176.3631016843742</v>
+        <v>176.8963988010664</v>
       </c>
       <c r="AC9">
-        <v>13.00000000000001</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AD9">
-        <v>-0.9979860845618934</v>
+        <v>-0.9985332693502192</v>
       </c>
       <c r="AE9">
-        <v>-0.06343323277920872</v>
+        <v>0.05414157368199048</v>
       </c>
       <c r="AF9">
-        <v>2.65839845364152</v>
+        <v>2.281820795495177</v>
       </c>
       <c r="AG9">
-        <v>2.65801447450702</v>
+        <v>2.281740370622594</v>
       </c>
       <c r="AH9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL9">
-        <v>-0.994262614666409</v>
+        <v>-0.7855925815230406</v>
       </c>
       <c r="AM9">
-        <v>0.9925208284367179</v>
+        <v>0.9095452538029476</v>
       </c>
       <c r="AN9">
-        <v>-2.651323782891174</v>
+        <v>-2.277041399063659</v>
       </c>
       <c r="AO9">
-        <v>-0.1048145629032953</v>
+        <v>0.14124748482445</v>
       </c>
       <c r="AP9">
-        <v>-4.52315797129816</v>
+        <v>-3.659126875043988</v>
       </c>
       <c r="AQ9">
-        <v>3.65213557072818</v>
+        <v>3.946624535019657</v>
       </c>
       <c r="AR9">
-        <v>4.189749352804028</v>
+        <v>3.304175784760246</v>
       </c>
       <c r="AS9">
-        <v>0.03593078782909975</v>
+        <v>0.03141395913416333</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1901,13 +1910,13 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C10" s="2">
         <v>46287</v>
       </c>
-      <c r="C10" s="2">
-        <v>46286</v>
-      </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -1916,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.9655620847251117</v>
+        <v>0.7689035290244188</v>
       </c>
       <c r="H10">
-        <v>2.096777369849961</v>
+        <v>2.10107261049345</v>
       </c>
       <c r="I10">
-        <v>0.4510764324801304</v>
+        <v>0.450452031522959</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1934,103 +1943,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N10">
-        <v>42.02481681485907</v>
+        <v>43.12673206254915</v>
       </c>
       <c r="O10">
-        <v>29.86156251277891</v>
+        <v>35.90261336003376</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>0.09196182282437389</v>
       </c>
       <c r="Q10">
-        <v>0.9655620847251117</v>
+        <v>0.846774451065512</v>
       </c>
       <c r="R10" t="s">
         <v>62</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T10">
-        <v>-0.7109343538734294</v>
+        <v>-0.5978205059167399</v>
       </c>
       <c r="U10">
-        <v>0.7197202381217118</v>
+        <v>0.6688986334359897</v>
       </c>
       <c r="V10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X10">
-        <v>0.9908280140512149</v>
+        <v>0.994299111589674</v>
       </c>
       <c r="Y10">
-        <v>0.9991991155146743</v>
+        <v>0.9995176230938265</v>
       </c>
       <c r="Z10">
-        <v>0.008371101463459429</v>
+        <v>0.005218511504152534</v>
       </c>
       <c r="AA10">
-        <v>0.6144610582570272</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>116.7666666385041</v>
+        <v>109.0394036561722</v>
       </c>
       <c r="AC10">
-        <v>-28</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD10">
-        <v>-0.4503581785973821</v>
+        <v>-0.3262183327945586</v>
       </c>
       <c r="AE10">
-        <v>0.8928479775249807</v>
+        <v>0.9452944511361201</v>
       </c>
       <c r="AF10">
-        <v>1.800215641900121</v>
+        <v>2.247947471938232</v>
       </c>
       <c r="AG10">
-        <v>1.798773877122283</v>
+        <v>2.246863113991477</v>
       </c>
       <c r="AH10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AI10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AK10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AL10">
-        <v>-0.3632517149615387</v>
+        <v>-0.3260609726044481</v>
       </c>
       <c r="AM10">
-        <v>0.7497097212193088</v>
+        <v>0.7868040498795141</v>
       </c>
       <c r="AN10">
-        <v>-0.8754817607296135</v>
+        <v>-0.8089699437799314</v>
       </c>
       <c r="AO10">
-        <v>1.554069485227286</v>
+        <v>2.083598681709422</v>
       </c>
       <c r="AP10">
-        <v>-0.5886128695847785</v>
+        <v>-0.3346738025946434</v>
       </c>
       <c r="AQ10">
-        <v>3.189245913176564</v>
+        <v>3.278481602830913</v>
       </c>
       <c r="AR10">
-        <v>0.5463548806730636</v>
+        <v>0.4572595628691817</v>
       </c>
       <c r="AS10">
-        <v>0.05339756294298168</v>
+        <v>0.07261745361128483</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2041,13 +2050,13 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C11" s="2">
         <v>46287</v>
       </c>
-      <c r="C11" s="2">
-        <v>46286</v>
-      </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2056,121 +2065,121 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.01093802734210199</v>
+        <v>0.05907275545969401</v>
       </c>
       <c r="H11">
-        <v>2.281221815650924</v>
+        <v>2.262277656396407</v>
       </c>
       <c r="I11">
-        <v>0.5317631192489489</v>
+        <v>0.5265802769592789</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0.6666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L11">
         <v>212</v>
       </c>
       <c r="M11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N11">
-        <v>-2287.199610175742</v>
+        <v>-2288.175105018431</v>
       </c>
       <c r="O11">
-        <v>-35.79982395963997</v>
+        <v>-37.31618417894602</v>
       </c>
       <c r="P11">
-        <v>0.643534845564956</v>
+        <v>0.4219894937623895</v>
       </c>
       <c r="Q11">
-        <v>0.03068470285528328</v>
+        <v>0.102200141385337</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="S11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="T11">
-        <v>0.8747428227636473</v>
+        <v>0.3792715393973716</v>
       </c>
       <c r="U11">
-        <v>0.7044609170831502</v>
+        <v>0.4424306633820686</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="X11">
-        <v>0.8032307277164809</v>
+        <v>0.9611433398136395</v>
       </c>
       <c r="Y11">
-        <v>0.8433065873580352</v>
+        <v>0.9870338826130057</v>
       </c>
       <c r="Z11">
-        <v>0.04007585964155436</v>
+        <v>0.0258905427993662</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-50.63457834155941</v>
+        <v>-110.3001532599342</v>
       </c>
       <c r="AC11">
-        <v>90</v>
+        <v>-69</v>
       </c>
       <c r="AD11">
-        <v>0.6342640483614705</v>
+        <v>-0.3469381603221821</v>
       </c>
       <c r="AE11">
-        <v>-0.7731164963678618</v>
+        <v>-0.9378880065936763</v>
       </c>
       <c r="AF11">
-        <v>0.4287114648084668</v>
+        <v>0.4396932089805301</v>
       </c>
       <c r="AG11">
-        <v>0.3615352023488925</v>
+        <v>0.4339920952186244</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AL11">
-        <v>0.2674395250538018</v>
+        <v>-0.1712198597047084</v>
       </c>
       <c r="AM11">
-        <v>0.6070657455659292</v>
+        <v>0.5657747095271159</v>
       </c>
       <c r="AN11">
-        <v>0.0627906675128186</v>
+        <v>-0.03360509406946684</v>
       </c>
       <c r="AO11">
-        <v>-0.3385811013406831</v>
+        <v>-0.4212699702445057</v>
       </c>
       <c r="AP11">
-        <v>-0.1469459846318279</v>
+        <v>-0.3247500522790193</v>
       </c>
       <c r="AQ11">
-        <v>-0.2679331550601287</v>
+        <v>-0.3386557400517989</v>
       </c>
       <c r="AR11">
-        <v>0.151127139077636</v>
+        <v>0.3371940299437112</v>
       </c>
       <c r="AS11">
-        <v>0.189138496785495</v>
+        <v>0.2251239832272708</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>Pair</t>
   </si>
@@ -199,15 +199,9 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
-    <t>UP_REVERSAL_WATCH</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -217,24 +211,15 @@
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>多头反转预警</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
     <t>TRANSITION</t>
   </si>
   <si>
@@ -256,15 +241,9 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>TURNING_DOWN</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
@@ -274,13 +253,7 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
     <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>向下转折带</t>
   </si>
 </sst>
 </file>
@@ -790,10 +763,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C2" s="2">
         <v>46288</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46287</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -805,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.2093737509907309</v>
+        <v>0.4830108028346309</v>
       </c>
       <c r="H2">
-        <v>1.080094616303197</v>
+        <v>1.080526961917032</v>
       </c>
       <c r="I2">
-        <v>0.2591860924200768</v>
+        <v>0.2592965650836586</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -820,106 +793,106 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>-0.5278195790061191</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-14.84873727737504</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.1457252795510106</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.2450894846574511</v>
+        <v>0.4830108028346309</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T2">
-        <v>-0.5472059317582344</v>
+        <v>-0.6570892863706981</v>
       </c>
       <c r="U2">
-        <v>0.6461936102511192</v>
+        <v>0.6955935713688013</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X2">
-        <v>0.9968306442832696</v>
+        <v>0.9942282671038949</v>
       </c>
       <c r="Y2">
-        <v>0.999803763839655</v>
+        <v>0.9996135700079486</v>
       </c>
       <c r="Z2">
-        <v>0.002973119556385351</v>
+        <v>0.005385302904053701</v>
       </c>
       <c r="AA2">
-        <v>0.7115228263201009</v>
+        <v>0.6133263391396896</v>
       </c>
       <c r="AB2">
-        <v>-99.84364096212249</v>
+        <v>-110.3527274422077</v>
       </c>
       <c r="AC2">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AD2">
-        <v>-0.1709600137076963</v>
+        <v>-0.3477986132223966</v>
       </c>
       <c r="AE2">
-        <v>-0.985277967739594</v>
+        <v>-0.9375692639163135</v>
       </c>
       <c r="AF2">
-        <v>1.070682856807244</v>
+        <v>1.027675916984822</v>
       </c>
       <c r="AG2">
-        <v>1.070472750114476</v>
+        <v>1.027278792188391</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AK2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AL2">
-        <v>-0.146272273381216</v>
+        <v>-0.2804479163329407</v>
       </c>
       <c r="AM2">
-        <v>0.6674818814331507</v>
+        <v>0.7099677896516908</v>
       </c>
       <c r="AN2">
-        <v>-0.1369034983993388</v>
+        <v>-0.30306000469083</v>
       </c>
       <c r="AO2">
-        <v>-1.058472612049463</v>
+        <v>-0.9757644934454882</v>
       </c>
       <c r="AP2">
-        <v>-0.5346054176647519</v>
+        <v>-0.8842826585876883</v>
       </c>
       <c r="AQ2">
-        <v>0.0283605067527304</v>
+        <v>-0.1393141209674965</v>
       </c>
       <c r="AR2">
-        <v>0.4856165403755571</v>
+        <v>0.8553251341179611</v>
       </c>
       <c r="AS2">
-        <v>0.173613368580384</v>
+        <v>0.1126787443049873</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -930,10 +903,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C3" s="2">
         <v>46288</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46287</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -945,121 +918,121 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.04694163332292873</v>
+        <v>0.2689586953865793</v>
       </c>
       <c r="H3">
-        <v>2.049582707219781</v>
+        <v>2.055403502380753</v>
       </c>
       <c r="I3">
-        <v>0.4536305434427991</v>
+        <v>0.454761472922082</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0.6666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L3">
         <v>225</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3">
-        <v>-0.1464096065507443</v>
+        <v>-0.1464803531272444</v>
       </c>
       <c r="O3">
-        <v>-51.42334399674927</v>
+        <v>-48.00386104357287</v>
       </c>
       <c r="P3">
-        <v>0.6774098120205421</v>
+        <v>0.3796269220752061</v>
       </c>
       <c r="Q3">
-        <v>0.1455147585763455</v>
+        <v>0.4335434675635367</v>
       </c>
       <c r="R3" t="s">
         <v>59</v>
       </c>
       <c r="S3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T3">
-        <v>0.4129561684468722</v>
+        <v>0.2070180677677997</v>
       </c>
       <c r="U3">
-        <v>0.5357659834023484</v>
+        <v>0.3680812380767515</v>
       </c>
       <c r="V3" t="s">
+        <v>66</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9966796895064721</v>
+      </c>
+      <c r="Y3">
+        <v>0.9996924303249665</v>
+      </c>
+      <c r="Z3">
+        <v>0.003012740818494342</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>-96.5215785744879</v>
+      </c>
+      <c r="AC3">
+        <v>-17</v>
+      </c>
+      <c r="AD3">
+        <v>-0.1135774019538207</v>
+      </c>
+      <c r="AE3">
+        <v>-0.9935291509389245</v>
+      </c>
+      <c r="AF3">
+        <v>2.270059873850374</v>
+      </c>
+      <c r="AG3">
+        <v>2.269361672272667</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI3" t="s">
         <v>70</v>
       </c>
-      <c r="W3" t="s">
-        <v>70</v>
-      </c>
-      <c r="X3">
-        <v>0.9976334296172309</v>
-      </c>
-      <c r="Y3">
-        <v>0.9997428304050235</v>
-      </c>
-      <c r="Z3">
-        <v>0.002109400787792648</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>-85.39922393047949</v>
-      </c>
-      <c r="AC3">
-        <v>-15</v>
-      </c>
-      <c r="AD3">
-        <v>0.08021242565986955</v>
-      </c>
-      <c r="AE3">
-        <v>-0.9967777920729173</v>
-      </c>
-      <c r="AF3">
-        <v>2.110675644730364</v>
-      </c>
-      <c r="AG3">
-        <v>2.110132843129682</v>
-      </c>
-      <c r="AH3" t="s">
+      <c r="AJ3" t="s">
         <v>73</v>
       </c>
-      <c r="AI3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>78</v>
-      </c>
       <c r="AK3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AL3">
-        <v>0.08019179746285052</v>
+        <v>-0.1135424689892106</v>
       </c>
       <c r="AM3">
-        <v>0.6883379886469313</v>
+        <v>0.6959674270694126</v>
       </c>
       <c r="AN3">
-        <v>0.240984797672557</v>
+        <v>-0.1784819731560597</v>
       </c>
       <c r="AO3">
-        <v>-2.091845367565583</v>
+        <v>-2.255471694803508</v>
       </c>
       <c r="AP3">
-        <v>-0.3948136949341936</v>
+        <v>-1.192907343146901</v>
       </c>
       <c r="AQ3">
-        <v>-1.616098126748459</v>
+        <v>-1.471257199994455</v>
       </c>
       <c r="AR3">
-        <v>0.5286548680489591</v>
+        <v>1.236629001477036</v>
       </c>
       <c r="AS3">
-        <v>0.2375715312852523</v>
+        <v>0.2533209608698126</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1070,10 +1043,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C4" s="2">
         <v>46288</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46287</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1082,16 +1055,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.4926462336262687</v>
+        <v>0.7983977380112539</v>
       </c>
       <c r="G4">
-        <v>2.073088797280267</v>
+        <v>2.375811432323905</v>
       </c>
       <c r="H4">
-        <v>2.080346391500886</v>
+        <v>2.081318286271561</v>
       </c>
       <c r="I4">
-        <v>0.4934610274365089</v>
+        <v>0.4934574035565198</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1103,103 +1076,103 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>0.1493523087924303</v>
+        <v>0.1973470373947746</v>
       </c>
       <c r="O4">
-        <v>4.999838170956509</v>
+        <v>6.587645501971473</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.073088797280267</v>
+        <v>2.375811432323905</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T4">
-        <v>-0.7642070699045426</v>
+        <v>-0.8243571875466386</v>
       </c>
       <c r="U4">
-        <v>0.8177839062277842</v>
+        <v>0.8906962567325648</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X4">
-        <v>0.998967183058051</v>
+        <v>0.9978799983892116</v>
       </c>
       <c r="Y4">
-        <v>0.9999751589071989</v>
+        <v>0.9999034465395575</v>
       </c>
       <c r="Z4">
-        <v>0.001007975849147913</v>
+        <v>0.002023448150345941</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-124.5614046355496</v>
+        <v>-131.3156443052732</v>
       </c>
       <c r="AC4">
-        <v>-10</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AD4">
-        <v>-0.5672891382821459</v>
+        <v>-0.6602067719977383</v>
       </c>
       <c r="AE4">
-        <v>-0.8235186904904468</v>
+        <v>-0.7510838955857904</v>
       </c>
       <c r="AF4">
-        <v>2.702412461124234</v>
+        <v>2.697210728344293</v>
       </c>
       <c r="AG4">
-        <v>2.7023453302455</v>
+        <v>2.696950303314928</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AK4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AL4">
-        <v>-0.5672750462000168</v>
+        <v>-0.6601430267492944</v>
       </c>
       <c r="AM4">
-        <v>0.8610512426607231</v>
+        <v>0.8893433459388245</v>
       </c>
       <c r="AN4">
-        <v>-1.488663435624243</v>
+        <v>-1.719822012607482</v>
       </c>
       <c r="AO4">
-        <v>-2.252073862699043</v>
+        <v>-2.070348970910865</v>
       </c>
       <c r="AP4">
-        <v>-2.96861681290742</v>
+        <v>-3.335704082077868</v>
       </c>
       <c r="AQ4">
-        <v>1.667210972507485</v>
+        <v>1.940600048762417</v>
       </c>
       <c r="AR4">
-        <v>2.740950933643604</v>
+        <v>3.086665026183349</v>
       </c>
       <c r="AS4">
-        <v>0.0608453629429361</v>
+        <v>0.05789927966228124</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1210,10 +1183,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C5" s="2">
         <v>46288</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46287</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1222,16 +1195,16 @@
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>0.5129785038932553</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1.531323994638813</v>
+        <v>1.909240718243277</v>
       </c>
       <c r="H5">
-        <v>1.522240540619557</v>
+        <v>1.524039611477305</v>
       </c>
       <c r="I5">
-        <v>0.3499422619881554</v>
+        <v>0.3508079315643451</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1243,103 +1216,103 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <v>0.005905830908348682</v>
+        <v>0.0105984229042196</v>
       </c>
       <c r="O5">
-        <v>1.560030805978906</v>
+        <v>2.641586623804074</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.531323994638813</v>
+        <v>1.909240718243277</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T5">
-        <v>-0.6666080153865663</v>
+        <v>-0.7471010554355209</v>
       </c>
       <c r="U5">
-        <v>0.7769005430959033</v>
+        <v>0.8861648483533932</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X5">
-        <v>0.9986505370245441</v>
+        <v>0.9980607427837912</v>
       </c>
       <c r="Y5">
-        <v>0.9999206423518406</v>
+        <v>0.9998774936296352</v>
       </c>
       <c r="Z5">
-        <v>0.001270105327296545</v>
+        <v>0.001816750845843984</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-112.7035812855123</v>
+        <v>-119.6151082460876</v>
       </c>
       <c r="AC5">
-        <v>-11</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD5">
-        <v>-0.3859637050200329</v>
+        <v>-0.4941711253433494</v>
       </c>
       <c r="AE5">
-        <v>-0.9225139665106481</v>
+        <v>-0.8693646524197356</v>
       </c>
       <c r="AF5">
-        <v>2.895073106386351</v>
+        <v>2.850862581377402</v>
       </c>
       <c r="AG5">
-        <v>2.894843360193379</v>
+        <v>2.850513332550149</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AL5">
-        <v>-0.3859330758481276</v>
+        <v>-0.4941105862324445</v>
       </c>
       <c r="AM5">
-        <v>0.8033281115250186</v>
+        <v>0.8369653791787706</v>
       </c>
       <c r="AN5">
-        <v>-1.057722188765269</v>
+        <v>-1.341166100762454</v>
       </c>
       <c r="AO5">
-        <v>-2.690737151312734</v>
+        <v>-2.50942208627491</v>
       </c>
       <c r="AP5">
-        <v>-2.370579042741876</v>
+        <v>-2.850159455517604</v>
       </c>
       <c r="AQ5">
-        <v>0.6611776113723781</v>
+        <v>0.9111780842076089</v>
       </c>
       <c r="AR5">
-        <v>2.224121156604697</v>
+        <v>2.682292018941203</v>
       </c>
       <c r="AS5">
-        <v>0.0828881653609035</v>
+        <v>0.07495387463071046</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1350,10 +1323,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C6" s="2">
         <v>46288</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46287</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1365,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.381248909600365</v>
+        <v>1.53164505827551</v>
       </c>
       <c r="H6">
-        <v>0.9546996021780038</v>
+        <v>0.9587406112476897</v>
       </c>
       <c r="I6">
-        <v>0.2571520464602783</v>
+        <v>0.2576871046750357</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1383,103 +1356,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>0.2319109096253461</v>
+        <v>0.2929330983515112</v>
       </c>
       <c r="O6">
-        <v>4.231013376539168</v>
+        <v>4.972432437219527</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.381248909600365</v>
+        <v>1.53164505827551</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
       </c>
       <c r="S6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T6">
-        <v>-0.789229280077872</v>
+        <v>-0.8223711890740208</v>
       </c>
       <c r="U6">
-        <v>0.9051524404477519</v>
+        <v>0.9200612304297192</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X6">
-        <v>0.9999249365275449</v>
+        <v>0.9996337705315739</v>
       </c>
       <c r="Y6">
-        <v>0.9999970576508379</v>
+        <v>0.9999767813856395</v>
       </c>
       <c r="Z6">
-        <v>7.2121123293023E-05</v>
+        <v>0.0003430108540656285</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-125.3421552880807</v>
+        <v>-130.1460534722882</v>
       </c>
       <c r="AC6">
-        <v>-3.000000000000004</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD6">
-        <v>-0.5784579399928681</v>
+        <v>-0.6447382537574189</v>
       </c>
       <c r="AE6">
-        <v>-0.8157122112971017</v>
+        <v>-0.7644034171442682</v>
       </c>
       <c r="AF6">
-        <v>1.773401255129343</v>
+        <v>1.768933955143183</v>
       </c>
       <c r="AG6">
-        <v>1.773396037163646</v>
+        <v>1.768892882947849</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AK6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AL6">
-        <v>-0.578456237967633</v>
+        <v>-0.6447232838285414</v>
       </c>
       <c r="AM6">
-        <v>0.8650299022740746</v>
+        <v>0.8849205896684339</v>
       </c>
       <c r="AN6">
-        <v>-1.017783425722924</v>
+        <v>-1.124696659556274</v>
       </c>
       <c r="AO6">
-        <v>-1.452100818022269</v>
+        <v>-1.364512082778895</v>
       </c>
       <c r="AP6">
-        <v>-1.857171237747023</v>
+        <v>-2.072038687377193</v>
       </c>
       <c r="AQ6">
-        <v>1.329157897606892</v>
+        <v>1.298911310092194</v>
       </c>
       <c r="AR6">
-        <v>1.697031421034574</v>
+        <v>1.916109695271846</v>
       </c>
       <c r="AS6">
-        <v>0.05670966601052702</v>
+        <v>0.05661839962510434</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1490,10 +1463,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C7" s="2">
         <v>46288</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46287</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1502,16 +1475,16 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0.6832713888004702</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1.619095300778423</v>
+        <v>2.095946280581374</v>
       </c>
       <c r="H7">
-        <v>1.482878494007738</v>
+        <v>1.484959937484297</v>
       </c>
       <c r="I7">
-        <v>0.3716259468055488</v>
+        <v>0.3724070675162787</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1523,103 +1496,103 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>0.0112485953468672</v>
+        <v>0.017816796894866</v>
       </c>
       <c r="O7">
-        <v>2.329418458045107</v>
+        <v>3.563868503045042</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.619095300778423</v>
+        <v>2.095946280581374</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T7">
-        <v>-0.6904655038694207</v>
+        <v>-0.754933602569243</v>
       </c>
       <c r="U7">
-        <v>0.8131919886960746</v>
+        <v>0.889705343267465</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X7">
-        <v>0.9997339323084558</v>
+        <v>0.9994295656147978</v>
       </c>
       <c r="Y7">
-        <v>0.999967214539059</v>
+        <v>0.9999408884452222</v>
       </c>
       <c r="Z7">
-        <v>0.00023328223060326</v>
+        <v>0.0005113228304244322</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-114.3798665051813</v>
+        <v>-120.6540198628737</v>
       </c>
       <c r="AC7">
-        <v>-4.999999999999995</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD7">
-        <v>-0.4127843939359378</v>
+        <v>-0.5098527180263543</v>
       </c>
       <c r="AE7">
-        <v>-0.9108287677291164</v>
+        <v>-0.8602617078082336</v>
       </c>
       <c r="AF7">
-        <v>2.872640984650549</v>
+        <v>3.023208866105928</v>
       </c>
       <c r="AG7">
-        <v>2.872546803791749</v>
+        <v>3.023030159529435</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AK7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AL7">
-        <v>-0.4127708606093133</v>
+        <v>-0.5098225798394841</v>
       </c>
       <c r="AM7">
-        <v>0.8126213546059401</v>
+        <v>0.8423133093768236</v>
       </c>
       <c r="AN7">
-        <v>-1.161244345024767</v>
+        <v>-1.505982560345274</v>
       </c>
       <c r="AO7">
-        <v>-2.626630382371999</v>
+        <v>-2.619424373215611</v>
       </c>
       <c r="AP7">
-        <v>-2.304505260688903</v>
+        <v>-2.968284586879674</v>
       </c>
       <c r="AQ7">
-        <v>0.9905931590872408</v>
+        <v>1.18822526655318</v>
       </c>
       <c r="AR7">
-        <v>2.146520531148934</v>
+        <v>2.785106010718397</v>
       </c>
       <c r="AS7">
-        <v>0.07468325775674514</v>
+        <v>0.07081211324606963</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1630,10 +1603,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C8" s="2">
         <v>46288</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46287</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1645,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.192273573372067</v>
+        <v>2.376780171594311</v>
       </c>
       <c r="H8">
-        <v>1.454573538347879</v>
+        <v>1.459751520383916</v>
       </c>
       <c r="I8">
-        <v>0.3621618433489849</v>
+        <v>0.3639059551069527</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1663,103 +1636,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N8">
-        <v>-0.04332863059197604</v>
+        <v>-0.04958470610677388</v>
       </c>
       <c r="O8">
-        <v>-12.21261985680828</v>
+        <v>-13.25794280929789</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.192273573372067</v>
+        <v>2.376780171594311</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="T8">
-        <v>0.9242740106740395</v>
+        <v>0.9572287493821052</v>
       </c>
       <c r="U8">
-        <v>0.9658409170466475</v>
+        <v>0.9806592389820111</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X8">
-        <v>0.9942339104021372</v>
+        <v>0.9933690031550378</v>
       </c>
       <c r="Y8">
-        <v>0.999670448973319</v>
+        <v>0.999625207040255</v>
       </c>
       <c r="Z8">
-        <v>0.00543653857118187</v>
+        <v>0.006256203885217193</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>31.94860947065497</v>
+        <v>23.87346857120675</v>
       </c>
       <c r="AC8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="AD8">
-        <v>0.8485230575437027</v>
+        <v>0.9144414623902793</v>
       </c>
       <c r="AE8">
-        <v>0.5291584080563081</v>
+        <v>0.4047181882020221</v>
       </c>
       <c r="AF8">
-        <v>2.036576973604223</v>
+        <v>1.997046909424981</v>
       </c>
       <c r="AG8">
-        <v>2.035905817571657</v>
+        <v>1.996298430303048</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AL8">
-        <v>0.8482434258989268</v>
+        <v>0.9140987361680766</v>
       </c>
       <c r="AM8">
-        <v>0.9483751407441491</v>
+        <v>0.9675472119477917</v>
       </c>
       <c r="AN8">
-        <v>1.659969719740997</v>
+        <v>1.770806310825148</v>
       </c>
       <c r="AO8">
-        <v>1.159505413854145</v>
+        <v>0.8942736127801956</v>
       </c>
       <c r="AP8">
-        <v>2.781852845213402</v>
+        <v>3.122413841577219</v>
       </c>
       <c r="AQ8">
-        <v>-3.240957977731926</v>
+        <v>-2.63079051722874</v>
       </c>
       <c r="AR8">
-        <v>2.446842755826611</v>
+        <v>2.850120757434095</v>
       </c>
       <c r="AS8">
-        <v>0.040442891064156</v>
+        <v>0.04436032822254267</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1770,10 +1743,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C9" s="2">
         <v>46288</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46287</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1782,16 +1755,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.4030843275967169</v>
+        <v>0.03357562127703215</v>
       </c>
       <c r="G9">
-        <v>2.977543930371167</v>
+        <v>2.49205161606413</v>
       </c>
       <c r="H9">
-        <v>3.106419556707859</v>
+        <v>3.11407191188433</v>
       </c>
       <c r="I9">
-        <v>0.6648853747844725</v>
+        <v>0.6667965099972272</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1803,103 +1776,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N9">
-        <v>0.7926158758419788</v>
+        <v>0.809069182831836</v>
       </c>
       <c r="O9">
-        <v>102.9753365050853</v>
+        <v>102.7669076360542</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.977543930371167</v>
+        <v>2.49205161606413</v>
       </c>
       <c r="R9" t="s">
         <v>61</v>
       </c>
       <c r="S9" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9">
+        <v>-0.9752996702053002</v>
+      </c>
+      <c r="U9">
+        <v>0.8438188640126402</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
         <v>67</v>
       </c>
-      <c r="T9">
-        <v>-0.999306556385563</v>
-      </c>
-      <c r="U9">
-        <v>0.9101417880330798</v>
-      </c>
-      <c r="V9" t="s">
-        <v>56</v>
-      </c>
-      <c r="W9" t="s">
-        <v>71</v>
-      </c>
       <c r="X9">
-        <v>0.999823504546148</v>
+        <v>0.9983991199334046</v>
       </c>
       <c r="Y9">
-        <v>0.9999647540802756</v>
+        <v>0.999590676914801</v>
       </c>
       <c r="Z9">
-        <v>0.000141249534127641</v>
+        <v>0.001191556981396391</v>
       </c>
       <c r="AA9">
-        <v>0.5735485146995495</v>
+        <v>0.3195501221615862</v>
       </c>
       <c r="AB9">
-        <v>176.8963988010664</v>
+        <v>160.8929859153165</v>
       </c>
       <c r="AC9">
-        <v>4.000000000000005</v>
+        <v>-11</v>
       </c>
       <c r="AD9">
-        <v>-0.9985332693502192</v>
+        <v>-0.9449088474309428</v>
       </c>
       <c r="AE9">
-        <v>0.05414157368199048</v>
+        <v>0.3273335761065877</v>
       </c>
       <c r="AF9">
-        <v>2.281820795495177</v>
+        <v>2.055750448008612</v>
       </c>
       <c r="AG9">
-        <v>2.281740370622594</v>
+        <v>2.054908981892834</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
       </c>
       <c r="AI9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AL9">
-        <v>-0.7855925815230406</v>
+        <v>-0.6231721093467566</v>
       </c>
       <c r="AM9">
-        <v>0.9095452538029476</v>
+        <v>0.8433063414120239</v>
       </c>
       <c r="AN9">
-        <v>-2.277041399063659</v>
+        <v>-1.953534880719627</v>
       </c>
       <c r="AO9">
-        <v>0.14124748482445</v>
+        <v>0.6295166517535071</v>
       </c>
       <c r="AP9">
-        <v>-3.659126875043988</v>
+        <v>-2.867520626012551</v>
       </c>
       <c r="AQ9">
-        <v>3.946624535019657</v>
+        <v>4.217005378068214</v>
       </c>
       <c r="AR9">
-        <v>3.304175784760246</v>
+        <v>2.504716256557524</v>
       </c>
       <c r="AS9">
-        <v>0.03141395913416333</v>
+        <v>0.02622049446504374</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1910,10 +1883,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C10" s="2">
         <v>46288</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46287</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1925,13 +1898,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.7689035290244188</v>
+        <v>0.2376599206115991</v>
       </c>
       <c r="H10">
-        <v>2.10107261049345</v>
+        <v>2.104958780599464</v>
       </c>
       <c r="I10">
-        <v>0.450452031522959</v>
+        <v>0.4499804263772595</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1943,103 +1916,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N10">
-        <v>43.12673206254915</v>
+        <v>43.93889379993216</v>
       </c>
       <c r="O10">
-        <v>35.90261336003376</v>
+        <v>37.0111917932101</v>
       </c>
       <c r="P10">
-        <v>0.09196182282437389</v>
+        <v>0.5212796104644144</v>
       </c>
       <c r="Q10">
-        <v>0.846774451065512</v>
+        <v>0.4964482938404959</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.5978205059167399</v>
+        <v>-0.5202907831583916</v>
       </c>
       <c r="U10">
-        <v>0.6688986334359897</v>
+        <v>0.6340495393606566</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
       </c>
       <c r="W10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X10">
-        <v>0.994299111589674</v>
+        <v>0.995839666978471</v>
       </c>
       <c r="Y10">
-        <v>0.9995176230938265</v>
+        <v>0.9996747477575215</v>
       </c>
       <c r="Z10">
-        <v>0.005218511504152534</v>
+        <v>0.003835080779050482</v>
       </c>
       <c r="AA10">
         <v>1</v>
       </c>
       <c r="AB10">
-        <v>109.0394036561722</v>
+        <v>101.3254505345612</v>
       </c>
       <c r="AC10">
-        <v>-21.99999999999999</v>
+        <v>-19</v>
       </c>
       <c r="AD10">
-        <v>-0.3262183327945586</v>
+        <v>-0.1963817096377843</v>
       </c>
       <c r="AE10">
-        <v>0.9452944511361201</v>
+        <v>0.9805275233871515</v>
       </c>
       <c r="AF10">
-        <v>2.247947471938232</v>
+        <v>2.399958928899351</v>
       </c>
       <c r="AG10">
-        <v>2.246863113991477</v>
+        <v>2.39917833687587</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
       </c>
       <c r="AI10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AL10">
-        <v>-0.3260609726044481</v>
+        <v>-0.1963178360463429</v>
       </c>
       <c r="AM10">
-        <v>0.7868040498795141</v>
+        <v>0.7405993536458721</v>
       </c>
       <c r="AN10">
-        <v>-0.8089699437799314</v>
+        <v>-0.5496875005070285</v>
       </c>
       <c r="AO10">
-        <v>2.083598681709422</v>
+        <v>2.325902149472054</v>
       </c>
       <c r="AP10">
-        <v>-0.3346738025946434</v>
+        <v>0.132020877264693</v>
       </c>
       <c r="AQ10">
-        <v>3.278481602830913</v>
+        <v>2.911735307341218</v>
       </c>
       <c r="AR10">
-        <v>0.4572595628691817</v>
+        <v>0.5490395199594185</v>
       </c>
       <c r="AS10">
-        <v>0.07261745361128483</v>
+        <v>0.1213421397373044</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2050,136 +2023,136 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C11" s="2">
         <v>46288</v>
       </c>
-      <c r="C11" s="2">
-        <v>46287</v>
-      </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.05907275545969401</v>
+        <v>0.313230502143933</v>
       </c>
       <c r="H11">
-        <v>2.262277656396407</v>
+        <v>2.244529229816875</v>
       </c>
       <c r="I11">
-        <v>0.5265802769592789</v>
+        <v>0.5219077851195376</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>212</v>
       </c>
       <c r="M11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N11">
-        <v>-2288.175105018431</v>
+        <v>-2280.660067373872</v>
       </c>
       <c r="O11">
-        <v>-37.31618417894602</v>
+        <v>-36.21327088945694</v>
       </c>
       <c r="P11">
-        <v>0.4219894937623895</v>
+        <v>0.1050098888483531</v>
       </c>
       <c r="Q11">
-        <v>0.102200141385337</v>
+        <v>0.3499820816353794</v>
       </c>
       <c r="R11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="T11">
-        <v>0.3792715393973716</v>
+        <v>-0.7779212152637645</v>
       </c>
       <c r="U11">
-        <v>0.4424306633820686</v>
+        <v>0.7498208223188599</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="X11">
-        <v>0.9611433398136395</v>
+        <v>0.991463224070397</v>
       </c>
       <c r="Y11">
-        <v>0.9870338826130057</v>
+        <v>0.9990251018006636</v>
       </c>
       <c r="Z11">
-        <v>0.0258905427993662</v>
+        <v>0.00756187773026662</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-110.3001532599342</v>
+        <v>-110.4389089368781</v>
       </c>
       <c r="AC11">
-        <v>-69</v>
+        <v>-27</v>
       </c>
       <c r="AD11">
-        <v>-0.3469381603221821</v>
+        <v>-0.3492084648411762</v>
       </c>
       <c r="AE11">
-        <v>-0.9378880065936763</v>
+        <v>-0.937045061927797</v>
       </c>
       <c r="AF11">
-        <v>0.4396932089805301</v>
+        <v>0.7173655820446126</v>
       </c>
       <c r="AG11">
-        <v>0.4339920952186244</v>
+        <v>0.7166662236304114</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AJ11" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AK11" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AL11">
-        <v>-0.1712198597047084</v>
+        <v>-0.1744340110688048</v>
       </c>
       <c r="AM11">
-        <v>0.5657747095271159</v>
+        <v>0.585867111841665</v>
       </c>
       <c r="AN11">
-        <v>-0.03360509406946684</v>
+        <v>-0.2059344731686537</v>
       </c>
       <c r="AO11">
-        <v>-0.4212699702445057</v>
+        <v>-0.6807757311370635</v>
       </c>
       <c r="AP11">
-        <v>-0.3247500522790193</v>
+        <v>-0.6926233149025872</v>
       </c>
       <c r="AQ11">
-        <v>-0.3386557400517989</v>
+        <v>-0.482024643841854</v>
       </c>
       <c r="AR11">
-        <v>0.3371940299437112</v>
+        <v>0.7153250269384762</v>
       </c>
       <c r="AS11">
-        <v>0.2251239832272708</v>
+        <v>0.1236947549394671</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -763,7 +763,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C2" s="2">
         <v>46288</v>
@@ -903,7 +903,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C3" s="2">
         <v>46288</v>
@@ -1043,7 +1043,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C4" s="2">
         <v>46288</v>
@@ -1183,7 +1183,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C5" s="2">
         <v>46288</v>
@@ -1323,7 +1323,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C6" s="2">
         <v>46288</v>
@@ -1463,7 +1463,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C7" s="2">
         <v>46288</v>
@@ -1603,7 +1603,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C8" s="2">
         <v>46288</v>
@@ -1743,7 +1743,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C9" s="2">
         <v>46288</v>
@@ -1883,7 +1883,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C10" s="2">
         <v>46288</v>
@@ -2023,7 +2023,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C11" s="2">
         <v>46288</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="73">
   <si>
     <t>Pair</t>
   </si>
@@ -193,9 +193,6 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
@@ -205,39 +202,24 @@
     <t>空头加速</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>NEUTRAL</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>TRANSITION</t>
-  </si>
-  <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>上涨</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
@@ -245,9 +227,6 @@
   </si>
   <si>
     <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -766,7 +745,7 @@
         <v>46290</v>
       </c>
       <c r="C2" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -778,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.4830108028346309</v>
+        <v>0.72159686465018</v>
       </c>
       <c r="H2">
-        <v>1.080526961917032</v>
+        <v>1.080918131758121</v>
       </c>
       <c r="I2">
-        <v>0.2592965650836586</v>
+        <v>0.2593855444655548</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -796,103 +775,103 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01491595963842547</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.3916859266570835</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.4830108028346309</v>
+        <v>0.72159686465018</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T2">
-        <v>-0.6570892863706981</v>
+        <v>-0.6576729416402983</v>
       </c>
       <c r="U2">
-        <v>0.6955935713688013</v>
+        <v>0.6958944975982615</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2">
+        <v>0.9964948708907034</v>
+      </c>
+      <c r="Y2">
+        <v>0.9997666954405091</v>
+      </c>
+      <c r="Z2">
+        <v>0.00327182454980568</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>-115.2487023089534</v>
+      </c>
+      <c r="AC2">
+        <v>-18</v>
+      </c>
+      <c r="AD2">
+        <v>-0.4265482548042499</v>
+      </c>
+      <c r="AE2">
+        <v>-0.9044648065698569</v>
+      </c>
+      <c r="AF2">
+        <v>1.22098522963009</v>
+      </c>
+      <c r="AG2">
+        <v>1.220700368208946</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>67</v>
       </c>
-      <c r="X2">
-        <v>0.9942282671038949</v>
-      </c>
-      <c r="Y2">
-        <v>0.9996135700079486</v>
-      </c>
-      <c r="Z2">
-        <v>0.005385302904053701</v>
-      </c>
-      <c r="AA2">
-        <v>0.6133263391396896</v>
-      </c>
-      <c r="AB2">
-        <v>-110.3527274422077</v>
-      </c>
-      <c r="AC2">
-        <v>-24</v>
-      </c>
-      <c r="AD2">
-        <v>-0.3477986132223966</v>
-      </c>
-      <c r="AE2">
-        <v>-0.9375692639163135</v>
-      </c>
-      <c r="AF2">
-        <v>1.027675916984822</v>
-      </c>
-      <c r="AG2">
-        <v>1.027278792188391</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>72</v>
-      </c>
       <c r="AK2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL2">
-        <v>-0.2804479163329407</v>
+        <v>-0.4264487391515612</v>
       </c>
       <c r="AM2">
-        <v>0.7099677896516908</v>
+        <v>0.8139638137495891</v>
       </c>
       <c r="AN2">
-        <v>-0.30306000469083</v>
+        <v>-0.4786861000143117</v>
       </c>
       <c r="AO2">
-        <v>-0.9757644934454882</v>
+        <v>-1.118584792062444</v>
       </c>
       <c r="AP2">
-        <v>-0.8842826585876883</v>
+        <v>-1.202583453339989</v>
       </c>
       <c r="AQ2">
-        <v>-0.1393141209674965</v>
+        <v>0.009187576265506802</v>
       </c>
       <c r="AR2">
-        <v>0.8553251341179611</v>
+        <v>1.156643411261429</v>
       </c>
       <c r="AS2">
-        <v>0.1126787443049873</v>
+        <v>0.09279337397242693</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -906,133 +885,133 @@
         <v>46290</v>
       </c>
       <c r="C3" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.2689586953865793</v>
+        <v>0.566725038997936</v>
       </c>
       <c r="H3">
-        <v>2.055403502380753</v>
+        <v>2.060669936097823</v>
       </c>
       <c r="I3">
-        <v>0.454761472922082</v>
+        <v>0.455789742937853</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>225</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N3">
-        <v>-0.1464803531272444</v>
+        <v>-0.145520266059832</v>
       </c>
       <c r="O3">
-        <v>-48.00386104357287</v>
+        <v>-44.75579360363923</v>
       </c>
       <c r="P3">
-        <v>0.3796269220752061</v>
+        <v>0.2048704098246262</v>
       </c>
       <c r="Q3">
-        <v>0.4335434675635367</v>
+        <v>0.7127455021173832</v>
       </c>
       <c r="R3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T3">
-        <v>0.2070180677677997</v>
+        <v>-0.5250351037526458</v>
       </c>
       <c r="U3">
-        <v>0.3680812380767515</v>
+        <v>0.6362120452480466</v>
       </c>
       <c r="V3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="X3">
-        <v>0.9966796895064721</v>
+        <v>0.9979326606587758</v>
       </c>
       <c r="Y3">
-        <v>0.9996924303249665</v>
+        <v>0.999784994237424</v>
       </c>
       <c r="Z3">
-        <v>0.003012740818494342</v>
+        <v>0.001852333578648113</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-96.5215785744879</v>
+        <v>-101.7923206715223</v>
       </c>
       <c r="AC3">
-        <v>-17</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>-0.1135774019538207</v>
+        <v>-0.2043648528338475</v>
       </c>
       <c r="AE3">
-        <v>-0.9935291509389245</v>
+        <v>-0.978894788486587</v>
       </c>
       <c r="AF3">
-        <v>2.270059873850374</v>
+        <v>2.368689988287638</v>
       </c>
       <c r="AG3">
-        <v>2.269361672272667</v>
+        <v>2.3681807062904</v>
       </c>
       <c r="AH3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AI3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK3" t="s">
         <v>70</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>77</v>
-      </c>
       <c r="AL3">
-        <v>-0.1135424689892106</v>
+        <v>-0.2043209132128203</v>
       </c>
       <c r="AM3">
-        <v>0.6959674270694126</v>
+        <v>0.7374858102473283</v>
       </c>
       <c r="AN3">
-        <v>-0.1784819731560597</v>
+        <v>-0.4230599295764431</v>
       </c>
       <c r="AO3">
-        <v>-2.255471694803508</v>
+        <v>-2.325626394417131</v>
       </c>
       <c r="AP3">
-        <v>-1.192907343146901</v>
+        <v>-1.404634614757629</v>
       </c>
       <c r="AQ3">
-        <v>-1.471257199994455</v>
+        <v>-0.5117315277336331</v>
       </c>
       <c r="AR3">
-        <v>1.236629001477036</v>
+        <v>1.360152190851854</v>
       </c>
       <c r="AS3">
-        <v>0.2533209608698126</v>
+        <v>0.1583226239061616</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1046,7 +1025,7 @@
         <v>46290</v>
       </c>
       <c r="C4" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1055,16 +1034,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.7983977380112539</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>2.375811432323905</v>
+        <v>2.606939258271708</v>
       </c>
       <c r="H4">
-        <v>2.081318286271561</v>
+        <v>2.08239858339308</v>
       </c>
       <c r="I4">
-        <v>0.4934574035565198</v>
+        <v>0.4935684210056361</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1076,103 +1055,103 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>0.1973470373947746</v>
+        <v>0.2509921912031103</v>
       </c>
       <c r="O4">
-        <v>6.587645501971473</v>
+        <v>8.652771920323893</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.375811432323905</v>
+        <v>2.606939258271708</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T4">
-        <v>-0.8243571875466386</v>
+        <v>-0.8650041178133678</v>
       </c>
       <c r="U4">
-        <v>0.8906962567325648</v>
+        <v>0.9392125146723864</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
+        <v>64</v>
+      </c>
+      <c r="X4">
+        <v>0.997161110589232</v>
+      </c>
+      <c r="Y4">
+        <v>0.9998426466254836</v>
+      </c>
+      <c r="Z4">
+        <v>0.002681536036251653</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>-136.8853034100549</v>
+      </c>
+      <c r="AC4">
+        <v>-16</v>
+      </c>
+      <c r="AD4">
+        <v>-0.7299869902260921</v>
+      </c>
+      <c r="AE4">
+        <v>-0.6834610406604398</v>
+      </c>
+      <c r="AF4">
+        <v>2.727296075538319</v>
+      </c>
+      <c r="AG4">
+        <v>2.726866926297528</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>67</v>
       </c>
-      <c r="X4">
-        <v>0.9978799983892116</v>
-      </c>
-      <c r="Y4">
-        <v>0.9999034465395575</v>
-      </c>
-      <c r="Z4">
-        <v>0.002023448150345941</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4">
-        <v>-131.3156443052732</v>
-      </c>
-      <c r="AC4">
-        <v>-13.99999999999999</v>
-      </c>
-      <c r="AD4">
-        <v>-0.6602067719977383</v>
-      </c>
-      <c r="AE4">
-        <v>-0.7510838955857904</v>
-      </c>
-      <c r="AF4">
-        <v>2.697210728344293</v>
-      </c>
-      <c r="AG4">
-        <v>2.696950303314928</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>72</v>
-      </c>
       <c r="AK4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL4">
-        <v>-0.6601430267492944</v>
+        <v>-0.7298721243098271</v>
       </c>
       <c r="AM4">
-        <v>0.8893433459388245</v>
+        <v>0.9110237886549594</v>
       </c>
       <c r="AN4">
-        <v>-1.719822012607482</v>
+        <v>-1.92260762015714</v>
       </c>
       <c r="AO4">
-        <v>-2.070348970910865</v>
+        <v>-1.923421855165394</v>
       </c>
       <c r="AP4">
-        <v>-3.335704082077868</v>
+        <v>-3.50897594146149</v>
       </c>
       <c r="AQ4">
-        <v>1.940600048762417</v>
+        <v>2.711789877950863</v>
       </c>
       <c r="AR4">
-        <v>3.086665026183349</v>
+        <v>3.193175629649289</v>
       </c>
       <c r="AS4">
-        <v>0.05789927966228124</v>
+        <v>0.0527815648785832</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1186,7 +1165,7 @@
         <v>46290</v>
       </c>
       <c r="C5" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1198,13 +1177,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1.909240718243277</v>
+        <v>1.937886361804994</v>
       </c>
       <c r="H5">
-        <v>1.524039611477305</v>
+        <v>1.525757664919904</v>
       </c>
       <c r="I5">
-        <v>0.3508079315643451</v>
+        <v>0.3516482356089946</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1216,103 +1195,103 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>0.0105984229042196</v>
+        <v>0.01625529113445391</v>
       </c>
       <c r="O5">
-        <v>2.641586623804074</v>
+        <v>3.883848039634012</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.909240718243277</v>
+        <v>1.937886361804994</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T5">
-        <v>-0.7471010554355209</v>
+        <v>-0.7961588187096806</v>
       </c>
       <c r="U5">
-        <v>0.8861648483533932</v>
+        <v>0.9082160858493072</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
+        <v>64</v>
+      </c>
+      <c r="X5">
+        <v>0.99703139500153</v>
+      </c>
+      <c r="Y5">
+        <v>0.9997784697198041</v>
+      </c>
+      <c r="Z5">
+        <v>0.002747074718274067</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-126.3184359725715</v>
+      </c>
+      <c r="AC5">
+        <v>-17</v>
+      </c>
+      <c r="AD5">
+        <v>-0.5922724704194963</v>
+      </c>
+      <c r="AE5">
+        <v>-0.8057377493844923</v>
+      </c>
+      <c r="AF5">
+        <v>2.529478349406693</v>
+      </c>
+      <c r="AG5">
+        <v>2.528917993359199</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="s">
         <v>67</v>
       </c>
-      <c r="X5">
-        <v>0.9980607427837912</v>
-      </c>
-      <c r="Y5">
-        <v>0.9998774936296352</v>
-      </c>
-      <c r="Z5">
-        <v>0.001816750845843984</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>-119.6151082460876</v>
-      </c>
-      <c r="AC5">
-        <v>-12.99999999999999</v>
-      </c>
-      <c r="AD5">
-        <v>-0.4941711253433494</v>
-      </c>
-      <c r="AE5">
-        <v>-0.8693646524197356</v>
-      </c>
-      <c r="AF5">
-        <v>2.850862581377402</v>
-      </c>
-      <c r="AG5">
-        <v>2.850513332550149</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>72</v>
-      </c>
       <c r="AK5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL5">
-        <v>-0.4941105862324445</v>
+        <v>-0.5921412641331719</v>
       </c>
       <c r="AM5">
-        <v>0.8369653791787706</v>
+        <v>0.8680458577953514</v>
       </c>
       <c r="AN5">
-        <v>-1.341166100762454</v>
+        <v>-1.417510206787846</v>
       </c>
       <c r="AO5">
-        <v>-2.50942208627491</v>
+        <v>-2.085903665482049</v>
       </c>
       <c r="AP5">
-        <v>-2.850159455517604</v>
+        <v>-2.658809421329499</v>
       </c>
       <c r="AQ5">
-        <v>0.9111780842076089</v>
+        <v>1.988827958919698</v>
       </c>
       <c r="AR5">
-        <v>2.682292018941203</v>
+        <v>2.400354864997008</v>
       </c>
       <c r="AS5">
-        <v>0.07495387463071046</v>
+        <v>0.06372231821619306</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1326,7 +1305,7 @@
         <v>46290</v>
       </c>
       <c r="C6" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1338,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.53164505827551</v>
+        <v>1.731094300173867</v>
       </c>
       <c r="H6">
-        <v>0.9587406112476897</v>
+        <v>0.9637151374197928</v>
       </c>
       <c r="I6">
-        <v>0.2576871046750357</v>
+        <v>0.2584993827927147</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1356,103 +1335,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N6">
-        <v>0.2929330983515112</v>
+        <v>0.3632808191684275</v>
       </c>
       <c r="O6">
-        <v>4.972432437219527</v>
+        <v>6.263848104388215</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.53164505827551</v>
+        <v>1.731094300173867</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
       </c>
       <c r="S6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T6">
-        <v>-0.8223711890740208</v>
+        <v>-0.8581893648443246</v>
       </c>
       <c r="U6">
-        <v>0.9200612304297192</v>
+        <v>0.9361672199703406</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
+        <v>64</v>
+      </c>
+      <c r="X6">
+        <v>0.9991045003726073</v>
+      </c>
+      <c r="Y6">
+        <v>0.9999280231615781</v>
+      </c>
+      <c r="Z6">
+        <v>0.0008235227889707986</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>-135.7554670436737</v>
+      </c>
+      <c r="AC6">
+        <v>-9</v>
+      </c>
+      <c r="AD6">
+        <v>-0.7163685218727499</v>
+      </c>
+      <c r="AE6">
+        <v>-0.6977221086291099</v>
+      </c>
+      <c r="AF6">
+        <v>1.825140094474432</v>
+      </c>
+      <c r="AG6">
+        <v>1.825008726660755</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>67</v>
       </c>
-      <c r="X6">
-        <v>0.9996337705315739</v>
-      </c>
-      <c r="Y6">
-        <v>0.9999767813856395</v>
-      </c>
-      <c r="Z6">
-        <v>0.0003430108540656285</v>
-      </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6">
-        <v>-130.1460534722882</v>
-      </c>
-      <c r="AC6">
-        <v>-5.999999999999996</v>
-      </c>
-      <c r="AD6">
-        <v>-0.6447382537574189</v>
-      </c>
-      <c r="AE6">
-        <v>-0.7644034171442682</v>
-      </c>
-      <c r="AF6">
-        <v>1.768933955143183</v>
-      </c>
-      <c r="AG6">
-        <v>1.768892882947849</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>72</v>
-      </c>
       <c r="AK6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL6">
-        <v>-0.6447232838285414</v>
+        <v>-0.7163169599314005</v>
       </c>
       <c r="AM6">
-        <v>0.8849205896684339</v>
+        <v>0.9067913366807934</v>
       </c>
       <c r="AN6">
-        <v>-1.124696659556274</v>
+        <v>-1.283492045000352</v>
       </c>
       <c r="AO6">
-        <v>-1.364512082778895</v>
+        <v>-1.295307354814334</v>
       </c>
       <c r="AP6">
-        <v>-2.072038687377193</v>
+        <v>-2.289981742105469</v>
       </c>
       <c r="AQ6">
-        <v>1.298911310092194</v>
+        <v>1.687538655759319</v>
       </c>
       <c r="AR6">
-        <v>1.916109695271846</v>
+        <v>2.096552420224453</v>
       </c>
       <c r="AS6">
-        <v>0.05661839962510434</v>
+        <v>0.05396018658389255</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1466,7 +1445,7 @@
         <v>46290</v>
       </c>
       <c r="C7" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1478,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.095946280581374</v>
+        <v>2.204056462375657</v>
       </c>
       <c r="H7">
-        <v>1.484959937484297</v>
+        <v>1.48808171393243</v>
       </c>
       <c r="I7">
-        <v>0.3724070675162787</v>
+        <v>0.3733528283151335</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1496,103 +1475,103 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>0.017816796894866</v>
+        <v>0.02581660735146568</v>
       </c>
       <c r="O7">
-        <v>3.563868503045042</v>
+        <v>4.979094956888244</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.095946280581374</v>
+        <v>2.204056462375657</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T7">
-        <v>-0.754933602569243</v>
+        <v>-0.8002262984732403</v>
       </c>
       <c r="U7">
-        <v>0.889705343267465</v>
+        <v>0.9100712051909596</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
+        <v>64</v>
+      </c>
+      <c r="X7">
+        <v>0.9988932287396515</v>
+      </c>
+      <c r="Y7">
+        <v>0.9998774835120062</v>
+      </c>
+      <c r="Z7">
+        <v>0.0009842547723547534</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>-126.9005655230236</v>
+      </c>
+      <c r="AC7">
+        <v>-10</v>
+      </c>
+      <c r="AD7">
+        <v>-0.6004281183751474</v>
+      </c>
+      <c r="AE7">
+        <v>-0.7996787321571581</v>
+      </c>
+      <c r="AF7">
+        <v>2.801404458058002</v>
+      </c>
+      <c r="AG7">
+        <v>2.801061239822351</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>67</v>
       </c>
-      <c r="X7">
-        <v>0.9994295656147978</v>
-      </c>
-      <c r="Y7">
-        <v>0.9999408884452222</v>
-      </c>
-      <c r="Z7">
-        <v>0.0005113228304244322</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>-120.6540198628737</v>
-      </c>
-      <c r="AC7">
-        <v>-6.999999999999997</v>
-      </c>
-      <c r="AD7">
-        <v>-0.5098527180263543</v>
-      </c>
-      <c r="AE7">
-        <v>-0.8602617078082336</v>
-      </c>
-      <c r="AF7">
-        <v>3.023208866105928</v>
-      </c>
-      <c r="AG7">
-        <v>3.023030159529435</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>72</v>
-      </c>
       <c r="AK7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL7">
-        <v>-0.5098225798394841</v>
+        <v>-0.6003545560307914</v>
       </c>
       <c r="AM7">
-        <v>0.8423133093768236</v>
+        <v>0.8707782775731258</v>
       </c>
       <c r="AN7">
-        <v>-1.505982560345274</v>
+        <v>-1.633709510762142</v>
       </c>
       <c r="AO7">
-        <v>-2.619424373215611</v>
+        <v>-2.271893086854237</v>
       </c>
       <c r="AP7">
-        <v>-2.968284586879674</v>
+        <v>-2.916394408212985</v>
       </c>
       <c r="AQ7">
-        <v>1.18822526655318</v>
+        <v>2.274414857222687</v>
       </c>
       <c r="AR7">
-        <v>2.785106010718397</v>
+        <v>2.63505261990162</v>
       </c>
       <c r="AS7">
-        <v>0.07081211324606963</v>
+        <v>0.06204851445747073</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1606,7 +1585,7 @@
         <v>46290</v>
       </c>
       <c r="C8" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1618,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.376780171594311</v>
+        <v>2.488771664565861</v>
       </c>
       <c r="H8">
-        <v>1.459751520383916</v>
+        <v>1.465616817171517</v>
       </c>
       <c r="I8">
-        <v>0.3639059551069527</v>
+        <v>0.3659733472301424</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1636,103 +1615,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8">
-        <v>-0.04958470610677388</v>
+        <v>-0.05648776622170187</v>
       </c>
       <c r="O8">
-        <v>-13.25794280929789</v>
+        <v>-14.59093592442489</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.376780171594311</v>
+        <v>2.488771664565861</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T8">
-        <v>0.9572287493821052</v>
+        <v>0.9753638670405722</v>
       </c>
       <c r="U8">
-        <v>0.9806592389820111</v>
+        <v>0.9888294149974884</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="X8">
-        <v>0.9933690031550378</v>
+        <v>0.994342387898999</v>
       </c>
       <c r="Y8">
-        <v>0.999625207040255</v>
+        <v>0.9996626993169238</v>
       </c>
       <c r="Z8">
-        <v>0.006256203885217193</v>
+        <v>0.005320311417924772</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>23.87346857120675</v>
+        <v>18.06239721480294</v>
       </c>
       <c r="AC8">
-        <v>-25</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.9144414623902793</v>
+        <v>0.9507194214928271</v>
       </c>
       <c r="AE8">
-        <v>0.4047181882020221</v>
+        <v>0.3100525465084012</v>
       </c>
       <c r="AF8">
-        <v>1.997046909424981</v>
+        <v>1.99432121118902</v>
       </c>
       <c r="AG8">
-        <v>1.996298430303048</v>
+        <v>1.993648525282213</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK8" t="s">
         <v>71</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>78</v>
-      </c>
       <c r="AL8">
-        <v>0.9140987361680766</v>
+        <v>0.9503987431825437</v>
       </c>
       <c r="AM8">
-        <v>0.9675472119477917</v>
+        <v>0.9783500314562832</v>
       </c>
       <c r="AN8">
-        <v>1.770806310825148</v>
+        <v>1.85546613991107</v>
       </c>
       <c r="AO8">
-        <v>0.8942736127801956</v>
+        <v>0.699775371572142</v>
       </c>
       <c r="AP8">
-        <v>3.122413841577219</v>
+        <v>3.25965202062125</v>
       </c>
       <c r="AQ8">
-        <v>-2.63079051722874</v>
+        <v>-2.679407041876462</v>
       </c>
       <c r="AR8">
-        <v>2.850120757434095</v>
+        <v>2.98272762231678</v>
       </c>
       <c r="AS8">
-        <v>0.04436032822254267</v>
+        <v>0.04498493168325392</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1746,7 +1725,7 @@
         <v>46290</v>
       </c>
       <c r="C9" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1755,16 +1734,16 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>0.03357562127703215</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2.49205161606413</v>
+        <v>1.857568777251797</v>
       </c>
       <c r="H9">
-        <v>3.11407191188433</v>
+        <v>3.120995471329708</v>
       </c>
       <c r="I9">
-        <v>0.6667965099972272</v>
+        <v>0.6682345756991037</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1776,103 +1755,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N9">
-        <v>0.809069182831836</v>
+        <v>0.8231333107501245</v>
       </c>
       <c r="O9">
-        <v>102.7669076360542</v>
+        <v>96.8270079443935</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.49205161606413</v>
+        <v>1.857568777251797</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9">
+        <v>-0.8754554507866911</v>
+      </c>
+      <c r="U9">
+        <v>0.7937111193351427</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
+        <v>64</v>
+      </c>
+      <c r="X9">
+        <v>0.993425039516516</v>
+      </c>
+      <c r="Y9">
+        <v>0.9990246659245268</v>
+      </c>
+      <c r="Z9">
+        <v>0.005599626408010816</v>
+      </c>
+      <c r="AA9">
+        <v>0.2831373626789613</v>
+      </c>
+      <c r="AB9">
+        <v>135.8800085737004</v>
+      </c>
+      <c r="AC9">
+        <v>-21.99999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>-0.7178834387986207</v>
+      </c>
+      <c r="AE9">
+        <v>0.6961633201330468</v>
+      </c>
+      <c r="AF9">
+        <v>2.029975428895328</v>
+      </c>
+      <c r="AG9">
+        <v>2.027995524687153</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="s">
         <v>65</v>
       </c>
-      <c r="T9">
-        <v>-0.9752996702053002</v>
-      </c>
-      <c r="U9">
-        <v>0.8438188640126402</v>
-      </c>
-      <c r="V9" t="s">
-        <v>56</v>
-      </c>
-      <c r="W9" t="s">
-        <v>67</v>
-      </c>
-      <c r="X9">
-        <v>0.9983991199334046</v>
-      </c>
-      <c r="Y9">
-        <v>0.999590676914801</v>
-      </c>
-      <c r="Z9">
-        <v>0.001191556981396391</v>
-      </c>
-      <c r="AA9">
-        <v>0.3195501221615862</v>
-      </c>
-      <c r="AB9">
-        <v>160.8929859153165</v>
-      </c>
-      <c r="AC9">
-        <v>-11</v>
-      </c>
-      <c r="AD9">
-        <v>-0.9449088474309428</v>
-      </c>
-      <c r="AE9">
-        <v>0.3273335761065877</v>
-      </c>
-      <c r="AF9">
-        <v>2.055750448008612</v>
-      </c>
-      <c r="AG9">
-        <v>2.054908981892834</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI9" t="s">
+      <c r="AJ9" t="s">
         <v>69</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>75</v>
-      </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AL9">
-        <v>-0.6231721093467566</v>
+        <v>-0.4601223200769247</v>
       </c>
       <c r="AM9">
-        <v>0.8433063414120239</v>
+        <v>0.7676310761284897</v>
       </c>
       <c r="AN9">
-        <v>-1.953534880719627</v>
+        <v>-1.499617419309893</v>
       </c>
       <c r="AO9">
-        <v>0.6295166517535071</v>
+        <v>1.348309231129061</v>
       </c>
       <c r="AP9">
-        <v>-2.867520626012551</v>
+        <v>-1.95746081059966</v>
       </c>
       <c r="AQ9">
-        <v>4.217005378068214</v>
+        <v>3.872641928994977</v>
       </c>
       <c r="AR9">
-        <v>2.504716256557524</v>
+        <v>1.646006478955865</v>
       </c>
       <c r="AS9">
-        <v>0.02622049446504374</v>
+        <v>0.02680040746982128</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1886,7 +1865,7 @@
         <v>46290</v>
       </c>
       <c r="C10" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1898,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.2376599206115991</v>
+        <v>0.2841135154704187</v>
       </c>
       <c r="H10">
-        <v>2.104958780599464</v>
+        <v>2.10847483926681</v>
       </c>
       <c r="I10">
-        <v>0.4499804263772595</v>
+        <v>0.4497220351137781</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1916,103 +1895,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10">
-        <v>43.93889379993216</v>
+        <v>44.54844849405576</v>
       </c>
       <c r="O10">
-        <v>37.0111917932101</v>
+        <v>35.14571462718875</v>
       </c>
       <c r="P10">
-        <v>0.5212796104644144</v>
+        <v>0.354046327207779</v>
       </c>
       <c r="Q10">
-        <v>0.4964482938404959</v>
+        <v>0.4398357458705979</v>
       </c>
       <c r="R10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" t="s">
+        <v>63</v>
+      </c>
+      <c r="T10">
+        <v>-0.614006259335212</v>
+      </c>
+      <c r="U10">
+        <v>0.6762239512074667</v>
+      </c>
+      <c r="V10" t="s">
+        <v>56</v>
+      </c>
+      <c r="W10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X10">
+        <v>0.9979604248402657</v>
+      </c>
+      <c r="Y10">
+        <v>0.999684538026485</v>
+      </c>
+      <c r="Z10">
+        <v>0.001724113186219345</v>
+      </c>
+      <c r="AA10">
+        <v>0.4977826390295005</v>
+      </c>
+      <c r="AB10">
+        <v>103.1243080525524</v>
+      </c>
+      <c r="AC10">
+        <v>-13.99999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>-0.2270645017380868</v>
+      </c>
+      <c r="AE10">
+        <v>0.9738797215521198</v>
+      </c>
+      <c r="AF10">
+        <v>1.730129892499474</v>
+      </c>
+      <c r="AG10">
+        <v>1.729584102309149</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI10" t="s">
         <v>65</v>
       </c>
-      <c r="T10">
-        <v>-0.5202907831583916</v>
-      </c>
-      <c r="U10">
-        <v>0.6340495393606566</v>
-      </c>
-      <c r="V10" t="s">
-        <v>56</v>
-      </c>
-      <c r="W10" t="s">
-        <v>67</v>
-      </c>
-      <c r="X10">
-        <v>0.995839666978471</v>
-      </c>
-      <c r="Y10">
-        <v>0.9996747477575215</v>
-      </c>
-      <c r="Z10">
-        <v>0.003835080779050482</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-      <c r="AB10">
-        <v>101.3254505345612</v>
-      </c>
-      <c r="AC10">
-        <v>-19</v>
-      </c>
-      <c r="AD10">
-        <v>-0.1963817096377843</v>
-      </c>
-      <c r="AE10">
-        <v>0.9805275233871515</v>
-      </c>
-      <c r="AF10">
-        <v>2.399958928899351</v>
-      </c>
-      <c r="AG10">
-        <v>2.39917833687587</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>56</v>
-      </c>
-      <c r="AI10" t="s">
+      <c r="AJ10" t="s">
         <v>69</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>75</v>
-      </c>
       <c r="AK10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AL10">
-        <v>-0.1963178360463429</v>
+        <v>-0.1699929910747425</v>
       </c>
       <c r="AM10">
-        <v>0.7405993536458721</v>
+        <v>0.6501038832630816</v>
       </c>
       <c r="AN10">
-        <v>-0.5496875005070285</v>
+        <v>-0.4469555849811924</v>
       </c>
       <c r="AO10">
-        <v>2.325902149472054</v>
+        <v>1.667747666634527</v>
       </c>
       <c r="AP10">
-        <v>0.132020877264693</v>
+        <v>-0.04342638805186327</v>
       </c>
       <c r="AQ10">
-        <v>2.911735307341218</v>
+        <v>1.64989536827254</v>
       </c>
       <c r="AR10">
-        <v>0.5490395199594185</v>
+        <v>0.2156359868502796</v>
       </c>
       <c r="AS10">
-        <v>0.1213421397373044</v>
+        <v>0.1164105558234287</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2026,7 +2005,7 @@
         <v>46290</v>
       </c>
       <c r="C11" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2038,13 +2017,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.313230502143933</v>
+        <v>0.3506227820907868</v>
       </c>
       <c r="H11">
-        <v>2.244529229816875</v>
+        <v>2.228471129578251</v>
       </c>
       <c r="I11">
-        <v>0.5219077851195376</v>
+        <v>0.5177330910534245</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2053,106 +2032,106 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>-2280.660067373872</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>-36.21327088945694</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0.1050098888483531</v>
+        <v>0.03814387567425254</v>
       </c>
       <c r="Q11">
-        <v>0.3499820816353794</v>
+        <v>0.3645272647575751</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T11">
-        <v>-0.7779212152637645</v>
+        <v>-0.7708715311066867</v>
       </c>
       <c r="U11">
-        <v>0.7498208223188599</v>
+        <v>0.7467909939190269</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="X11">
-        <v>0.991463224070397</v>
+        <v>0.9974681728261124</v>
       </c>
       <c r="Y11">
-        <v>0.9990251018006636</v>
+        <v>0.9995952196840717</v>
       </c>
       <c r="Z11">
-        <v>0.00756187773026662</v>
+        <v>0.002127046857959281</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-110.4389089368781</v>
+        <v>-109.1960761664299</v>
       </c>
       <c r="AC11">
-        <v>-27</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AD11">
-        <v>-0.3492084648411762</v>
+        <v>-0.3288019714707134</v>
       </c>
       <c r="AE11">
-        <v>-0.937045061927797</v>
+        <v>-0.9443988900655126</v>
       </c>
       <c r="AF11">
-        <v>0.7173655820446126</v>
+        <v>0.8140448658633753</v>
       </c>
       <c r="AG11">
-        <v>0.7166662236304114</v>
+        <v>0.8137153565253914</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="AK11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AL11">
-        <v>-0.1744340110688048</v>
+        <v>-0.1643344394524118</v>
       </c>
       <c r="AM11">
-        <v>0.585867111841665</v>
+        <v>0.5838487033228706</v>
       </c>
       <c r="AN11">
-        <v>-0.2059344731686537</v>
+        <v>-0.2435543012591954</v>
       </c>
       <c r="AO11">
-        <v>-0.6807757311370635</v>
+        <v>-0.7745960668631813</v>
       </c>
       <c r="AP11">
-        <v>-0.6926233149025872</v>
+        <v>-0.5990815336725037</v>
       </c>
       <c r="AQ11">
-        <v>-0.482024643841854</v>
+        <v>0.03399497494145383</v>
       </c>
       <c r="AR11">
-        <v>0.7153250269384762</v>
+        <v>0.5748397811172627</v>
       </c>
       <c r="AS11">
-        <v>0.1236947549394671</v>
+        <v>0.09766810005178962</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -742,10 +742,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46291</v>
+      </c>
+      <c r="C2" s="2">
         <v>46290</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46289</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -757,13 +757,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.72159686465018</v>
+        <v>0.7854436532796554</v>
       </c>
       <c r="H2">
-        <v>1.080918131758121</v>
+        <v>1.08127204732863</v>
       </c>
       <c r="I2">
-        <v>0.2593855444655548</v>
+        <v>0.2594586945279614</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -775,19 +775,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2">
-        <v>0.01491595963842547</v>
+        <v>0.03467249514915023</v>
       </c>
       <c r="O2">
-        <v>0.3916859266570835</v>
+        <v>0.8987168260536653</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.72159686465018</v>
+        <v>0.7854436532796554</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -796,10 +796,10 @@
         <v>61</v>
       </c>
       <c r="T2">
-        <v>-0.6576729416402983</v>
+        <v>-0.6883344829636022</v>
       </c>
       <c r="U2">
-        <v>0.6958944975982615</v>
+        <v>0.7097055200273884</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -808,34 +808,34 @@
         <v>64</v>
       </c>
       <c r="X2">
-        <v>0.9964948708907034</v>
+        <v>0.9974786857007411</v>
       </c>
       <c r="Y2">
-        <v>0.9997666954405091</v>
+        <v>0.9998200107750694</v>
       </c>
       <c r="Z2">
-        <v>0.00327182454980568</v>
+        <v>0.002341325074328382</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-115.2487023089534</v>
+        <v>-118.5497975325826</v>
       </c>
       <c r="AC2">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="AD2">
-        <v>-0.4265482548042499</v>
+        <v>-0.4779223870539749</v>
       </c>
       <c r="AE2">
-        <v>-0.9044648065698569</v>
+        <v>-0.8784020673658678</v>
       </c>
       <c r="AF2">
-        <v>1.22098522963009</v>
+        <v>1.22831605599548</v>
       </c>
       <c r="AG2">
-        <v>1.220700368208946</v>
+        <v>1.228094972340592</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -850,28 +850,28 @@
         <v>70</v>
       </c>
       <c r="AL2">
-        <v>-0.4264487391515612</v>
+        <v>-0.4778363661739521</v>
       </c>
       <c r="AM2">
-        <v>0.8139638137495891</v>
+        <v>0.8317376753168102</v>
       </c>
       <c r="AN2">
-        <v>-0.4786861000143117</v>
+        <v>-0.5516853420326328</v>
       </c>
       <c r="AO2">
-        <v>-1.118584792062444</v>
+        <v>-1.093985872863719</v>
       </c>
       <c r="AP2">
-        <v>-1.202583453339989</v>
+        <v>-1.18034673663606</v>
       </c>
       <c r="AQ2">
-        <v>0.009187576265506802</v>
+        <v>0.5677450671431065</v>
       </c>
       <c r="AR2">
-        <v>1.156643411261429</v>
+        <v>1.084772897096356</v>
       </c>
       <c r="AS2">
-        <v>0.09279337397242693</v>
+        <v>0.07717363047104363</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -882,7 +882,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C3" s="2">
         <v>46289</v>
@@ -1022,7 +1022,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C4" s="2">
         <v>46289</v>
@@ -1162,7 +1162,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C5" s="2">
         <v>46289</v>
@@ -1302,7 +1302,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C6" s="2">
         <v>46289</v>
@@ -1442,7 +1442,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C7" s="2">
         <v>46289</v>
@@ -1582,7 +1582,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C8" s="2">
         <v>46289</v>
@@ -1722,7 +1722,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C9" s="2">
         <v>46289</v>
@@ -1862,7 +1862,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C10" s="2">
         <v>46289</v>
@@ -2002,7 +2002,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C11" s="2">
         <v>46289</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -742,7 +742,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C2" s="2">
         <v>46290</v>
@@ -882,10 +882,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C3" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -897,13 +897,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.566725038997936</v>
+        <v>0.9932868956067169</v>
       </c>
       <c r="H3">
-        <v>2.060669936097823</v>
+        <v>2.065434804698981</v>
       </c>
       <c r="I3">
-        <v>0.455789742937853</v>
+        <v>0.4566680310549422</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -912,22 +912,22 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>-0.145520266059832</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>-44.75579360363923</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.2048704098246262</v>
+        <v>0.05564030419769859</v>
       </c>
       <c r="Q3">
-        <v>0.7127455021173832</v>
+        <v>1.05180991948502</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -936,10 +936,10 @@
         <v>61</v>
       </c>
       <c r="T3">
-        <v>-0.5250351037526458</v>
+        <v>-0.5645177567596933</v>
       </c>
       <c r="U3">
-        <v>0.6362120452480466</v>
+        <v>0.6539994770128366</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -948,34 +948,34 @@
         <v>64</v>
       </c>
       <c r="X3">
-        <v>0.9979326606587758</v>
+        <v>0.9989173894192011</v>
       </c>
       <c r="Y3">
-        <v>0.999784994237424</v>
+        <v>0.9998659458838982</v>
       </c>
       <c r="Z3">
-        <v>0.001852333578648113</v>
+        <v>0.0009485564646971589</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-101.7923206715223</v>
+        <v>-105.6956783367861</v>
       </c>
       <c r="AC3">
-        <v>-12.99999999999999</v>
+        <v>-9</v>
       </c>
       <c r="AD3">
-        <v>-0.2043648528338475</v>
+        <v>-0.2705278320129815</v>
       </c>
       <c r="AE3">
-        <v>-0.978894788486587</v>
+        <v>-0.9627121543360487</v>
       </c>
       <c r="AF3">
-        <v>2.368689988287638</v>
+        <v>2.746041155134045</v>
       </c>
       <c r="AG3">
-        <v>2.3681807062904</v>
+        <v>2.745673037014214</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -990,28 +990,28 @@
         <v>70</v>
       </c>
       <c r="AL3">
-        <v>-0.2043209132128203</v>
+        <v>-0.27049156664358</v>
       </c>
       <c r="AM3">
-        <v>0.7374858102473283</v>
+        <v>0.7641073423462377</v>
       </c>
       <c r="AN3">
-        <v>-0.4230599295764431</v>
+        <v>-0.6965267282036537</v>
       </c>
       <c r="AO3">
-        <v>-2.325626394417131</v>
+        <v>-2.653163019204379</v>
       </c>
       <c r="AP3">
-        <v>-1.404634614757629</v>
+        <v>-1.758527870195961</v>
       </c>
       <c r="AQ3">
-        <v>-0.5117315277336331</v>
+        <v>0.1702143361458303</v>
       </c>
       <c r="AR3">
-        <v>1.360152190851854</v>
+        <v>1.650793431524987</v>
       </c>
       <c r="AS3">
-        <v>0.1583226239061616</v>
+        <v>0.1133605887801404</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1022,10 +1022,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C4" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1034,16 +1034,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0.9148333723278068</v>
       </c>
       <c r="G4">
-        <v>2.606939258271708</v>
+        <v>2.493281471206344</v>
       </c>
       <c r="H4">
-        <v>2.08239858339308</v>
+        <v>2.083630976431574</v>
       </c>
       <c r="I4">
-        <v>0.4935684210056361</v>
+        <v>0.4937530609893399</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1055,19 +1055,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>0.2509921912031103</v>
+        <v>0.3070736204848126</v>
       </c>
       <c r="O4">
-        <v>8.652771920323893</v>
+        <v>10.27984382302097</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.606939258271708</v>
+        <v>2.493281471206344</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1076,10 +1076,10 @@
         <v>61</v>
       </c>
       <c r="T4">
-        <v>-0.8650041178133678</v>
+        <v>-0.9005834154530278</v>
       </c>
       <c r="U4">
-        <v>0.9392125146723864</v>
+        <v>0.9424138742155972</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1088,34 +1088,34 @@
         <v>64</v>
       </c>
       <c r="X4">
-        <v>0.997161110589232</v>
+        <v>0.9956313638485386</v>
       </c>
       <c r="Y4">
-        <v>0.9998426466254836</v>
+        <v>0.9997053256502548</v>
       </c>
       <c r="Z4">
-        <v>0.002681536036251653</v>
+        <v>0.004073961801716264</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-136.8853034100549</v>
+        <v>-143.5032023394873</v>
       </c>
       <c r="AC4">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="AD4">
-        <v>-0.7299869902260921</v>
+        <v>-0.8038901048208</v>
       </c>
       <c r="AE4">
-        <v>-0.6834610406604398</v>
+        <v>-0.5947778571628261</v>
       </c>
       <c r="AF4">
-        <v>2.727296075538319</v>
+        <v>2.440060508764631</v>
       </c>
       <c r="AG4">
-        <v>2.726866926297528</v>
+        <v>2.439341485520872</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1130,28 +1130,28 @@
         <v>70</v>
       </c>
       <c r="AL4">
-        <v>-0.7298721243098271</v>
+        <v>-0.8036532190268953</v>
       </c>
       <c r="AM4">
-        <v>0.9110237886549594</v>
+        <v>0.9342438322494659</v>
       </c>
       <c r="AN4">
-        <v>-1.92260762015714</v>
+        <v>-1.887874379105325</v>
       </c>
       <c r="AO4">
-        <v>-1.923421855165394</v>
+        <v>-1.529025323777559</v>
       </c>
       <c r="AP4">
-        <v>-3.50897594146149</v>
+        <v>-3.149732462578228</v>
       </c>
       <c r="AQ4">
-        <v>2.711789877950863</v>
+        <v>3.462882975329206</v>
       </c>
       <c r="AR4">
-        <v>3.193175629649289</v>
+        <v>2.781737744488757</v>
       </c>
       <c r="AS4">
-        <v>0.0527815648785832</v>
+        <v>0.04546708782908851</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1162,10 +1162,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C5" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1177,13 +1177,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1.937886361804994</v>
+        <v>2.129473063872976</v>
       </c>
       <c r="H5">
-        <v>1.525757664919904</v>
+        <v>1.527975134195223</v>
       </c>
       <c r="I5">
-        <v>0.3516482356089946</v>
+        <v>0.3525153895196541</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1195,19 +1195,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>0.01625529113445391</v>
+        <v>0.02253113271321679</v>
       </c>
       <c r="O5">
-        <v>3.883848039634012</v>
+        <v>5.405927300514748</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.937886361804994</v>
+        <v>2.129473063872976</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1216,10 +1216,10 @@
         <v>61</v>
       </c>
       <c r="T5">
-        <v>-0.7961588187096806</v>
+        <v>-0.8077528568583739</v>
       </c>
       <c r="U5">
-        <v>0.9082160858493072</v>
+        <v>0.9134586544216092</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1228,34 +1228,34 @@
         <v>64</v>
       </c>
       <c r="X5">
-        <v>0.99703139500153</v>
+        <v>0.9984001462343809</v>
       </c>
       <c r="Y5">
-        <v>0.9997784697198041</v>
+        <v>0.9998794753413637</v>
       </c>
       <c r="Z5">
-        <v>0.002747074718274067</v>
+        <v>0.001479329106982785</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-126.3184359725715</v>
+        <v>-127.9869909050153</v>
       </c>
       <c r="AC5">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="AD5">
-        <v>-0.5922724704194963</v>
+        <v>-0.6154825404024911</v>
       </c>
       <c r="AE5">
-        <v>-0.8057377493844923</v>
+        <v>-0.7881505201798042</v>
       </c>
       <c r="AF5">
-        <v>2.529478349406693</v>
+        <v>2.672770356969893</v>
       </c>
       <c r="AG5">
-        <v>2.528917993359199</v>
+        <v>2.672448222235006</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1270,28 +1270,28 @@
         <v>70</v>
       </c>
       <c r="AL5">
-        <v>-0.5921412641331719</v>
+        <v>-0.6154083595794124</v>
       </c>
       <c r="AM5">
-        <v>0.8680458577953514</v>
+        <v>0.8760997784776414</v>
       </c>
       <c r="AN5">
-        <v>-1.417510206787846</v>
+        <v>-1.588081467671415</v>
       </c>
       <c r="AO5">
-        <v>-2.085903665482049</v>
+        <v>-2.144495083360733</v>
       </c>
       <c r="AP5">
-        <v>-2.658809421329499</v>
+        <v>-2.788446245796797</v>
       </c>
       <c r="AQ5">
-        <v>1.988827958919698</v>
+        <v>2.57285487600075</v>
       </c>
       <c r="AR5">
-        <v>2.400354864997008</v>
+        <v>2.486618874765054</v>
       </c>
       <c r="AS5">
-        <v>0.06372231821619306</v>
+        <v>0.05668533341722131</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1302,10 +1302,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C6" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1317,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.731094300173867</v>
+        <v>1.680550403729014</v>
       </c>
       <c r="H6">
-        <v>0.9637151374197928</v>
+        <v>0.9686837632029885</v>
       </c>
       <c r="I6">
-        <v>0.2584993827927147</v>
+        <v>0.2595313339248795</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N6">
-        <v>0.3632808191684275</v>
+        <v>0.4383421996337605</v>
       </c>
       <c r="O6">
-        <v>6.263848104388215</v>
+        <v>7.421801507961066</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.731094300173867</v>
+        <v>1.680550403729014</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
@@ -1356,10 +1356,10 @@
         <v>61</v>
       </c>
       <c r="T6">
-        <v>-0.8581893648443246</v>
+        <v>-0.8855271921817665</v>
       </c>
       <c r="U6">
-        <v>0.9361672199703406</v>
+        <v>0.9484558051191534</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1368,34 +1368,34 @@
         <v>64</v>
       </c>
       <c r="X6">
-        <v>0.9991045003726073</v>
+        <v>0.9986046254089905</v>
       </c>
       <c r="Y6">
-        <v>0.9999280231615781</v>
+        <v>0.9998742745494339</v>
       </c>
       <c r="Z6">
-        <v>0.0008235227889707986</v>
+        <v>0.001269649140443363</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-135.7554670436737</v>
+        <v>-140.4473711516528</v>
       </c>
       <c r="AC6">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="AD6">
-        <v>-0.7163685218727499</v>
+        <v>-0.7710399904085061</v>
       </c>
       <c r="AE6">
-        <v>-0.6977221086291099</v>
+        <v>-0.6367867250428912</v>
       </c>
       <c r="AF6">
-        <v>1.825140094474432</v>
+        <v>1.697376826024428</v>
       </c>
       <c r="AG6">
-        <v>1.825008726660755</v>
+        <v>1.697163422558196</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1410,28 +1410,28 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>-0.7163169599314005</v>
+        <v>-0.7709430510583075</v>
       </c>
       <c r="AM6">
-        <v>0.9067913366807934</v>
+        <v>0.9242730690792125</v>
       </c>
       <c r="AN6">
-        <v>-1.283492045000352</v>
+        <v>-1.281459118945528</v>
       </c>
       <c r="AO6">
-        <v>-1.295307354814334</v>
+        <v>-1.109466462516039</v>
       </c>
       <c r="AP6">
-        <v>-2.289981742105469</v>
+        <v>-2.07682591302683</v>
       </c>
       <c r="AQ6">
-        <v>1.687538655759319</v>
+        <v>2.337058766020589</v>
       </c>
       <c r="AR6">
-        <v>2.096552420224453</v>
+        <v>1.830539036054295</v>
       </c>
       <c r="AS6">
-        <v>0.05396018658389255</v>
+        <v>0.0466328275709414</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1442,10 +1442,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C7" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.204056462375657</v>
+        <v>2.433491918712662</v>
       </c>
       <c r="H7">
-        <v>1.48808171393243</v>
+        <v>1.49349504330372</v>
       </c>
       <c r="I7">
-        <v>0.3733528283151335</v>
+        <v>0.3745812891432713</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1475,19 +1475,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>0.02581660735146568</v>
+        <v>0.03471399276487881</v>
       </c>
       <c r="O7">
-        <v>4.979094956888244</v>
+        <v>6.853700447162623</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.204056462375657</v>
+        <v>2.433491918712662</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
@@ -1496,10 +1496,10 @@
         <v>61</v>
       </c>
       <c r="T7">
-        <v>-0.8002262984732403</v>
+        <v>-0.8071098751366853</v>
       </c>
       <c r="U7">
-        <v>0.9100712051909596</v>
+        <v>0.9131857171886492</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1508,34 +1508,34 @@
         <v>64</v>
       </c>
       <c r="X7">
-        <v>0.9988932287396515</v>
+        <v>0.9995584060950488</v>
       </c>
       <c r="Y7">
-        <v>0.9998774835120062</v>
+        <v>0.9999450935085634</v>
       </c>
       <c r="Z7">
-        <v>0.0009842547723547534</v>
+        <v>0.0003866874135146636</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-126.9005655230236</v>
+        <v>-127.894478809305</v>
       </c>
       <c r="AC7">
-        <v>-10</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD7">
-        <v>-0.6004281183751474</v>
+        <v>-0.6142091587718395</v>
       </c>
       <c r="AE7">
-        <v>-0.7996787321571581</v>
+        <v>-0.7891432755088199</v>
       </c>
       <c r="AF7">
-        <v>2.801404458058002</v>
+        <v>3.046913628950144</v>
       </c>
       <c r="AG7">
-        <v>2.801061239822351</v>
+        <v>3.046746333613068</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1550,28 +1550,28 @@
         <v>70</v>
       </c>
       <c r="AL7">
-        <v>-0.6003545560307914</v>
+        <v>-0.614175434701923</v>
       </c>
       <c r="AM7">
-        <v>0.8707782775731258</v>
+        <v>0.8759707461057231</v>
       </c>
       <c r="AN7">
-        <v>-1.633709510762142</v>
+        <v>-1.840866142847872</v>
       </c>
       <c r="AO7">
-        <v>-2.271893086854237</v>
+        <v>-2.426251652530377</v>
       </c>
       <c r="AP7">
-        <v>-2.916394408212985</v>
+        <v>-3.063933652710714</v>
       </c>
       <c r="AQ7">
-        <v>2.274414857222687</v>
+        <v>3.14378323842924</v>
       </c>
       <c r="AR7">
-        <v>2.63505261990162</v>
+        <v>2.709019752958548</v>
       </c>
       <c r="AS7">
-        <v>0.06204851445747073</v>
+        <v>0.05515189502550502</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1582,10 +1582,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C8" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1597,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.488771664565861</v>
+        <v>2.771955978776556</v>
       </c>
       <c r="H8">
-        <v>1.465616817171517</v>
+        <v>1.473436547489832</v>
       </c>
       <c r="I8">
-        <v>0.3659733472301424</v>
+        <v>0.368490582696668</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1615,19 +1615,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8">
-        <v>-0.05648776622170187</v>
+        <v>-0.06385511093960826</v>
       </c>
       <c r="O8">
-        <v>-14.59093592442489</v>
+        <v>-17.61693867680597</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.488771664565861</v>
+        <v>2.771955978776556</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
@@ -1636,10 +1636,10 @@
         <v>62</v>
       </c>
       <c r="T8">
-        <v>0.9753638670405722</v>
+        <v>0.966604633832096</v>
       </c>
       <c r="U8">
-        <v>0.9888294149974884</v>
+        <v>0.9849232799787089</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1648,34 +1648,34 @@
         <v>64</v>
       </c>
       <c r="X8">
-        <v>0.994342387898999</v>
+        <v>0.9981184323924035</v>
       </c>
       <c r="Y8">
-        <v>0.9996626993169238</v>
+        <v>0.9998047790170624</v>
       </c>
       <c r="Z8">
-        <v>0.005320311417924772</v>
+        <v>0.001686346624658941</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>18.06239721480294</v>
+        <v>21.06030066615424</v>
       </c>
       <c r="AC8">
-        <v>-22.99999999999999</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD8">
-        <v>0.9507194214928271</v>
+        <v>0.9332027469149962</v>
       </c>
       <c r="AE8">
-        <v>0.3100525465084012</v>
+        <v>0.3593502930989561</v>
       </c>
       <c r="AF8">
-        <v>1.99432121118902</v>
+        <v>2.259589516151934</v>
       </c>
       <c r="AG8">
-        <v>1.993648525282213</v>
+        <v>2.259148396865556</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1690,28 +1690,28 @@
         <v>71</v>
       </c>
       <c r="AL8">
-        <v>0.9503987431825437</v>
+        <v>0.9330205661574634</v>
       </c>
       <c r="AM8">
-        <v>0.9783500314562832</v>
+        <v>0.9733599994677484</v>
       </c>
       <c r="AN8">
-        <v>1.85546613991107</v>
+        <v>2.083345892564772</v>
       </c>
       <c r="AO8">
-        <v>0.699775371572142</v>
+        <v>0.8638397659875174</v>
       </c>
       <c r="AP8">
-        <v>3.25965202062125</v>
+        <v>3.558600649852225</v>
       </c>
       <c r="AQ8">
-        <v>-2.679407041876462</v>
+        <v>-3.261242385719994</v>
       </c>
       <c r="AR8">
-        <v>2.98272762231678</v>
+        <v>3.226954040271941</v>
       </c>
       <c r="AS8">
-        <v>0.04498493168325392</v>
+        <v>0.04354998175148109</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1722,10 +1722,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C9" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.857568777251797</v>
+        <v>1.553656358261324</v>
       </c>
       <c r="H9">
-        <v>3.120995471329708</v>
+        <v>3.127259644161241</v>
       </c>
       <c r="I9">
-        <v>0.6682345756991037</v>
+        <v>0.6691965418736109</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1755,19 +1755,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N9">
-        <v>0.8231333107501245</v>
+        <v>0.834836405122935</v>
       </c>
       <c r="O9">
-        <v>96.8270079443935</v>
+        <v>99.63097495287241</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>0.004538955066842571</v>
       </c>
       <c r="Q9">
-        <v>1.857568777251797</v>
+        <v>1.560740489212863</v>
       </c>
       <c r="R9" t="s">
         <v>60</v>
@@ -1776,10 +1776,10 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.8754554507866911</v>
+        <v>-0.7441634316464502</v>
       </c>
       <c r="U9">
-        <v>0.7937111193351427</v>
+        <v>0.7347092904436736</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1788,34 +1788,34 @@
         <v>64</v>
       </c>
       <c r="X9">
-        <v>0.993425039516516</v>
+        <v>0.9956899706691014</v>
       </c>
       <c r="Y9">
-        <v>0.9990246659245268</v>
+        <v>0.9993429848110841</v>
       </c>
       <c r="Z9">
-        <v>0.005599626408010816</v>
+        <v>0.003653014141982713</v>
       </c>
       <c r="AA9">
-        <v>0.2831373626789613</v>
+        <v>0.6314948200763472</v>
       </c>
       <c r="AB9">
-        <v>135.8800085737004</v>
+        <v>121.1266661180417</v>
       </c>
       <c r="AC9">
-        <v>-21.99999999999999</v>
+        <v>-18</v>
       </c>
       <c r="AD9">
-        <v>-0.7178834387986207</v>
+        <v>-0.516931789508032</v>
       </c>
       <c r="AE9">
-        <v>0.6961633201330468</v>
+        <v>0.856026591290261</v>
       </c>
       <c r="AF9">
-        <v>2.029975428895328</v>
+        <v>2.360279607884177</v>
       </c>
       <c r="AG9">
-        <v>2.027995524687153</v>
+        <v>2.358728868331709</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1830,28 +1830,28 @@
         <v>72</v>
       </c>
       <c r="AL9">
-        <v>-0.4601223200769247</v>
+        <v>-0.4214087145027491</v>
       </c>
       <c r="AM9">
-        <v>0.7676310761284897</v>
+        <v>0.7760809504182696</v>
       </c>
       <c r="AN9">
-        <v>-1.499617419309893</v>
+        <v>-1.271926308750624</v>
       </c>
       <c r="AO9">
-        <v>1.348309231129061</v>
+        <v>1.976159184924614</v>
       </c>
       <c r="AP9">
-        <v>-1.95746081059966</v>
+        <v>-1.59135535249199</v>
       </c>
       <c r="AQ9">
-        <v>3.872641928994977</v>
+        <v>3.276585817871569</v>
       </c>
       <c r="AR9">
-        <v>1.646006478955865</v>
+        <v>1.352819908812047</v>
       </c>
       <c r="AS9">
-        <v>0.02680040746982128</v>
+        <v>0.03378396755525835</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1862,10 +1862,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C10" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.2841135154704187</v>
+        <v>0.4656618797617593</v>
       </c>
       <c r="H10">
-        <v>2.10847483926681</v>
+        <v>2.111656035203933</v>
       </c>
       <c r="I10">
-        <v>0.4497220351137781</v>
+        <v>0.4496128010101789</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1895,19 +1895,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N10">
-        <v>44.54844849405576</v>
+        <v>45.09844138244251</v>
       </c>
       <c r="O10">
-        <v>35.14571462718875</v>
+        <v>42.01065801811109</v>
       </c>
       <c r="P10">
-        <v>0.354046327207779</v>
+        <v>0.1435783044370041</v>
       </c>
       <c r="Q10">
-        <v>0.4398357458705979</v>
+        <v>0.5437296628218202</v>
       </c>
       <c r="R10" t="s">
         <v>60</v>
@@ -1916,10 +1916,10 @@
         <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.614006259335212</v>
+        <v>-0.6372822385028896</v>
       </c>
       <c r="U10">
-        <v>0.6762239512074667</v>
+        <v>0.6866487673838128</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
@@ -1928,34 +1928,34 @@
         <v>64</v>
       </c>
       <c r="X10">
-        <v>0.9979604248402657</v>
+        <v>0.9992719902673382</v>
       </c>
       <c r="Y10">
-        <v>0.999684538026485</v>
+        <v>0.9994870402300498</v>
       </c>
       <c r="Z10">
-        <v>0.001724113186219345</v>
+        <v>0.0002150499627115998</v>
       </c>
       <c r="AA10">
-        <v>0.4977826390295005</v>
+        <v>0.4989245714908739</v>
       </c>
       <c r="AB10">
-        <v>103.1243080525524</v>
+        <v>105.9025552549323</v>
       </c>
       <c r="AC10">
-        <v>-13.99999999999999</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD10">
-        <v>-0.2270645017380868</v>
+        <v>-0.2740021097855445</v>
       </c>
       <c r="AE10">
-        <v>0.9738797215521198</v>
+        <v>0.961729090665906</v>
       </c>
       <c r="AF10">
-        <v>1.730129892499474</v>
+        <v>1.736216886912628</v>
       </c>
       <c r="AG10">
-        <v>1.729584102309149</v>
+        <v>1.735326277497734</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
@@ -1970,28 +1970,28 @@
         <v>72</v>
       </c>
       <c r="AL10">
-        <v>-0.1699929910747425</v>
+        <v>-0.205248909031391</v>
       </c>
       <c r="AM10">
-        <v>0.6501038832630816</v>
+        <v>0.6680714303987534</v>
       </c>
       <c r="AN10">
-        <v>-0.4469555849811924</v>
+        <v>-0.4969293061111932</v>
       </c>
       <c r="AO10">
-        <v>1.667747666634527</v>
+        <v>1.662264372548948</v>
       </c>
       <c r="AP10">
-        <v>-0.04342638805186327</v>
+        <v>-0.2879211642521388</v>
       </c>
       <c r="AQ10">
-        <v>1.64989536827254</v>
+        <v>1.0851574638904</v>
       </c>
       <c r="AR10">
-        <v>0.2156359868502796</v>
+        <v>0.2744702378443663</v>
       </c>
       <c r="AS10">
-        <v>0.1164105558234287</v>
+        <v>0.09156387277068113</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2002,10 +2002,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C11" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2017,13 +2017,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.3506227820907868</v>
+        <v>0.461376602456803</v>
       </c>
       <c r="H11">
-        <v>2.228471129578251</v>
+        <v>2.213942372219496</v>
       </c>
       <c r="I11">
-        <v>0.5177330910534245</v>
+        <v>0.5140111663621287</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2035,19 +2035,19 @@
         <v>213</v>
       </c>
       <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>17.93401925713394</v>
+      </c>
+      <c r="O11">
+        <v>0.2897440636087854</v>
+      </c>
+      <c r="P11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0.03814387567425254</v>
-      </c>
       <c r="Q11">
-        <v>0.3645272647575751</v>
+        <v>0.461376602456803</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2056,10 +2056,10 @@
         <v>61</v>
       </c>
       <c r="T11">
-        <v>-0.7708715311066867</v>
+        <v>-0.76950823222412</v>
       </c>
       <c r="U11">
-        <v>0.7467909939190269</v>
+        <v>0.7462381362649918</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2068,34 +2068,34 @@
         <v>64</v>
       </c>
       <c r="X11">
-        <v>0.9974681728261124</v>
+        <v>0.9993462258891704</v>
       </c>
       <c r="Y11">
-        <v>0.9995952196840717</v>
+        <v>0.9998377270565512</v>
       </c>
       <c r="Z11">
-        <v>0.002127046857959281</v>
+        <v>0.0004915011673807257</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>-109.1960761664299</v>
+        <v>-108.9605010459745</v>
       </c>
       <c r="AC11">
-        <v>-13.99999999999999</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD11">
-        <v>-0.3288019714707134</v>
+        <v>-0.3249162491209054</v>
       </c>
       <c r="AE11">
-        <v>-0.9443988900655126</v>
+        <v>-0.9457427932885356</v>
       </c>
       <c r="AF11">
-        <v>0.8140448658633753</v>
+        <v>1.046046605310706</v>
       </c>
       <c r="AG11">
-        <v>0.8137153565253914</v>
+        <v>1.045876860249077</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2110,28 +2110,28 @@
         <v>70</v>
       </c>
       <c r="AL11">
-        <v>-0.1643344394524118</v>
+        <v>-0.1624317620023931</v>
       </c>
       <c r="AM11">
-        <v>0.5838487033228706</v>
+        <v>0.5854529060921151</v>
       </c>
       <c r="AN11">
-        <v>-0.2435543012591954</v>
+        <v>-0.325902664262283</v>
       </c>
       <c r="AO11">
-        <v>-0.7745960668631813</v>
+        <v>-0.9932626463738097</v>
       </c>
       <c r="AP11">
-        <v>-0.5990815336725037</v>
+        <v>-0.6796074969203546</v>
       </c>
       <c r="AQ11">
-        <v>0.03399497494145383</v>
+        <v>0.2419988380794569</v>
       </c>
       <c r="AR11">
-        <v>0.5748397811172627</v>
+        <v>0.6383726808067267</v>
       </c>
       <c r="AS11">
-        <v>0.09766810005178962</v>
+        <v>0.07976782075966257</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -742,10 +742,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C2" s="2">
         <v>46293</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46290</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -754,16 +754,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1139093758378123</v>
       </c>
       <c r="G2">
-        <v>0.7854436532796554</v>
+        <v>0.8812195371627741</v>
       </c>
       <c r="H2">
-        <v>1.08127204732863</v>
+        <v>1.081592256654329</v>
       </c>
       <c r="I2">
-        <v>0.2594586945279614</v>
+        <v>0.2594892325167979</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -775,19 +775,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>0.03467249514915023</v>
+        <v>0.0578653068683871</v>
       </c>
       <c r="O2">
-        <v>0.8987168260536653</v>
+        <v>1.467332541491438</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.7854436532796554</v>
+        <v>0.8812195371627741</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -796,10 +796,10 @@
         <v>61</v>
       </c>
       <c r="T2">
-        <v>-0.6883344829636022</v>
+        <v>-0.7168960933814398</v>
       </c>
       <c r="U2">
-        <v>0.7097055200273884</v>
+        <v>0.7396580646989981</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -808,34 +808,34 @@
         <v>64</v>
       </c>
       <c r="X2">
-        <v>0.9974786857007411</v>
+        <v>0.9984431301870489</v>
       </c>
       <c r="Y2">
-        <v>0.9998200107750694</v>
+        <v>0.9998736652067134</v>
       </c>
       <c r="Z2">
-        <v>0.002341325074328382</v>
+        <v>0.001430535019664503</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-118.5497975325826</v>
+        <v>-121.0171635773847</v>
       </c>
       <c r="AC2">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="AD2">
-        <v>-0.4779223870539749</v>
+        <v>-0.5152948256368708</v>
       </c>
       <c r="AE2">
-        <v>-0.8784020673658678</v>
+        <v>-0.8570129769565143</v>
       </c>
       <c r="AF2">
-        <v>1.22831605599548</v>
+        <v>1.290483447979541</v>
       </c>
       <c r="AG2">
-        <v>1.228094972340592</v>
+        <v>1.290320415019901</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -850,28 +850,28 @@
         <v>70</v>
       </c>
       <c r="AL2">
-        <v>-0.4778363661739521</v>
+        <v>-0.5152297259715923</v>
       </c>
       <c r="AM2">
-        <v>0.8317376753168102</v>
+        <v>0.844495057941078</v>
       </c>
       <c r="AN2">
-        <v>-0.5516853420326328</v>
+        <v>-0.6365195457344136</v>
       </c>
       <c r="AO2">
-        <v>-1.093985872863719</v>
+        <v>-1.120271831010521</v>
       </c>
       <c r="AP2">
-        <v>-1.18034673663606</v>
+        <v>-1.246666538707811</v>
       </c>
       <c r="AQ2">
-        <v>0.5677450671431065</v>
+        <v>0.8468396378540953</v>
       </c>
       <c r="AR2">
-        <v>1.084772897096356</v>
+        <v>1.13024247798072</v>
       </c>
       <c r="AS2">
-        <v>0.07717363047104363</v>
+        <v>0.06699448381555198</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -882,10 +882,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C3" s="2">
         <v>46293</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46290</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -897,13 +897,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.9932868956067169</v>
+        <v>1.231225676064555</v>
       </c>
       <c r="H3">
-        <v>2.065434804698981</v>
+        <v>2.069745876290506</v>
       </c>
       <c r="I3">
-        <v>0.4566680310549422</v>
+        <v>0.4573414775166103</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -915,19 +915,19 @@
         <v>226</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0.002624563346400701</v>
+      </c>
+      <c r="O3">
+        <v>0.7637473882687553</v>
+      </c>
+      <c r="P3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0.05564030419769859</v>
-      </c>
       <c r="Q3">
-        <v>1.05180991948502</v>
+        <v>1.231225676064555</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -936,10 +936,10 @@
         <v>61</v>
       </c>
       <c r="T3">
-        <v>-0.5645177567596933</v>
+        <v>-0.595924863504193</v>
       </c>
       <c r="U3">
-        <v>0.6539994770128366</v>
+        <v>0.6681437470584861</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -948,34 +948,34 @@
         <v>64</v>
       </c>
       <c r="X3">
-        <v>0.9989173894192011</v>
+        <v>0.9993471737759962</v>
       </c>
       <c r="Y3">
-        <v>0.9998659458838982</v>
+        <v>0.9999102339263967</v>
       </c>
       <c r="Z3">
-        <v>0.0009485564646971589</v>
+        <v>0.0005630601504004185</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-105.6956783367861</v>
+        <v>-108.8535103508429</v>
       </c>
       <c r="AC3">
-        <v>-9</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD3">
-        <v>-0.2705278320129815</v>
+        <v>-0.3231496604105653</v>
       </c>
       <c r="AE3">
-        <v>-0.9627121543360487</v>
+        <v>-0.9463478731293986</v>
       </c>
       <c r="AF3">
-        <v>2.746041155134045</v>
+        <v>2.796318663035616</v>
       </c>
       <c r="AG3">
-        <v>2.745673037014214</v>
+        <v>2.796067648488691</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -990,28 +990,28 @@
         <v>70</v>
       </c>
       <c r="AL3">
-        <v>-0.27049156664358</v>
+        <v>-0.323120652534364</v>
       </c>
       <c r="AM3">
-        <v>0.7641073423462377</v>
+        <v>0.7834993593713424</v>
       </c>
       <c r="AN3">
-        <v>-0.6965267282036537</v>
+        <v>-0.8666558135598412</v>
       </c>
       <c r="AO3">
-        <v>-2.653163019204379</v>
+        <v>-2.656708430055078</v>
       </c>
       <c r="AP3">
-        <v>-1.758527870195961</v>
+        <v>-1.837967646475184</v>
       </c>
       <c r="AQ3">
-        <v>0.1702143361458303</v>
+        <v>0.9485436712745416</v>
       </c>
       <c r="AR3">
-        <v>1.650793431524987</v>
+        <v>1.667661908120894</v>
       </c>
       <c r="AS3">
-        <v>0.1133605887801404</v>
+        <v>0.08942747084043955</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1022,10 +1022,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C4" s="2">
         <v>46293</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46290</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1034,16 +1034,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.9148333723278068</v>
+        <v>0.9516467148497846</v>
       </c>
       <c r="G4">
-        <v>2.493281471206344</v>
+        <v>2.531869505183189</v>
       </c>
       <c r="H4">
-        <v>2.083630976431574</v>
+        <v>2.085541146852794</v>
       </c>
       <c r="I4">
-        <v>0.4937530609893399</v>
+        <v>0.494112260374618</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1055,19 +1055,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>0.3070736204848126</v>
+        <v>0.3651071830342192</v>
       </c>
       <c r="O4">
-        <v>10.27984382302097</v>
+        <v>11.78308105689042</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.493281471206344</v>
+        <v>2.531869505183189</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1076,10 +1076,10 @@
         <v>61</v>
       </c>
       <c r="T4">
-        <v>-0.9005834154530278</v>
+        <v>-0.9269663208517464</v>
       </c>
       <c r="U4">
-        <v>0.9424138742155972</v>
+        <v>0.9598096798408658</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1088,34 +1088,34 @@
         <v>64</v>
       </c>
       <c r="X4">
-        <v>0.9956313638485386</v>
+        <v>0.9955736897369908</v>
       </c>
       <c r="Y4">
-        <v>0.9997053256502548</v>
+        <v>0.9997113129204496</v>
       </c>
       <c r="Z4">
-        <v>0.004073961801716264</v>
+        <v>0.004137623183458783</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-143.5032023394873</v>
+        <v>-148.7663191074937</v>
       </c>
       <c r="AC4">
         <v>-20</v>
       </c>
       <c r="AD4">
-        <v>-0.8038901048208</v>
+        <v>-0.8550595941124134</v>
       </c>
       <c r="AE4">
-        <v>-0.5947778571628261</v>
+        <v>-0.5185297392785827</v>
       </c>
       <c r="AF4">
-        <v>2.440060508764631</v>
+        <v>2.325578566536405</v>
       </c>
       <c r="AG4">
-        <v>2.439341485520872</v>
+        <v>2.324907202051766</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1130,28 +1130,28 @@
         <v>70</v>
       </c>
       <c r="AL4">
-        <v>-0.8036532190268953</v>
+        <v>-0.8548127494553475</v>
       </c>
       <c r="AM4">
-        <v>0.9342438322494659</v>
+        <v>0.949901971502339</v>
       </c>
       <c r="AN4">
-        <v>-1.887874379105325</v>
+        <v>-1.925842983037204</v>
       </c>
       <c r="AO4">
-        <v>-1.529025323777559</v>
+        <v>-1.2851741782499</v>
       </c>
       <c r="AP4">
-        <v>-3.149732462578228</v>
+        <v>-3.153265573276221</v>
       </c>
       <c r="AQ4">
-        <v>3.462882975329206</v>
+        <v>3.442020031094641</v>
       </c>
       <c r="AR4">
-        <v>2.781737744488757</v>
+        <v>2.802616292963461</v>
       </c>
       <c r="AS4">
-        <v>0.04546708782908851</v>
+        <v>0.04343244169028213</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1162,10 +1162,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C5" s="2">
         <v>46293</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46290</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1177,13 +1177,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.129473063872976</v>
+        <v>2.319262127002522</v>
       </c>
       <c r="H5">
-        <v>1.527975134195223</v>
+        <v>1.531389839362863</v>
       </c>
       <c r="I5">
-        <v>0.3525153895196541</v>
+        <v>0.353568694688965</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1195,19 +1195,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>0.02253113271321679</v>
+        <v>0.02951947894482791</v>
       </c>
       <c r="O5">
-        <v>5.405927300514748</v>
+        <v>7.014132811058923</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.129473063872976</v>
+        <v>2.319262127002522</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1216,10 +1216,10 @@
         <v>61</v>
       </c>
       <c r="T5">
-        <v>-0.8077528568583739</v>
+        <v>-0.8233672241928232</v>
       </c>
       <c r="U5">
-        <v>0.9134586544216092</v>
+        <v>0.9204933629019073</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1228,34 +1228,34 @@
         <v>64</v>
       </c>
       <c r="X5">
-        <v>0.9984001462343809</v>
+        <v>0.9989450532474263</v>
       </c>
       <c r="Y5">
-        <v>0.9998794753413637</v>
+        <v>0.9999124480605475</v>
       </c>
       <c r="Z5">
-        <v>0.001479329106982785</v>
+        <v>0.0009673948131211363</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-127.9869909050153</v>
+        <v>-130.2946815533073</v>
       </c>
       <c r="AC5">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AD5">
-        <v>-0.6154825404024911</v>
+        <v>-0.6467189824894843</v>
       </c>
       <c r="AE5">
-        <v>-0.7881505201798042</v>
+        <v>-0.7627283642868974</v>
       </c>
       <c r="AF5">
-        <v>2.672770356969893</v>
+        <v>2.775812026853298</v>
       </c>
       <c r="AG5">
-        <v>2.672448222235006</v>
+        <v>2.775568999126791</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1270,28 +1270,28 @@
         <v>70</v>
       </c>
       <c r="AL5">
-        <v>-0.6154083595794124</v>
+        <v>-0.6466623609882867</v>
       </c>
       <c r="AM5">
-        <v>0.8760997784776414</v>
+        <v>0.8861291279153403</v>
       </c>
       <c r="AN5">
-        <v>-1.588081467671415</v>
+        <v>-1.748288201739388</v>
       </c>
       <c r="AO5">
-        <v>-2.144495083360733</v>
+        <v>-2.152294668115119</v>
       </c>
       <c r="AP5">
-        <v>-2.788446245796797</v>
+        <v>-2.951780375378513</v>
       </c>
       <c r="AQ5">
-        <v>2.57285487600075</v>
+        <v>2.943748028975494</v>
       </c>
       <c r="AR5">
-        <v>2.486618874765054</v>
+        <v>2.626531266664112</v>
       </c>
       <c r="AS5">
-        <v>0.05668533341722131</v>
+        <v>0.05237282435131042</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1302,10 +1302,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C6" s="2">
         <v>46293</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46290</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1317,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.680550403729014</v>
+        <v>1.650686963337997</v>
       </c>
       <c r="H6">
-        <v>0.9686837632029885</v>
+        <v>0.9732946177983135</v>
       </c>
       <c r="I6">
-        <v>0.2595313339248795</v>
+        <v>0.2607567582113898</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N6">
-        <v>0.4383421996337605</v>
+        <v>0.515025549799811</v>
       </c>
       <c r="O6">
-        <v>7.421801507961066</v>
+        <v>8.462364529308605</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.680550403729014</v>
+        <v>1.650686963337997</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
@@ -1356,10 +1356,10 @@
         <v>61</v>
       </c>
       <c r="T6">
-        <v>-0.8855271921817665</v>
+        <v>-0.9156846880096801</v>
       </c>
       <c r="U6">
-        <v>0.9484558051191534</v>
+        <v>0.9620062704350962</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1368,34 +1368,34 @@
         <v>64</v>
       </c>
       <c r="X6">
-        <v>0.9986046254089905</v>
+        <v>0.9977833792572974</v>
       </c>
       <c r="Y6">
-        <v>0.9998742745494339</v>
+        <v>0.9997926433229609</v>
       </c>
       <c r="Z6">
-        <v>0.001269649140443363</v>
+        <v>0.002009264065663485</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-140.4473711516528</v>
+        <v>-146.2378611632244</v>
       </c>
       <c r="AC6">
-        <v>-11</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AD6">
-        <v>-0.7710399904085061</v>
+        <v>-0.8313518890504025</v>
       </c>
       <c r="AE6">
-        <v>-0.6367867250428912</v>
+        <v>-0.5557463779210147</v>
       </c>
       <c r="AF6">
-        <v>1.697376826024428</v>
+        <v>1.571632948526466</v>
       </c>
       <c r="AG6">
-        <v>1.697163422558196</v>
+        <v>1.571307059940734</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1410,28 +1410,28 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>-0.7709430510583075</v>
+        <v>-0.8311795026852388</v>
       </c>
       <c r="AM6">
-        <v>0.9242730690792125</v>
+        <v>0.9429933139314797</v>
       </c>
       <c r="AN6">
-        <v>-1.281459118945528</v>
+        <v>-1.276388143369669</v>
       </c>
       <c r="AO6">
-        <v>-1.109466462516039</v>
+        <v>-0.9110023757400542</v>
       </c>
       <c r="AP6">
-        <v>-2.07682591302683</v>
+        <v>-1.963456515348875</v>
       </c>
       <c r="AQ6">
-        <v>2.337058766020589</v>
+        <v>2.544165157925495</v>
       </c>
       <c r="AR6">
-        <v>1.830539036054295</v>
+        <v>1.708720613577435</v>
       </c>
       <c r="AS6">
-        <v>0.0466328275709414</v>
+        <v>0.04226451964451648</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1442,10 +1442,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C7" s="2">
         <v>46293</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46290</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.433491918712662</v>
+        <v>2.466913398925232</v>
       </c>
       <c r="H7">
-        <v>1.49349504330372</v>
+        <v>1.501697225512758</v>
       </c>
       <c r="I7">
-        <v>0.3745812891432713</v>
+        <v>0.376115250925031</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1475,19 +1475,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>0.03471399276487881</v>
+        <v>0.04423126579828961</v>
       </c>
       <c r="O7">
-        <v>6.853700447162623</v>
+        <v>8.708166519140073</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.433491918712662</v>
+        <v>2.466913398925232</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
@@ -1496,10 +1496,10 @@
         <v>61</v>
       </c>
       <c r="T7">
-        <v>-0.8071098751366853</v>
+        <v>-0.8287815975951317</v>
       </c>
       <c r="U7">
-        <v>0.9131857171886492</v>
+        <v>0.9229361870932464</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1508,34 +1508,34 @@
         <v>64</v>
       </c>
       <c r="X7">
-        <v>0.9995584060950488</v>
+        <v>0.999515533404938</v>
       </c>
       <c r="Y7">
-        <v>0.9999450935085634</v>
+        <v>0.9999378727017488</v>
       </c>
       <c r="Z7">
-        <v>0.0003866874135146636</v>
+        <v>0.000422339296810792</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-127.894478809305</v>
+        <v>-131.1134829237438</v>
       </c>
       <c r="AC7">
-        <v>-5.999999999999996</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD7">
-        <v>-0.6142091587718395</v>
+        <v>-0.657552557192601</v>
       </c>
       <c r="AE7">
-        <v>-0.7891432755088199</v>
+        <v>-0.7534086769672029</v>
       </c>
       <c r="AF7">
-        <v>3.046913628950144</v>
+        <v>2.960427632166058</v>
       </c>
       <c r="AG7">
-        <v>3.046746333613068</v>
+        <v>2.960243708795603</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1550,28 +1550,28 @@
         <v>70</v>
       </c>
       <c r="AL7">
-        <v>-0.614175434701923</v>
+        <v>-0.6575117052287645</v>
       </c>
       <c r="AM7">
-        <v>0.8759707461057231</v>
+        <v>0.8900777640785847</v>
       </c>
       <c r="AN7">
-        <v>-1.840866142847872</v>
+        <v>-1.911796185433251</v>
       </c>
       <c r="AO7">
-        <v>-2.426251652530377</v>
+        <v>-2.258467911996093</v>
       </c>
       <c r="AP7">
-        <v>-3.063933652710714</v>
+        <v>-2.913296091257616</v>
       </c>
       <c r="AQ7">
-        <v>3.14378323842924</v>
+        <v>3.95866498724083</v>
       </c>
       <c r="AR7">
-        <v>2.709019752958548</v>
+        <v>2.499134567504587</v>
       </c>
       <c r="AS7">
-        <v>0.05515189502550502</v>
+        <v>0.04777505683205054</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1582,10 +1582,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C8" s="2">
         <v>46293</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46290</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1597,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.771955978776556</v>
+        <v>2.932167664138002</v>
       </c>
       <c r="H8">
-        <v>1.473436547489832</v>
+        <v>1.482697717419926</v>
       </c>
       <c r="I8">
-        <v>0.368490582696668</v>
+        <v>0.3714517619459159</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1615,19 +1615,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8">
-        <v>-0.06385511093960826</v>
+        <v>-0.07178289812976513</v>
       </c>
       <c r="O8">
-        <v>-17.61693867680597</v>
+        <v>-18.94900676565885</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.771955978776556</v>
+        <v>2.932167664138002</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
@@ -1636,10 +1636,10 @@
         <v>62</v>
       </c>
       <c r="T8">
-        <v>0.966604633832096</v>
+        <v>0.9218538591375706</v>
       </c>
       <c r="U8">
-        <v>0.9849232799787089</v>
+        <v>0.9647819294336638</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1648,34 +1648,34 @@
         <v>64</v>
       </c>
       <c r="X8">
-        <v>0.9981184323924035</v>
+        <v>0.9997844237732523</v>
       </c>
       <c r="Y8">
-        <v>0.9998047790170624</v>
+        <v>0.9997907712870285</v>
       </c>
       <c r="Z8">
-        <v>0.001686346624658941</v>
+        <v>6.347513776261415E-06</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>21.06030066615424</v>
+        <v>32.46800368571632</v>
       </c>
       <c r="AC8">
-        <v>-12.99999999999999</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AD8">
-        <v>0.9332027469149962</v>
+        <v>0.8436913644369721</v>
       </c>
       <c r="AE8">
-        <v>0.3593502930989561</v>
+        <v>0.5368285402011337</v>
       </c>
       <c r="AF8">
-        <v>2.259589516151934</v>
+        <v>2.59579621950908</v>
       </c>
       <c r="AG8">
-        <v>2.259148396865556</v>
+        <v>2.595253104406936</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1690,28 +1690,28 @@
         <v>71</v>
       </c>
       <c r="AL8">
-        <v>0.9330205661574634</v>
+        <v>0.8435148399786458</v>
       </c>
       <c r="AM8">
-        <v>0.9733599994677484</v>
+        <v>0.9462415230111136</v>
       </c>
       <c r="AN8">
-        <v>2.083345892564772</v>
+        <v>2.192111888492398</v>
       </c>
       <c r="AO8">
-        <v>0.8638397659875174</v>
+        <v>1.389207911484684</v>
       </c>
       <c r="AP8">
-        <v>3.558600649852225</v>
+        <v>3.807126716510738</v>
       </c>
       <c r="AQ8">
-        <v>-3.261242385719994</v>
+        <v>-3.104391978020509</v>
       </c>
       <c r="AR8">
-        <v>3.226954040271941</v>
+        <v>3.489051630129082</v>
       </c>
       <c r="AS8">
-        <v>0.04354998175148109</v>
+        <v>0.04528437513625278</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1722,10 +1722,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C9" s="2">
         <v>46293</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46290</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.553656358261324</v>
+        <v>1.59972298782819</v>
       </c>
       <c r="H9">
-        <v>3.127259644161241</v>
+        <v>3.132927229104057</v>
       </c>
       <c r="I9">
-        <v>0.6691965418736109</v>
+        <v>0.6697449107308657</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1755,19 +1755,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9">
-        <v>0.834836405122935</v>
+        <v>0.8458175525478211</v>
       </c>
       <c r="O9">
-        <v>99.63097495287241</v>
+        <v>90.909721205864</v>
       </c>
       <c r="P9">
-        <v>0.004538955066842571</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.560740489212863</v>
+        <v>1.59972298782819</v>
       </c>
       <c r="R9" t="s">
         <v>60</v>
@@ -1776,10 +1776,10 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.7441634316464502</v>
+        <v>-0.8233824537727303</v>
       </c>
       <c r="U9">
-        <v>0.7347092904436736</v>
+        <v>0.7704458387086559</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1788,34 +1788,34 @@
         <v>64</v>
       </c>
       <c r="X9">
-        <v>0.9956899706691014</v>
+        <v>0.9995493275225033</v>
       </c>
       <c r="Y9">
-        <v>0.9993429848110841</v>
+        <v>0.9996949380437088</v>
       </c>
       <c r="Z9">
-        <v>0.003653014141982713</v>
+        <v>0.0001456105212055414</v>
       </c>
       <c r="AA9">
-        <v>0.6314948200763472</v>
+        <v>0.2643328411100709</v>
       </c>
       <c r="AB9">
-        <v>121.1266661180417</v>
+        <v>126.5017684982347</v>
       </c>
       <c r="AC9">
-        <v>-18</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD9">
-        <v>-0.516931789508032</v>
+        <v>-0.594847598407908</v>
       </c>
       <c r="AE9">
-        <v>0.856026591290261</v>
+        <v>0.8038385003645597</v>
       </c>
       <c r="AF9">
-        <v>2.360279607884177</v>
+        <v>2.023619844487391</v>
       </c>
       <c r="AG9">
-        <v>2.358728868331709</v>
+        <v>2.023002515058842</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1830,28 +1830,28 @@
         <v>72</v>
       </c>
       <c r="AL9">
-        <v>-0.4214087145027491</v>
+        <v>-0.3759279607465731</v>
       </c>
       <c r="AM9">
-        <v>0.7760809504182696</v>
+        <v>0.7267869082306386</v>
       </c>
       <c r="AN9">
-        <v>-1.271926308750624</v>
+        <v>-1.215020172870769</v>
       </c>
       <c r="AO9">
-        <v>1.976159184924614</v>
+        <v>1.617118747976555</v>
       </c>
       <c r="AP9">
-        <v>-1.59135535249199</v>
+        <v>-1.990772269975929</v>
       </c>
       <c r="AQ9">
-        <v>3.276585817871569</v>
+        <v>1.494423962202693</v>
       </c>
       <c r="AR9">
-        <v>1.352819908812047</v>
+        <v>1.904882111597325</v>
       </c>
       <c r="AS9">
-        <v>0.03378396755525835</v>
+        <v>0.0295144521936399</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1862,10 +1862,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C10" s="2">
         <v>46293</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46290</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.4656618797617593</v>
+        <v>0.6027559670788827</v>
       </c>
       <c r="H10">
-        <v>2.111656035203933</v>
+        <v>2.114534260099425</v>
       </c>
       <c r="I10">
-        <v>0.4496128010101789</v>
+        <v>0.4495675378177471</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1895,19 +1895,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10">
-        <v>45.09844138244251</v>
+        <v>45.62701541458623</v>
       </c>
       <c r="O10">
-        <v>42.01065801811109</v>
+        <v>44.15873739616363</v>
       </c>
       <c r="P10">
-        <v>0.1435783044370041</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.5437296628218202</v>
+        <v>0.6027559670788827</v>
       </c>
       <c r="R10" t="s">
         <v>60</v>
@@ -1916,10 +1916,10 @@
         <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.6372822385028896</v>
+        <v>-0.7533042661490058</v>
       </c>
       <c r="U10">
-        <v>0.6866487673838128</v>
+        <v>0.7385549057734455</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
@@ -1928,34 +1928,34 @@
         <v>64</v>
       </c>
       <c r="X10">
-        <v>0.9992719902673382</v>
+        <v>0.9976707654523389</v>
       </c>
       <c r="Y10">
-        <v>0.9994870402300498</v>
+        <v>0.9982719440255712</v>
       </c>
       <c r="Z10">
-        <v>0.0002150499627115998</v>
+        <v>0.000601178573232275</v>
       </c>
       <c r="AA10">
-        <v>0.4989245714908739</v>
+        <v>0.1322712175335533</v>
       </c>
       <c r="AB10">
-        <v>105.9025552549323</v>
+        <v>111.7585844870444</v>
       </c>
       <c r="AC10">
-        <v>-4.999999999999995</v>
+        <v>9</v>
       </c>
       <c r="AD10">
-        <v>-0.2740021097855445</v>
+        <v>-0.370696594622404</v>
       </c>
       <c r="AE10">
-        <v>0.961729090665906</v>
+        <v>0.9287540227290286</v>
       </c>
       <c r="AF10">
-        <v>1.736216886912628</v>
+        <v>1.46527622652169</v>
       </c>
       <c r="AG10">
-        <v>1.735326277497734</v>
+        <v>1.462744147184261</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
@@ -1970,28 +1970,28 @@
         <v>72</v>
       </c>
       <c r="AL10">
-        <v>-0.205248909031391</v>
+        <v>-0.2095018845882451</v>
       </c>
       <c r="AM10">
-        <v>0.6680714303987534</v>
+        <v>0.6274303558378602</v>
       </c>
       <c r="AN10">
-        <v>-0.4969293061111932</v>
+        <v>-0.5068419590390092</v>
       </c>
       <c r="AO10">
-        <v>1.662264372548948</v>
+        <v>1.371187588717483</v>
       </c>
       <c r="AP10">
-        <v>-0.2879211642521388</v>
+        <v>-0.5107035571324423</v>
       </c>
       <c r="AQ10">
-        <v>1.0851574638904</v>
+        <v>0.6156979308825091</v>
       </c>
       <c r="AR10">
-        <v>0.2744702378443663</v>
+        <v>0.5221834591978205</v>
       </c>
       <c r="AS10">
-        <v>0.09156387277068113</v>
+        <v>0.06418697643014314</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2002,10 +2002,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C11" s="2">
         <v>46293</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46290</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2017,13 +2017,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.461376602456803</v>
+        <v>0.8442669667037336</v>
       </c>
       <c r="H11">
-        <v>2.213942372219496</v>
+        <v>2.200797306037765</v>
       </c>
       <c r="I11">
-        <v>0.5140111663621287</v>
+        <v>0.5106466810612449</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2035,19 +2035,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>17.93401925713394</v>
+        <v>47.79718145008715</v>
       </c>
       <c r="O11">
-        <v>0.2897440636087854</v>
+        <v>0.6942003468106805</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.461376602456803</v>
+        <v>0.8442669667037336</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2056,10 +2056,10 @@
         <v>61</v>
       </c>
       <c r="T11">
-        <v>-0.76950823222412</v>
+        <v>-0.799413457057678</v>
       </c>
       <c r="U11">
-        <v>0.7462381362649918</v>
+        <v>0.7597236630877668</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2068,34 +2068,34 @@
         <v>64</v>
       </c>
       <c r="X11">
-        <v>0.9993462258891704</v>
+        <v>0.9995146556046763</v>
       </c>
       <c r="Y11">
-        <v>0.9998377270565512</v>
+        <v>0.9999504296472475</v>
       </c>
       <c r="Z11">
-        <v>0.0004915011673807257</v>
+        <v>0.0004357740425711132</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.01423705444324133</v>
       </c>
       <c r="AB11">
-        <v>-108.9605010459745</v>
+        <v>-114.9934161293111</v>
       </c>
       <c r="AC11">
-        <v>-6.999999999999997</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD11">
-        <v>-0.3249162491209054</v>
+        <v>-0.4225141149225828</v>
       </c>
       <c r="AE11">
-        <v>-0.9457427932885356</v>
+        <v>-0.9063563442108112</v>
       </c>
       <c r="AF11">
-        <v>1.046046605310706</v>
+        <v>1.390456156993545</v>
       </c>
       <c r="AG11">
-        <v>1.045876860249077</v>
+        <v>1.390387231591355</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2110,28 +2110,28 @@
         <v>70</v>
       </c>
       <c r="AL11">
-        <v>-0.1624317620023931</v>
+        <v>-0.2142541145113562</v>
       </c>
       <c r="AM11">
-        <v>0.5854529060921151</v>
+        <v>0.6172400075338201</v>
       </c>
       <c r="AN11">
-        <v>-0.325902664262283</v>
+        <v>-0.5744807373974551</v>
       </c>
       <c r="AO11">
-        <v>-0.9932626463738097</v>
+        <v>-1.265489614079226</v>
       </c>
       <c r="AP11">
-        <v>-0.6796074969203546</v>
+        <v>-1.325059533461581</v>
       </c>
       <c r="AQ11">
-        <v>0.2419988380794569</v>
+        <v>-0.2605068332565275</v>
       </c>
       <c r="AR11">
-        <v>0.6383726808067267</v>
+        <v>1.324012771455588</v>
       </c>
       <c r="AS11">
-        <v>0.07976782075966257</v>
+        <v>0.08229525472093058</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -742,10 +742,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C2" s="2">
         <v>46294</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46293</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -754,16 +754,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.1139093758378123</v>
+        <v>0.3875237439433573</v>
       </c>
       <c r="G2">
-        <v>0.8812195371627741</v>
+        <v>1.023507931409482</v>
       </c>
       <c r="H2">
-        <v>1.081592256654329</v>
+        <v>1.081881969853771</v>
       </c>
       <c r="I2">
-        <v>0.2594892325167979</v>
+        <v>0.2594949391580547</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -775,19 +775,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>0.0578653068683871</v>
+        <v>0.08580697460070541</v>
       </c>
       <c r="O2">
-        <v>1.467332541491438</v>
+        <v>2.073991996840375</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.8812195371627741</v>
+        <v>1.023507931409482</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -796,10 +796,10 @@
         <v>61</v>
       </c>
       <c r="T2">
-        <v>-0.7168960933814398</v>
+        <v>-0.734687963719556</v>
       </c>
       <c r="U2">
-        <v>0.7396580646989981</v>
+        <v>0.7887195394723627</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -808,34 +808,34 @@
         <v>64</v>
       </c>
       <c r="X2">
-        <v>0.9984431301870489</v>
+        <v>0.999413872836842</v>
       </c>
       <c r="Y2">
-        <v>0.9998736652067134</v>
+        <v>0.9999255768282354</v>
       </c>
       <c r="Z2">
-        <v>0.001430535019664503</v>
+        <v>0.0005117039913933308</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-121.0171635773847</v>
+        <v>-121.4780406646686</v>
       </c>
       <c r="AC2">
-        <v>-12</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AD2">
-        <v>-0.5152948256368708</v>
+        <v>-0.5221717411748173</v>
       </c>
       <c r="AE2">
-        <v>-0.8570129769565143</v>
+        <v>-0.8528403559391755</v>
       </c>
       <c r="AF2">
-        <v>1.290483447979541</v>
+        <v>1.457898159031333</v>
       </c>
       <c r="AG2">
-        <v>1.290320415019901</v>
+        <v>1.457789657626228</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -850,28 +850,28 @@
         <v>70</v>
       </c>
       <c r="AL2">
-        <v>-0.5152297259715923</v>
+        <v>-0.5221328794976332</v>
       </c>
       <c r="AM2">
-        <v>0.844495057941078</v>
+        <v>0.8471886320641755</v>
       </c>
       <c r="AN2">
-        <v>-0.6365195457344136</v>
+        <v>-0.7440078990797057</v>
       </c>
       <c r="AO2">
-        <v>-1.120271831010521</v>
+        <v>-1.252768306779863</v>
       </c>
       <c r="AP2">
-        <v>-1.246666538707811</v>
+        <v>-1.422315781665723</v>
       </c>
       <c r="AQ2">
-        <v>0.8468396378540953</v>
+        <v>0.9086215531623327</v>
       </c>
       <c r="AR2">
-        <v>1.13024247798072</v>
+        <v>1.303750748746877</v>
       </c>
       <c r="AS2">
-        <v>0.06699448381555198</v>
+        <v>0.0629122811876793</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -882,10 +882,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C3" s="2">
         <v>46294</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46293</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -897,13 +897,13 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1.231225676064555</v>
+        <v>1.580657490691484</v>
       </c>
       <c r="H3">
-        <v>2.069745876290506</v>
+        <v>2.073646369635218</v>
       </c>
       <c r="I3">
-        <v>0.4573414775166103</v>
+        <v>0.4578055743872117</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -915,19 +915,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>0.002624563346400701</v>
+        <v>0.006096319197139738</v>
       </c>
       <c r="O3">
-        <v>0.7637473882687553</v>
+        <v>1.746081603108766</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.231225676064555</v>
+        <v>1.580657490691484</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -936,10 +936,10 @@
         <v>61</v>
       </c>
       <c r="T3">
-        <v>-0.595924863504193</v>
+        <v>-0.6458738715279175</v>
       </c>
       <c r="U3">
-        <v>0.6681437470584861</v>
+        <v>0.6906240438363735</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -948,34 +948,34 @@
         <v>64</v>
       </c>
       <c r="X3">
-        <v>0.9993471737759962</v>
+        <v>0.9992455557111756</v>
       </c>
       <c r="Y3">
-        <v>0.9999102339263967</v>
+        <v>0.9999232065952424</v>
       </c>
       <c r="Z3">
-        <v>0.0005630601504004185</v>
+        <v>0.0006776508840667939</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-108.8535103508429</v>
+        <v>-114.0052517395412</v>
       </c>
       <c r="AC3">
-        <v>-6.999999999999997</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD3">
-        <v>-0.3231496604105653</v>
+        <v>-0.4068203770775038</v>
       </c>
       <c r="AE3">
-        <v>-0.9463478731293986</v>
+        <v>-0.9135081722647683</v>
       </c>
       <c r="AF3">
-        <v>2.796318663035616</v>
+        <v>2.898625258923872</v>
       </c>
       <c r="AG3">
-        <v>2.796067648488691</v>
+        <v>2.898402663621122</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -990,28 +990,28 @@
         <v>70</v>
       </c>
       <c r="AL3">
-        <v>-0.323120652534364</v>
+        <v>-0.4067891359556232</v>
       </c>
       <c r="AM3">
-        <v>0.7834993593713424</v>
+        <v>0.8105194080324716</v>
       </c>
       <c r="AN3">
-        <v>-0.8666558135598412</v>
+        <v>-1.135727345137667</v>
       </c>
       <c r="AO3">
-        <v>-2.656708430055078</v>
+        <v>-2.664484724449971</v>
       </c>
       <c r="AP3">
-        <v>-1.837967646475184</v>
+        <v>-2.252117691376024</v>
       </c>
       <c r="AQ3">
-        <v>0.9485436712745416</v>
+        <v>1.300479567144253</v>
       </c>
       <c r="AR3">
-        <v>1.667661908120894</v>
+        <v>2.054119478603557</v>
       </c>
       <c r="AS3">
-        <v>0.08942747084043955</v>
+        <v>0.07666551599409556</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1022,10 +1022,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C4" s="2">
         <v>46294</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46293</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1034,16 +1034,16 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>0.9516467148497846</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>2.531869505183189</v>
+        <v>2.608829370559007</v>
       </c>
       <c r="H4">
-        <v>2.085541146852794</v>
+        <v>2.088818639521052</v>
       </c>
       <c r="I4">
-        <v>0.494112260374618</v>
+        <v>0.4946572449696312</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1055,19 +1055,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>0.3651071830342192</v>
+        <v>0.4273259009971911</v>
       </c>
       <c r="O4">
-        <v>11.78308105689042</v>
+        <v>13.05096556274141</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.531869505183189</v>
+        <v>2.608829370559007</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1076,10 +1076,10 @@
         <v>61</v>
       </c>
       <c r="T4">
-        <v>-0.9269663208517464</v>
+        <v>-0.9312250164575222</v>
       </c>
       <c r="U4">
-        <v>0.9598096798408658</v>
+        <v>0.969012578960153</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1088,34 +1088,34 @@
         <v>64</v>
       </c>
       <c r="X4">
-        <v>0.9955736897369908</v>
+        <v>0.9977389620162824</v>
       </c>
       <c r="Y4">
-        <v>0.9997113129204496</v>
+        <v>0.9998452862170725</v>
       </c>
       <c r="Z4">
-        <v>0.004137623183458783</v>
+        <v>0.002106324200790044</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-148.7663191074937</v>
+        <v>-149.5915908669479</v>
       </c>
       <c r="AC4">
-        <v>-20</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AD4">
-        <v>-0.8550595941124134</v>
+        <v>-0.8624393908306924</v>
       </c>
       <c r="AE4">
-        <v>-0.5185297392785827</v>
+        <v>-0.5061603472651568</v>
       </c>
       <c r="AF4">
-        <v>2.325578566536405</v>
+        <v>2.339620582215759</v>
       </c>
       <c r="AG4">
-        <v>2.324907202051766</v>
+        <v>2.339258610664869</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1130,28 +1130,28 @@
         <v>70</v>
       </c>
       <c r="AL4">
-        <v>-0.8548127494553475</v>
+        <v>-0.8623059595699913</v>
       </c>
       <c r="AM4">
-        <v>0.949901971502339</v>
+        <v>0.9520876357080611</v>
       </c>
       <c r="AN4">
-        <v>-1.925842983037204</v>
+        <v>-1.977952480195611</v>
       </c>
       <c r="AO4">
-        <v>-1.2851741782499</v>
+        <v>-1.239678744082058</v>
       </c>
       <c r="AP4">
-        <v>-3.153265573276221</v>
+        <v>-3.267881377329152</v>
       </c>
       <c r="AQ4">
-        <v>3.442020031094641</v>
+        <v>3.219450918109771</v>
       </c>
       <c r="AR4">
-        <v>2.802616292963461</v>
+        <v>2.945769017765066</v>
       </c>
       <c r="AS4">
-        <v>0.04343244169028213</v>
+        <v>0.04393354478081245</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1162,10 +1162,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C5" s="2">
         <v>46294</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46293</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1177,13 +1177,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.319262127002522</v>
+        <v>2.448355559158069</v>
       </c>
       <c r="H5">
-        <v>1.531389839362863</v>
+        <v>1.534825744873344</v>
       </c>
       <c r="I5">
-        <v>0.353568694688965</v>
+        <v>0.3548660334225586</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1195,19 +1195,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>0.02951947894482791</v>
+        <v>0.03713734760323029</v>
       </c>
       <c r="O5">
-        <v>7.014132811058923</v>
+        <v>8.825714928623762</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.319262127002522</v>
+        <v>2.448355559158069</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1216,10 +1216,10 @@
         <v>61</v>
       </c>
       <c r="T5">
-        <v>-0.8233672241928232</v>
+        <v>-0.8679424902676787</v>
       </c>
       <c r="U5">
-        <v>0.9204933629019073</v>
+        <v>0.9405322076889344</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1228,34 +1228,34 @@
         <v>64</v>
       </c>
       <c r="X5">
-        <v>0.9989450532474263</v>
+        <v>0.9977810367969649</v>
       </c>
       <c r="Y5">
-        <v>0.9999124480605475</v>
+        <v>0.999832348273916</v>
       </c>
       <c r="Z5">
-        <v>0.0009673948131211363</v>
+        <v>0.002051311476951034</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-130.2946815533073</v>
+        <v>-137.3801750828664</v>
       </c>
       <c r="AC5">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="AD5">
-        <v>-0.6467189824894843</v>
+        <v>-0.7358628371535323</v>
       </c>
       <c r="AE5">
-        <v>-0.7627283642868974</v>
+        <v>-0.6771306261692451</v>
       </c>
       <c r="AF5">
-        <v>2.775812026853298</v>
+        <v>2.631684725734282</v>
       </c>
       <c r="AG5">
-        <v>2.775568999126791</v>
+        <v>2.631243519247504</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1270,28 +1270,28 @@
         <v>70</v>
       </c>
       <c r="AL5">
-        <v>-0.6466623609882867</v>
+        <v>-0.7357394684787224</v>
       </c>
       <c r="AM5">
-        <v>0.8861291279153403</v>
+        <v>0.9135148954568622</v>
       </c>
       <c r="AN5">
-        <v>-1.748288201739388</v>
+        <v>-1.872197956013963</v>
       </c>
       <c r="AO5">
-        <v>-2.152294668115119</v>
+        <v>-1.841178257824594</v>
       </c>
       <c r="AP5">
-        <v>-2.951780375378513</v>
+        <v>-2.999864441677517</v>
       </c>
       <c r="AQ5">
-        <v>2.943748028975494</v>
+        <v>3.456865937544864</v>
       </c>
       <c r="AR5">
-        <v>2.626531266664112</v>
+        <v>2.638502559097331</v>
       </c>
       <c r="AS5">
-        <v>0.05237282435131042</v>
+        <v>0.04790185056712054</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1302,10 +1302,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C6" s="2">
         <v>46294</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46293</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1317,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.650686963337997</v>
+        <v>1.686218320861796</v>
       </c>
       <c r="H6">
-        <v>0.9732946177983135</v>
+        <v>0.977603654310369</v>
       </c>
       <c r="I6">
-        <v>0.2607567582113898</v>
+        <v>0.2621702942601331</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N6">
-        <v>0.515025549799811</v>
+        <v>0.5944865380829603</v>
       </c>
       <c r="O6">
-        <v>8.462364529308605</v>
+        <v>9.568869752306895</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.650686963337997</v>
+        <v>1.686218320861796</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
@@ -1356,10 +1356,10 @@
         <v>61</v>
       </c>
       <c r="T6">
-        <v>-0.9156846880096801</v>
+        <v>-0.9310160695900964</v>
       </c>
       <c r="U6">
-        <v>0.9620062704350962</v>
+        <v>0.9689184193132682</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1368,34 +1368,34 @@
         <v>64</v>
       </c>
       <c r="X6">
-        <v>0.9977833792572974</v>
+        <v>0.9981715742369812</v>
       </c>
       <c r="Y6">
-        <v>0.9997926433229609</v>
+        <v>0.9998447519908988</v>
       </c>
       <c r="Z6">
-        <v>0.002009264065663485</v>
+        <v>0.001673177753917621</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-146.2378611632244</v>
+        <v>-149.5443119926976</v>
       </c>
       <c r="AC6">
-        <v>-13.99999999999999</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD6">
-        <v>-0.8313518890504025</v>
+        <v>-0.8620214278994317</v>
       </c>
       <c r="AE6">
-        <v>-0.5557463779210147</v>
+        <v>-0.5068718357161155</v>
       </c>
       <c r="AF6">
-        <v>1.571632948526466</v>
+        <v>1.545982279947867</v>
       </c>
       <c r="AG6">
-        <v>1.571307059940734</v>
+        <v>1.545742269276799</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1410,28 +1410,28 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>-0.8311795026852388</v>
+        <v>-0.8618876007889478</v>
       </c>
       <c r="AM6">
-        <v>0.9429933139314797</v>
+        <v>0.9524285422341819</v>
       </c>
       <c r="AN6">
-        <v>-1.276388143369669</v>
+        <v>-1.307642339867632</v>
       </c>
       <c r="AO6">
-        <v>-0.9110023757400542</v>
+        <v>-0.8193903906115763</v>
       </c>
       <c r="AP6">
-        <v>-1.963456515348875</v>
+        <v>-1.985887170759058</v>
       </c>
       <c r="AQ6">
-        <v>2.544165157925495</v>
+        <v>2.55210889701048</v>
       </c>
       <c r="AR6">
-        <v>1.708720613577435</v>
+        <v>1.738626987625601</v>
       </c>
       <c r="AS6">
-        <v>0.04226451964451648</v>
+        <v>0.04082366221641366</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1442,10 +1442,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C7" s="2">
         <v>46294</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46293</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.466913398925232</v>
+        <v>2.191816852613451</v>
       </c>
       <c r="H7">
-        <v>1.501697225512758</v>
+        <v>1.509463048023154</v>
       </c>
       <c r="I7">
-        <v>0.376115250925031</v>
+        <v>0.3777831208959462</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1475,19 +1475,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>0.04423126579828961</v>
+        <v>0.05380602698166632</v>
       </c>
       <c r="O7">
-        <v>8.708166519140073</v>
+        <v>10.01441608273496</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.466913398925232</v>
+        <v>2.191816852613451</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
@@ -1496,10 +1496,10 @@
         <v>61</v>
       </c>
       <c r="T7">
-        <v>-0.8287815975951317</v>
+        <v>-0.9047095565525618</v>
       </c>
       <c r="U7">
-        <v>0.9229361870932464</v>
+        <v>0.9569307161286699</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1508,34 +1508,34 @@
         <v>64</v>
       </c>
       <c r="X7">
-        <v>0.999515533404938</v>
+        <v>0.9949606768837319</v>
       </c>
       <c r="Y7">
-        <v>0.9999378727017488</v>
+        <v>0.9992456627200683</v>
       </c>
       <c r="Z7">
-        <v>0.000422339296810792</v>
+        <v>0.004284985836336408</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-131.1134829237438</v>
+        <v>-144.032197867296</v>
       </c>
       <c r="AC7">
-        <v>-6.999999999999997</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>-0.657552557192601</v>
+        <v>-0.8093471777076577</v>
       </c>
       <c r="AE7">
-        <v>-0.7534086769672029</v>
+        <v>-0.5873305252893375</v>
       </c>
       <c r="AF7">
-        <v>2.960427632166058</v>
+        <v>2.274281913738901</v>
       </c>
       <c r="AG7">
-        <v>2.960243708795603</v>
+        <v>2.272566338106293</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1550,28 +1550,28 @@
         <v>70</v>
       </c>
       <c r="AL7">
-        <v>-0.6575117052287645</v>
+        <v>-0.8087366569591053</v>
       </c>
       <c r="AM7">
-        <v>0.8900777640785847</v>
+        <v>0.9366725589471102</v>
       </c>
       <c r="AN7">
-        <v>-1.911796185433251</v>
+        <v>-1.756786577883378</v>
       </c>
       <c r="AO7">
-        <v>-2.258467911996093</v>
+        <v>-1.426204797739647</v>
       </c>
       <c r="AP7">
-        <v>-2.913296091257616</v>
+        <v>-2.342231527080917</v>
       </c>
       <c r="AQ7">
-        <v>3.95866498724083</v>
+        <v>4.49810636208657</v>
       </c>
       <c r="AR7">
-        <v>2.499134567504587</v>
+        <v>1.904298802940368</v>
       </c>
       <c r="AS7">
-        <v>0.04777505683205054</v>
+        <v>0.03911717544807258</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1582,10 +1582,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C8" s="2">
         <v>46294</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46293</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1597,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.932167664138002</v>
+        <v>3.293394736705306</v>
       </c>
       <c r="H8">
-        <v>1.482697717419926</v>
+        <v>1.491186502164883</v>
       </c>
       <c r="I8">
-        <v>0.3714517619459159</v>
+        <v>0.3750222724914655</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1615,19 +1615,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8">
-        <v>-0.07178289812976513</v>
+        <v>-0.0804372068006162</v>
       </c>
       <c r="O8">
-        <v>-18.94900676565885</v>
+        <v>-22.01604878218242</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.932167664138002</v>
+        <v>3.293394736705306</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
@@ -1636,10 +1636,10 @@
         <v>62</v>
       </c>
       <c r="T8">
-        <v>0.9218538591375706</v>
+        <v>0.9106606642624933</v>
       </c>
       <c r="U8">
-        <v>0.9647819294336638</v>
+        <v>0.9597737270081802</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1648,34 +1648,34 @@
         <v>64</v>
       </c>
       <c r="X8">
-        <v>0.9997844237732523</v>
+        <v>0.9998866109712756</v>
       </c>
       <c r="Y8">
-        <v>0.9997907712870285</v>
+        <v>0.9999057123602327</v>
       </c>
       <c r="Z8">
-        <v>6.347513776261415E-06</v>
+        <v>1.910138895711011E-05</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>32.46800368571632</v>
+        <v>34.78356273707708</v>
       </c>
       <c r="AC8">
         <v>1.000000000000001</v>
       </c>
       <c r="AD8">
-        <v>0.8436913644369721</v>
+        <v>0.8213129041355656</v>
       </c>
       <c r="AE8">
-        <v>0.5368285402011337</v>
+        <v>0.5704779693383464</v>
       </c>
       <c r="AF8">
-        <v>2.59579621950908</v>
+        <v>2.99731258365313</v>
       </c>
       <c r="AG8">
-        <v>2.595253104406936</v>
+        <v>2.997029974123973</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1690,28 +1690,28 @@
         <v>71</v>
       </c>
       <c r="AL8">
-        <v>0.8435148399786458</v>
+        <v>0.8212354644803243</v>
       </c>
       <c r="AM8">
-        <v>0.9462415230111136</v>
+        <v>0.9395174548097359</v>
       </c>
       <c r="AN8">
-        <v>2.192111888492398</v>
+        <v>2.464555010315478</v>
       </c>
       <c r="AO8">
-        <v>1.389207911484684</v>
+        <v>1.705231389955091</v>
       </c>
       <c r="AP8">
-        <v>3.807126716510738</v>
+        <v>4.2639503565686</v>
       </c>
       <c r="AQ8">
-        <v>-3.104391978020509</v>
+        <v>-3.495735030421925</v>
       </c>
       <c r="AR8">
-        <v>3.489051630129082</v>
+        <v>3.904446306804026</v>
       </c>
       <c r="AS8">
-        <v>0.04528437513625278</v>
+        <v>0.04562277171343429</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1722,10 +1722,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C9" s="2">
         <v>46294</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46293</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.59972298782819</v>
+        <v>1.601962707376349</v>
       </c>
       <c r="H9">
-        <v>3.132927229104057</v>
+        <v>3.138055044052319</v>
       </c>
       <c r="I9">
-        <v>0.6697449107308657</v>
+        <v>0.6698803318225415</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1755,19 +1755,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N9">
-        <v>0.8458175525478211</v>
+        <v>0.8570774490351964</v>
       </c>
       <c r="O9">
-        <v>90.909721205864</v>
+        <v>91.04354707305379</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.59972298782819</v>
+        <v>1.601962707376349</v>
       </c>
       <c r="R9" t="s">
         <v>60</v>
@@ -1776,10 +1776,10 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.8233824537727303</v>
+        <v>-0.8875092570303886</v>
       </c>
       <c r="U9">
-        <v>0.7704458387086559</v>
+        <v>0.799294106389153</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1788,34 +1788,34 @@
         <v>64</v>
       </c>
       <c r="X9">
-        <v>0.9995493275225033</v>
+        <v>0.998982502220201</v>
       </c>
       <c r="Y9">
-        <v>0.9996949380437088</v>
+        <v>0.9996597629019126</v>
       </c>
       <c r="Z9">
-        <v>0.0001456105212055414</v>
+        <v>0.0006772606817115889</v>
       </c>
       <c r="AA9">
-        <v>0.2643328411100709</v>
+        <v>0.01427563709587434</v>
       </c>
       <c r="AB9">
-        <v>126.5017684982347</v>
+        <v>132.5391637230116</v>
       </c>
       <c r="AC9">
-        <v>-3.999999999999993</v>
+        <v>7.999999999999998</v>
       </c>
       <c r="AD9">
-        <v>-0.594847598407908</v>
+        <v>-0.6760940052895485</v>
       </c>
       <c r="AE9">
-        <v>0.8038385003645597</v>
+        <v>0.7368153744402568</v>
       </c>
       <c r="AF9">
-        <v>2.023619844487391</v>
+        <v>1.795491592514916</v>
       </c>
       <c r="AG9">
-        <v>2.023002515058842</v>
+        <v>1.794880699665838</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1830,28 +1830,28 @@
         <v>72</v>
       </c>
       <c r="AL9">
-        <v>-0.3759279607465731</v>
+        <v>-0.342756180916133</v>
       </c>
       <c r="AM9">
-        <v>0.7267869082306386</v>
+        <v>0.7010553573831118</v>
       </c>
       <c r="AN9">
-        <v>-1.215020172870769</v>
+        <v>-1.191355127502856</v>
       </c>
       <c r="AO9">
-        <v>1.617118747976555</v>
+        <v>1.340860156058459</v>
       </c>
       <c r="AP9">
-        <v>-1.990772269975929</v>
+        <v>-2.101978656319525</v>
       </c>
       <c r="AQ9">
-        <v>1.494423962202693</v>
+        <v>1.119580104648711</v>
       </c>
       <c r="AR9">
-        <v>1.904882111597325</v>
+        <v>2.035641485288978</v>
       </c>
       <c r="AS9">
-        <v>0.0295144521936399</v>
+        <v>0.03005925759064645</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1862,10 +1862,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C10" s="2">
         <v>46294</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46293</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.6027559670788827</v>
+        <v>0.6064542638378875</v>
       </c>
       <c r="H10">
-        <v>2.114534260099425</v>
+        <v>2.117138368338203</v>
       </c>
       <c r="I10">
-        <v>0.4495675378177471</v>
+        <v>0.4496051547675751</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1895,19 +1895,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N10">
-        <v>45.62701541458623</v>
+        <v>46.14289602836235</v>
       </c>
       <c r="O10">
-        <v>44.15873739616363</v>
+        <v>44.16795736339884</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.6027559670788827</v>
+        <v>0.6064542638378875</v>
       </c>
       <c r="R10" t="s">
         <v>60</v>
@@ -1916,10 +1916,10 @@
         <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.7533042661490058</v>
+        <v>-0.8683317575861065</v>
       </c>
       <c r="U10">
-        <v>0.7385549057734455</v>
+        <v>0.7877528177119205</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
@@ -1928,34 +1928,34 @@
         <v>64</v>
       </c>
       <c r="X10">
-        <v>0.9976707654523389</v>
+        <v>0.9729935197228257</v>
       </c>
       <c r="Y10">
-        <v>0.9982719440255712</v>
+        <v>0.9880141071926903</v>
       </c>
       <c r="Z10">
-        <v>0.000601178573232275</v>
+        <v>0.01502058746986468</v>
       </c>
       <c r="AA10">
-        <v>0.1322712175335533</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>111.7585844870444</v>
+        <v>127.6849818985768</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>47.99999999999999</v>
       </c>
       <c r="AD10">
-        <v>-0.370696594622404</v>
+        <v>-0.6113196273735488</v>
       </c>
       <c r="AE10">
-        <v>0.9287540227290286</v>
+        <v>0.791383796389505</v>
       </c>
       <c r="AF10">
-        <v>1.46527622652169</v>
+        <v>1.040250627303208</v>
       </c>
       <c r="AG10">
-        <v>1.462744147184261</v>
+        <v>1.027782294791615</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
@@ -1970,28 +1970,28 @@
         <v>72</v>
       </c>
       <c r="AL10">
-        <v>-0.2095018845882451</v>
+        <v>-0.3019962079244225</v>
       </c>
       <c r="AM10">
-        <v>0.6274303558378602</v>
+        <v>0.6722534140912019</v>
       </c>
       <c r="AN10">
-        <v>-0.5068419590390092</v>
+        <v>-0.4863212653666539</v>
       </c>
       <c r="AO10">
-        <v>1.371187588717483</v>
+        <v>0.8876675396272942</v>
       </c>
       <c r="AP10">
-        <v>-0.5107035571324423</v>
+        <v>-0.6207243804159661</v>
       </c>
       <c r="AQ10">
-        <v>0.6156979308825091</v>
+        <v>0.4121811549329377</v>
       </c>
       <c r="AR10">
-        <v>0.5221834591978205</v>
+        <v>0.6299719581735045</v>
       </c>
       <c r="AS10">
-        <v>0.06418697643014314</v>
+        <v>0.0463160775886956</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2002,10 +2002,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C11" s="2">
         <v>46294</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46293</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2017,13 +2017,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.8442669667037336</v>
+        <v>1.041925313923938</v>
       </c>
       <c r="H11">
-        <v>2.200797306037765</v>
+        <v>2.188904150920961</v>
       </c>
       <c r="I11">
-        <v>0.5106466810612449</v>
+        <v>0.5076110935743041</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2035,19 +2035,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>47.79718145008715</v>
+        <v>92.43081000303509</v>
       </c>
       <c r="O11">
-        <v>0.6942003468106805</v>
+        <v>1.368657383899616</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.8442669667037336</v>
+        <v>1.041925313923938</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2056,10 +2056,10 @@
         <v>61</v>
       </c>
       <c r="T11">
-        <v>-0.799413457057678</v>
+        <v>-0.7672334316389841</v>
       </c>
       <c r="U11">
-        <v>0.7597236630877668</v>
+        <v>0.7452492951360262</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2068,34 +2068,34 @@
         <v>64</v>
       </c>
       <c r="X11">
-        <v>0.9995146556046763</v>
+        <v>0.9996673857942195</v>
       </c>
       <c r="Y11">
-        <v>0.9999504296472475</v>
+        <v>0.9999770035939334</v>
       </c>
       <c r="Z11">
-        <v>0.0004357740425711132</v>
+        <v>0.000309617799713835</v>
       </c>
       <c r="AA11">
-        <v>0.01423705444324133</v>
+        <v>0.2757833170547879</v>
       </c>
       <c r="AB11">
-        <v>-114.9934161293111</v>
+        <v>-118.0579048274395</v>
       </c>
       <c r="AC11">
-        <v>-5.999999999999996</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD11">
-        <v>-0.4225141149225828</v>
+        <v>-0.4703636561113492</v>
       </c>
       <c r="AE11">
-        <v>-0.9063563442108112</v>
+        <v>-0.8824726800357984</v>
       </c>
       <c r="AF11">
-        <v>1.390456156993545</v>
+        <v>1.592194252029057</v>
       </c>
       <c r="AG11">
-        <v>1.390387231591355</v>
+        <v>1.5921576372835</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2110,28 +2110,28 @@
         <v>70</v>
       </c>
       <c r="AL11">
-        <v>-0.2142541145113562</v>
+        <v>-0.3000341528419926</v>
       </c>
       <c r="AM11">
-        <v>0.6172400075338201</v>
+        <v>0.6851678841211011</v>
       </c>
       <c r="AN11">
-        <v>-0.5744807373974551</v>
+        <v>-0.736119286372471</v>
       </c>
       <c r="AO11">
-        <v>-1.265489614079226</v>
+        <v>-1.411213946911632</v>
       </c>
       <c r="AP11">
-        <v>-1.325059533461581</v>
+        <v>-1.524934214595735</v>
       </c>
       <c r="AQ11">
-        <v>-0.2605068332565275</v>
+        <v>0.2709319473538737</v>
       </c>
       <c r="AR11">
-        <v>1.324012771455588</v>
+        <v>1.466348748653392</v>
       </c>
       <c r="AS11">
-        <v>0.08229525472093058</v>
+        <v>0.0739321825409195</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -745,7 +745,7 @@
         <v>46296</v>
       </c>
       <c r="C2" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -754,16 +754,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.3875237439433573</v>
+        <v>0.9039271599898244</v>
       </c>
       <c r="G2">
-        <v>1.023507931409482</v>
+        <v>1.292937086363888</v>
       </c>
       <c r="H2">
-        <v>1.081881969853771</v>
+        <v>1.08323641924324</v>
       </c>
       <c r="I2">
-        <v>0.2594949391580547</v>
+        <v>0.259577329642715</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -775,19 +775,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>0.08580697460070541</v>
+        <v>0.1202261556356571</v>
       </c>
       <c r="O2">
-        <v>2.073991996840375</v>
+        <v>2.971481849620806</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.023507931409482</v>
+        <v>1.292937086363888</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -796,10 +796,10 @@
         <v>61</v>
       </c>
       <c r="T2">
-        <v>-0.734687963719556</v>
+        <v>-0.795840700863802</v>
       </c>
       <c r="U2">
-        <v>0.7887195394723627</v>
+        <v>0.893703816089003</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -808,34 +808,34 @@
         <v>64</v>
       </c>
       <c r="X2">
-        <v>0.999413872836842</v>
+        <v>0.999148425475805</v>
       </c>
       <c r="Y2">
-        <v>0.9999255768282354</v>
+        <v>0.9999457068072733</v>
       </c>
       <c r="Z2">
-        <v>0.0005117039913933308</v>
+        <v>0.0007972813314683913</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-121.4780406646686</v>
+        <v>-126.7300280378528</v>
       </c>
       <c r="AC2">
-        <v>-6.999999999999997</v>
+        <v>-9</v>
       </c>
       <c r="AD2">
-        <v>-0.5221717411748173</v>
+        <v>-0.5980452659787504</v>
       </c>
       <c r="AE2">
-        <v>-0.8528403559391755</v>
+        <v>-0.8014623259021011</v>
       </c>
       <c r="AF2">
-        <v>1.457898159031333</v>
+        <v>1.612172341808819</v>
       </c>
       <c r="AG2">
-        <v>1.457789657626228</v>
+        <v>1.612084811825156</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -850,28 +850,28 @@
         <v>70</v>
       </c>
       <c r="AL2">
-        <v>-0.5221328794976332</v>
+        <v>-0.5980127961918653</v>
       </c>
       <c r="AM2">
-        <v>0.8471886320641755</v>
+        <v>0.870165774698108</v>
       </c>
       <c r="AN2">
-        <v>-0.7440078990797057</v>
+        <v>-0.940598851906124</v>
       </c>
       <c r="AO2">
-        <v>-1.252768306779863</v>
+        <v>-1.307650064117717</v>
       </c>
       <c r="AP2">
-        <v>-1.422315781665723</v>
+        <v>-1.788621567071688</v>
       </c>
       <c r="AQ2">
-        <v>0.9086215531623327</v>
+        <v>1.027296053135507</v>
       </c>
       <c r="AR2">
-        <v>1.303750748746877</v>
+        <v>1.656572150677154</v>
       </c>
       <c r="AS2">
-        <v>0.0629122811876793</v>
+        <v>0.06152534985375147</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -885,7 +885,7 @@
         <v>46296</v>
       </c>
       <c r="C3" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -894,16 +894,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.2855066308341941</v>
       </c>
       <c r="G3">
-        <v>1.580657490691484</v>
+        <v>1.880633460185654</v>
       </c>
       <c r="H3">
-        <v>2.073646369635218</v>
+        <v>2.077175387423291</v>
       </c>
       <c r="I3">
-        <v>0.4578055743872117</v>
+        <v>0.4581538534314971</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -915,19 +915,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>0.006096319197139738</v>
+        <v>0.01049249985663591</v>
       </c>
       <c r="O3">
-        <v>1.746081603108766</v>
+        <v>3.001225824760506</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.580657490691484</v>
+        <v>1.880633460185654</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -936,10 +936,10 @@
         <v>61</v>
       </c>
       <c r="T3">
-        <v>-0.6458738715279175</v>
+        <v>-0.7235236151413669</v>
       </c>
       <c r="U3">
-        <v>0.6906240438363735</v>
+        <v>0.7683804230674002</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -948,34 +948,34 @@
         <v>64</v>
       </c>
       <c r="X3">
-        <v>0.9992455557111756</v>
+        <v>0.9986044133396391</v>
       </c>
       <c r="Y3">
-        <v>0.9999232065952424</v>
+        <v>0.9998752065146239</v>
       </c>
       <c r="Z3">
-        <v>0.0006776508840667939</v>
+        <v>0.001270793174984797</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-114.0052517395412</v>
+        <v>-120.7452217488702</v>
       </c>
       <c r="AC3">
-        <v>-7.999999999999998</v>
+        <v>-11</v>
       </c>
       <c r="AD3">
-        <v>-0.4068203770775038</v>
+        <v>-0.5112214130575213</v>
       </c>
       <c r="AE3">
-        <v>-0.9135081722647683</v>
+        <v>-0.8594490484208306</v>
       </c>
       <c r="AF3">
-        <v>2.898625258923872</v>
+        <v>2.816067563547034</v>
       </c>
       <c r="AG3">
-        <v>2.898402663621122</v>
+        <v>2.815716136660725</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -990,28 +990,28 @@
         <v>70</v>
       </c>
       <c r="AL3">
-        <v>-0.4067891359556232</v>
+        <v>-0.511157615955587</v>
       </c>
       <c r="AM3">
-        <v>0.8105194080324716</v>
+        <v>0.8431946044942086</v>
       </c>
       <c r="AN3">
-        <v>-1.135727345137667</v>
+        <v>-1.380707035153005</v>
       </c>
       <c r="AO3">
-        <v>-2.664484724449971</v>
+        <v>-2.449850074260372</v>
       </c>
       <c r="AP3">
-        <v>-2.252117691376024</v>
+        <v>-2.550765209518937</v>
       </c>
       <c r="AQ3">
-        <v>1.300479567144253</v>
+        <v>1.908526650114289</v>
       </c>
       <c r="AR3">
-        <v>2.054119478603557</v>
+        <v>2.300377809545366</v>
       </c>
       <c r="AS3">
-        <v>0.07666551599409556</v>
+        <v>0.06752094468777455</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1025,7 +1025,7 @@
         <v>46296</v>
       </c>
       <c r="C4" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1037,13 +1037,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2.608829370559007</v>
+        <v>2.705070514113462</v>
       </c>
       <c r="H4">
-        <v>2.088818639521052</v>
+        <v>2.093925894981043</v>
       </c>
       <c r="I4">
-        <v>0.4946572449696312</v>
+        <v>0.4954317052403744</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1055,19 +1055,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N4">
-        <v>0.4273259009971911</v>
+        <v>0.4941413098854273</v>
       </c>
       <c r="O4">
-        <v>13.05096556274141</v>
+        <v>14.76622911077049</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.608829370559007</v>
+        <v>2.705070514113462</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1076,10 +1076,10 @@
         <v>61</v>
       </c>
       <c r="T4">
-        <v>-0.9312250164575222</v>
+        <v>-0.9537670107020406</v>
       </c>
       <c r="U4">
-        <v>0.969012578960153</v>
+        <v>0.9791527777605064</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1088,34 +1088,34 @@
         <v>64</v>
       </c>
       <c r="X4">
-        <v>0.9977389620162824</v>
+        <v>0.9973396414355159</v>
       </c>
       <c r="Y4">
-        <v>0.9998452862170725</v>
+        <v>0.999830491778352</v>
       </c>
       <c r="Z4">
-        <v>0.002106324200790044</v>
+        <v>0.002490850342836137</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-149.5915908669479</v>
+        <v>-155.1656961041744</v>
       </c>
       <c r="AC4">
-        <v>-13.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AD4">
-        <v>-0.8624393908306924</v>
+        <v>-0.9075261832036445</v>
       </c>
       <c r="AE4">
-        <v>-0.5061603472651568</v>
+        <v>-0.419995508071009</v>
       </c>
       <c r="AF4">
-        <v>2.339620582215759</v>
+        <v>2.310443326772446</v>
       </c>
       <c r="AG4">
-        <v>2.339258610664869</v>
+        <v>2.310051687632906</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1130,28 +1130,28 @@
         <v>70</v>
       </c>
       <c r="AL4">
-        <v>-0.8623059595699913</v>
+        <v>-0.9073723500542307</v>
       </c>
       <c r="AM4">
-        <v>0.9520876357080611</v>
+        <v>0.9657125306530133</v>
       </c>
       <c r="AN4">
-        <v>-1.977952480195611</v>
+        <v>-2.057925361683973</v>
       </c>
       <c r="AO4">
-        <v>-1.239678744082058</v>
+        <v>-1.036690202182976</v>
       </c>
       <c r="AP4">
-        <v>-3.267881377329152</v>
+        <v>-3.355195142784461</v>
       </c>
       <c r="AQ4">
-        <v>3.219450918109771</v>
+        <v>3.372322007769957</v>
       </c>
       <c r="AR4">
-        <v>2.945769017765066</v>
+        <v>3.022937930816534</v>
       </c>
       <c r="AS4">
-        <v>0.04393354478081245</v>
+        <v>0.04323997620335489</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1165,7 +1165,7 @@
         <v>46296</v>
       </c>
       <c r="C5" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1177,13 +1177,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.448355559158069</v>
+        <v>2.48292018664256</v>
       </c>
       <c r="H5">
-        <v>1.534825744873344</v>
+        <v>1.538272371080229</v>
       </c>
       <c r="I5">
-        <v>0.3548660334225586</v>
+        <v>0.3564353161137003</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1195,19 +1195,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5">
-        <v>0.03713734760323029</v>
+        <v>0.04546823783629431</v>
       </c>
       <c r="O5">
-        <v>8.825714928623762</v>
+        <v>9.801452455279424</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.448355559158069</v>
+        <v>2.48292018664256</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1216,10 +1216,10 @@
         <v>61</v>
       </c>
       <c r="T5">
-        <v>-0.8679424902676787</v>
+        <v>-0.9063526665320979</v>
       </c>
       <c r="U5">
-        <v>0.9405322076889344</v>
+        <v>0.9578006969677269</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1228,34 +1228,34 @@
         <v>64</v>
       </c>
       <c r="X5">
-        <v>0.9977810367969649</v>
+        <v>0.9969401553528484</v>
       </c>
       <c r="Y5">
-        <v>0.999832348273916</v>
+        <v>0.9997679881131314</v>
       </c>
       <c r="Z5">
-        <v>0.002051311476951034</v>
+        <v>0.002827832760282978</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-137.3801750828664</v>
+        <v>-144.3589612871395</v>
       </c>
       <c r="AC5">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="AD5">
-        <v>-0.7358628371535323</v>
+        <v>-0.8126836007274972</v>
       </c>
       <c r="AE5">
-        <v>-0.6771306261692451</v>
+        <v>-0.5827052128723321</v>
       </c>
       <c r="AF5">
-        <v>2.631684725734282</v>
+        <v>2.40271221089104</v>
       </c>
       <c r="AG5">
-        <v>2.631243519247504</v>
+        <v>2.402154753097389</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1270,28 +1270,28 @@
         <v>70</v>
       </c>
       <c r="AL5">
-        <v>-0.7357394684787224</v>
+        <v>-0.8124950484718653</v>
       </c>
       <c r="AM5">
-        <v>0.9135148954568622</v>
+        <v>0.9365796182124053</v>
       </c>
       <c r="AN5">
-        <v>-1.872197956013963</v>
+        <v>-1.893505965617223</v>
       </c>
       <c r="AO5">
-        <v>-1.841178257824594</v>
+        <v>-1.467101241271337</v>
       </c>
       <c r="AP5">
-        <v>-2.999864441677517</v>
+        <v>-3.056251015761235</v>
       </c>
       <c r="AQ5">
-        <v>3.456865937544864</v>
+        <v>3.205348086151252</v>
       </c>
       <c r="AR5">
-        <v>2.638502559097331</v>
+        <v>2.728059091268482</v>
       </c>
       <c r="AS5">
-        <v>0.04790185056712054</v>
+        <v>0.04762838563626552</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1305,7 +1305,7 @@
         <v>46296</v>
       </c>
       <c r="C6" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1317,13 +1317,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.686218320861796</v>
+        <v>1.616572460132184</v>
       </c>
       <c r="H6">
-        <v>0.977603654310369</v>
+        <v>0.9829147730296028</v>
       </c>
       <c r="I6">
-        <v>0.2621702942601331</v>
+        <v>0.2637127711567357</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1335,19 +1335,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6">
-        <v>0.5944865380829603</v>
+        <v>0.6751154385407371</v>
       </c>
       <c r="O6">
-        <v>9.568869752306895</v>
+        <v>10.77021336140749</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.686218320861796</v>
+        <v>1.616572460132184</v>
       </c>
       <c r="R6" t="s">
         <v>58</v>
@@ -1356,10 +1356,10 @@
         <v>61</v>
       </c>
       <c r="T6">
-        <v>-0.9310160695900964</v>
+        <v>-0.9818373332182917</v>
       </c>
       <c r="U6">
-        <v>0.9689184193132682</v>
+        <v>0.9916260459944204</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1368,34 +1368,34 @@
         <v>64</v>
       </c>
       <c r="X6">
-        <v>0.9981715742369812</v>
+        <v>0.9919022010740305</v>
       </c>
       <c r="Y6">
-        <v>0.9998447519908988</v>
+        <v>0.9991969841847563</v>
       </c>
       <c r="Z6">
-        <v>0.001673177753917621</v>
+        <v>0.007294783110725844</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-149.5443119926976</v>
+        <v>-164.5063510536556</v>
       </c>
       <c r="AC6">
-        <v>-12.99999999999999</v>
+        <v>-27</v>
       </c>
       <c r="AD6">
-        <v>-0.8620214278994317</v>
+        <v>-0.9636600698065861</v>
       </c>
       <c r="AE6">
-        <v>-0.5068718357161155</v>
+        <v>-0.2671315590872138</v>
       </c>
       <c r="AF6">
-        <v>1.545982279947867</v>
+        <v>1.360944228914682</v>
       </c>
       <c r="AG6">
-        <v>1.545742269276799</v>
+        <v>1.359851369175199</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1410,28 +1410,28 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>-0.8618876007889478</v>
+        <v>-0.9628862355300126</v>
       </c>
       <c r="AM6">
-        <v>0.9524285422341819</v>
+        <v>0.9833178748673881</v>
       </c>
       <c r="AN6">
-        <v>-1.307642339867632</v>
+        <v>-1.276534132260322</v>
       </c>
       <c r="AO6">
-        <v>-0.8193903906115763</v>
+        <v>-0.4390378921614405</v>
       </c>
       <c r="AP6">
-        <v>-1.985887170759058</v>
+        <v>-1.806419332275516</v>
       </c>
       <c r="AQ6">
-        <v>2.55210889701048</v>
+        <v>2.816401832666294</v>
       </c>
       <c r="AR6">
-        <v>1.738626987625601</v>
+        <v>1.544142849550404</v>
       </c>
       <c r="AS6">
-        <v>0.04082366221641366</v>
+        <v>0.03666060359501535</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>46296</v>
       </c>
       <c r="C7" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.191816852613451</v>
+        <v>2.088257853924038</v>
       </c>
       <c r="H7">
-        <v>1.509463048023154</v>
+        <v>1.517433605238748</v>
       </c>
       <c r="I7">
-        <v>0.3777831208959462</v>
+        <v>0.3795290827545978</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1475,19 +1475,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>0.05380602698166632</v>
+        <v>0.06340265329516924</v>
       </c>
       <c r="O7">
-        <v>10.01441608273496</v>
+        <v>10.89192154282304</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.191816852613451</v>
+        <v>2.088257853924038</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
@@ -1496,10 +1496,10 @@
         <v>61</v>
       </c>
       <c r="T7">
-        <v>-0.9047095565525618</v>
+        <v>-0.9721408351059729</v>
       </c>
       <c r="U7">
-        <v>0.9569307161286699</v>
+        <v>0.9869858172170075</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1508,34 +1508,34 @@
         <v>64</v>
       </c>
       <c r="X7">
-        <v>0.9949606768837319</v>
+        <v>0.9849566056741544</v>
       </c>
       <c r="Y7">
-        <v>0.9992456627200683</v>
+        <v>0.9980897656772786</v>
       </c>
       <c r="Z7">
-        <v>0.004284985836336408</v>
+        <v>0.01313316000312414</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-144.032197867296</v>
+        <v>-160.7742284166306</v>
       </c>
       <c r="AC7">
-        <v>-21.99999999999999</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>-0.8093471777076577</v>
+        <v>-0.9442283508264429</v>
       </c>
       <c r="AE7">
-        <v>-0.5873305252893375</v>
+        <v>-0.3292913929873902</v>
       </c>
       <c r="AF7">
-        <v>2.274281913738901</v>
+        <v>1.870023817185445</v>
       </c>
       <c r="AG7">
-        <v>2.272566338106293</v>
+        <v>1.866451633505551</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1550,28 +1550,28 @@
         <v>70</v>
       </c>
       <c r="AL7">
-        <v>-0.8087366569591053</v>
+        <v>-0.9424246534222075</v>
       </c>
       <c r="AM7">
-        <v>0.9366725589471102</v>
+        <v>0.9769265843431376</v>
       </c>
       <c r="AN7">
-        <v>-1.756786577883378</v>
+        <v>-1.675686243201328</v>
       </c>
       <c r="AO7">
-        <v>-1.426204797739647</v>
+        <v>-0.7646194488281861</v>
       </c>
       <c r="AP7">
-        <v>-2.342231527080917</v>
+        <v>-2.214383829346423</v>
       </c>
       <c r="AQ7">
-        <v>4.49810636208657</v>
+        <v>4.050922111619149</v>
       </c>
       <c r="AR7">
-        <v>1.904298802940368</v>
+        <v>1.837490612426009</v>
       </c>
       <c r="AS7">
-        <v>0.03911717544807258</v>
+        <v>0.03782225927895106</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1585,7 +1585,7 @@
         <v>46296</v>
       </c>
       <c r="C8" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1597,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>3.293394736705306</v>
+        <v>3.378740912970246</v>
       </c>
       <c r="H8">
-        <v>1.491186502164883</v>
+        <v>1.499279494793825</v>
       </c>
       <c r="I8">
-        <v>0.3750222724914655</v>
+        <v>0.3791762932647163</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1615,19 +1615,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N8">
-        <v>-0.0804372068006162</v>
+        <v>-0.08967032640047667</v>
       </c>
       <c r="O8">
-        <v>-22.01604878218242</v>
+        <v>-24.15827132890749</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.293394736705306</v>
+        <v>3.378740912970246</v>
       </c>
       <c r="R8" t="s">
         <v>59</v>
@@ -1636,10 +1636,10 @@
         <v>62</v>
       </c>
       <c r="T8">
-        <v>0.9106606642624933</v>
+        <v>0.9306934926262588</v>
       </c>
       <c r="U8">
-        <v>0.9597737270081802</v>
+        <v>0.9688101444556124</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1648,34 +1648,34 @@
         <v>64</v>
       </c>
       <c r="X8">
-        <v>0.9998866109712756</v>
+        <v>0.9998652578425244</v>
       </c>
       <c r="Y8">
-        <v>0.9999057123602327</v>
+        <v>0.9999922910951836</v>
       </c>
       <c r="Z8">
-        <v>1.910138895711011E-05</v>
+        <v>0.00012703325265917</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>34.78356273707708</v>
+        <v>30.52738825204341</v>
       </c>
       <c r="AC8">
-        <v>1.000000000000001</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD8">
-        <v>0.8213129041355656</v>
+        <v>0.8613864509711305</v>
       </c>
       <c r="AE8">
-        <v>0.5704779693383464</v>
+        <v>0.5079501767726439</v>
       </c>
       <c r="AF8">
-        <v>2.99731258365313</v>
+        <v>2.973292881918074</v>
       </c>
       <c r="AG8">
-        <v>2.997029974123973</v>
+        <v>2.973269961086256</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1690,28 +1690,28 @@
         <v>71</v>
       </c>
       <c r="AL8">
-        <v>0.8212354644803243</v>
+        <v>0.8613798106249698</v>
       </c>
       <c r="AM8">
-        <v>0.9395174548097359</v>
+        <v>0.9518200568779011</v>
       </c>
       <c r="AN8">
-        <v>2.464555010315478</v>
+        <v>2.549126527825603</v>
       </c>
       <c r="AO8">
-        <v>1.705231389955091</v>
+        <v>1.529719679925059</v>
       </c>
       <c r="AP8">
-        <v>4.2639503565686</v>
+        <v>4.288121635869815</v>
       </c>
       <c r="AQ8">
-        <v>-3.495735030421925</v>
+        <v>-3.984759872388338</v>
       </c>
       <c r="AR8">
-        <v>3.904446306804026</v>
+        <v>3.884106796188359</v>
       </c>
       <c r="AS8">
-        <v>0.04562277171343429</v>
+        <v>0.04395453531168182</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>46296</v>
       </c>
       <c r="C9" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.601962707376349</v>
+        <v>1.305286412125909</v>
       </c>
       <c r="H9">
-        <v>3.138055044052319</v>
+        <v>3.142694495672174</v>
       </c>
       <c r="I9">
-        <v>0.6698803318225415</v>
+        <v>0.6696902861742862</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1755,19 +1755,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N9">
-        <v>0.8570774490351964</v>
+        <v>0.8676034335289364</v>
       </c>
       <c r="O9">
-        <v>91.04354707305379</v>
+        <v>86.76344204725422</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.601962707376349</v>
+        <v>1.305286412125909</v>
       </c>
       <c r="R9" t="s">
         <v>60</v>
@@ -1776,10 +1776,10 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.8875092570303886</v>
+        <v>-0.8922180012993804</v>
       </c>
       <c r="U9">
-        <v>0.799294106389153</v>
+        <v>0.8014244115365977</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1788,34 +1788,34 @@
         <v>64</v>
       </c>
       <c r="X9">
-        <v>0.998982502220201</v>
+        <v>0.9981244334717523</v>
       </c>
       <c r="Y9">
-        <v>0.9996597629019126</v>
+        <v>0.9997052438075062</v>
       </c>
       <c r="Z9">
-        <v>0.0006772606817115889</v>
+        <v>0.001580810335753968</v>
       </c>
       <c r="AA9">
-        <v>0.01427563709587434</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>132.5391637230116</v>
+        <v>133.1799076199624</v>
       </c>
       <c r="AC9">
-        <v>7.999999999999998</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AD9">
-        <v>-0.6760940052895485</v>
+        <v>-0.6842914304466994</v>
       </c>
       <c r="AE9">
-        <v>0.7368153744402568</v>
+        <v>0.7292086383314518</v>
       </c>
       <c r="AF9">
-        <v>1.795491592514916</v>
+        <v>1.484966742089692</v>
       </c>
       <c r="AG9">
-        <v>1.794880699665838</v>
+        <v>1.484529038946814</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1830,28 +1830,28 @@
         <v>72</v>
       </c>
       <c r="AL9">
-        <v>-0.342756180916133</v>
+        <v>-0.3420448656550524</v>
       </c>
       <c r="AM9">
-        <v>0.7010553573831118</v>
+        <v>0.7012332975526965</v>
       </c>
       <c r="AN9">
-        <v>-1.191355127502856</v>
+        <v>-0.983698823497191</v>
       </c>
       <c r="AO9">
-        <v>1.340860156058459</v>
+        <v>1.108692421264028</v>
       </c>
       <c r="AP9">
-        <v>-2.101978656319525</v>
+        <v>-1.66527450442444</v>
       </c>
       <c r="AQ9">
-        <v>1.119580104648711</v>
+        <v>1.289303196796456</v>
       </c>
       <c r="AR9">
-        <v>2.035641485288978</v>
+        <v>1.574602384132876</v>
       </c>
       <c r="AS9">
-        <v>0.03005925759064645</v>
+        <v>0.02633977942627003</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1865,7 +1865,7 @@
         <v>46296</v>
       </c>
       <c r="C10" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.6064542638378875</v>
+        <v>0.3424523408692119</v>
       </c>
       <c r="H10">
-        <v>2.117138368338203</v>
+        <v>2.119494466268526</v>
       </c>
       <c r="I10">
-        <v>0.4496051547675751</v>
+        <v>0.4497847541212192</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1895,19 +1895,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N10">
-        <v>46.14289602836235</v>
+        <v>46.58664648135557</v>
       </c>
       <c r="O10">
-        <v>44.16795736339884</v>
+        <v>42.58794284756122</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>0.1663948653018025</v>
       </c>
       <c r="Q10">
-        <v>0.6064542638378875</v>
+        <v>0.4108088189658225</v>
       </c>
       <c r="R10" t="s">
         <v>60</v>
@@ -1916,10 +1916,10 @@
         <v>63</v>
       </c>
       <c r="T10">
-        <v>-0.8683317575861065</v>
+        <v>-0.9353001500868481</v>
       </c>
       <c r="U10">
-        <v>0.7877528177119205</v>
+        <v>0.8131384431632092</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
@@ -1928,34 +1928,34 @@
         <v>64</v>
       </c>
       <c r="X10">
-        <v>0.9729935197228257</v>
+        <v>0.9084620100189639</v>
       </c>
       <c r="Y10">
-        <v>0.9880141071926903</v>
+        <v>0.96901350249651</v>
       </c>
       <c r="Z10">
-        <v>0.01502058746986468</v>
+        <v>0.0605514924775461</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>127.6849818985768</v>
+        <v>143.7584485979793</v>
       </c>
       <c r="AC10">
-        <v>47.99999999999999</v>
+        <v>90</v>
       </c>
       <c r="AD10">
-        <v>-0.6113196273735488</v>
+        <v>-0.8065317875677571</v>
       </c>
       <c r="AE10">
-        <v>0.791383796389505</v>
+        <v>0.5911907269593784</v>
       </c>
       <c r="AF10">
-        <v>1.040250627303208</v>
+        <v>0.6693071077586706</v>
       </c>
       <c r="AG10">
-        <v>1.027782294791615</v>
+        <v>0.6485676247350385</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
@@ -1970,28 +1970,28 @@
         <v>72</v>
       </c>
       <c r="AL10">
-        <v>-0.3019962079244225</v>
+        <v>-0.3907700961729017</v>
       </c>
       <c r="AM10">
-        <v>0.6722534140912019</v>
+        <v>0.7233679184644034</v>
       </c>
       <c r="AN10">
-        <v>-0.4863212653666539</v>
+        <v>-0.3468659020247033</v>
       </c>
       <c r="AO10">
-        <v>0.8876675396272942</v>
+        <v>0.4993964211198217</v>
       </c>
       <c r="AP10">
-        <v>-0.6207243804159661</v>
+        <v>-0.3497518955610466</v>
       </c>
       <c r="AQ10">
-        <v>0.4121811549329377</v>
+        <v>0.6296139460443165</v>
       </c>
       <c r="AR10">
-        <v>0.6299719581735045</v>
+        <v>0.3260613169725994</v>
       </c>
       <c r="AS10">
-        <v>0.0463160775886956</v>
+        <v>0.05164229119801473</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2005,7 +2005,7 @@
         <v>46296</v>
       </c>
       <c r="C11" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2017,13 +2017,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.041925313923938</v>
+        <v>1.184094117988854</v>
       </c>
       <c r="H11">
-        <v>2.188904150920961</v>
+        <v>2.178143677243853</v>
       </c>
       <c r="I11">
-        <v>0.5076110935743041</v>
+        <v>0.5048565869577177</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2035,19 +2035,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>92.43081000303509</v>
+        <v>145.9393412564551</v>
       </c>
       <c r="O11">
-        <v>1.368657383899616</v>
+        <v>2.199502406130128</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.041925313923938</v>
+        <v>1.184094117988854</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2056,10 +2056,10 @@
         <v>61</v>
       </c>
       <c r="T11">
-        <v>-0.7672334316389841</v>
+        <v>-0.8035130852316634</v>
       </c>
       <c r="U11">
-        <v>0.7452492951360262</v>
+        <v>0.7615723161265613</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2068,34 +2068,34 @@
         <v>64</v>
       </c>
       <c r="X11">
-        <v>0.9996673857942195</v>
+        <v>0.999290290295659</v>
       </c>
       <c r="Y11">
-        <v>0.9999770035939334</v>
+        <v>0.9999657110892508</v>
       </c>
       <c r="Z11">
-        <v>0.000309617799713835</v>
+        <v>0.000675420793591841</v>
       </c>
       <c r="AA11">
-        <v>0.2757833170547879</v>
+        <v>0.2858700109977305</v>
       </c>
       <c r="AB11">
-        <v>-118.0579048274395</v>
+        <v>-123.778093395207</v>
       </c>
       <c r="AC11">
-        <v>-4.999999999999995</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD11">
-        <v>-0.4703636561113492</v>
+        <v>-0.5559778542657846</v>
       </c>
       <c r="AE11">
-        <v>-0.8824726800357984</v>
+        <v>-0.8311971039206127</v>
       </c>
       <c r="AF11">
-        <v>1.592194252029057</v>
+        <v>1.59227966168652</v>
       </c>
       <c r="AG11">
-        <v>1.5921576372835</v>
+        <v>1.592225064151312</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2110,28 +2110,28 @@
         <v>70</v>
       </c>
       <c r="AL11">
-        <v>-0.3000341528419926</v>
+        <v>-0.3574453679570265</v>
       </c>
       <c r="AM11">
-        <v>0.6851678841211011</v>
+        <v>0.7141599891641723</v>
       </c>
       <c r="AN11">
-        <v>-0.736119286372471</v>
+        <v>-0.863648980598598</v>
       </c>
       <c r="AO11">
-        <v>-1.411213946911632</v>
+        <v>-1.336363537718617</v>
       </c>
       <c r="AP11">
-        <v>-1.524934214595735</v>
+        <v>-1.621296341443538</v>
       </c>
       <c r="AQ11">
-        <v>0.2709319473538737</v>
+        <v>0.8466860714347184</v>
       </c>
       <c r="AR11">
-        <v>1.466348748653392</v>
+        <v>1.50767916435789</v>
       </c>
       <c r="AS11">
-        <v>0.0739321825409195</v>
+        <v>0.06530245464231241</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -193,6 +193,9 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
@@ -202,6 +205,9 @@
     <t>空头加速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
@@ -220,6 +226,9 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
@@ -227,6 +236,9 @@
   </si>
   <si>
     <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -742,10 +754,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C2" s="2">
         <v>46296</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46295</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -754,16 +766,16 @@
         <v>-1</v>
       </c>
       <c r="F2">
-        <v>0.9039271599898244</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1.292937086363888</v>
+        <v>1.436117214086973</v>
       </c>
       <c r="H2">
-        <v>1.08323641924324</v>
+        <v>1.086065056773773</v>
       </c>
       <c r="I2">
-        <v>0.259577329642715</v>
+        <v>0.2598070738741146</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -775,103 +787,103 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>0.1202261556356571</v>
+        <v>0.161201512681778</v>
       </c>
       <c r="O2">
-        <v>2.971481849620806</v>
+        <v>3.887652542669212</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.292937086363888</v>
+        <v>1.436117214086973</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
       </c>
       <c r="S2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T2">
-        <v>-0.795840700863802</v>
+        <v>-0.8324927566148754</v>
       </c>
       <c r="U2">
-        <v>0.893703816089003</v>
+        <v>0.9246058751830176</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X2">
-        <v>0.999148425475805</v>
+        <v>0.9988875274815423</v>
       </c>
       <c r="Y2">
-        <v>0.9999457068072733</v>
+        <v>0.9999365388252949</v>
       </c>
       <c r="Z2">
-        <v>0.0007972813314683913</v>
+        <v>0.001049011343752571</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-126.7300280378528</v>
+        <v>-131.6803984646848</v>
       </c>
       <c r="AC2">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="AD2">
-        <v>-0.5980452659787504</v>
+        <v>-0.6649748823486659</v>
       </c>
       <c r="AE2">
-        <v>-0.8014623259021011</v>
+        <v>-0.7468657214288108</v>
       </c>
       <c r="AF2">
-        <v>1.612172341808819</v>
+        <v>1.630624588226658</v>
       </c>
       <c r="AG2">
-        <v>1.612084811825156</v>
+        <v>1.630521106874786</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL2">
-        <v>-0.5980127961918653</v>
+        <v>-0.6649326822614826</v>
       </c>
       <c r="AM2">
-        <v>0.870165774698108</v>
+        <v>0.8907932093356834</v>
       </c>
       <c r="AN2">
-        <v>-0.940598851906124</v>
+        <v>-1.058581563827818</v>
       </c>
       <c r="AO2">
-        <v>-1.307650064117717</v>
+        <v>-1.237913132438912</v>
       </c>
       <c r="AP2">
-        <v>-1.788621567071688</v>
+        <v>-1.927592862822559</v>
       </c>
       <c r="AQ2">
-        <v>1.027296053135507</v>
+        <v>1.362787785936421</v>
       </c>
       <c r="AR2">
-        <v>1.656572150677154</v>
+        <v>1.764276295525329</v>
       </c>
       <c r="AS2">
-        <v>0.06152534985375147</v>
+        <v>0.05784695971846391</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -882,10 +894,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C3" s="2">
         <v>46296</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46295</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -894,16 +906,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.2855066308341941</v>
+        <v>0.4559350349948318</v>
       </c>
       <c r="G3">
-        <v>1.880633460185654</v>
+        <v>2.039962344502193</v>
       </c>
       <c r="H3">
-        <v>2.077175387423291</v>
+        <v>2.080368308279167</v>
       </c>
       <c r="I3">
-        <v>0.4581538534314971</v>
+        <v>0.4584817413588667</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -915,103 +927,103 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>0.01049249985663591</v>
+        <v>0.01571417618322567</v>
       </c>
       <c r="O3">
-        <v>3.001225824760506</v>
+        <v>4.26394934712977</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.880633460185654</v>
+        <v>2.039962344502193</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T3">
-        <v>-0.7235236151413669</v>
+        <v>-0.7640048563958072</v>
       </c>
       <c r="U3">
-        <v>0.7683804230674002</v>
+        <v>0.8121651451941891</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X3">
-        <v>0.9986044133396391</v>
+        <v>0.9988570305802786</v>
       </c>
       <c r="Y3">
-        <v>0.9998752065146239</v>
+        <v>0.9998908182674044</v>
       </c>
       <c r="Z3">
-        <v>0.001270793174984797</v>
+        <v>0.001033787687125809</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-120.7452217488702</v>
+        <v>-124.7305232386064</v>
       </c>
       <c r="AC3">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AD3">
-        <v>-0.5112214130575213</v>
+        <v>-0.5697174242557334</v>
       </c>
       <c r="AE3">
-        <v>-0.8594490484208306</v>
+        <v>-0.8218406515252289</v>
       </c>
       <c r="AF3">
-        <v>2.816067563547034</v>
+        <v>2.763393780614182</v>
       </c>
       <c r="AG3">
-        <v>2.815716136660725</v>
+        <v>2.763092068493371</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL3">
-        <v>-0.511157615955587</v>
+        <v>-0.5696552215202633</v>
       </c>
       <c r="AM3">
-        <v>0.8431946044942086</v>
+        <v>0.8617887040323801</v>
       </c>
       <c r="AN3">
-        <v>-1.380707035153005</v>
+        <v>-1.523950601975966</v>
       </c>
       <c r="AO3">
-        <v>-2.449850074260372</v>
+        <v>-2.301406853944384</v>
       </c>
       <c r="AP3">
-        <v>-2.550765209518937</v>
+        <v>-2.652459802625317</v>
       </c>
       <c r="AQ3">
-        <v>1.908526650114289</v>
+        <v>2.408154409026348</v>
       </c>
       <c r="AR3">
-        <v>2.300377809545366</v>
+        <v>2.365246036986357</v>
       </c>
       <c r="AS3">
-        <v>0.06752094468777455</v>
+        <v>0.06058873091954324</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1022,10 +1034,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C4" s="2">
         <v>46296</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46295</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1037,13 +1049,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2.705070514113462</v>
+        <v>2.857204220469094</v>
       </c>
       <c r="H4">
-        <v>2.093925894981043</v>
+        <v>2.099825150341695</v>
       </c>
       <c r="I4">
-        <v>0.4954317052403744</v>
+        <v>0.4964730140235191</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1055,103 +1067,103 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4">
-        <v>0.4941413098854273</v>
+        <v>0.5675689683350956</v>
       </c>
       <c r="O4">
-        <v>14.76622911077049</v>
+        <v>15.61707066959776</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.705070514113462</v>
+        <v>2.857204220469094</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4">
-        <v>-0.9537670107020406</v>
+        <v>-0.9372718221868184</v>
       </c>
       <c r="U4">
-        <v>0.9791527777605064</v>
+        <v>0.9717498527387396</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X4">
-        <v>0.9973396414355159</v>
+        <v>0.9995596249631102</v>
       </c>
       <c r="Y4">
-        <v>0.999830491778352</v>
+        <v>0.9999101310186854</v>
       </c>
       <c r="Z4">
-        <v>0.002490850342836137</v>
+        <v>0.0003505060555751838</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-155.1656961041744</v>
+        <v>-150.990345926623</v>
       </c>
       <c r="AC4">
-        <v>-16</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD4">
-        <v>-0.9075261832036445</v>
+        <v>-0.8745380065495315</v>
       </c>
       <c r="AE4">
-        <v>-0.419995508071009</v>
+        <v>-0.4849569827318414</v>
       </c>
       <c r="AF4">
-        <v>2.310443326772446</v>
+        <v>2.470906877006796</v>
       </c>
       <c r="AG4">
-        <v>2.310051687632906</v>
+        <v>2.470684819122837</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL4">
-        <v>-0.9073723500542307</v>
+        <v>-0.874459412709762</v>
       </c>
       <c r="AM4">
-        <v>0.9657125306530133</v>
+        <v>0.9553502360627675</v>
       </c>
       <c r="AN4">
-        <v>-2.057925361683973</v>
+        <v>-2.145904883336818</v>
       </c>
       <c r="AO4">
-        <v>-1.036690202182976</v>
+        <v>-1.222741549119324</v>
       </c>
       <c r="AP4">
-        <v>-3.355195142784461</v>
+        <v>-3.654036973284544</v>
       </c>
       <c r="AQ4">
-        <v>3.372322007769957</v>
+        <v>2.911302453698565</v>
       </c>
       <c r="AR4">
-        <v>3.022937930816534</v>
+        <v>3.361581629454079</v>
       </c>
       <c r="AS4">
-        <v>0.04323997620335489</v>
+        <v>0.04653141172421118</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1162,10 +1174,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C5" s="2">
         <v>46296</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46295</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1177,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.48292018664256</v>
+        <v>2.679185503841806</v>
       </c>
       <c r="H5">
-        <v>1.538272371080229</v>
+        <v>1.541991342139128</v>
       </c>
       <c r="I5">
-        <v>0.3564353161137003</v>
+        <v>0.3583632125303415</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1195,103 +1207,103 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>0.04546823783629431</v>
+        <v>0.05503432320538648</v>
       </c>
       <c r="O5">
-        <v>9.801452455279424</v>
+        <v>10.70409175986957</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.48292018664256</v>
+        <v>2.679185503841806</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
       </c>
       <c r="S5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T5">
-        <v>-0.9063526665320979</v>
+        <v>-0.8835016086238986</v>
       </c>
       <c r="U5">
-        <v>0.9578006969677269</v>
+        <v>0.9475566658037164</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X5">
-        <v>0.9969401553528484</v>
+        <v>0.9996484084534735</v>
       </c>
       <c r="Y5">
-        <v>0.9997679881131314</v>
+        <v>0.9999237676918484</v>
       </c>
       <c r="Z5">
-        <v>0.002827832760282978</v>
+        <v>0.0002753592383749615</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-144.3589612871395</v>
+        <v>-140.0847447279974</v>
       </c>
       <c r="AC5">
-        <v>-17</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD5">
-        <v>-0.8126836007274972</v>
+        <v>-0.7669943356294604</v>
       </c>
       <c r="AE5">
-        <v>-0.5827052128723321</v>
+        <v>-0.6416538701763769</v>
       </c>
       <c r="AF5">
-        <v>2.40271221089104</v>
+        <v>2.646940165690181</v>
       </c>
       <c r="AG5">
-        <v>2.402154753097389</v>
+        <v>2.646738383331812</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL5">
-        <v>-0.8124950484718653</v>
+        <v>-0.7669358658809162</v>
       </c>
       <c r="AM5">
-        <v>0.9365796182124053</v>
+        <v>0.9224527554252537</v>
       </c>
       <c r="AN5">
-        <v>-1.893505965617223</v>
+        <v>-2.012734723500569</v>
       </c>
       <c r="AO5">
-        <v>-1.467101241271337</v>
+        <v>-1.717633643535347</v>
       </c>
       <c r="AP5">
-        <v>-3.056251015761235</v>
+        <v>-3.419068369064508</v>
       </c>
       <c r="AQ5">
-        <v>3.205348086151252</v>
+        <v>2.732463485735718</v>
       </c>
       <c r="AR5">
-        <v>2.728059091268482</v>
+        <v>3.1331921734011</v>
       </c>
       <c r="AS5">
-        <v>0.04762838563626552</v>
+        <v>0.05079242637154264</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1302,10 +1314,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C6" s="2">
         <v>46296</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46295</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1317,13 +1329,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.616572460132184</v>
+        <v>1.627240488486849</v>
       </c>
       <c r="H6">
-        <v>0.9829147730296028</v>
+        <v>0.9915653063969215</v>
       </c>
       <c r="I6">
-        <v>0.2637127711567357</v>
+        <v>0.2653715721284291</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1335,103 +1347,103 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N6">
-        <v>0.6751154385407371</v>
+        <v>0.7567574172829159</v>
       </c>
       <c r="O6">
-        <v>10.77021336140749</v>
+        <v>11.61383390550828</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.616572460132184</v>
+        <v>1.627240488486849</v>
       </c>
       <c r="R6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T6">
-        <v>-0.9818373332182917</v>
+        <v>-0.9940211326421459</v>
       </c>
       <c r="U6">
-        <v>0.9916260459944204</v>
+        <v>0.9971626583140305</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X6">
-        <v>0.9919022010740305</v>
+        <v>0.9932128951423037</v>
       </c>
       <c r="Y6">
-        <v>0.9991969841847563</v>
+        <v>0.9994125945002593</v>
       </c>
       <c r="Z6">
-        <v>0.007294783110725844</v>
+        <v>0.006199699357955613</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-164.5063510536556</v>
+        <v>-171.1292623209555</v>
       </c>
       <c r="AC6">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="AD6">
-        <v>-0.9636600698065861</v>
+        <v>-0.9880387512005313</v>
       </c>
       <c r="AE6">
-        <v>-0.2671315590872138</v>
+        <v>-0.1542057914803935</v>
       </c>
       <c r="AF6">
-        <v>1.360944228914682</v>
+        <v>1.315213925417059</v>
       </c>
       <c r="AG6">
-        <v>1.359851369175199</v>
+        <v>1.314441361523933</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AL6">
-        <v>-0.9628862355300126</v>
+        <v>-0.9874583718041192</v>
       </c>
       <c r="AM6">
-        <v>0.9833178748673881</v>
+        <v>0.9905963388632689</v>
       </c>
       <c r="AN6">
-        <v>-1.276534132260322</v>
+        <v>-1.277873527068895</v>
       </c>
       <c r="AO6">
-        <v>-0.4390378921614405</v>
+        <v>-0.2709725081015805</v>
       </c>
       <c r="AP6">
-        <v>-1.806419332275516</v>
+        <v>-1.843404713991136</v>
       </c>
       <c r="AQ6">
-        <v>2.816401832666294</v>
+        <v>2.5773153998553</v>
       </c>
       <c r="AR6">
-        <v>1.544142849550404</v>
+        <v>1.609260271222911</v>
       </c>
       <c r="AS6">
-        <v>0.03666060359501535</v>
+        <v>0.03739796381320831</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1442,10 +1454,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C7" s="2">
         <v>46296</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46295</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1457,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.088257853924038</v>
+        <v>2.137214015356746</v>
       </c>
       <c r="H7">
-        <v>1.517433605238748</v>
+        <v>1.526188649542833</v>
       </c>
       <c r="I7">
-        <v>0.3795290827545978</v>
+        <v>0.3813656127454732</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1475,103 +1487,103 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>0.06340265329516924</v>
+        <v>0.07345864706042519</v>
       </c>
       <c r="O7">
-        <v>10.89192154282304</v>
+        <v>12.06146788067725</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.088257853924038</v>
+        <v>2.137214015356746</v>
       </c>
       <c r="R7" t="s">
         <v>58</v>
       </c>
       <c r="S7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T7">
-        <v>-0.9721408351059729</v>
+        <v>-0.9795687248641783</v>
       </c>
       <c r="U7">
-        <v>0.9869858172170075</v>
+        <v>0.9906040627503265</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X7">
-        <v>0.9849566056741544</v>
+        <v>0.9921059691695141</v>
       </c>
       <c r="Y7">
-        <v>0.9980897656772786</v>
+        <v>0.9991925462457855</v>
       </c>
       <c r="Z7">
-        <v>0.01313316000312414</v>
+        <v>0.007086577076271361</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-160.7742284166306</v>
+        <v>-163.5608725506031</v>
       </c>
       <c r="AC7">
-        <v>-37.99999999999999</v>
+        <v>-27</v>
       </c>
       <c r="AD7">
-        <v>-0.9442283508264429</v>
+        <v>-0.9591209390869654</v>
       </c>
       <c r="AE7">
-        <v>-0.3292913929873902</v>
+        <v>-0.2829965091744729</v>
       </c>
       <c r="AF7">
-        <v>1.870023817185445</v>
+        <v>1.824440321202454</v>
       </c>
       <c r="AG7">
-        <v>1.866451633505551</v>
+        <v>1.822967170015759</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL7">
-        <v>-0.9424246534222075</v>
+        <v>-0.9583464932839538</v>
       </c>
       <c r="AM7">
-        <v>0.9769265843431376</v>
+        <v>0.9816195552636744</v>
       </c>
       <c r="AN7">
-        <v>-1.675686243201328</v>
+        <v>-1.700671729753976</v>
       </c>
       <c r="AO7">
-        <v>-0.7646194488281861</v>
+        <v>-0.6196399847827141</v>
       </c>
       <c r="AP7">
-        <v>-2.214383829346423</v>
+        <v>-2.319054224479197</v>
       </c>
       <c r="AQ7">
-        <v>4.050922111619149</v>
+        <v>3.681947944800657</v>
       </c>
       <c r="AR7">
-        <v>1.837490612426009</v>
+        <v>1.985039928428203</v>
       </c>
       <c r="AS7">
-        <v>0.03782225927895106</v>
+        <v>0.0388941176562674</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1582,10 +1594,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C8" s="2">
         <v>46296</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46295</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1597,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>3.378740912970246</v>
+        <v>2.608637289688342</v>
       </c>
       <c r="H8">
-        <v>1.499279494793825</v>
+        <v>1.507390855606517</v>
       </c>
       <c r="I8">
-        <v>0.3791762932647163</v>
+        <v>0.3833092535888495</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1615,103 +1627,103 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N8">
-        <v>-0.08967032640047667</v>
+        <v>-0.09872875270128371</v>
       </c>
       <c r="O8">
-        <v>-24.15827132890749</v>
+        <v>-23.38554331812834</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.378740912970246</v>
+        <v>2.608637289688342</v>
       </c>
       <c r="R8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T8">
-        <v>0.9306934926262588</v>
+        <v>0.9796349403972437</v>
       </c>
       <c r="U8">
-        <v>0.9688101444556124</v>
+        <v>0.9907448616739116</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X8">
-        <v>0.9998652578425244</v>
+        <v>0.9959580309917501</v>
       </c>
       <c r="Y8">
-        <v>0.9999922910951836</v>
+        <v>0.9996365539806078</v>
       </c>
       <c r="Z8">
-        <v>0.00012703325265917</v>
+        <v>0.003678522988857735</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>30.52738825204341</v>
+        <v>16.41044730187966</v>
       </c>
       <c r="AC8">
-        <v>-3.999999999999993</v>
+        <v>-19</v>
       </c>
       <c r="AD8">
-        <v>0.8613864509711305</v>
+        <v>0.95926247650358</v>
       </c>
       <c r="AE8">
-        <v>0.5079501767726439</v>
+        <v>0.2825163732816537</v>
       </c>
       <c r="AF8">
-        <v>2.973292881918074</v>
+        <v>2.174191416125687</v>
       </c>
       <c r="AG8">
-        <v>2.973269961086256</v>
+        <v>2.173401214910099</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AJ8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AL8">
-        <v>0.8613798106249698</v>
+        <v>0.9589138363749424</v>
       </c>
       <c r="AM8">
-        <v>0.9518200568779011</v>
+        <v>0.9825022639046214</v>
       </c>
       <c r="AN8">
-        <v>2.549126527825603</v>
+        <v>2.05009011765739</v>
       </c>
       <c r="AO8">
-        <v>1.529719679925059</v>
+        <v>0.6972104431422118</v>
       </c>
       <c r="AP8">
-        <v>4.288121635869815</v>
+        <v>2.973943519718391</v>
       </c>
       <c r="AQ8">
-        <v>-3.984759872388338</v>
+        <v>-4.716551146444409</v>
       </c>
       <c r="AR8">
-        <v>3.884106796188359</v>
+        <v>2.52479207909921</v>
       </c>
       <c r="AS8">
-        <v>0.04395453531168182</v>
+        <v>0.03432848626443592</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1722,10 +1734,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C9" s="2">
         <v>46296</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46295</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1737,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.305286412125909</v>
+        <v>1.19362427702495</v>
       </c>
       <c r="H9">
-        <v>3.142694495672174</v>
+        <v>3.146892094756805</v>
       </c>
       <c r="I9">
-        <v>0.6696902861742862</v>
+        <v>0.6692210364231993</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1755,103 +1767,103 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N9">
-        <v>0.8676034335289364</v>
+        <v>0.8774298833026817</v>
       </c>
       <c r="O9">
-        <v>86.76344204725422</v>
+        <v>78.29950834201922</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.305286412125909</v>
+        <v>1.19362427702495</v>
       </c>
       <c r="R9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T9">
-        <v>-0.8922180012993804</v>
+        <v>-0.9664049471866771</v>
       </c>
       <c r="U9">
-        <v>0.8014244115365977</v>
+        <v>0.8343774977760345</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
       </c>
       <c r="W9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X9">
-        <v>0.9981244334717523</v>
+        <v>0.9798488680699102</v>
       </c>
       <c r="Y9">
-        <v>0.9997052438075062</v>
+        <v>0.9979810861681192</v>
       </c>
       <c r="Z9">
-        <v>0.001580810335753968</v>
+        <v>0.01813221809820897</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>133.1799076199624</v>
+        <v>154.3537461065839</v>
       </c>
       <c r="AC9">
-        <v>13.00000000000001</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="AD9">
-        <v>-0.6842914304466994</v>
+        <v>-0.9014834172147076</v>
       </c>
       <c r="AE9">
-        <v>0.7292086383314518</v>
+        <v>0.4328136417523059</v>
       </c>
       <c r="AF9">
-        <v>1.484966742089692</v>
+        <v>1.041368645360425</v>
       </c>
       <c r="AG9">
-        <v>1.484529038946814</v>
+        <v>1.03926621179822</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
       </c>
       <c r="AI9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AL9">
-        <v>-0.3420448656550524</v>
+        <v>-0.4498316999372408</v>
       </c>
       <c r="AM9">
-        <v>0.7012332975526965</v>
+        <v>0.7653579103828585</v>
       </c>
       <c r="AN9">
-        <v>-0.983698823497191</v>
+        <v>-0.875977160782628</v>
       </c>
       <c r="AO9">
-        <v>1.108692421264028</v>
+        <v>0.5233042074103007</v>
       </c>
       <c r="AP9">
-        <v>-1.66527450442444</v>
+        <v>-1.621531224814846</v>
       </c>
       <c r="AQ9">
-        <v>1.289303196796456</v>
+        <v>0.7595991782462008</v>
       </c>
       <c r="AR9">
-        <v>1.574602384132876</v>
+        <v>1.57002796163998</v>
       </c>
       <c r="AS9">
-        <v>0.02633977942627003</v>
+        <v>0.0292032996026361</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1862,10 +1874,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C10" s="2">
         <v>46296</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46295</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1877,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.3424523408692119</v>
+        <v>0.2618113337995194</v>
       </c>
       <c r="H10">
-        <v>2.119494466268526</v>
+        <v>2.121626173919771</v>
       </c>
       <c r="I10">
-        <v>0.4497847541212192</v>
+        <v>0.4501141586743788</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1895,103 +1907,103 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N10">
-        <v>46.58664648135557</v>
+        <v>46.93204185534117</v>
       </c>
       <c r="O10">
-        <v>42.58794284756122</v>
+        <v>42.19287757102428</v>
       </c>
       <c r="P10">
-        <v>0.1663948653018025</v>
+        <v>0.2246478771389435</v>
       </c>
       <c r="Q10">
-        <v>0.4108088189658225</v>
+        <v>0.3376676558689659</v>
       </c>
       <c r="R10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.9353001500868481</v>
+        <v>-0.9040330999209918</v>
       </c>
       <c r="U10">
-        <v>0.8131384431632092</v>
+        <v>0.8034816978108861</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
       </c>
       <c r="W10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X10">
-        <v>0.9084620100189639</v>
+        <v>0.9561496847485932</v>
       </c>
       <c r="Y10">
-        <v>0.96901350249651</v>
+        <v>0.9866672113857586</v>
       </c>
       <c r="Z10">
-        <v>0.0605514924775461</v>
+        <v>0.03051752663716545</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>143.7584485979793</v>
+        <v>135.7624140442337</v>
       </c>
       <c r="AC10">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AD10">
-        <v>-0.8065317875677571</v>
+        <v>-0.7164531140400342</v>
       </c>
       <c r="AE10">
-        <v>0.5911907269593784</v>
+        <v>0.6976352452265708</v>
       </c>
       <c r="AF10">
-        <v>0.6693071077586706</v>
+        <v>0.5621106412718877</v>
       </c>
       <c r="AG10">
-        <v>0.6485676247350385</v>
+        <v>0.554616138913994</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
       </c>
       <c r="AI10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AL10">
-        <v>-0.3907700961729017</v>
+        <v>-0.3534503980592617</v>
       </c>
       <c r="AM10">
-        <v>0.7233679184644034</v>
+        <v>0.7027950690557376</v>
       </c>
       <c r="AN10">
-        <v>-0.3468659020247033</v>
+        <v>-0.2799160452746512</v>
       </c>
       <c r="AO10">
-        <v>0.4993964211198217</v>
+        <v>0.4588162104022177</v>
       </c>
       <c r="AP10">
-        <v>-0.3497518955610466</v>
+        <v>-0.3114098830211929</v>
       </c>
       <c r="AQ10">
-        <v>0.6296139460443165</v>
+        <v>0.4534600500415369</v>
       </c>
       <c r="AR10">
-        <v>0.3260613169725994</v>
+        <v>0.296562298165182</v>
       </c>
       <c r="AS10">
-        <v>0.05164229119801473</v>
+        <v>0.04982926094192065</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2002,10 +2014,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C11" s="2">
         <v>46296</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46295</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2017,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.184094117988854</v>
+        <v>1.199086584005827</v>
       </c>
       <c r="H11">
-        <v>2.178143677243853</v>
+        <v>2.168408010583612</v>
       </c>
       <c r="I11">
-        <v>0.5048565869577177</v>
+        <v>0.5023165677932655</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2035,103 +2047,103 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>145.9393412564551</v>
+        <v>206.0218873980091</v>
       </c>
       <c r="O11">
-        <v>2.199502406130128</v>
+        <v>2.942764439155958</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.184094117988854</v>
+        <v>1.199086584005827</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
       </c>
       <c r="S11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T11">
-        <v>-0.8035130852316634</v>
+        <v>-0.8009341781493173</v>
       </c>
       <c r="U11">
-        <v>0.7615723161265613</v>
+        <v>0.7604161503618175</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X11">
-        <v>0.999290290295659</v>
+        <v>0.9997525184128232</v>
       </c>
       <c r="Y11">
-        <v>0.9999657110892508</v>
+        <v>0.999983080778499</v>
       </c>
       <c r="Z11">
-        <v>0.000675420793591841</v>
+        <v>0.0002305623656757572</v>
       </c>
       <c r="AA11">
-        <v>0.2858700109977305</v>
+        <v>0.329685621292421</v>
       </c>
       <c r="AB11">
-        <v>-123.778093395207</v>
+        <v>-124.2504419493343</v>
       </c>
       <c r="AC11">
-        <v>-7.999999999999998</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AD11">
-        <v>-0.5559778542657846</v>
+        <v>-0.5628113035543927</v>
       </c>
       <c r="AE11">
-        <v>-0.8311971039206127</v>
+        <v>-0.8265854079231045</v>
       </c>
       <c r="AF11">
-        <v>1.59227966168652</v>
+        <v>1.619556839052417</v>
       </c>
       <c r="AG11">
-        <v>1.592225064151312</v>
+        <v>1.619529437411523</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AJ11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AK11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AL11">
-        <v>-0.3574453679570265</v>
+        <v>-0.3741747180665119</v>
       </c>
       <c r="AM11">
-        <v>0.7141599891641723</v>
+        <v>0.7261714516087068</v>
       </c>
       <c r="AN11">
-        <v>-0.863648980598598</v>
+        <v>-0.8978914120511587</v>
       </c>
       <c r="AO11">
-        <v>-1.336363537718617</v>
+        <v>-1.347389051822805</v>
       </c>
       <c r="AP11">
-        <v>-1.621296341443538</v>
+        <v>-1.544103667012919</v>
       </c>
       <c r="AQ11">
-        <v>0.8466860714347184</v>
+        <v>1.272710087346403</v>
       </c>
       <c r="AR11">
-        <v>1.50767916435789</v>
+        <v>1.396927745736445</v>
       </c>
       <c r="AS11">
-        <v>0.06530245464231241</v>
+        <v>0.05735427992379936</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -754,10 +754,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C2" s="2">
         <v>46297</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46296</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -769,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.436117214086973</v>
+        <v>1.463615183089874</v>
       </c>
       <c r="H2">
-        <v>1.086065056773773</v>
+        <v>1.089940719005927</v>
       </c>
       <c r="I2">
-        <v>0.2598070738741146</v>
+        <v>0.2601853149853618</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -787,19 +787,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N2">
-        <v>0.161201512681778</v>
+        <v>0.2063844305582309</v>
       </c>
       <c r="O2">
-        <v>3.887652542669212</v>
+        <v>4.913747879009642</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.436117214086973</v>
+        <v>1.463615183089874</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -808,10 +808,10 @@
         <v>62</v>
       </c>
       <c r="T2">
-        <v>-0.8324927566148754</v>
+        <v>-0.8450594482724709</v>
       </c>
       <c r="U2">
-        <v>0.9246058751830176</v>
+        <v>0.9302633338376369</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -820,34 +820,34 @@
         <v>66</v>
       </c>
       <c r="X2">
-        <v>0.9988875274815423</v>
+        <v>0.9992242976487614</v>
       </c>
       <c r="Y2">
-        <v>0.9999365388252949</v>
+        <v>0.9999463284600998</v>
       </c>
       <c r="Z2">
-        <v>0.001049011343752571</v>
+        <v>0.00072203081133837</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-131.6803984646848</v>
+        <v>-133.6388628858862</v>
       </c>
       <c r="AC2">
-        <v>-10</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AD2">
-        <v>-0.6649748823486659</v>
+        <v>-0.6901105802005867</v>
       </c>
       <c r="AE2">
-        <v>-0.7468657214288108</v>
+        <v>-0.72370393607829</v>
       </c>
       <c r="AF2">
-        <v>1.630624588226658</v>
+        <v>1.633042919395576</v>
       </c>
       <c r="AG2">
-        <v>1.630521106874786</v>
+        <v>1.632955271467369</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -862,28 +862,28 @@
         <v>73</v>
       </c>
       <c r="AL2">
-        <v>-0.6649326822614826</v>
+        <v>-0.6900735409030458</v>
       </c>
       <c r="AM2">
-        <v>0.8907932093356834</v>
+        <v>0.899352430585687</v>
       </c>
       <c r="AN2">
-        <v>-1.058581563827818</v>
+        <v>-1.106432633112826</v>
       </c>
       <c r="AO2">
-        <v>-1.237913132438912</v>
+        <v>-1.199374953179614</v>
       </c>
       <c r="AP2">
-        <v>-1.927592862822559</v>
+        <v>-1.849504232112959</v>
       </c>
       <c r="AQ2">
-        <v>1.362787785936421</v>
+        <v>1.904964899468453</v>
       </c>
       <c r="AR2">
-        <v>1.764276295525329</v>
+        <v>1.640925519332009</v>
       </c>
       <c r="AS2">
-        <v>0.05784695971846391</v>
+        <v>0.05107972290349189</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -894,7 +894,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C3" s="2">
         <v>46296</v>
@@ -1034,10 +1034,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C4" s="2">
         <v>46297</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46296</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1049,13 +1049,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2.857204220469094</v>
+        <v>3.1134405973988</v>
       </c>
       <c r="H4">
-        <v>2.099825150341695</v>
+        <v>2.10568325675378</v>
       </c>
       <c r="I4">
-        <v>0.4964730140235191</v>
+        <v>0.4978642577314586</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1067,19 +1067,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N4">
-        <v>0.5675689683350956</v>
+        <v>0.6485467814605768</v>
       </c>
       <c r="O4">
-        <v>15.61707066959776</v>
+        <v>18.15204906127163</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.857204220469094</v>
+        <v>3.1134405973988</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1088,10 +1088,10 @@
         <v>62</v>
       </c>
       <c r="T4">
-        <v>-0.9372718221868184</v>
+        <v>-0.9179262337987019</v>
       </c>
       <c r="U4">
-        <v>0.9717498527387396</v>
+        <v>0.9630490710525563</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1100,34 +1100,34 @@
         <v>66</v>
       </c>
       <c r="X4">
-        <v>0.9995596249631102</v>
+        <v>0.9999290633725623</v>
       </c>
       <c r="Y4">
-        <v>0.9999101310186854</v>
+        <v>0.9999290633725623</v>
       </c>
       <c r="Z4">
-        <v>0.0003505060555751838</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-150.990345926623</v>
+        <v>-146.7040998612845</v>
       </c>
       <c r="AC4">
-        <v>-5.999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>-0.8745380065495315</v>
+        <v>-0.8358466451482032</v>
       </c>
       <c r="AE4">
-        <v>-0.4849569827318414</v>
+        <v>-0.548963009495625</v>
       </c>
       <c r="AF4">
-        <v>2.470906877006796</v>
+        <v>2.811893072350632</v>
       </c>
       <c r="AG4">
-        <v>2.470684819122837</v>
+        <v>2.811693606139364</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1142,28 +1142,28 @@
         <v>73</v>
       </c>
       <c r="AL4">
-        <v>-0.874459412709762</v>
+        <v>-0.8357873530061413</v>
       </c>
       <c r="AM4">
-        <v>0.9553502360627675</v>
+        <v>0.9438551948879159</v>
       </c>
       <c r="AN4">
-        <v>-2.145904883336818</v>
+        <v>-2.350144667876241</v>
       </c>
       <c r="AO4">
-        <v>-1.222741549119324</v>
+        <v>-1.543515783805872</v>
       </c>
       <c r="AP4">
-        <v>-3.654036973284544</v>
+        <v>-3.933391754439335</v>
       </c>
       <c r="AQ4">
-        <v>2.911302453698565</v>
+        <v>3.431344064360473</v>
       </c>
       <c r="AR4">
-        <v>3.361581629454079</v>
+        <v>3.588006011818242</v>
       </c>
       <c r="AS4">
-        <v>0.04653141172421118</v>
+        <v>0.04582647224627837</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1174,7 +1174,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C5" s="2">
         <v>46296</v>
@@ -1314,10 +1314,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C6" s="2">
         <v>46297</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46296</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1329,13 +1329,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.627240488486849</v>
+        <v>1.570244421407061</v>
       </c>
       <c r="H6">
-        <v>0.9915653063969215</v>
+        <v>1.002336870575205</v>
       </c>
       <c r="I6">
-        <v>0.2653715721284291</v>
+        <v>0.267104540735901</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1347,19 +1347,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6">
-        <v>0.7567574172829159</v>
+        <v>0.8396455699237848</v>
       </c>
       <c r="O6">
-        <v>11.61383390550828</v>
+        <v>12.68127856534591</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.627240488486849</v>
+        <v>1.570244421407061</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1368,10 +1368,10 @@
         <v>63</v>
       </c>
       <c r="T6">
-        <v>-0.9940211326421459</v>
+        <v>-0.9962572872601604</v>
       </c>
       <c r="U6">
-        <v>0.9971626583140305</v>
+        <v>0.9982219692857099</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1380,34 +1380,34 @@
         <v>66</v>
       </c>
       <c r="X6">
-        <v>0.9932128951423037</v>
+        <v>0.9961486854723911</v>
       </c>
       <c r="Y6">
-        <v>0.9994125945002593</v>
+        <v>0.999624760074551</v>
       </c>
       <c r="Z6">
-        <v>0.006199699357955613</v>
+        <v>0.003476074602159929</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-171.1292623209555</v>
+        <v>-172.9845108296907</v>
       </c>
       <c r="AC6">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AD6">
-        <v>-0.9880387512005313</v>
+        <v>-0.9925131695778808</v>
       </c>
       <c r="AE6">
-        <v>-0.1542057914803935</v>
+        <v>-0.122137660917789</v>
       </c>
       <c r="AF6">
-        <v>1.315213925417059</v>
+        <v>1.267982853816817</v>
       </c>
       <c r="AG6">
-        <v>1.314441361523933</v>
+        <v>1.26750705602528</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1422,28 +1422,28 @@
         <v>74</v>
       </c>
       <c r="AL6">
-        <v>-0.9874583718041192</v>
+        <v>-0.9921407390101213</v>
       </c>
       <c r="AM6">
-        <v>0.9905963388632689</v>
+        <v>0.9923127082335879</v>
       </c>
       <c r="AN6">
-        <v>-1.277873527068895</v>
+        <v>-1.246160489784905</v>
       </c>
       <c r="AO6">
-        <v>-0.2709725081015805</v>
+        <v>-0.2061656177606775</v>
       </c>
       <c r="AP6">
-        <v>-1.843404713991136</v>
+        <v>-1.722603599910343</v>
       </c>
       <c r="AQ6">
-        <v>2.5773153998553</v>
+        <v>2.679459988838541</v>
       </c>
       <c r="AR6">
-        <v>1.609260271222911</v>
+        <v>1.484448322388167</v>
       </c>
       <c r="AS6">
-        <v>0.03739796381320831</v>
+        <v>0.03539939110579538</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C7" s="2">
         <v>46296</v>
@@ -1594,7 +1594,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C8" s="2">
         <v>46296</v>
@@ -1734,7 +1734,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C9" s="2">
         <v>46296</v>
@@ -1874,7 +1874,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C10" s="2">
         <v>46296</v>
@@ -2014,7 +2014,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C11" s="2">
         <v>46296</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -196,7 +196,7 @@
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
+    <t>UP_STEADY</t>
   </si>
   <si>
     <t>DOWN_DECELERATING</t>
@@ -208,7 +208,7 @@
     <t>空头稳态</t>
   </si>
   <si>
-    <t>多头加速</t>
+    <t>多头稳态</t>
   </si>
   <si>
     <t>空头减速</t>
@@ -229,7 +229,7 @@
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
+    <t>UP_SLOPE</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
@@ -241,7 +241,7 @@
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
+    <t>上升坡延续</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
@@ -754,7 +754,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C2" s="2">
         <v>46297</v>
@@ -894,10 +894,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C3" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -906,16 +906,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.4559350349948318</v>
+        <v>0.6476295876202839</v>
       </c>
       <c r="G3">
-        <v>2.039962344502193</v>
+        <v>2.221462233986172</v>
       </c>
       <c r="H3">
-        <v>2.080368308279167</v>
+        <v>2.085981509973992</v>
       </c>
       <c r="I3">
-        <v>0.4584817413588667</v>
+        <v>0.4588535611189569</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -927,19 +927,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>0.01571417618322567</v>
+        <v>0.02149392036229251</v>
       </c>
       <c r="O3">
-        <v>4.26394934712977</v>
+        <v>6.183394330054415</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.039962344502193</v>
+        <v>2.221462233986172</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -948,10 +948,10 @@
         <v>62</v>
       </c>
       <c r="T3">
-        <v>-0.7640048563958072</v>
+        <v>-0.8152999060570199</v>
       </c>
       <c r="U3">
-        <v>0.8121651451941891</v>
+        <v>0.8639857864506869</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -960,34 +960,34 @@
         <v>66</v>
       </c>
       <c r="X3">
-        <v>0.9988570305802786</v>
+        <v>0.9981998134715281</v>
       </c>
       <c r="Y3">
-        <v>0.9998908182674044</v>
+        <v>0.9998255623279414</v>
       </c>
       <c r="Z3">
-        <v>0.001033787687125809</v>
+        <v>0.001625748856413312</v>
       </c>
       <c r="AA3">
         <v>1</v>
       </c>
       <c r="AB3">
-        <v>-124.7305232386064</v>
+        <v>-130.6716504042479</v>
       </c>
       <c r="AC3">
-        <v>-10</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>-0.5697174242557334</v>
+        <v>-0.6517232038624154</v>
       </c>
       <c r="AE3">
-        <v>-0.8218406515252289</v>
+        <v>-0.7584568976199693</v>
       </c>
       <c r="AF3">
-        <v>2.763393780614182</v>
+        <v>2.722893393706393</v>
       </c>
       <c r="AG3">
-        <v>2.763092068493371</v>
+        <v>2.722418418521531</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1002,28 +1002,28 @@
         <v>73</v>
       </c>
       <c r="AL3">
-        <v>-0.5696552215202633</v>
+        <v>-0.6516095187839072</v>
       </c>
       <c r="AM3">
-        <v>0.8617887040323801</v>
+        <v>0.8876921592364666</v>
       </c>
       <c r="AN3">
-        <v>-1.523950601975966</v>
+        <v>-1.709742231684434</v>
       </c>
       <c r="AO3">
-        <v>-2.301406853944384</v>
+        <v>-2.112879613523765</v>
       </c>
       <c r="AP3">
-        <v>-2.652459802625317</v>
+        <v>-2.676659359883749</v>
       </c>
       <c r="AQ3">
-        <v>2.408154409026348</v>
+        <v>3.48691946774025</v>
       </c>
       <c r="AR3">
-        <v>2.365246036986357</v>
+        <v>2.299539616987486</v>
       </c>
       <c r="AS3">
-        <v>0.06058873091954324</v>
+        <v>0.05175832491358315</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1034,7 +1034,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C4" s="2">
         <v>46297</v>
@@ -1174,10 +1174,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C5" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2.679185503841806</v>
+        <v>3.052787287013346</v>
       </c>
       <c r="H5">
-        <v>1.541991342139128</v>
+        <v>1.54586857318655</v>
       </c>
       <c r="I5">
-        <v>0.3583632125303415</v>
+        <v>0.3608424989397961</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1207,19 +1207,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>0.05503432320538648</v>
+        <v>0.06577047889194094</v>
       </c>
       <c r="O5">
-        <v>10.70409175986957</v>
+        <v>13.73386090666224</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.679185503841806</v>
+        <v>3.052787287013346</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1228,10 +1228,10 @@
         <v>62</v>
       </c>
       <c r="T5">
-        <v>-0.8835016086238986</v>
+        <v>-0.891041205370296</v>
       </c>
       <c r="U5">
-        <v>0.9475566658037164</v>
+        <v>0.9509582065410651</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1240,34 +1240,34 @@
         <v>66</v>
       </c>
       <c r="X5">
-        <v>0.9996484084534735</v>
+        <v>0.9997811180292288</v>
       </c>
       <c r="Y5">
-        <v>0.9999237676918484</v>
+        <v>0.9999586564977279</v>
       </c>
       <c r="Z5">
-        <v>0.0002753592383749615</v>
+        <v>0.0001775384684991055</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-140.0847447279974</v>
+        <v>-141.4512221898441</v>
       </c>
       <c r="AC5">
-        <v>-4.999999999999995</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD5">
-        <v>-0.7669943356294604</v>
+        <v>-0.7820779058161692</v>
       </c>
       <c r="AE5">
-        <v>-0.6416538701763769</v>
+        <v>-0.6231806714221768</v>
       </c>
       <c r="AF5">
-        <v>2.646940165690181</v>
+        <v>2.989890271676168</v>
       </c>
       <c r="AG5">
-        <v>2.646738383331812</v>
+        <v>2.989766659140928</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1282,28 +1282,28 @@
         <v>73</v>
       </c>
       <c r="AL5">
-        <v>-0.7669358658809162</v>
+        <v>-0.7820455719764932</v>
       </c>
       <c r="AM5">
-        <v>0.9224527554252537</v>
+        <v>0.9274205860666791</v>
       </c>
       <c r="AN5">
-        <v>-2.012734723500569</v>
+        <v>-2.322853513699059</v>
       </c>
       <c r="AO5">
-        <v>-1.717633643535347</v>
+        <v>-1.88145753411371</v>
       </c>
       <c r="AP5">
-        <v>-3.419068369064508</v>
+        <v>-3.775023293907783</v>
       </c>
       <c r="AQ5">
-        <v>2.732463485735718</v>
+        <v>3.724128517196357</v>
       </c>
       <c r="AR5">
-        <v>3.1331921734011</v>
+        <v>3.393437940830339</v>
       </c>
       <c r="AS5">
-        <v>0.05079242637154264</v>
+        <v>0.0479221030158419</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1314,7 +1314,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C6" s="2">
         <v>46297</v>
@@ -1454,10 +1454,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C7" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1469,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.137214015356746</v>
+        <v>2.146278781367343</v>
       </c>
       <c r="H7">
-        <v>1.526188649542833</v>
+        <v>1.534891772957541</v>
       </c>
       <c r="I7">
-        <v>0.3813656127454732</v>
+        <v>0.3832782983662435</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,31 +1487,31 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7">
-        <v>0.07345864706042519</v>
+        <v>0.08376294488396037</v>
       </c>
       <c r="O7">
-        <v>12.06146788067725</v>
+        <v>14.1782278850857</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.137214015356746</v>
+        <v>2.146278781367343</v>
       </c>
       <c r="R7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T7">
-        <v>-0.9795687248641783</v>
+        <v>-0.9971076933219547</v>
       </c>
       <c r="U7">
-        <v>0.9906040627503265</v>
+        <v>0.9984662328369414</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1520,34 +1520,34 @@
         <v>66</v>
       </c>
       <c r="X7">
-        <v>0.9921059691695141</v>
+        <v>0.9900547097423993</v>
       </c>
       <c r="Y7">
-        <v>0.9991925462457855</v>
+        <v>0.9990710833682475</v>
       </c>
       <c r="Z7">
-        <v>0.007086577076271361</v>
+        <v>0.009016373625848173</v>
       </c>
       <c r="AA7">
         <v>1</v>
       </c>
       <c r="AB7">
-        <v>-163.5608725506031</v>
+        <v>-173.8328374355906</v>
       </c>
       <c r="AC7">
-        <v>-27</v>
+        <v>-30.99999999999999</v>
       </c>
       <c r="AD7">
-        <v>-0.9591209390869654</v>
+        <v>-0.9942126974340801</v>
       </c>
       <c r="AE7">
-        <v>-0.2829965091744729</v>
+        <v>-0.1074295688386122</v>
       </c>
       <c r="AF7">
-        <v>1.824440321202454</v>
+        <v>1.780987250297063</v>
       </c>
       <c r="AG7">
-        <v>1.822967170015759</v>
+        <v>1.779332861619323</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1556,34 +1556,34 @@
         <v>67</v>
       </c>
       <c r="AJ7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL7">
-        <v>-0.9583464932839538</v>
+        <v>-0.993289156723934</v>
       </c>
       <c r="AM7">
-        <v>0.9816195552636744</v>
+        <v>0.9925145540429726</v>
       </c>
       <c r="AN7">
-        <v>-1.700671729753976</v>
+        <v>-1.73512953719635</v>
       </c>
       <c r="AO7">
-        <v>-0.6196399847827141</v>
+        <v>-0.313789042006236</v>
       </c>
       <c r="AP7">
-        <v>-2.319054224479197</v>
+        <v>-2.212107403362016</v>
       </c>
       <c r="AQ7">
-        <v>3.681947944800657</v>
+        <v>4.1232762300579</v>
       </c>
       <c r="AR7">
-        <v>1.985039928428203</v>
+        <v>1.846950093617659</v>
       </c>
       <c r="AS7">
-        <v>0.0388941176562674</v>
+        <v>0.03616089577425368</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1594,10 +1594,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C8" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1609,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.608637289688342</v>
+        <v>2.465037919765153</v>
       </c>
       <c r="H8">
-        <v>1.507390855606517</v>
+        <v>1.516205423007265</v>
       </c>
       <c r="I8">
-        <v>0.3833092535888495</v>
+        <v>0.3873298034763542</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1627,19 +1627,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8">
-        <v>-0.09872875270128371</v>
+        <v>-0.1072021524017984</v>
       </c>
       <c r="O8">
-        <v>-23.38554331812834</v>
+        <v>-25.34115886239229</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.608637289688342</v>
+        <v>2.465037919765153</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1648,10 +1648,10 @@
         <v>64</v>
       </c>
       <c r="T8">
-        <v>0.9796349403972437</v>
+        <v>0.9962834818469217</v>
       </c>
       <c r="U8">
-        <v>0.9907448616739116</v>
+        <v>0.9981878746310084</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1660,34 +1660,34 @@
         <v>66</v>
       </c>
       <c r="X8">
-        <v>0.9959580309917501</v>
+        <v>0.9934844645919709</v>
       </c>
       <c r="Y8">
-        <v>0.9996365539806078</v>
+        <v>0.9994412311995745</v>
       </c>
       <c r="Z8">
-        <v>0.003678522988857735</v>
+        <v>0.005956766607603581</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>16.41044730187966</v>
+        <v>6.991186755245489</v>
       </c>
       <c r="AC8">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="AD8">
-        <v>0.95926247650358</v>
+        <v>0.992564885858424</v>
       </c>
       <c r="AE8">
-        <v>0.2825163732816537</v>
+        <v>0.1217166683772349</v>
       </c>
       <c r="AF8">
-        <v>2.174191416125687</v>
+        <v>2.004127892259483</v>
       </c>
       <c r="AG8">
-        <v>2.173401214910099</v>
+        <v>2.003008048121226</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1702,28 +1702,28 @@
         <v>75</v>
       </c>
       <c r="AL8">
-        <v>0.9589138363749424</v>
+        <v>0.9920102715678084</v>
       </c>
       <c r="AM8">
-        <v>0.9825022639046214</v>
+        <v>0.9928469825342465</v>
       </c>
       <c r="AN8">
-        <v>2.05009011765739</v>
+        <v>1.960061041963213</v>
       </c>
       <c r="AO8">
-        <v>0.6972104431422118</v>
+        <v>0.3500288017584413</v>
       </c>
       <c r="AP8">
-        <v>2.973943519718391</v>
+        <v>2.708348477042971</v>
       </c>
       <c r="AQ8">
-        <v>-4.716551146444409</v>
+        <v>-4.670177103758457</v>
       </c>
       <c r="AR8">
-        <v>2.52479207909921</v>
+        <v>2.285629500781877</v>
       </c>
       <c r="AS8">
-        <v>0.03432848626443592</v>
+        <v>0.03151276095421195</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1734,10 +1734,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C9" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1749,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.19362427702495</v>
+        <v>1.285725995326295</v>
       </c>
       <c r="H9">
-        <v>3.146892094756805</v>
+        <v>3.150689922500043</v>
       </c>
       <c r="I9">
-        <v>0.6692210364231993</v>
+        <v>0.6685389093936323</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1767,31 +1767,31 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N9">
-        <v>0.8774298833026817</v>
+        <v>0.8872829461587431</v>
       </c>
       <c r="O9">
-        <v>78.29950834201922</v>
+        <v>83.20413440652698</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.19362427702495</v>
+        <v>1.285725995326295</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.9664049471866771</v>
+        <v>-0.9993283430045486</v>
       </c>
       <c r="U9">
-        <v>0.8343774977760345</v>
+        <v>0.8490288919884816</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1800,34 +1800,34 @@
         <v>66</v>
       </c>
       <c r="X9">
-        <v>0.9798488680699102</v>
+        <v>0.9649554530681491</v>
       </c>
       <c r="Y9">
-        <v>0.9979810861681192</v>
+        <v>0.997324550545739</v>
       </c>
       <c r="Z9">
-        <v>0.01813221809820897</v>
+        <v>0.03236909747758987</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>154.3537461065839</v>
+        <v>176.4025569540482</v>
       </c>
       <c r="AC9">
-        <v>42.00000000000001</v>
+        <v>53.00000000000001</v>
       </c>
       <c r="AD9">
-        <v>-0.9014834172147076</v>
+        <v>-0.9980295296037169</v>
       </c>
       <c r="AE9">
-        <v>0.4328136417523059</v>
+        <v>0.06274598026155627</v>
       </c>
       <c r="AF9">
-        <v>1.041368645360425</v>
+        <v>0.9726153333670159</v>
       </c>
       <c r="AG9">
-        <v>1.03926621179822</v>
+        <v>0.9700131502041532</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1836,34 +1836,34 @@
         <v>67</v>
       </c>
       <c r="AJ9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AL9">
-        <v>-0.4498316999372408</v>
+        <v>-0.4976796760217012</v>
       </c>
       <c r="AM9">
-        <v>0.7653579103828585</v>
+        <v>0.7935656771619158</v>
       </c>
       <c r="AN9">
-        <v>-0.875977160782628</v>
+        <v>-0.927412727153209</v>
       </c>
       <c r="AO9">
-        <v>0.5233042074103007</v>
+        <v>0.1440315104885368</v>
       </c>
       <c r="AP9">
-        <v>-1.621531224814846</v>
+        <v>-1.816656800577983</v>
       </c>
       <c r="AQ9">
-        <v>0.7595991782462008</v>
+        <v>0.6012046257110735</v>
       </c>
       <c r="AR9">
-        <v>1.57002796163998</v>
+        <v>1.771224108307004</v>
       </c>
       <c r="AS9">
-        <v>0.0292032996026361</v>
+        <v>0.03271182940138548</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1874,10 +1874,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C10" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1889,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.2618113337995194</v>
+        <v>0.1759201018796525</v>
       </c>
       <c r="H10">
-        <v>2.121626173919771</v>
+        <v>2.123554861794707</v>
       </c>
       <c r="I10">
-        <v>0.4501141586743788</v>
+        <v>0.4506142627209715</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1907,19 +1907,19 @@
         <v>233</v>
       </c>
       <c r="M10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N10">
-        <v>46.93204185534117</v>
+        <v>47.20297848534669</v>
       </c>
       <c r="O10">
-        <v>42.19287757102428</v>
+        <v>47.02495543975326</v>
       </c>
       <c r="P10">
-        <v>0.2246478771389435</v>
+        <v>0.3638982418148696</v>
       </c>
       <c r="Q10">
-        <v>0.3376676558689659</v>
+        <v>0.2765596850126186</v>
       </c>
       <c r="R10" t="s">
         <v>61</v>
@@ -1928,10 +1928,10 @@
         <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.9040330999209918</v>
+        <v>-0.7976630934848853</v>
       </c>
       <c r="U10">
-        <v>0.8034816978108861</v>
+        <v>0.7588861098037478</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
@@ -1940,34 +1940,34 @@
         <v>66</v>
       </c>
       <c r="X10">
-        <v>0.9561496847485932</v>
+        <v>0.997307822291014</v>
       </c>
       <c r="Y10">
-        <v>0.9866672113857586</v>
+        <v>0.9997508709421974</v>
       </c>
       <c r="Z10">
-        <v>0.03051752663716545</v>
+        <v>0.002443048651183388</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>135.7624140442337</v>
+        <v>114.0381403485021</v>
       </c>
       <c r="AC10">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="AD10">
-        <v>-0.7164531140400342</v>
+        <v>-0.407344676974959</v>
       </c>
       <c r="AE10">
-        <v>0.6976352452265708</v>
+        <v>0.9132745009799443</v>
       </c>
       <c r="AF10">
-        <v>0.5621106412718877</v>
+        <v>0.6475431509208871</v>
       </c>
       <c r="AG10">
-        <v>0.554616138913994</v>
+        <v>0.6473818291058117</v>
       </c>
       <c r="AH10" t="s">
         <v>56</v>
@@ -1982,28 +1982,28 @@
         <v>76</v>
       </c>
       <c r="AL10">
-        <v>-0.3534503980592617</v>
+        <v>-0.2036215977896917</v>
       </c>
       <c r="AM10">
-        <v>0.7027950690557376</v>
+        <v>0.6134016422533884</v>
       </c>
       <c r="AN10">
-        <v>-0.2799160452746512</v>
+        <v>-0.2296472657165816</v>
       </c>
       <c r="AO10">
-        <v>0.4588162104022177</v>
+        <v>0.6035889157375692</v>
       </c>
       <c r="AP10">
-        <v>-0.3114098830211929</v>
+        <v>-0.2556816737650891</v>
       </c>
       <c r="AQ10">
-        <v>0.4534600500415369</v>
+        <v>0.3946921492060487</v>
       </c>
       <c r="AR10">
-        <v>0.296562298165182</v>
+        <v>0.2433294980053786</v>
       </c>
       <c r="AS10">
-        <v>0.04982926094192065</v>
+        <v>0.05809710445912196</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2014,10 +2014,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C11" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.199086584005827</v>
+        <v>1.427443740981068</v>
       </c>
       <c r="H11">
-        <v>2.168408010583612</v>
+        <v>2.159599550271965</v>
       </c>
       <c r="I11">
-        <v>0.5023165677932655</v>
+        <v>0.4999859571844159</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2047,19 +2047,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>206.0218873980091</v>
+        <v>273.3607018772811</v>
       </c>
       <c r="O11">
-        <v>2.942764439155958</v>
+        <v>4.085825590026248</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.199086584005827</v>
+        <v>1.427443740981068</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2068,10 +2068,10 @@
         <v>62</v>
       </c>
       <c r="T11">
-        <v>-0.8009341781493173</v>
+        <v>-0.771919016304465</v>
       </c>
       <c r="U11">
-        <v>0.7604161503618175</v>
+        <v>0.7473612893329706</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2080,34 +2080,34 @@
         <v>66</v>
       </c>
       <c r="X11">
-        <v>0.9997525184128232</v>
+        <v>0.9998986114694594</v>
       </c>
       <c r="Y11">
-        <v>0.999983080778499</v>
+        <v>0.9999909279838457</v>
       </c>
       <c r="Z11">
-        <v>0.0002305623656757572</v>
+        <v>9.231651438634803E-05</v>
       </c>
       <c r="AA11">
-        <v>0.329685621292421</v>
+        <v>0.6685907682296063</v>
       </c>
       <c r="AB11">
-        <v>-124.2504419493343</v>
+        <v>-125.1481539265188</v>
       </c>
       <c r="AC11">
-        <v>-4.999999999999995</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AD11">
-        <v>-0.5628113035543927</v>
+        <v>-0.5756926583694939</v>
       </c>
       <c r="AE11">
-        <v>-0.8265854079231045</v>
+        <v>-0.8176661684938817</v>
       </c>
       <c r="AF11">
-        <v>1.619556839052417</v>
+        <v>1.88051364434871</v>
       </c>
       <c r="AG11">
-        <v>1.619529437411523</v>
+        <v>1.88049658429855</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2122,28 +2122,28 @@
         <v>73</v>
       </c>
       <c r="AL11">
-        <v>-0.3741747180665119</v>
+        <v>-0.4802933702777059</v>
       </c>
       <c r="AM11">
-        <v>0.7261714516087068</v>
+        <v>0.7982537553042506</v>
       </c>
       <c r="AN11">
-        <v>-0.8978914120511587</v>
+        <v>-1.073416863306361</v>
       </c>
       <c r="AO11">
-        <v>-1.347389051822805</v>
+        <v>-1.543823420466639</v>
       </c>
       <c r="AP11">
-        <v>-1.544103667012919</v>
+        <v>-1.816192253452593</v>
       </c>
       <c r="AQ11">
-        <v>1.272710087346403</v>
+        <v>1.501229997671825</v>
       </c>
       <c r="AR11">
-        <v>1.396927745736445</v>
+        <v>1.650245314925916</v>
       </c>
       <c r="AS11">
-        <v>0.05735427992379936</v>
+        <v>0.05446013764576514</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -754,7 +754,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C2" s="2">
         <v>46297</v>
@@ -894,7 +894,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C3" s="2">
         <v>46297</v>
@@ -1034,7 +1034,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C4" s="2">
         <v>46297</v>
@@ -1174,7 +1174,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C5" s="2">
         <v>46297</v>
@@ -1314,7 +1314,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C6" s="2">
         <v>46297</v>
@@ -1454,7 +1454,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C7" s="2">
         <v>46297</v>
@@ -1594,7 +1594,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C8" s="2">
         <v>46297</v>
@@ -1734,7 +1734,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C9" s="2">
         <v>46297</v>
@@ -1874,7 +1874,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C10" s="2">
         <v>46297</v>
@@ -2014,7 +2014,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C11" s="2">
         <v>46297</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>Pair</t>
   </si>
@@ -214,15 +214,24 @@
     <t>空头减速</t>
   </si>
   <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
@@ -232,7 +241,7 @@
     <t>UP_SLOPE</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
+    <t>TRANSITION_ZONE</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
@@ -244,7 +253,7 @@
     <t>上升坡延续</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
+    <t>地形转换区</t>
   </si>
 </sst>
 </file>
@@ -754,10 +763,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C2" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -769,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.463615183089874</v>
+        <v>1.41384031359683</v>
       </c>
       <c r="H2">
-        <v>1.089940719005927</v>
+        <v>1.105275202717707</v>
       </c>
       <c r="I2">
-        <v>0.2601853149853618</v>
+        <v>0.2612822449488148</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -787,19 +796,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N2">
-        <v>0.2063844305582309</v>
+        <v>0.2995842253285217</v>
       </c>
       <c r="O2">
-        <v>4.913747879009642</v>
+        <v>7.309861363611423</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.463615183089874</v>
+        <v>1.41384031359683</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -808,82 +817,82 @@
         <v>62</v>
       </c>
       <c r="T2">
-        <v>-0.8450594482724709</v>
+        <v>-0.9312053040770206</v>
       </c>
       <c r="U2">
-        <v>0.9302633338376369</v>
+        <v>0.9689152835989751</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X2">
-        <v>0.9992242976487614</v>
+        <v>0.9947843742605199</v>
       </c>
       <c r="Y2">
-        <v>0.9999463284600998</v>
+        <v>0.9994915870572633</v>
       </c>
       <c r="Z2">
-        <v>0.00072203081133837</v>
+        <v>0.004707212796743354</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-133.6388628858862</v>
+        <v>-149.5843723307099</v>
       </c>
       <c r="AC2">
-        <v>-7.999999999999998</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AD2">
-        <v>-0.6901105802005867</v>
+        <v>-0.8623756142488881</v>
       </c>
       <c r="AE2">
-        <v>-0.72370393607829</v>
+        <v>-0.5062689995929565</v>
       </c>
       <c r="AF2">
-        <v>1.633042919395576</v>
+        <v>1.355474298724338</v>
       </c>
       <c r="AG2">
-        <v>1.632955271467369</v>
+        <v>1.35478515804732</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL2">
-        <v>-0.6900735409030458</v>
+        <v>-0.8619371713251034</v>
       </c>
       <c r="AM2">
-        <v>0.899352430585687</v>
+        <v>0.9528918082725243</v>
       </c>
       <c r="AN2">
-        <v>-1.106432633112826</v>
+        <v>-1.123718285723238</v>
       </c>
       <c r="AO2">
-        <v>-1.199374953179614</v>
+        <v>-0.7452867368265162</v>
       </c>
       <c r="AP2">
-        <v>-1.849504232112959</v>
+        <v>-1.552801375349311</v>
       </c>
       <c r="AQ2">
-        <v>1.904964899468453</v>
+        <v>2.72310269088192</v>
       </c>
       <c r="AR2">
-        <v>1.640925519332009</v>
+        <v>1.291695185302931</v>
       </c>
       <c r="AS2">
-        <v>0.05107972290349189</v>
+        <v>0.03761954314789425</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -894,10 +903,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C3" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -906,16 +915,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.6476295876202839</v>
+        <v>0.5206325096177565</v>
       </c>
       <c r="G3">
-        <v>2.221462233986172</v>
+        <v>2.114622406007593</v>
       </c>
       <c r="H3">
-        <v>2.085981509973992</v>
+        <v>2.095655054844892</v>
       </c>
       <c r="I3">
-        <v>0.4588535611189569</v>
+        <v>0.4596472148588735</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -927,19 +936,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N3">
-        <v>0.02149392036229251</v>
+        <v>0.03313462076284382</v>
       </c>
       <c r="O3">
-        <v>6.183394330054415</v>
+        <v>10.03753523054891</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.221462233986172</v>
+        <v>2.114622406007593</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -948,82 +957,82 @@
         <v>62</v>
       </c>
       <c r="T3">
-        <v>-0.8152999060570199</v>
+        <v>-0.9471943794584506</v>
       </c>
       <c r="U3">
-        <v>0.8639857864506869</v>
+        <v>0.9038615815922336</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X3">
-        <v>0.9981998134715281</v>
+        <v>0.9855665940889367</v>
       </c>
       <c r="Y3">
-        <v>0.9998255623279414</v>
+        <v>0.9981169375730693</v>
       </c>
       <c r="Z3">
-        <v>0.001625748856413312</v>
+        <v>0.01255034348413264</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.9303371883403148</v>
       </c>
       <c r="AB3">
-        <v>-130.6716504042479</v>
+        <v>-154.212432023279</v>
       </c>
       <c r="AC3">
-        <v>-12.99999999999999</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AD3">
-        <v>-0.6517232038624154</v>
+        <v>-0.90041318653816</v>
       </c>
       <c r="AE3">
-        <v>-0.7584568976199693</v>
+        <v>-0.4350357381965263</v>
       </c>
       <c r="AF3">
-        <v>2.722893393706393</v>
+        <v>2.059164955897933</v>
       </c>
       <c r="AG3">
-        <v>2.722418418521531</v>
+        <v>2.055287419738629</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
       </c>
       <c r="AI3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL3">
-        <v>-0.6516095187839072</v>
+        <v>-0.8674140530242463</v>
       </c>
       <c r="AM3">
-        <v>0.8876921592364666</v>
+        <v>0.9501034015349541</v>
       </c>
       <c r="AN3">
-        <v>-1.709742231684434</v>
+        <v>-1.730949690210708</v>
       </c>
       <c r="AO3">
-        <v>-2.112879613523765</v>
+        <v>-1.059460664405853</v>
       </c>
       <c r="AP3">
-        <v>-2.676659359883749</v>
+        <v>-2.102664683571918</v>
       </c>
       <c r="AQ3">
-        <v>3.48691946774025</v>
+        <v>4.863130987710345</v>
       </c>
       <c r="AR3">
-        <v>2.299539616987486</v>
+        <v>1.648412988117296</v>
       </c>
       <c r="AS3">
-        <v>0.05175832491358315</v>
+        <v>0.03619280163420795</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1034,10 +1043,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C4" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1049,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.1134405973988</v>
+        <v>3.143653764222756</v>
       </c>
       <c r="H4">
-        <v>2.10568325675378</v>
+        <v>2.119598450092666</v>
       </c>
       <c r="I4">
-        <v>0.4978642577314586</v>
+        <v>0.5014370952287174</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1067,19 +1076,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N4">
-        <v>0.6485467814605768</v>
+        <v>0.8273435263671126</v>
       </c>
       <c r="O4">
-        <v>18.15204906127163</v>
+        <v>21.69471693039816</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.1134405973988</v>
+        <v>3.143653764222756</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1088,82 +1097,82 @@
         <v>62</v>
       </c>
       <c r="T4">
-        <v>-0.9179262337987019</v>
+        <v>-0.9318473998340459</v>
       </c>
       <c r="U4">
-        <v>0.9630490710525563</v>
+        <v>0.9693302174354312</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X4">
-        <v>0.9999290633725623</v>
+        <v>0.9998639469371158</v>
       </c>
       <c r="Y4">
-        <v>0.9999290633725623</v>
+        <v>0.9999955500404425</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.0001316031033267162</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-146.7040998612845</v>
+        <v>-149.7339664761072</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD4">
-        <v>-0.8358466451482032</v>
+        <v>-0.8636944963904277</v>
       </c>
       <c r="AE4">
-        <v>-0.548963009495625</v>
+        <v>-0.5040156911296367</v>
       </c>
       <c r="AF4">
-        <v>2.811893072350632</v>
+        <v>2.811519713741461</v>
       </c>
       <c r="AG4">
-        <v>2.811693606139364</v>
+        <v>2.81150720259244</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL4">
-        <v>-0.8357873530061413</v>
+        <v>-0.8636906529848487</v>
       </c>
       <c r="AM4">
-        <v>0.9438551948879159</v>
+        <v>0.952854627449048</v>
       </c>
       <c r="AN4">
-        <v>-2.350144667876241</v>
+        <v>-2.416449289337514</v>
       </c>
       <c r="AO4">
-        <v>-1.543515783805872</v>
+        <v>-1.436407037481282</v>
       </c>
       <c r="AP4">
-        <v>-3.933391754439335</v>
+        <v>-3.791539223637096</v>
       </c>
       <c r="AQ4">
-        <v>3.431344064360473</v>
+        <v>4.317520847982976</v>
       </c>
       <c r="AR4">
-        <v>3.588006011818242</v>
+        <v>3.369330601403916</v>
       </c>
       <c r="AS4">
-        <v>0.04582647224627837</v>
+        <v>0.04168109321489994</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1174,10 +1183,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C5" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1189,13 +1198,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.052787287013346</v>
+        <v>3.256613153033321</v>
       </c>
       <c r="H5">
-        <v>1.54586857318655</v>
+        <v>1.555059337462569</v>
       </c>
       <c r="I5">
-        <v>0.3608424989397961</v>
+        <v>0.3669789523319065</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1207,19 +1216,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N5">
-        <v>0.06577047889194094</v>
+        <v>0.08875405194201892</v>
       </c>
       <c r="O5">
-        <v>13.73386090666224</v>
+        <v>19.16638480932065</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.052787287013346</v>
+        <v>3.256613153033321</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1228,82 +1237,82 @@
         <v>62</v>
       </c>
       <c r="T5">
-        <v>-0.891041205370296</v>
+        <v>-0.9199361538026168</v>
       </c>
       <c r="U5">
-        <v>0.9509582065410651</v>
+        <v>0.9639637521852494</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X5">
-        <v>0.9997811180292288</v>
+        <v>0.9996608270469176</v>
       </c>
       <c r="Y5">
-        <v>0.9999586564977279</v>
+        <v>0.9999699318962872</v>
       </c>
       <c r="Z5">
-        <v>0.0001775384684991055</v>
+        <v>0.0003091048493696347</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-141.4512221898441</v>
+        <v>-147.1263839496164</v>
       </c>
       <c r="AC5">
-        <v>-3.999999999999993</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AD5">
-        <v>-0.7820779058161692</v>
+        <v>-0.8398699001648156</v>
       </c>
       <c r="AE5">
-        <v>-0.6231806714221768</v>
+        <v>-0.5427877585181364</v>
       </c>
       <c r="AF5">
-        <v>2.989890271676168</v>
+        <v>3.060293914397783</v>
       </c>
       <c r="AG5">
-        <v>2.989766659140928</v>
+        <v>3.060201897162974</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL5">
-        <v>-0.7820455719764932</v>
+        <v>-0.8398446468695522</v>
       </c>
       <c r="AM5">
-        <v>0.9274205860666791</v>
+        <v>0.9458517462217577</v>
       </c>
       <c r="AN5">
-        <v>-2.322853513699059</v>
+        <v>-2.547891424492321</v>
       </c>
       <c r="AO5">
-        <v>-1.88145753411371</v>
+        <v>-1.693309253773119</v>
       </c>
       <c r="AP5">
-        <v>-3.775023293907783</v>
+        <v>-3.732074298369752</v>
       </c>
       <c r="AQ5">
-        <v>3.724128517196357</v>
+        <v>5.170479060669843</v>
       </c>
       <c r="AR5">
-        <v>3.393437940830339</v>
+        <v>3.236897597500552</v>
       </c>
       <c r="AS5">
-        <v>0.0479221030158419</v>
+        <v>0.04065799994258394</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1314,10 +1323,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C6" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1329,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.570244421407061</v>
+        <v>1.506347676435477</v>
       </c>
       <c r="H6">
-        <v>1.002336870575205</v>
+        <v>1.024853166731697</v>
       </c>
       <c r="I6">
-        <v>0.267104540735901</v>
+        <v>0.2707077475271902</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1347,19 +1356,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N6">
-        <v>0.8396455699237848</v>
+        <v>1.004104688179759</v>
       </c>
       <c r="O6">
-        <v>12.68127856534591</v>
+        <v>15.38975688834037</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.570244421407061</v>
+        <v>1.506347676435477</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1368,82 +1377,82 @@
         <v>63</v>
       </c>
       <c r="T6">
-        <v>-0.9962572872601604</v>
+        <v>-0.9978536348105105</v>
       </c>
       <c r="U6">
-        <v>0.9982219692857099</v>
+        <v>0.9989361574110378</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X6">
-        <v>0.9961486854723911</v>
+        <v>0.9952147850261742</v>
       </c>
       <c r="Y6">
-        <v>0.999624760074551</v>
+        <v>0.9996080869852325</v>
       </c>
       <c r="Z6">
-        <v>0.003476074602159929</v>
+        <v>0.004393301959058293</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>-172.9845108296907</v>
+        <v>174.6886794591638</v>
       </c>
       <c r="AC6">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="AD6">
-        <v>-0.9925131695778808</v>
+        <v>-0.9957064281027668</v>
       </c>
       <c r="AE6">
-        <v>-0.122137660917789</v>
+        <v>0.09256732163582181</v>
       </c>
       <c r="AF6">
-        <v>1.267982853816817</v>
+        <v>1.223851284350529</v>
       </c>
       <c r="AG6">
-        <v>1.26750705602528</v>
+        <v>1.223371641104052</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AK6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL6">
-        <v>-0.9921407390101213</v>
+        <v>-0.9953161977947057</v>
       </c>
       <c r="AM6">
-        <v>0.9923127082335879</v>
+        <v>0.9936570242774376</v>
       </c>
       <c r="AN6">
-        <v>-1.246160489784905</v>
+        <v>-1.216661059825341</v>
       </c>
       <c r="AO6">
-        <v>-0.2061656177606775</v>
+        <v>0.05698617845660994</v>
       </c>
       <c r="AP6">
-        <v>-1.722603599910343</v>
+        <v>-1.560013788358898</v>
       </c>
       <c r="AQ6">
-        <v>2.679459988838541</v>
+        <v>2.84983750976704</v>
       </c>
       <c r="AR6">
-        <v>1.484448322388167</v>
+        <v>1.31691237659644</v>
       </c>
       <c r="AS6">
-        <v>0.03539939110579538</v>
+        <v>0.0327848973214919</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1454,10 +1463,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C7" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1469,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.146278781367343</v>
+        <v>1.974934095296505</v>
       </c>
       <c r="H7">
-        <v>1.534891772957541</v>
+        <v>1.551800357269528</v>
       </c>
       <c r="I7">
-        <v>0.3832782983662435</v>
+        <v>0.3869761348177421</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1487,19 +1496,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N7">
-        <v>0.08376294488396037</v>
+        <v>0.1031387441839681</v>
       </c>
       <c r="O7">
-        <v>14.1782278850857</v>
+        <v>18.55251726295192</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.146278781367343</v>
+        <v>1.974934095296505</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1508,82 +1517,82 @@
         <v>63</v>
       </c>
       <c r="T7">
-        <v>-0.9971076933219547</v>
+        <v>-0.9971996562992052</v>
       </c>
       <c r="U7">
-        <v>0.9984662328369414</v>
+        <v>0.9985561363126866</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X7">
-        <v>0.9900547097423993</v>
+        <v>0.993184407156307</v>
       </c>
       <c r="Y7">
-        <v>0.9990710833682475</v>
+        <v>0.9992651639121771</v>
       </c>
       <c r="Z7">
-        <v>0.009016373625848173</v>
+        <v>0.006080756755870165</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0.8503939498892883</v>
       </c>
       <c r="AB7">
-        <v>-173.8328374355906</v>
+        <v>173.7705818678119</v>
       </c>
       <c r="AC7">
-        <v>-30.99999999999999</v>
+        <v>-25</v>
       </c>
       <c r="AD7">
-        <v>-0.9942126974340801</v>
+        <v>-0.9940953813917636</v>
       </c>
       <c r="AE7">
-        <v>-0.1074295688386122</v>
+        <v>0.1085097815662903</v>
       </c>
       <c r="AF7">
-        <v>1.780987250297063</v>
+        <v>1.670098654188152</v>
       </c>
       <c r="AG7">
-        <v>1.779332861619323</v>
+        <v>1.66887140542683</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL7">
-        <v>-0.993289156723934</v>
+        <v>-0.9190581859065532</v>
       </c>
       <c r="AM7">
-        <v>0.9925145540429726</v>
+        <v>0.9630370270288057</v>
       </c>
       <c r="AN7">
-        <v>-1.73512953719635</v>
+        <v>-1.656667388225915</v>
       </c>
       <c r="AO7">
-        <v>-0.313789042006236</v>
+        <v>0.08241201497533358</v>
       </c>
       <c r="AP7">
-        <v>-2.212107403362016</v>
+        <v>-1.77255413036166</v>
       </c>
       <c r="AQ7">
-        <v>4.1232762300579</v>
+        <v>4.572304537091131</v>
       </c>
       <c r="AR7">
-        <v>1.846950093617659</v>
+        <v>1.397114876266881</v>
       </c>
       <c r="AS7">
-        <v>0.03616089577425368</v>
+        <v>0.03342123157228699</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1594,10 +1603,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C8" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1609,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.465037919765153</v>
+        <v>2.696719377268863</v>
       </c>
       <c r="H8">
-        <v>1.516205423007265</v>
+        <v>1.534246513459467</v>
       </c>
       <c r="I8">
-        <v>0.3873298034763542</v>
+        <v>0.3951889928469492</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1627,19 +1636,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N8">
-        <v>-0.1072021524017984</v>
+        <v>-0.1238265950782886</v>
       </c>
       <c r="O8">
-        <v>-25.34115886239229</v>
+        <v>-31.52236259834622</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.465037919765153</v>
+        <v>2.696719377268863</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1648,82 +1657,82 @@
         <v>64</v>
       </c>
       <c r="T8">
-        <v>0.9962834818469217</v>
+        <v>0.9889860594949241</v>
       </c>
       <c r="U8">
-        <v>0.9981878746310084</v>
+        <v>0.994894244187264</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
       </c>
       <c r="W8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X8">
-        <v>0.9934844645919709</v>
+        <v>0.9928011071871833</v>
       </c>
       <c r="Y8">
-        <v>0.9994412311995745</v>
+        <v>0.9994020696581923</v>
       </c>
       <c r="Z8">
-        <v>0.005956766607603581</v>
+        <v>0.006600962471009053</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>6.991186755245489</v>
+        <v>-12.05007180912457</v>
       </c>
       <c r="AC8">
         <v>-25</v>
       </c>
       <c r="AD8">
-        <v>0.992564885858424</v>
+        <v>0.97796552948057</v>
       </c>
       <c r="AE8">
-        <v>0.1217166683772349</v>
+        <v>-0.2087664320425777</v>
       </c>
       <c r="AF8">
-        <v>2.004127892259483</v>
+        <v>2.16357849369615</v>
       </c>
       <c r="AG8">
-        <v>2.003008048121226</v>
+        <v>2.162284824467887</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
       </c>
       <c r="AI8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AL8">
-        <v>0.9920102715678084</v>
+        <v>0.9773807742172516</v>
       </c>
       <c r="AM8">
-        <v>0.9928469825342465</v>
+        <v>0.9881850231608122</v>
       </c>
       <c r="AN8">
-        <v>1.960061041963213</v>
+        <v>2.120294982223862</v>
       </c>
       <c r="AO8">
-        <v>0.3500288017584413</v>
+        <v>-0.3438991264746123</v>
       </c>
       <c r="AP8">
-        <v>2.708348477042971</v>
+        <v>3.047661417731772</v>
       </c>
       <c r="AQ8">
-        <v>-4.670177103758457</v>
+        <v>-4.240237424373629</v>
       </c>
       <c r="AR8">
-        <v>2.285629500781877</v>
+        <v>2.684528356714271</v>
       </c>
       <c r="AS8">
-        <v>0.03151276095421195</v>
+        <v>0.03330240042484071</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1734,10 +1743,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C9" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1749,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.285725995326295</v>
+        <v>1.461090899523458</v>
       </c>
       <c r="H9">
-        <v>3.150689922500043</v>
+        <v>3.157234931762766</v>
       </c>
       <c r="I9">
-        <v>0.6685389093936323</v>
+        <v>0.6667392117677121</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1767,19 +1776,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N9">
-        <v>0.8872829461587431</v>
+        <v>0.9079067916752052</v>
       </c>
       <c r="O9">
-        <v>83.20413440652698</v>
+        <v>89.26049918155144</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.285725995326295</v>
+        <v>1.461090899523458</v>
       </c>
       <c r="R9" t="s">
         <v>59</v>
@@ -1788,82 +1797,82 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.9993283430045486</v>
+        <v>-0.9986655881761152</v>
       </c>
       <c r="U9">
-        <v>0.8490288919884816</v>
+        <v>0.8491583172689934</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
       </c>
       <c r="W9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X9">
-        <v>0.9649554530681491</v>
+        <v>0.9919876446769322</v>
       </c>
       <c r="Y9">
-        <v>0.997324550545739</v>
+        <v>0.9990352103589665</v>
       </c>
       <c r="Z9">
-        <v>0.03236909747758987</v>
+        <v>0.00704756568203424</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>176.4025569540482</v>
+        <v>174.9313750264995</v>
       </c>
       <c r="AC9">
-        <v>53.00000000000001</v>
+        <v>25</v>
       </c>
       <c r="AD9">
-        <v>-0.9980295296037169</v>
+        <v>-0.99608959436648</v>
       </c>
       <c r="AE9">
-        <v>0.06274598026155627</v>
+        <v>0.0883488539530722</v>
       </c>
       <c r="AF9">
-        <v>0.9726153333670159</v>
+        <v>1.052682576426869</v>
       </c>
       <c r="AG9">
-        <v>0.9700131502041532</v>
+        <v>1.051666959181836</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
       </c>
       <c r="AI9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AK9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL9">
-        <v>-0.4976796760217012</v>
+        <v>-0.497564288722147</v>
       </c>
       <c r="AM9">
-        <v>0.7935656771619158</v>
+        <v>0.792502680820846</v>
       </c>
       <c r="AN9">
-        <v>-0.927412727153209</v>
+        <v>-1.03560922134312</v>
       </c>
       <c r="AO9">
-        <v>0.1440315104885368</v>
+        <v>0.1340434818816628</v>
       </c>
       <c r="AP9">
-        <v>-1.816656800577983</v>
+        <v>-2.148195515030185</v>
       </c>
       <c r="AQ9">
-        <v>0.6012046257110735</v>
+        <v>0.5831554618618305</v>
       </c>
       <c r="AR9">
-        <v>1.771224108307004</v>
+        <v>2.083980118395606</v>
       </c>
       <c r="AS9">
-        <v>0.03271182940138548</v>
+        <v>0.03991014076490834</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1874,10 +1883,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C10" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1889,37 +1898,37 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.1759201018796525</v>
+        <v>0.002177776906038563</v>
       </c>
       <c r="H10">
-        <v>2.123554861794707</v>
+        <v>2.126878677633599</v>
       </c>
       <c r="I10">
-        <v>0.4506142627209715</v>
+        <v>0.4522136443902205</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L10">
         <v>233</v>
       </c>
       <c r="M10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N10">
-        <v>47.20297848534669</v>
+        <v>47.47164507601001</v>
       </c>
       <c r="O10">
-        <v>47.02495543975326</v>
+        <v>51.4219529625238</v>
       </c>
       <c r="P10">
-        <v>0.3638982418148696</v>
+        <v>0.9303800585245253</v>
       </c>
       <c r="Q10">
-        <v>0.2765596850126186</v>
+        <v>0.03128093560385624</v>
       </c>
       <c r="R10" t="s">
         <v>61</v>
@@ -1928,82 +1937,82 @@
         <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.7976630934848853</v>
+        <v>-0.6507469057837999</v>
       </c>
       <c r="U10">
-        <v>0.7588861098037478</v>
+        <v>0.6678042029930771</v>
       </c>
       <c r="V10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="W10" t="s">
         <v>66</v>
       </c>
       <c r="X10">
-        <v>0.997307822291014</v>
+        <v>0.9997836355595584</v>
       </c>
       <c r="Y10">
-        <v>0.9997508709421974</v>
+        <v>0.9998723815614684</v>
       </c>
       <c r="Z10">
-        <v>0.002443048651183388</v>
+        <v>8.874600191000059E-05</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>114.0381403485021</v>
+        <v>91.78558942711715</v>
       </c>
       <c r="AC10">
-        <v>18</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AD10">
-        <v>-0.407344676974959</v>
+        <v>-0.03115937024934096</v>
       </c>
       <c r="AE10">
-        <v>0.9132745009799443</v>
+        <v>0.9995144289332017</v>
       </c>
       <c r="AF10">
-        <v>0.6475431509208871</v>
+        <v>1.024557967224546</v>
       </c>
       <c r="AG10">
-        <v>0.6473818291058117</v>
+        <v>1.024427214736584</v>
       </c>
       <c r="AH10" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AI10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="AJ10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AL10">
-        <v>-0.2036215977896917</v>
+        <v>-0.01557769686958205</v>
       </c>
       <c r="AM10">
-        <v>0.6134016422533884</v>
+        <v>0.4448547990031296</v>
       </c>
       <c r="AN10">
-        <v>-0.2296472657165816</v>
+        <v>-0.03853955374076883</v>
       </c>
       <c r="AO10">
-        <v>0.6035889157375692</v>
+        <v>1.023611027881948</v>
       </c>
       <c r="AP10">
-        <v>-0.2556816737650891</v>
+        <v>0.02052277034608236</v>
       </c>
       <c r="AQ10">
-        <v>0.3946921492060487</v>
+        <v>0.2014498284857335</v>
       </c>
       <c r="AR10">
-        <v>0.2433294980053786</v>
+        <v>0.08409136317548631</v>
       </c>
       <c r="AS10">
-        <v>0.05809710445912196</v>
+        <v>0.4296556374545773</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2014,10 +2023,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C11" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2029,13 +2038,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.427443740981068</v>
+        <v>1.599304465565033</v>
       </c>
       <c r="H11">
-        <v>2.159599550271965</v>
+        <v>2.144419437263232</v>
       </c>
       <c r="I11">
-        <v>0.4999859571844159</v>
+        <v>0.4958535634912872</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2047,19 +2056,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>273.3607018772811</v>
+        <v>421.9793121360855</v>
       </c>
       <c r="O11">
-        <v>4.085825590026248</v>
+        <v>6.952742301537844</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.427443740981068</v>
+        <v>1.599304465565033</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2068,82 +2077,82 @@
         <v>62</v>
       </c>
       <c r="T11">
-        <v>-0.771919016304465</v>
+        <v>-0.9369233410214868</v>
       </c>
       <c r="U11">
-        <v>0.7473612893329706</v>
+        <v>0.8214132020955007</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X11">
-        <v>0.9998986114694594</v>
+        <v>0.9934472995233304</v>
       </c>
       <c r="Y11">
-        <v>0.9999909279838457</v>
+        <v>0.9991907945433268</v>
       </c>
       <c r="Z11">
-        <v>9.231651438634803E-05</v>
+        <v>0.005743495019996381</v>
       </c>
       <c r="AA11">
-        <v>0.6685907682296063</v>
+        <v>0.2482464792281063</v>
       </c>
       <c r="AB11">
-        <v>-125.1481539265188</v>
+        <v>-148.6047692938305</v>
       </c>
       <c r="AC11">
-        <v>-3.000000000000004</v>
+        <v>-25</v>
       </c>
       <c r="AD11">
-        <v>-0.5756926583694939</v>
+        <v>-0.853594163097612</v>
       </c>
       <c r="AE11">
-        <v>-0.8176661684938817</v>
+        <v>-0.5209385805694251</v>
       </c>
       <c r="AF11">
-        <v>1.88051364434871</v>
+        <v>1.538737355565149</v>
       </c>
       <c r="AG11">
-        <v>1.88049658429855</v>
+        <v>1.537492200900638</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
       </c>
       <c r="AI11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AJ11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AK11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AL11">
-        <v>-0.4802933702777059</v>
+        <v>-0.5323168518364058</v>
       </c>
       <c r="AM11">
-        <v>0.7982537553042506</v>
+        <v>0.7990491246692972</v>
       </c>
       <c r="AN11">
-        <v>-1.073416863306361</v>
+        <v>-1.255285529206324</v>
       </c>
       <c r="AO11">
-        <v>-1.543823420466639</v>
+        <v>-0.8723776306932588</v>
       </c>
       <c r="AP11">
-        <v>-1.816192253452593</v>
+        <v>-1.811219957742462</v>
       </c>
       <c r="AQ11">
-        <v>1.501229997671825</v>
+        <v>2.541659773996094</v>
       </c>
       <c r="AR11">
-        <v>1.650245314925916</v>
+        <v>1.564963027451948</v>
       </c>
       <c r="AS11">
-        <v>0.05446013764576514</v>
+        <v>0.04263465463848008</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -196,10 +196,10 @@
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
-    <t>DOWN_DECELERATING</t>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
   </si>
   <si>
     <t>空头加速</t>
@@ -208,10 +208,10 @@
     <t>空头稳态</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
-    <t>空头减速</t>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>多头加速</t>
   </si>
   <si>
     <t>NEUTRAL</t>
@@ -238,7 +238,7 @@
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
+    <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
     <t>TRANSITION_ZONE</t>
@@ -250,7 +250,7 @@
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>上升坡延续</t>
+    <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>地形转换区</t>
@@ -763,10 +763,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C2" s="2">
         <v>46302</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46301</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -778,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.41384031359683</v>
+        <v>1.45055166491455</v>
       </c>
       <c r="H2">
-        <v>1.105275202717707</v>
+        <v>1.113907924887103</v>
       </c>
       <c r="I2">
-        <v>0.2612822449488148</v>
+        <v>0.2619921489733854</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -796,19 +796,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N2">
-        <v>0.2995842253285217</v>
+        <v>0.3457803432777749</v>
       </c>
       <c r="O2">
-        <v>7.309861363611423</v>
+        <v>8.659972819121426</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.41384031359683</v>
+        <v>1.45055166491455</v>
       </c>
       <c r="R2" t="s">
         <v>58</v>
@@ -817,10 +817,10 @@
         <v>62</v>
       </c>
       <c r="T2">
-        <v>-0.9312053040770206</v>
+        <v>-0.9834030781674964</v>
       </c>
       <c r="U2">
-        <v>0.9689152835989751</v>
+        <v>0.9921912264379433</v>
       </c>
       <c r="V2" t="s">
         <v>56</v>
@@ -829,34 +829,34 @@
         <v>67</v>
       </c>
       <c r="X2">
-        <v>0.9947843742605199</v>
+        <v>0.9860834492617808</v>
       </c>
       <c r="Y2">
-        <v>0.9994915870572633</v>
+        <v>0.9986393650502798</v>
       </c>
       <c r="Z2">
-        <v>0.004707212796743354</v>
+        <v>0.01255591578849902</v>
       </c>
       <c r="AA2">
         <v>1</v>
       </c>
       <c r="AB2">
-        <v>-149.5843723307099</v>
+        <v>-165.1910654254902</v>
       </c>
       <c r="AC2">
-        <v>-22.99999999999999</v>
+        <v>-36</v>
       </c>
       <c r="AD2">
-        <v>-0.8623756142488881</v>
+        <v>-0.9667835432148884</v>
       </c>
       <c r="AE2">
-        <v>-0.5062689995929565</v>
+        <v>-0.255596519085973</v>
       </c>
       <c r="AF2">
-        <v>1.355474298724338</v>
+        <v>1.249831379699399</v>
       </c>
       <c r="AG2">
-        <v>1.35478515804732</v>
+        <v>1.248130815442922</v>
       </c>
       <c r="AH2" t="s">
         <v>56</v>
@@ -871,28 +871,28 @@
         <v>76</v>
       </c>
       <c r="AL2">
-        <v>-0.8619371713251034</v>
+        <v>-0.9654681037371758</v>
       </c>
       <c r="AM2">
-        <v>0.9528918082725243</v>
+        <v>0.9841882005477584</v>
       </c>
       <c r="AN2">
-        <v>-1.123718285723238</v>
+        <v>-1.160528554167572</v>
       </c>
       <c r="AO2">
-        <v>-0.7452867368265162</v>
+        <v>-0.4148216390195625</v>
       </c>
       <c r="AP2">
-        <v>-1.552801375349311</v>
+        <v>-1.555536263347624</v>
       </c>
       <c r="AQ2">
-        <v>2.72310269088192</v>
+        <v>2.77309859881427</v>
       </c>
       <c r="AR2">
-        <v>1.291695185302931</v>
+        <v>1.301521619601928</v>
       </c>
       <c r="AS2">
-        <v>0.03761954314789425</v>
+        <v>0.03580426789537371</v>
       </c>
       <c r="AT2" t="b">
         <v>1</v>
@@ -903,10 +903,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C3" s="2">
         <v>46302</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46301</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
@@ -915,16 +915,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.5206325096177565</v>
+        <v>0.6133616187621953</v>
       </c>
       <c r="G3">
-        <v>2.114622406007593</v>
+        <v>2.204449411330788</v>
       </c>
       <c r="H3">
-        <v>2.095655054844892</v>
+        <v>2.10013293826063</v>
       </c>
       <c r="I3">
-        <v>0.4596472148588735</v>
+        <v>0.460104902387594</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -936,19 +936,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3">
-        <v>0.03313462076284382</v>
+        <v>0.03905020330546696</v>
       </c>
       <c r="O3">
-        <v>10.03753523054891</v>
+        <v>11.348268734334</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.114622406007593</v>
+        <v>2.204449411330788</v>
       </c>
       <c r="R3" t="s">
         <v>58</v>
@@ -957,10 +957,10 @@
         <v>62</v>
       </c>
       <c r="T3">
-        <v>-0.9471943794584506</v>
+        <v>-0.9758541079835924</v>
       </c>
       <c r="U3">
-        <v>0.9038615815922336</v>
+        <v>0.9308345985550868</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
@@ -969,34 +969,34 @@
         <v>67</v>
       </c>
       <c r="X3">
-        <v>0.9855665940889367</v>
+        <v>0.9876952040239989</v>
       </c>
       <c r="Y3">
-        <v>0.9981169375730693</v>
+        <v>0.9987840285925634</v>
       </c>
       <c r="Z3">
-        <v>0.01255034348413264</v>
+        <v>0.01108882456856453</v>
       </c>
       <c r="AA3">
-        <v>0.9303371883403148</v>
+        <v>0.7789797891513551</v>
       </c>
       <c r="AB3">
-        <v>-154.212432023279</v>
+        <v>-162.0211462119973</v>
       </c>
       <c r="AC3">
-        <v>-37.99999999999999</v>
+        <v>-35</v>
       </c>
       <c r="AD3">
-        <v>-0.90041318653816</v>
+        <v>-0.9511705007376822</v>
       </c>
       <c r="AE3">
-        <v>-0.4350357381965263</v>
+        <v>-0.3086659659347415</v>
       </c>
       <c r="AF3">
-        <v>2.059164955897933</v>
+        <v>1.953404081165554</v>
       </c>
       <c r="AG3">
-        <v>2.055287419738629</v>
+        <v>1.951028797655687</v>
       </c>
       <c r="AH3" t="s">
         <v>56</v>
@@ -1011,28 +1011,28 @@
         <v>76</v>
       </c>
       <c r="AL3">
-        <v>-0.8674140530242463</v>
+        <v>-0.8450277678526964</v>
       </c>
       <c r="AM3">
-        <v>0.9501034015349541</v>
+        <v>0.934996782145068</v>
       </c>
       <c r="AN3">
-        <v>-1.730949690210708</v>
+        <v>-1.777695303795773</v>
       </c>
       <c r="AO3">
-        <v>-1.059460664405853</v>
+        <v>-0.7498397685437406</v>
       </c>
       <c r="AP3">
-        <v>-2.102664683571918</v>
+        <v>-2.291567922100585</v>
       </c>
       <c r="AQ3">
-        <v>4.863130987710345</v>
+        <v>4.222128439541687</v>
       </c>
       <c r="AR3">
-        <v>1.648412988117296</v>
+        <v>1.911713276317474</v>
       </c>
       <c r="AS3">
-        <v>0.03619280163420795</v>
+        <v>0.03816490609269878</v>
       </c>
       <c r="AT3" t="b">
         <v>1</v>
@@ -1043,10 +1043,10 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C4" s="2">
         <v>46302</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46301</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.143653764222756</v>
+        <v>3.117324038070099</v>
       </c>
       <c r="H4">
-        <v>2.119598450092666</v>
+        <v>2.127566056903347</v>
       </c>
       <c r="I4">
-        <v>0.5014370952287174</v>
+        <v>0.5035748575194741</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1076,19 +1076,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4">
-        <v>0.8273435263671126</v>
+        <v>0.9222159681974055</v>
       </c>
       <c r="O4">
-        <v>21.69471693039816</v>
+        <v>22.60729041282379</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.143653764222756</v>
+        <v>3.117324038070099</v>
       </c>
       <c r="R4" t="s">
         <v>58</v>
@@ -1097,10 +1097,10 @@
         <v>62</v>
       </c>
       <c r="T4">
-        <v>-0.9318473998340459</v>
+        <v>-0.9318949938952101</v>
       </c>
       <c r="U4">
-        <v>0.9693302174354312</v>
+        <v>0.9693518816195936</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
@@ -1109,34 +1109,34 @@
         <v>67</v>
       </c>
       <c r="X4">
-        <v>0.9998639469371158</v>
+        <v>0.9999396996338579</v>
       </c>
       <c r="Y4">
-        <v>0.9999955500404425</v>
+        <v>0.9999965374669967</v>
       </c>
       <c r="Z4">
-        <v>0.0001316031033267162</v>
+        <v>5.683783313881197E-05</v>
       </c>
       <c r="AA4">
         <v>1</v>
       </c>
       <c r="AB4">
-        <v>-149.7339664761072</v>
+        <v>-149.744796748058</v>
       </c>
       <c r="AC4">
-        <v>-3.999999999999993</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AD4">
-        <v>-0.8636944963904277</v>
+        <v>-0.8637897519737722</v>
       </c>
       <c r="AE4">
-        <v>-0.5040156911296367</v>
+        <v>-0.5038524232204199</v>
       </c>
       <c r="AF4">
-        <v>2.811519713741461</v>
+        <v>2.776289179400995</v>
       </c>
       <c r="AG4">
-        <v>2.81150720259244</v>
+        <v>2.776279566408084</v>
       </c>
       <c r="AH4" t="s">
         <v>56</v>
@@ -1151,28 +1151,28 @@
         <v>76</v>
       </c>
       <c r="AL4">
-        <v>-0.8636906529848487</v>
+        <v>-0.863786761073248</v>
       </c>
       <c r="AM4">
-        <v>0.952854627449048</v>
+        <v>0.9528864746495984</v>
       </c>
       <c r="AN4">
-        <v>-2.416449289337514</v>
+        <v>-2.392376283787254</v>
       </c>
       <c r="AO4">
-        <v>-1.436407037481282</v>
+        <v>-1.408328011633546</v>
       </c>
       <c r="AP4">
-        <v>-3.791539223637096</v>
+        <v>-3.771937364661929</v>
       </c>
       <c r="AQ4">
-        <v>4.317520847982976</v>
+        <v>4.099146198948727</v>
       </c>
       <c r="AR4">
-        <v>3.369330601403916</v>
+        <v>3.376428300448871</v>
       </c>
       <c r="AS4">
-        <v>0.04168109321489994</v>
+        <v>0.04166159370654634</v>
       </c>
       <c r="AT4" t="b">
         <v>1</v>
@@ -1183,10 +1183,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C5" s="2">
         <v>46302</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46301</v>
       </c>
       <c r="D5" t="s">
         <v>56</v>
@@ -1198,13 +1198,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.256613153033321</v>
+        <v>3.34311840529356</v>
       </c>
       <c r="H5">
-        <v>1.555059337462569</v>
+        <v>1.560039919670461</v>
       </c>
       <c r="I5">
-        <v>0.3669789523319065</v>
+        <v>0.3708325029217538</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1216,19 +1216,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N5">
-        <v>0.08875405194201892</v>
+        <v>0.1010795149831908</v>
       </c>
       <c r="O5">
-        <v>19.16638480932065</v>
+        <v>20.35401955792393</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.256613153033321</v>
+        <v>3.34311840529356</v>
       </c>
       <c r="R5" t="s">
         <v>58</v>
@@ -1237,10 +1237,10 @@
         <v>62</v>
       </c>
       <c r="T5">
-        <v>-0.9199361538026168</v>
+        <v>-0.9246486633344464</v>
       </c>
       <c r="U5">
-        <v>0.9639637521852494</v>
+        <v>0.966086802965567</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
@@ -1249,34 +1249,34 @@
         <v>67</v>
       </c>
       <c r="X5">
-        <v>0.9996608270469176</v>
+        <v>0.9998253189548801</v>
       </c>
       <c r="Y5">
-        <v>0.9999699318962872</v>
+        <v>0.9999796178602646</v>
       </c>
       <c r="Z5">
-        <v>0.0003091048493696347</v>
+        <v>0.0001542989053844313</v>
       </c>
       <c r="AA5">
         <v>1</v>
       </c>
       <c r="AB5">
-        <v>-147.1263839496164</v>
+        <v>-148.1351581301081</v>
       </c>
       <c r="AC5">
-        <v>-5.999999999999996</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AD5">
-        <v>-0.8398699001648156</v>
+        <v>-0.8492957908161154</v>
       </c>
       <c r="AE5">
-        <v>-0.5427877585181364</v>
+        <v>-0.5279172849055325</v>
       </c>
       <c r="AF5">
-        <v>3.060293914397783</v>
+        <v>3.063656103627598</v>
       </c>
       <c r="AG5">
-        <v>3.060201897162974</v>
+        <v>3.063593659760793</v>
       </c>
       <c r="AH5" t="s">
         <v>56</v>
@@ -1291,28 +1291,28 @@
         <v>76</v>
       </c>
       <c r="AL5">
-        <v>-0.8398446468695522</v>
+        <v>-0.8492784803506302</v>
       </c>
       <c r="AM5">
-        <v>0.9458517462217577</v>
+        <v>0.9484288963646974</v>
       </c>
       <c r="AN5">
-        <v>-2.547891424492321</v>
+        <v>-2.588035441970133</v>
       </c>
       <c r="AO5">
-        <v>-1.693309253773119</v>
+        <v>-1.638530576511015</v>
       </c>
       <c r="AP5">
-        <v>-3.732074298369752</v>
+        <v>-3.939449303748471</v>
       </c>
       <c r="AQ5">
-        <v>5.170479060669843</v>
+        <v>4.600080156351499</v>
       </c>
       <c r="AR5">
-        <v>3.236897597500552</v>
+        <v>3.502935469794273</v>
       </c>
       <c r="AS5">
-        <v>0.04065799994258394</v>
+        <v>0.04235138087486535</v>
       </c>
       <c r="AT5" t="b">
         <v>1</v>
@@ -1323,10 +1323,10 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C6" s="2">
         <v>46302</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46301</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -1338,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.506347676435477</v>
+        <v>1.540104790959755</v>
       </c>
       <c r="H6">
-        <v>1.024853166731697</v>
+        <v>1.035676755161413</v>
       </c>
       <c r="I6">
-        <v>0.2707077475271902</v>
+        <v>0.272551274072573</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1356,19 +1356,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N6">
-        <v>1.004104688179759</v>
+        <v>1.083754393010875</v>
       </c>
       <c r="O6">
-        <v>15.38975688834037</v>
+        <v>16.73530420920823</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.506347676435477</v>
+        <v>1.540104790959755</v>
       </c>
       <c r="R6" t="s">
         <v>59</v>
@@ -1377,10 +1377,10 @@
         <v>63</v>
       </c>
       <c r="T6">
-        <v>-0.9978536348105105</v>
+        <v>-0.9998770847917888</v>
       </c>
       <c r="U6">
-        <v>0.9989361574110378</v>
+        <v>0.9998852909602977</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
@@ -1389,34 +1389,34 @@
         <v>67</v>
       </c>
       <c r="X6">
-        <v>0.9952147850261742</v>
+        <v>0.9990103250926596</v>
       </c>
       <c r="Y6">
-        <v>0.9996080869852325</v>
+        <v>0.9997624112159706</v>
       </c>
       <c r="Z6">
-        <v>0.004393301959058293</v>
+        <v>0.0007520861233110132</v>
       </c>
       <c r="AA6">
         <v>1</v>
       </c>
       <c r="AB6">
-        <v>174.6886794591638</v>
+        <v>178.7294547482969</v>
       </c>
       <c r="AC6">
-        <v>-21</v>
+        <v>-9</v>
       </c>
       <c r="AD6">
-        <v>-0.9957064281027668</v>
+        <v>-0.999754140373363</v>
       </c>
       <c r="AE6">
-        <v>0.09256732163582181</v>
+        <v>0.02217338057938198</v>
       </c>
       <c r="AF6">
-        <v>1.223851284350529</v>
+        <v>1.235323385037874</v>
       </c>
       <c r="AG6">
-        <v>1.223371641104052</v>
+        <v>1.235029886056939</v>
       </c>
       <c r="AH6" t="s">
         <v>56</v>
@@ -1431,28 +1431,28 @@
         <v>77</v>
       </c>
       <c r="AL6">
-        <v>-0.9953161977947057</v>
+        <v>-0.9995166100028233</v>
       </c>
       <c r="AM6">
-        <v>0.9936570242774376</v>
+        <v>0.9947645386166181</v>
       </c>
       <c r="AN6">
-        <v>-1.216661059825341</v>
+        <v>-1.234097001384251</v>
       </c>
       <c r="AO6">
-        <v>0.05698617845660994</v>
+        <v>0.003068617618633421</v>
       </c>
       <c r="AP6">
-        <v>-1.560013788358898</v>
+        <v>-1.632617315044742</v>
       </c>
       <c r="AQ6">
-        <v>2.84983750976704</v>
+        <v>2.63470103692516</v>
       </c>
       <c r="AR6">
-        <v>1.31691237659644</v>
+        <v>1.413334024223858</v>
       </c>
       <c r="AS6">
-        <v>0.0327848973214919</v>
+        <v>0.03385698280653627</v>
       </c>
       <c r="AT6" t="b">
         <v>1</v>
@@ -1463,10 +1463,10 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C7" s="2">
         <v>46302</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46301</v>
       </c>
       <c r="D7" t="s">
         <v>56</v>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1.974934095296505</v>
+        <v>2.013370626712889</v>
       </c>
       <c r="H7">
-        <v>1.551800357269528</v>
+        <v>1.559964560183154</v>
       </c>
       <c r="I7">
-        <v>0.3869761348177421</v>
+        <v>0.388791668623207</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1496,19 +1496,19 @@
         <v>240</v>
       </c>
       <c r="M7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7">
-        <v>0.1031387441839681</v>
+        <v>0.1125994368890572</v>
       </c>
       <c r="O7">
-        <v>18.55251726295192</v>
+        <v>19.02017515017851</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.974934095296505</v>
+        <v>2.013370626712889</v>
       </c>
       <c r="R7" t="s">
         <v>59</v>
@@ -1517,10 +1517,10 @@
         <v>63</v>
       </c>
       <c r="T7">
-        <v>-0.9971996562992052</v>
+        <v>-0.9997675492920802</v>
       </c>
       <c r="U7">
-        <v>0.9985561363126866</v>
+        <v>0.9997626282502808</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
@@ -1529,34 +1529,34 @@
         <v>67</v>
       </c>
       <c r="X7">
-        <v>0.993184407156307</v>
+        <v>0.9984794302515808</v>
       </c>
       <c r="Y7">
-        <v>0.9992651639121771</v>
+        <v>0.9994689242753788</v>
       </c>
       <c r="Z7">
-        <v>0.006080756755870165</v>
+        <v>0.0009894940237979988</v>
       </c>
       <c r="AA7">
-        <v>0.8503939498892883</v>
+        <v>0.80410148193718</v>
       </c>
       <c r="AB7">
-        <v>173.7705818678119</v>
+        <v>178.1899570853641</v>
       </c>
       <c r="AC7">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="AD7">
-        <v>-0.9940953813917636</v>
+        <v>-0.9995010392730865</v>
       </c>
       <c r="AE7">
-        <v>0.1085097815662903</v>
+        <v>0.03158595403054688</v>
       </c>
       <c r="AF7">
-        <v>1.670098654188152</v>
+        <v>1.643017775099271</v>
       </c>
       <c r="AG7">
-        <v>1.66887140542683</v>
+        <v>1.642145208243794</v>
       </c>
       <c r="AH7" t="s">
         <v>56</v>
@@ -1571,28 +1571,28 @@
         <v>77</v>
       </c>
       <c r="AL7">
-        <v>-0.9190581859065532</v>
+        <v>-0.9011218348550127</v>
       </c>
       <c r="AM7">
-        <v>0.9630370270288057</v>
+        <v>0.9551107866849627</v>
       </c>
       <c r="AN7">
-        <v>-1.656667388225915</v>
+        <v>-1.640455754305864</v>
       </c>
       <c r="AO7">
-        <v>0.08241201497533358</v>
+        <v>0.01445650272255401</v>
       </c>
       <c r="AP7">
-        <v>-1.77255413036166</v>
+        <v>-2.00388182563575</v>
       </c>
       <c r="AQ7">
-        <v>4.572304537091131</v>
+        <v>3.604303994921653</v>
       </c>
       <c r="AR7">
-        <v>1.397114876266881</v>
+        <v>1.716975064652542</v>
       </c>
       <c r="AS7">
-        <v>0.03342123157228699</v>
+        <v>0.03582629987187833</v>
       </c>
       <c r="AT7" t="b">
         <v>1</v>
@@ -1603,10 +1603,10 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C8" s="2">
         <v>46302</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46301</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -1618,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.696719377268863</v>
+        <v>2.776844219695286</v>
       </c>
       <c r="H8">
-        <v>1.534246513459467</v>
+        <v>1.543124662848573</v>
       </c>
       <c r="I8">
-        <v>0.3951889928469492</v>
+        <v>0.3992866396903339</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1636,19 +1636,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8">
-        <v>-0.1238265950782886</v>
+        <v>-0.1322157148217848</v>
       </c>
       <c r="O8">
-        <v>-31.52236259834622</v>
+        <v>-33.94498454988074</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.696719377268863</v>
+        <v>2.776844219695286</v>
       </c>
       <c r="R8" t="s">
         <v>60</v>
@@ -1657,10 +1657,10 @@
         <v>64</v>
       </c>
       <c r="T8">
-        <v>0.9889860594949241</v>
+        <v>0.9815614463182903</v>
       </c>
       <c r="U8">
-        <v>0.994894244187264</v>
+        <v>0.9915972031276785</v>
       </c>
       <c r="V8" t="s">
         <v>57</v>
@@ -1669,34 +1669,34 @@
         <v>67</v>
       </c>
       <c r="X8">
-        <v>0.9928011071871833</v>
+        <v>0.9959956465844917</v>
       </c>
       <c r="Y8">
-        <v>0.9994020696581923</v>
+        <v>0.9995782091377913</v>
       </c>
       <c r="Z8">
-        <v>0.006600962471009053</v>
+        <v>0.003582562553299584</v>
       </c>
       <c r="AA8">
         <v>1</v>
       </c>
       <c r="AB8">
-        <v>-12.05007180912457</v>
+        <v>-15.61010744709516</v>
       </c>
       <c r="AC8">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AD8">
-        <v>0.97796552948057</v>
+        <v>0.9631151121413833</v>
       </c>
       <c r="AE8">
-        <v>-0.2087664320425777</v>
+        <v>-0.2690897262343743</v>
       </c>
       <c r="AF8">
-        <v>2.16357849369615</v>
+        <v>2.239664437625493</v>
       </c>
       <c r="AG8">
-        <v>2.162284824467887</v>
+        <v>2.238719767631289</v>
       </c>
       <c r="AH8" t="s">
         <v>57</v>
@@ -1711,28 +1711,28 @@
         <v>78</v>
       </c>
       <c r="AL8">
-        <v>0.9773807742172516</v>
+        <v>0.962708878987827</v>
       </c>
       <c r="AM8">
-        <v>0.9881850231608122</v>
+        <v>0.9836270268585893</v>
       </c>
       <c r="AN8">
-        <v>2.120294982223862</v>
+        <v>2.169259678534663</v>
       </c>
       <c r="AO8">
-        <v>-0.3438991264746123</v>
+        <v>-0.5199204015390586</v>
       </c>
       <c r="AP8">
-        <v>3.047661417731772</v>
+        <v>3.193281331514531</v>
       </c>
       <c r="AQ8">
-        <v>-4.240237424373629</v>
+        <v>-4.01984093452021</v>
       </c>
       <c r="AR8">
-        <v>2.684528356714271</v>
+        <v>2.850847450119219</v>
       </c>
       <c r="AS8">
-        <v>0.03330240042484071</v>
+        <v>0.03439919988035113</v>
       </c>
       <c r="AT8" t="b">
         <v>1</v>
@@ -1743,10 +1743,10 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C9" s="2">
         <v>46302</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46301</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1758,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.461090899523458</v>
+        <v>1.473457504260679</v>
       </c>
       <c r="H9">
-        <v>3.157234931762766</v>
+        <v>3.160047727410198</v>
       </c>
       <c r="I9">
-        <v>0.6667392117677121</v>
+        <v>0.6656818204332902</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1776,19 +1776,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N9">
-        <v>0.9079067916752052</v>
+        <v>0.9183141238047977</v>
       </c>
       <c r="O9">
-        <v>89.26049918155144</v>
+        <v>93.84916952527379</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.461090899523458</v>
+        <v>1.473457504260679</v>
       </c>
       <c r="R9" t="s">
         <v>59</v>
@@ -1797,10 +1797,10 @@
         <v>63</v>
       </c>
       <c r="T9">
-        <v>-0.9986655881761152</v>
+        <v>-0.9973821418480858</v>
       </c>
       <c r="U9">
-        <v>0.8491583172689934</v>
+        <v>0.8485921692882007</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
@@ -1809,34 +1809,34 @@
         <v>67</v>
       </c>
       <c r="X9">
-        <v>0.9919876446769322</v>
+        <v>0.9919068040049454</v>
       </c>
       <c r="Y9">
-        <v>0.9990352103589665</v>
+        <v>0.999080821826248</v>
       </c>
       <c r="Z9">
-        <v>0.00704756568203424</v>
+        <v>0.00717401782130267</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>174.9313750264995</v>
+        <v>-172.8985318845068</v>
       </c>
       <c r="AC9">
         <v>25</v>
       </c>
       <c r="AD9">
-        <v>-0.99608959436648</v>
+        <v>-0.992328770463571</v>
       </c>
       <c r="AE9">
-        <v>0.0883488539530722</v>
+        <v>-0.1236269036668696</v>
       </c>
       <c r="AF9">
-        <v>1.052682576426869</v>
+        <v>1.063217649210645</v>
       </c>
       <c r="AG9">
-        <v>1.051666959181836</v>
+        <v>1.062240362753543</v>
       </c>
       <c r="AH9" t="s">
         <v>56</v>
@@ -1851,28 +1851,28 @@
         <v>77</v>
       </c>
       <c r="AL9">
-        <v>-0.497564288722147</v>
+        <v>-0.4957083217582874</v>
       </c>
       <c r="AM9">
-        <v>0.792502680820846</v>
+        <v>0.7916245929786799</v>
       </c>
       <c r="AN9">
-        <v>-1.03560922134312</v>
+        <v>-1.050693820784933</v>
       </c>
       <c r="AO9">
-        <v>0.1340434818816628</v>
+        <v>-0.09083334132185701</v>
       </c>
       <c r="AP9">
-        <v>-2.148195515030185</v>
+        <v>-2.145484640321218</v>
       </c>
       <c r="AQ9">
-        <v>0.5831554618618305</v>
+        <v>0.838610488219484</v>
       </c>
       <c r="AR9">
-        <v>2.083980118395606</v>
+        <v>2.053129172877732</v>
       </c>
       <c r="AS9">
-        <v>0.03991014076490834</v>
+        <v>0.03834883866385444</v>
       </c>
       <c r="AT9" t="b">
         <v>1</v>
@@ -1883,52 +1883,52 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C10" s="2">
         <v>46302</v>
       </c>
-      <c r="C10" s="2">
-        <v>46301</v>
-      </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.002177776906038563</v>
+        <v>0.006113735974351001</v>
       </c>
       <c r="H10">
-        <v>2.126878677633599</v>
+        <v>2.128307127059598</v>
       </c>
       <c r="I10">
-        <v>0.4522136443902205</v>
+        <v>0.4532851510562988</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>233</v>
       </c>
       <c r="M10">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N10">
-        <v>47.47164507601001</v>
+        <v>47.47320071264336</v>
       </c>
       <c r="O10">
-        <v>51.4219529625238</v>
+        <v>58.24422136333424</v>
       </c>
       <c r="P10">
-        <v>0.9303800585245253</v>
+        <v>0.888667934626775</v>
       </c>
       <c r="Q10">
-        <v>0.03128093560385624</v>
+        <v>0.05491442158964323</v>
       </c>
       <c r="R10" t="s">
         <v>61</v>
@@ -1937,10 +1937,10 @@
         <v>65</v>
       </c>
       <c r="T10">
-        <v>-0.6507469057837999</v>
+        <v>0.6728424278029234</v>
       </c>
       <c r="U10">
-        <v>0.6678042029930771</v>
+        <v>0.7027442126399238</v>
       </c>
       <c r="V10" t="s">
         <v>66</v>
@@ -1949,34 +1949,34 @@
         <v>66</v>
       </c>
       <c r="X10">
-        <v>0.9997836355595584</v>
+        <v>0.9998444424980971</v>
       </c>
       <c r="Y10">
-        <v>0.9998723815614684</v>
+        <v>0.999860480514433</v>
       </c>
       <c r="Z10">
-        <v>8.874600191000059E-05</v>
+        <v>1.60380163358731E-05</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>91.78558942711715</v>
+        <v>87.60390032828413</v>
       </c>
       <c r="AC10">
-        <v>-3.000000000000004</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="AD10">
-        <v>-0.03115937024934096</v>
+        <v>0.04180763977384645</v>
       </c>
       <c r="AE10">
-        <v>0.9995144289332017</v>
+        <v>0.999125678409148</v>
       </c>
       <c r="AF10">
-        <v>1.024557967224546</v>
+        <v>1.011655291152606</v>
       </c>
       <c r="AG10">
-        <v>1.024427214736584</v>
+        <v>1.011514145526813</v>
       </c>
       <c r="AH10" t="s">
         <v>68</v>
@@ -1991,28 +1991,28 @@
         <v>79</v>
       </c>
       <c r="AL10">
-        <v>-0.01557769686958205</v>
+        <v>0.02090090339672621</v>
       </c>
       <c r="AM10">
-        <v>0.4448547990031296</v>
+        <v>0.4489464051765425</v>
       </c>
       <c r="AN10">
-        <v>-0.03853955374076883</v>
+        <v>0.03983407559273991</v>
       </c>
       <c r="AO10">
-        <v>1.023611027881948</v>
+        <v>1.010713257934639</v>
       </c>
       <c r="AP10">
-        <v>0.02052277034608236</v>
+        <v>0.07047616432409684</v>
       </c>
       <c r="AQ10">
-        <v>0.2014498284857335</v>
+        <v>-0.08944521840588067</v>
       </c>
       <c r="AR10">
-        <v>0.08409136317548631</v>
+        <v>0.1074088415136309</v>
       </c>
       <c r="AS10">
-        <v>0.4296556374545773</v>
+        <v>0.4236470329044199</v>
       </c>
       <c r="AT10" t="b">
         <v>1</v>
@@ -2023,10 +2023,10 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C11" s="2">
         <v>46302</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46301</v>
       </c>
       <c r="D11" t="s">
         <v>56</v>
@@ -2035,16 +2035,16 @@
         <v>-1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.08818545360662332</v>
       </c>
       <c r="G11">
-        <v>1.599304465565033</v>
+        <v>1.730993707506369</v>
       </c>
       <c r="H11">
-        <v>2.144419437263232</v>
+        <v>2.137895602982097</v>
       </c>
       <c r="I11">
-        <v>0.4958535634912872</v>
+        <v>0.494035360138838</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -2056,19 +2056,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>421.9793121360855</v>
+        <v>500.9309440775959</v>
       </c>
       <c r="O11">
-        <v>6.952742301537844</v>
+        <v>8.29802367296301</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.599304465565033</v>
+        <v>1.730993707506369</v>
       </c>
       <c r="R11" t="s">
         <v>58</v>
@@ -2077,10 +2077,10 @@
         <v>62</v>
       </c>
       <c r="T11">
-        <v>-0.9369233410214868</v>
+        <v>-0.947146817769185</v>
       </c>
       <c r="U11">
-        <v>0.8214132020955007</v>
+        <v>0.8393497317922511</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
@@ -2089,34 +2089,34 @@
         <v>67</v>
       </c>
       <c r="X11">
-        <v>0.9934472995233304</v>
+        <v>0.9961507507434484</v>
       </c>
       <c r="Y11">
-        <v>0.9991907945433268</v>
+        <v>0.9996233830204979</v>
       </c>
       <c r="Z11">
-        <v>0.005743495019996381</v>
+        <v>0.003472632277049525</v>
       </c>
       <c r="AA11">
-        <v>0.2482464792281063</v>
+        <v>0.3116808528742547</v>
       </c>
       <c r="AB11">
-        <v>-148.6047692938305</v>
+        <v>-151.6205708619519</v>
       </c>
       <c r="AC11">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AD11">
-        <v>-0.853594163097612</v>
+        <v>-0.8798192791817795</v>
       </c>
       <c r="AE11">
-        <v>-0.5209385805694251</v>
+        <v>-0.4753083588367176</v>
       </c>
       <c r="AF11">
-        <v>1.538737355565149</v>
+        <v>1.582974126982653</v>
       </c>
       <c r="AG11">
-        <v>1.537492200900638</v>
+        <v>1.582377952048319</v>
       </c>
       <c r="AH11" t="s">
         <v>56</v>
@@ -2131,28 +2131,28 @@
         <v>76</v>
       </c>
       <c r="AL11">
-        <v>-0.5323168518364058</v>
+        <v>-0.5768037353207548</v>
       </c>
       <c r="AM11">
-        <v>0.7990491246692972</v>
+        <v>0.8197787197684544</v>
       </c>
       <c r="AN11">
-        <v>-1.255285529206324</v>
+        <v>-1.353656303502145</v>
       </c>
       <c r="AO11">
-        <v>-0.8723776306932588</v>
+        <v>-0.8088064505157689</v>
       </c>
       <c r="AP11">
-        <v>-1.811219957742462</v>
+        <v>-1.976335778246574</v>
       </c>
       <c r="AQ11">
-        <v>2.541659773996094</v>
+        <v>2.514447121742387</v>
       </c>
       <c r="AR11">
-        <v>1.564963027451948</v>
+        <v>1.740052641499567</v>
       </c>
       <c r="AS11">
-        <v>0.04263465463848008</v>
+        <v>0.04247612412069771</v>
       </c>
       <c r="AT11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,72 @@
   </si>
   <si>
     <t>UP</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
   </si>
 </sst>
 </file>
@@ -465,10 +615,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,19 +673,103 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C2" s="2">
         <v>46304</v>
       </c>
-      <c r="C2" s="2">
-        <v>46303</v>
-      </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -544,13 +778,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.457646960458371</v>
+        <v>1.409466085787301</v>
       </c>
       <c r="H2">
-        <v>1.122622988512002</v>
+        <v>1.130598053381138</v>
       </c>
       <c r="I2">
-        <v>0.2628014074075203</v>
+        <v>0.2636793178254253</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,51 +796,135 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N2">
-        <v>0.3921550719992011</v>
+        <v>0.4376966575181223</v>
       </c>
       <c r="O2">
-        <v>9.902370016032398</v>
+        <v>11.27337038276129</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.457646960458371</v>
-      </c>
-      <c r="R2" t="b">
+        <v>1.409466085787301</v>
+      </c>
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>-0.9936108756894084</v>
+      </c>
+      <c r="U2">
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2">
+        <v>0.9830789661578925</v>
+      </c>
+      <c r="Y2">
+        <v>0.9986663353030091</v>
+      </c>
+      <c r="Z2">
+        <v>0.0155873691451166</v>
+      </c>
+      <c r="AA2">
+        <v>0.8524073679593994</v>
+      </c>
+      <c r="AB2">
+        <v>170.5867373744173</v>
+      </c>
+      <c r="AC2">
+        <v>-39</v>
+      </c>
+      <c r="AD2">
+        <v>-0.9865343290569012</v>
+      </c>
+      <c r="AE2">
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AF2">
+        <v>1.174174108804757</v>
+      </c>
+      <c r="AG2">
+        <v>1.172608154247723</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL2">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AM2">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AN2">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AO2">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AP2">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AQ2">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AR2">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AS2">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C3" s="2">
         <v>46303</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.2490613807029616</v>
+        <v>0.2458364833958997</v>
       </c>
       <c r="G3">
-        <v>1.877789107100387</v>
+        <v>1.870085070879273</v>
       </c>
       <c r="H3">
-        <v>2.10927295930818</v>
+        <v>2.104184356589154</v>
       </c>
       <c r="I3">
-        <v>0.4612360043588652</v>
+        <v>0.4605288926548181</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -621,33 +939,117 @@
         <v>9</v>
       </c>
       <c r="N3">
-        <v>0.04480215492926085</v>
+        <v>0.04502509199272384</v>
       </c>
       <c r="O3">
-        <v>12.00555400535275</v>
+        <v>11.9781717415323</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.877789107100387</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.870085070879273</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>-0.9995938486339263</v>
+      </c>
+      <c r="U3">
+        <v>0.8861237918375293</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3">
+        <v>0.9726962613374817</v>
+      </c>
+      <c r="Y3">
+        <v>0.9977243497715103</v>
+      </c>
+      <c r="Z3">
+        <v>0.02502808843402859</v>
+      </c>
+      <c r="AA3">
+        <v>0.2911998906324461</v>
+      </c>
+      <c r="AB3">
+        <v>177.4683987736891</v>
+      </c>
+      <c r="AC3">
+        <v>-51</v>
+      </c>
+      <c r="AD3">
+        <v>-0.9990240115521648</v>
+      </c>
+      <c r="AE3">
+        <v>0.04417040120057805</v>
+      </c>
+      <c r="AF3">
+        <v>1.599602943090012</v>
+      </c>
+      <c r="AG3">
+        <v>1.595962806287076</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL3">
+        <v>-0.6435021214474587</v>
+      </c>
+      <c r="AM3">
+        <v>0.8519747578786325</v>
+      </c>
+      <c r="AN3">
+        <v>-1.551665785897048</v>
+      </c>
+      <c r="AO3">
+        <v>-0.11508525126393</v>
+      </c>
+      <c r="AP3">
+        <v>-1.756890816628371</v>
+      </c>
+      <c r="AQ3">
+        <v>4.266061616456902</v>
+      </c>
+      <c r="AR3">
+        <v>1.386310705155682</v>
+      </c>
+      <c r="AS3">
+        <v>0.03450630755689727</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C4" s="2">
         <v>46304</v>
       </c>
-      <c r="C4" s="2">
-        <v>46303</v>
-      </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -656,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.087842468067774</v>
+        <v>3.061238907503078</v>
       </c>
       <c r="H4">
-        <v>2.135764628541327</v>
+        <v>2.144948439746529</v>
       </c>
       <c r="I4">
-        <v>0.5059109680100777</v>
+        <v>0.508413981025873</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,36 +1076,120 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4">
-        <v>1.020717871363677</v>
+        <v>1.121462178765505</v>
       </c>
       <c r="O4">
-        <v>24.55335085754545</v>
+        <v>26.11956496875241</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.087842468067774</v>
-      </c>
-      <c r="R4" t="b">
+        <v>3.061238907503078</v>
+      </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4">
+        <v>-0.9746198314191159</v>
+      </c>
+      <c r="U4">
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>67</v>
+      </c>
+      <c r="X4">
+        <v>0.9988690732883357</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999069643803437</v>
+      </c>
+      <c r="Z4">
+        <v>0.001037891092007914</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>-161.6656935826206</v>
+      </c>
+      <c r="AC4">
+        <v>-10</v>
+      </c>
+      <c r="AD4">
+        <v>-0.9492373013588192</v>
+      </c>
+      <c r="AE4">
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AF4">
+        <v>2.525506296381413</v>
+      </c>
+      <c r="AG4">
+        <v>2.525271334338183</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL4">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AM4">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AN4">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AO4">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AP4">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AQ4">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AR4">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AS4">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C5" s="2">
         <v>46303</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -712,13 +1198,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.111706344378135</v>
+        <v>3.200473376265913</v>
       </c>
       <c r="H5">
-        <v>1.568245288453487</v>
+        <v>1.564615132617328</v>
       </c>
       <c r="I5">
-        <v>0.3751578685088984</v>
+        <v>0.3750525258138685</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,33 +1219,117 @@
         <v>14</v>
       </c>
       <c r="N5">
-        <v>0.1130254913636479</v>
+        <v>0.1140602187943121</v>
       </c>
       <c r="O5">
-        <v>21.13754847837387</v>
+        <v>21.80288180120646</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.111706344378135</v>
-      </c>
-      <c r="R5" t="b">
+        <v>3.200473376265913</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5">
+        <v>-0.9664969282168556</v>
+      </c>
+      <c r="U5">
+        <v>0.9848763988887411</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5">
+        <v>0.9979536316306246</v>
+      </c>
+      <c r="Y5">
+        <v>0.9998111247646242</v>
+      </c>
+      <c r="Z5">
+        <v>0.001857493133999633</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-158.9054107864368</v>
+      </c>
+      <c r="AC5">
+        <v>-13.99999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>-0.9329875273377329</v>
+      </c>
+      <c r="AE5">
+        <v>-0.3599087020790454</v>
+      </c>
+      <c r="AF5">
+        <v>2.724599040335355</v>
+      </c>
+      <c r="AG5">
+        <v>2.724084431050307</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL5">
+        <v>-0.9328113090989043</v>
+      </c>
+      <c r="AM5">
+        <v>0.9738630519562776</v>
+      </c>
+      <c r="AN5">
+        <v>-2.505823902354199</v>
+      </c>
+      <c r="AO5">
+        <v>-1.05543138205493</v>
+      </c>
+      <c r="AP5">
+        <v>-3.653403311976424</v>
+      </c>
+      <c r="AQ5">
+        <v>4.91948676051057</v>
+      </c>
+      <c r="AR5">
+        <v>3.194076018056693</v>
+      </c>
+      <c r="AS5">
+        <v>0.03978066608440503</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
+        <v>46305</v>
+      </c>
+      <c r="C6" s="2">
         <v>46304</v>
       </c>
-      <c r="C6" s="2">
-        <v>46303</v>
-      </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -768,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.529786498764099</v>
+        <v>1.504100250601936</v>
       </c>
       <c r="H6">
-        <v>1.045883784457304</v>
+        <v>1.05594420166307</v>
       </c>
       <c r="I6">
-        <v>0.274418015078282</v>
+        <v>0.2762929629565562</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,51 +1356,135 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6">
-        <v>1.162822722246057</v>
+        <v>1.240579442678092</v>
       </c>
       <c r="O6">
-        <v>18.28440288812819</v>
+        <v>19.36978586921844</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.529786498764099</v>
-      </c>
-      <c r="R6" t="b">
+        <v>1.504100250601936</v>
+      </c>
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>-0.9944317966357554</v>
+      </c>
+      <c r="U6">
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>67</v>
+      </c>
+      <c r="X6">
+        <v>0.9993821361914992</v>
+      </c>
+      <c r="Y6">
+        <v>0.999844833119245</v>
+      </c>
+      <c r="Z6">
+        <v>0.0004626969277458093</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>171.4408444705665</v>
+      </c>
+      <c r="AC6">
+        <v>-6.999999999999997</v>
+      </c>
+      <c r="AD6">
+        <v>-0.9888627291366784</v>
+      </c>
+      <c r="AE6">
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AF6">
+        <v>1.218537813310831</v>
+      </c>
+      <c r="AG6">
+        <v>1.218348736599258</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL6">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AM6">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AN6">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AO6">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AP6">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AQ6">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AR6">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AS6">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C7" s="2">
         <v>46303</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0.993999687655255</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1.954194566810592</v>
+        <v>1.966146195077531</v>
       </c>
       <c r="H7">
-        <v>1.567713223681541</v>
+        <v>1.567903323901254</v>
       </c>
       <c r="I7">
-        <v>0.3911756958425071</v>
+        <v>0.3905824146853478</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,39 +1493,123 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M7">
         <v>15</v>
       </c>
       <c r="N7">
-        <v>0.1214346310023462</v>
+        <v>0.1222345183552425</v>
       </c>
       <c r="O7">
-        <v>20.41653457467086</v>
+        <v>20.58810463153745</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.954194566810592</v>
-      </c>
-      <c r="R7" t="b">
+        <v>1.966146195077531</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>-0.9906297688353383</v>
+      </c>
+      <c r="U7">
+        <v>0.9957038738817446</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>67</v>
+      </c>
+      <c r="X7">
+        <v>0.9970801206088488</v>
+      </c>
+      <c r="Y7">
+        <v>0.9996819116233699</v>
+      </c>
+      <c r="Z7">
+        <v>0.002601791014521182</v>
+      </c>
+      <c r="AA7">
+        <v>0.7881904656904419</v>
+      </c>
+      <c r="AB7">
+        <v>168.4527775590838</v>
+      </c>
+      <c r="AC7">
+        <v>-16</v>
+      </c>
+      <c r="AD7">
+        <v>-0.9797600553410217</v>
+      </c>
+      <c r="AE7">
+        <v>0.2001755078878486</v>
+      </c>
+      <c r="AF7">
+        <v>1.637102448555761</v>
+      </c>
+      <c r="AG7">
+        <v>1.636581705295523</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL7">
+        <v>-0.8757201497780056</v>
+      </c>
+      <c r="AM7">
+        <v>0.946173802198252</v>
+      </c>
+      <c r="AN7">
+        <v>-1.609977239368594</v>
+      </c>
+      <c r="AO7">
+        <v>0.2691642661490886</v>
+      </c>
+      <c r="AP7">
+        <v>-1.922705979066893</v>
+      </c>
+      <c r="AQ7">
+        <v>3.652326886723105</v>
+      </c>
+      <c r="AR7">
+        <v>1.63064600777599</v>
+      </c>
+      <c r="AS7">
+        <v>0.03520651073548164</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C8" s="2">
         <v>46303</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +1618,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.522454260273243</v>
+        <v>2.608648260835368</v>
       </c>
       <c r="H8">
-        <v>1.567685157121949</v>
+        <v>1.55345123304648</v>
       </c>
       <c r="I8">
-        <v>0.4062326555580175</v>
+        <v>0.4034120950100881</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,36 +1636,120 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8">
-        <v>-0.1374444030486318</v>
+        <v>-0.1404944593194422</v>
       </c>
       <c r="O8">
-        <v>-34.21446733074064</v>
+        <v>-35.71676830347195</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.522454260273243</v>
-      </c>
-      <c r="R8" t="b">
+        <v>2.608648260835368</v>
+      </c>
+      <c r="R8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8">
+        <v>0.9947843442471344</v>
+      </c>
+      <c r="U8">
+        <v>0.9975588236658219</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>67</v>
+      </c>
+      <c r="X8">
+        <v>0.9993868592788797</v>
+      </c>
+      <c r="Y8">
+        <v>0.9996234750184455</v>
+      </c>
+      <c r="Z8">
+        <v>0.0002366157395657931</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-8.283736904266698</v>
+      </c>
+      <c r="AC8">
+        <v>-4.999999999999995</v>
+      </c>
+      <c r="AD8">
+        <v>0.9895667239298753</v>
+      </c>
+      <c r="AE8">
+        <v>-0.1440753236702729</v>
+      </c>
+      <c r="AF8">
+        <v>2.081229424910327</v>
+      </c>
+      <c r="AG8">
+        <v>2.080445790039502</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL8">
+        <v>0.9891941273374006</v>
+      </c>
+      <c r="AM8">
+        <v>0.9918665639464317</v>
+      </c>
+      <c r="AN8">
+        <v>2.061287736769802</v>
+      </c>
+      <c r="AO8">
+        <v>-0.278026538595509</v>
+      </c>
+      <c r="AP8">
+        <v>2.902286626427481</v>
+      </c>
+      <c r="AQ8">
+        <v>-4.208624520274346</v>
+      </c>
+      <c r="AR8">
+        <v>2.545408818367472</v>
+      </c>
+      <c r="AS8">
+        <v>0.03247779659324525</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C9" s="2">
         <v>46303</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.604464541811283</v>
+        <v>1.599741836940297</v>
       </c>
       <c r="H9">
-        <v>3.15690042390516</v>
+        <v>3.162592637757875</v>
       </c>
       <c r="I9">
-        <v>0.6664350846899324</v>
+        <v>0.6645293496200504</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,33 +1779,117 @@
         <v>61</v>
       </c>
       <c r="N9">
-        <v>0.9286909664120506</v>
+        <v>0.9292252731588642</v>
       </c>
       <c r="O9">
-        <v>89.70692744864142</v>
+        <v>90.12854249843625</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.604464541811283</v>
-      </c>
-      <c r="R9" t="b">
+        <v>1.599741836940297</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9">
+        <v>-0.9832340230473647</v>
+      </c>
+      <c r="U9">
+        <v>0.8423036380005806</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X9">
+        <v>0.9957545769418508</v>
+      </c>
+      <c r="Y9">
+        <v>0.9993933105170658</v>
+      </c>
+      <c r="Z9">
+        <v>0.003638733575215047</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>-161.9673021607393</v>
+      </c>
+      <c r="AC9">
+        <v>18</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9508800100850302</v>
+      </c>
+      <c r="AE9">
+        <v>-0.3095596976686286</v>
+      </c>
+      <c r="AF9">
+        <v>1.173349573022067</v>
+      </c>
+      <c r="AG9">
+        <v>1.172637714176309</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL9">
+        <v>-0.4751515605916896</v>
+      </c>
+      <c r="AM9">
+        <v>0.7781613949933719</v>
+      </c>
+      <c r="AN9">
+        <v>-1.119423828492007</v>
+      </c>
+      <c r="AO9">
+        <v>-0.3346260015955845</v>
+      </c>
+      <c r="AP9">
+        <v>-2.414739600526622</v>
+      </c>
+      <c r="AQ9">
+        <v>0.4690975117885404</v>
+      </c>
+      <c r="AR9">
+        <v>2.349218443534146</v>
+      </c>
+      <c r="AS9">
+        <v>0.04593511142073507</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C10" s="2">
         <v>46303</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -992,13 +1898,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.01458900230138204</v>
+        <v>0.02407460330786746</v>
       </c>
       <c r="H10">
-        <v>2.146018824821271</v>
+        <v>2.129599533683122</v>
       </c>
       <c r="I10">
-        <v>0.4601327315942376</v>
+        <v>0.4545067732229432</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1019,27 +1925,111 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0.8420764530212462</v>
+        <v>0.7898199770008263</v>
       </c>
       <c r="Q10">
-        <v>0.09238015850381559</v>
-      </c>
-      <c r="R10" t="b">
+        <v>0.1145427760656497</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>0.6928206902461822</v>
+      </c>
+      <c r="U10">
+        <v>0.7117406889278118</v>
+      </c>
+      <c r="V10" t="s">
+        <v>66</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9998689243285915</v>
+      </c>
+      <c r="Y10">
+        <v>0.9998855132681196</v>
+      </c>
+      <c r="Z10">
+        <v>1.658893952805052E-05</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>84.24150280635747</v>
+      </c>
+      <c r="AC10">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="AD10">
+        <v>0.1003356183271042</v>
+      </c>
+      <c r="AE10">
+        <v>0.9949536490183438</v>
+      </c>
+      <c r="AF10">
+        <v>0.9934418319390013</v>
+      </c>
+      <c r="AG10">
+        <v>0.9933280960303493</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL10">
+        <v>0.05016206561503538</v>
+      </c>
+      <c r="AM10">
+        <v>0.5048307433445822</v>
+      </c>
+      <c r="AN10">
+        <v>0.1020999449508141</v>
+      </c>
+      <c r="AO10">
+        <v>0.9880503871214641</v>
+      </c>
+      <c r="AP10">
+        <v>0.07027793773615976</v>
+      </c>
+      <c r="AQ10">
+        <v>-0.3980355034554053</v>
+      </c>
+      <c r="AR10">
+        <v>0.1188075714840639</v>
+      </c>
+      <c r="AS10">
+        <v>0.1681991453159395</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C11" s="2">
         <v>46303</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1048,13 +2038,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.450586121121411</v>
+        <v>1.463127748378913</v>
       </c>
       <c r="H11">
-        <v>2.132217841361726</v>
+        <v>2.131993086251547</v>
       </c>
       <c r="I11">
-        <v>0.4924008787700996</v>
+        <v>0.4922869000740082</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2059,102 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>575.4945875826924</v>
+        <v>580.6389529528534</v>
       </c>
       <c r="O11">
-        <v>8.750155278062145</v>
+        <v>8.835954218101302</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.450586121121411</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.463127748378913</v>
+      </c>
+      <c r="R11" t="s">
+        <v>59</v>
+      </c>
+      <c r="S11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T11">
+        <v>-0.9849837491747254</v>
+      </c>
+      <c r="U11">
+        <v>0.8430269307424129</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>67</v>
+      </c>
+      <c r="X11">
+        <v>0.9915760367782144</v>
+      </c>
+      <c r="Y11">
+        <v>0.9991369744551456</v>
+      </c>
+      <c r="Z11">
+        <v>0.007560937676931223</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>-162.9401487027914</v>
+      </c>
+      <c r="AC11">
+        <v>-28</v>
+      </c>
+      <c r="AD11">
+        <v>-0.9559988221363884</v>
+      </c>
+      <c r="AE11">
+        <v>-0.2933705030739082</v>
+      </c>
+      <c r="AF11">
+        <v>1.276457947176837</v>
+      </c>
+      <c r="AG11">
+        <v>1.275356331361491</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL11">
+        <v>-0.477586885366017</v>
+      </c>
+      <c r="AM11">
+        <v>0.7810759562582975</v>
+      </c>
+      <c r="AN11">
+        <v>-1.182397965058</v>
+      </c>
+      <c r="AO11">
+        <v>-0.4516021298893421</v>
+      </c>
+      <c r="AP11">
+        <v>-1.509037865407516</v>
+      </c>
+      <c r="AQ11">
+        <v>2.784771657094342</v>
+      </c>
+      <c r="AR11">
+        <v>1.25894103794398</v>
+      </c>
+      <c r="AS11">
+        <v>0.03614420961279985</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>UP</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +664,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46307</v>
@@ -535,7 +760,7 @@
         <v>46304</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -576,13 +801,97 @@
       <c r="Q2">
         <v>1.409466085787301</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>-0.9936108756894084</v>
+      </c>
+      <c r="U2">
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9830789661578925</v>
+      </c>
+      <c r="Y2">
+        <v>0.9986663353030091</v>
+      </c>
+      <c r="Z2">
+        <v>0.0155873691451166</v>
+      </c>
+      <c r="AA2">
+        <v>0.8524073679593994</v>
+      </c>
+      <c r="AB2">
+        <v>170.5867373744173</v>
+      </c>
+      <c r="AC2">
+        <v>-39</v>
+      </c>
+      <c r="AD2">
+        <v>-0.9865343290569012</v>
+      </c>
+      <c r="AE2">
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AF2">
+        <v>1.174174108804757</v>
+      </c>
+      <c r="AG2">
+        <v>1.172608154247723</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AM2">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AN2">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AO2">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AP2">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AQ2">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AR2">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AS2">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46307</v>
@@ -591,22 +900,22 @@
         <v>46304</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.2535097888689165</v>
+        <v>0.249996583801431</v>
       </c>
       <c r="G3">
-        <v>1.884873205538164</v>
+        <v>1.877381592236885</v>
       </c>
       <c r="H3">
-        <v>2.1124538994417</v>
+        <v>2.107849925553058</v>
       </c>
       <c r="I3">
-        <v>0.4616424580498004</v>
+        <v>0.4609303681136894</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -621,24 +930,108 @@
         <v>10</v>
       </c>
       <c r="N3">
-        <v>0.05054754016811804</v>
+        <v>0.05078727218478785</v>
       </c>
       <c r="O3">
-        <v>14.06610141827979</v>
+        <v>14.02686546827844</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.884873205538164</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.877381592236885</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>-0.992675505904978</v>
+      </c>
+      <c r="U3">
+        <v>0.8837936080072615</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9791746236644459</v>
+      </c>
+      <c r="Y3">
+        <v>0.998360571119227</v>
+      </c>
+      <c r="Z3">
+        <v>0.01918594745478119</v>
+      </c>
+      <c r="AA3">
+        <v>0.302875974097834</v>
+      </c>
+      <c r="AB3">
+        <v>169.2744964234522</v>
+      </c>
+      <c r="AC3">
+        <v>-44</v>
+      </c>
+      <c r="AD3">
+        <v>-0.9825300550219199</v>
+      </c>
+      <c r="AE3">
+        <v>0.1861039789435543</v>
+      </c>
+      <c r="AF3">
+        <v>1.611686083375807</v>
+      </c>
+      <c r="AG3">
+        <v>1.60904383866398</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>-0.6390080726695654</v>
+      </c>
+      <c r="AM3">
+        <v>0.8495928345362319</v>
+      </c>
+      <c r="AN3">
+        <v>-1.571999080587123</v>
+      </c>
+      <c r="AO3">
+        <v>0.1388823164316986</v>
+      </c>
+      <c r="AP3">
+        <v>-1.696045041873733</v>
+      </c>
+      <c r="AQ3">
+        <v>4.329319079501524</v>
+      </c>
+      <c r="AR3">
+        <v>1.334531895020916</v>
+      </c>
+      <c r="AS3">
+        <v>0.03445051121093546</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46307</v>
@@ -647,7 +1040,7 @@
         <v>46304</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -688,13 +1081,97 @@
       <c r="Q4">
         <v>3.061238907503078</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4">
+        <v>-0.9746198314191159</v>
+      </c>
+      <c r="U4">
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9988690732883357</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999069643803437</v>
+      </c>
+      <c r="Z4">
+        <v>0.001037891092007914</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>-161.6656935826206</v>
+      </c>
+      <c r="AC4">
+        <v>-10</v>
+      </c>
+      <c r="AD4">
+        <v>-0.9492373013588192</v>
+      </c>
+      <c r="AE4">
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AF4">
+        <v>2.525506296381413</v>
+      </c>
+      <c r="AG4">
+        <v>2.525271334338183</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AM4">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AN4">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AO4">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AP4">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AQ4">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AR4">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AS4">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46307</v>
@@ -703,7 +1180,7 @@
         <v>46304</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -712,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.304917062447236</v>
+        <v>3.395165354385198</v>
       </c>
       <c r="H5">
-        <v>1.573012539040566</v>
+        <v>1.569230158922102</v>
       </c>
       <c r="I5">
-        <v>0.3794752425920948</v>
+        <v>0.3797330850051044</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1210,108 @@
         <v>15</v>
       </c>
       <c r="N5">
-        <v>0.1262195097216988</v>
+        <v>0.1273382226672909</v>
       </c>
       <c r="O5">
-        <v>24.4984491349477</v>
+        <v>25.28343663795292</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.304917062447236</v>
-      </c>
-      <c r="R5" t="b">
+        <v>3.395165354385198</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5">
+        <v>-0.9766829969796371</v>
+      </c>
+      <c r="U5">
+        <v>0.989470875962453</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9983653756192612</v>
+      </c>
+      <c r="Y5">
+        <v>0.9998541092864648</v>
+      </c>
+      <c r="Z5">
+        <v>0.00148873366720359</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-162.4326069517044</v>
+      </c>
+      <c r="AC5">
+        <v>-12</v>
+      </c>
+      <c r="AD5">
+        <v>-0.9533625917287122</v>
+      </c>
+      <c r="AE5">
+        <v>-0.3018273822772097</v>
+      </c>
+      <c r="AF5">
+        <v>2.829434226887861</v>
+      </c>
+      <c r="AG5">
+        <v>2.829021438709599</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5">
+        <v>-0.9532235049799471</v>
+      </c>
+      <c r="AM5">
+        <v>0.980174823462981</v>
+      </c>
+      <c r="AN5">
+        <v>-2.669941367678096</v>
+      </c>
+      <c r="AO5">
+        <v>-0.9224748832514461</v>
+      </c>
+      <c r="AP5">
+        <v>-3.823959005266689</v>
+      </c>
+      <c r="AQ5">
+        <v>5.345176519911814</v>
+      </c>
+      <c r="AR5">
+        <v>3.333493334301382</v>
+      </c>
+      <c r="AS5">
+        <v>0.03855261537263439</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46307</v>
@@ -759,7 +1320,7 @@
         <v>46304</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -800,13 +1361,97 @@
       <c r="Q6">
         <v>1.504100250601936</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>-0.9944317966357554</v>
+      </c>
+      <c r="U6">
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9993821361914992</v>
+      </c>
+      <c r="Y6">
+        <v>0.999844833119245</v>
+      </c>
+      <c r="Z6">
+        <v>0.0004626969277458093</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>171.4408444705665</v>
+      </c>
+      <c r="AC6">
+        <v>-6.999999999999997</v>
+      </c>
+      <c r="AD6">
+        <v>-0.9888627291366784</v>
+      </c>
+      <c r="AE6">
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AF6">
+        <v>1.218537813310831</v>
+      </c>
+      <c r="AG6">
+        <v>1.218348736599258</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AM6">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AN6">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AO6">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AP6">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AQ6">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AR6">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AS6">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46307</v>
@@ -815,7 +1460,7 @@
         <v>46304</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -824,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.043382501726599</v>
+        <v>2.055793720422582</v>
       </c>
       <c r="H7">
-        <v>1.575628027371263</v>
+        <v>1.575800022808146</v>
       </c>
       <c r="I7">
-        <v>0.3929459169170794</v>
+        <v>0.3923889515279693</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1484,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M7">
         <v>16</v>
       </c>
       <c r="N7">
-        <v>0.1308318170298734</v>
+        <v>0.1316697360813863</v>
       </c>
       <c r="O7">
-        <v>23.73212540059888</v>
+        <v>23.93062839334551</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.043382501726599</v>
-      </c>
-      <c r="R7" t="b">
+        <v>2.055793720422582</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>-0.987873502193279</v>
+      </c>
+      <c r="U7">
+        <v>0.9944785455584353</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9985420346456884</v>
+      </c>
+      <c r="Y7">
+        <v>0.9997418782858389</v>
+      </c>
+      <c r="Z7">
+        <v>0.001199843640150577</v>
+      </c>
+      <c r="AA7">
+        <v>0.909492657910695</v>
+      </c>
+      <c r="AB7">
+        <v>167.1577415465099</v>
+      </c>
+      <c r="AC7">
+        <v>-11</v>
+      </c>
+      <c r="AD7">
+        <v>-0.9749856861839791</v>
+      </c>
+      <c r="AE7">
+        <v>0.2222676578730147</v>
+      </c>
+      <c r="AF7">
+        <v>1.728995607025598</v>
+      </c>
+      <c r="AG7">
+        <v>1.728549315715735</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>-0.9306237284556287</v>
+      </c>
+      <c r="AM7">
+        <v>0.969103005779609</v>
+      </c>
+      <c r="AN7">
+        <v>-1.692389824687916</v>
+      </c>
+      <c r="AO7">
+        <v>0.3413676704089463</v>
+      </c>
+      <c r="AP7">
+        <v>-1.971374147575125</v>
+      </c>
+      <c r="AQ7">
+        <v>3.946461092591154</v>
+      </c>
+      <c r="AR7">
+        <v>1.657084790809492</v>
+      </c>
+      <c r="AS7">
+        <v>0.03467259371844893</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46307</v>
@@ -871,7 +1600,7 @@
         <v>46304</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.417729807169544</v>
+        <v>2.495726305891031</v>
       </c>
       <c r="H8">
-        <v>1.578354981289127</v>
+        <v>1.564924548622461</v>
       </c>
       <c r="I8">
-        <v>0.4100123744543149</v>
+        <v>0.407489295099085</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,27 +1627,111 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8">
-        <v>-0.1451739593515612</v>
+        <v>-0.148324654945674</v>
       </c>
       <c r="O8">
-        <v>-37.64466439936768</v>
+        <v>-39.31361547215906</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.417729807169544</v>
-      </c>
-      <c r="R8" t="b">
+        <v>2.495726305891031</v>
+      </c>
+      <c r="R8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8">
+        <v>0.9893909414873521</v>
+      </c>
+      <c r="U8">
+        <v>0.9951752336444051</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9994426358848775</v>
+      </c>
+      <c r="Y8">
+        <v>0.9997972399003866</v>
+      </c>
+      <c r="Z8">
+        <v>0.0003546040155091301</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-11.82453471546573</v>
+      </c>
+      <c r="AC8">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="AD8">
+        <v>0.9787797314446991</v>
+      </c>
+      <c r="AE8">
+        <v>-0.2049151954176232</v>
+      </c>
+      <c r="AF8">
+        <v>2.040881481502186</v>
+      </c>
+      <c r="AG8">
+        <v>2.040467672169698</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>0.9785812739688518</v>
+      </c>
+      <c r="AM8">
+        <v>0.9889795393949125</v>
+      </c>
+      <c r="AN8">
+        <v>2.001710751052217</v>
+      </c>
+      <c r="AO8">
+        <v>-0.3920580590569097</v>
+      </c>
+      <c r="AP8">
+        <v>2.651466514246533</v>
+      </c>
+      <c r="AQ8">
+        <v>-4.514083647108024</v>
+      </c>
+      <c r="AR8">
+        <v>2.276727884740602</v>
+      </c>
+      <c r="AS8">
+        <v>0.03055609335754993</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46307</v>
@@ -927,7 +1740,7 @@
         <v>46304</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.773592640123581</v>
+        <v>1.772050083852844</v>
       </c>
       <c r="H9">
-        <v>3.159002446795351</v>
+        <v>3.164895175691488</v>
       </c>
       <c r="I9">
-        <v>0.6652035302125137</v>
+        <v>0.6632881899924825</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1770,108 @@
         <v>62</v>
       </c>
       <c r="N9">
-        <v>0.9406058386467335</v>
+        <v>0.9410497707757011</v>
       </c>
       <c r="O9">
-        <v>96.36649645850214</v>
+        <v>96.83360986997846</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.773592640123581</v>
-      </c>
-      <c r="R9" t="b">
+        <v>1.772050083852844</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9">
+        <v>-0.9774719878463359</v>
+      </c>
+      <c r="U9">
+        <v>0.8397681994766076</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9985522643523761</v>
+      </c>
+      <c r="Y9">
+        <v>0.9996232197830258</v>
+      </c>
+      <c r="Z9">
+        <v>0.001070955430649723</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>-159.0685841963589</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9340087311689881</v>
+      </c>
+      <c r="AE9">
+        <v>-0.357250178586515</v>
+      </c>
+      <c r="AF9">
+        <v>1.328781940802602</v>
+      </c>
+      <c r="AG9">
+        <v>1.328281282054635</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL9">
+        <v>-0.4668284075783012</v>
+      </c>
+      <c r="AM9">
+        <v>0.7730708670312956</v>
+      </c>
+      <c r="AN9">
+        <v>-1.245880694328789</v>
+      </c>
+      <c r="AO9">
+        <v>-0.4564362172145745</v>
+      </c>
+      <c r="AP9">
+        <v>-2.653729337996243</v>
+      </c>
+      <c r="AQ9">
+        <v>0.7435308808855795</v>
+      </c>
+      <c r="AR9">
+        <v>2.553571094002639</v>
+      </c>
+      <c r="AS9">
+        <v>0.04666586162306566</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46307</v>
@@ -983,7 +1880,7 @@
         <v>46304</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.05059162212856247</v>
+        <v>0.06615792576073938</v>
       </c>
       <c r="H10">
-        <v>2.147298618164212</v>
+        <v>2.130768853961548</v>
       </c>
       <c r="I10">
-        <v>0.4614954638355948</v>
+        <v>0.4558456962075934</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,24 +1910,108 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>-0.09132556336280957</v>
+        <v>-0.1049184608324582</v>
       </c>
       <c r="O10">
-        <v>-0.1247008570251954</v>
+        <v>-0.1432613334296702</v>
       </c>
       <c r="P10">
-        <v>0.7036459393545751</v>
+        <v>0.6571310145802066</v>
       </c>
       <c r="Q10">
-        <v>0.1707134432994769</v>
-      </c>
-      <c r="R10" t="b">
+        <v>0.192953952016799</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>0.7162025119611628</v>
+      </c>
+      <c r="U10">
+        <v>0.7222628639974663</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9998279877285189</v>
+      </c>
+      <c r="Y10">
+        <v>0.9998869344597723</v>
+      </c>
+      <c r="Z10">
+        <v>5.894673125339533E-05</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>80.28096206226725</v>
+      </c>
+      <c r="AC10">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD10">
+        <v>0.1688168945785773</v>
+      </c>
+      <c r="AE10">
+        <v>0.9856474299184499</v>
+      </c>
+      <c r="AF10">
+        <v>0.9968508542326273</v>
+      </c>
+      <c r="AG10">
+        <v>0.9967381447522671</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>0.08439890360259611</v>
+      </c>
+      <c r="AM10">
+        <v>0.5355619450914663</v>
+      </c>
+      <c r="AN10">
+        <v>0.1757691715172014</v>
+      </c>
+      <c r="AO10">
+        <v>0.9810580982504591</v>
+      </c>
+      <c r="AP10">
+        <v>0.1037209690977838</v>
+      </c>
+      <c r="AQ10">
+        <v>-0.641657935670563</v>
+      </c>
+      <c r="AR10">
+        <v>0.1500875380662124</v>
+      </c>
+      <c r="AS10">
+        <v>0.1002903356201814</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46307</v>
@@ -1039,7 +2020,7 @@
         <v>46304</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.444037059975954</v>
+        <v>1.453657243820792</v>
       </c>
       <c r="H11">
-        <v>2.126856063833116</v>
+        <v>2.126652713971526</v>
       </c>
       <c r="I11">
-        <v>0.4907204127433946</v>
+        <v>0.4906097142253848</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2050,102 @@
         <v>11</v>
       </c>
       <c r="N11">
-        <v>650.0727136135667</v>
+        <v>655.801719061159</v>
       </c>
       <c r="O11">
-        <v>10.78850144394449</v>
+        <v>10.89378089197991</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.444037059975954</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.453657243820792</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>-0.9987753755745803</v>
+      </c>
+      <c r="U11">
+        <v>0.8489103186503497</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9756859928972897</v>
+      </c>
+      <c r="Y11">
+        <v>0.9978455985671545</v>
+      </c>
+      <c r="Z11">
+        <v>0.02215960566986475</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>175.1425807481146</v>
+      </c>
+      <c r="AC11">
+        <v>-46.99999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>-0.9964085006983606</v>
+      </c>
+      <c r="AE11">
+        <v>0.08467644144651515</v>
+      </c>
+      <c r="AF11">
+        <v>1.23679653839303</v>
+      </c>
+      <c r="AG11">
+        <v>1.234131982158578</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>-0.4971309183983783</v>
+      </c>
+      <c r="AM11">
+        <v>0.7932020759331244</v>
+      </c>
+      <c r="AN11">
+        <v>-1.206425120164056</v>
+      </c>
+      <c r="AO11">
+        <v>-0.02690346497028458</v>
+      </c>
+      <c r="AP11">
+        <v>-1.36143194983145</v>
+      </c>
+      <c r="AQ11">
+        <v>3.199793938222641</v>
+      </c>
+      <c r="AR11">
+        <v>1.089023131623034</v>
+      </c>
+      <c r="AS11">
+        <v>0.03310955849925291</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>UP</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +664,94 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
         <v>46308</v>
@@ -535,7 +760,7 @@
         <v>46307</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -576,13 +801,97 @@
       <c r="Q2">
         <v>1.453416665520049</v>
       </c>
-      <c r="R2" t="b">
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>-0.9959638211245221</v>
+      </c>
+      <c r="U2">
+        <v>0.9979875156176221</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9935164668181142</v>
+      </c>
+      <c r="Y2">
+        <v>0.9992151844463486</v>
+      </c>
+      <c r="Z2">
+        <v>0.005698717628234373</v>
+      </c>
+      <c r="AA2">
+        <v>0.8752183312826824</v>
+      </c>
+      <c r="AB2">
+        <v>172.5542169613442</v>
+      </c>
+      <c r="AC2">
+        <v>-24</v>
+      </c>
+      <c r="AD2">
+        <v>-0.9915679297775538</v>
+      </c>
+      <c r="AE2">
+        <v>0.1295879648603839</v>
+      </c>
+      <c r="AF2">
+        <v>1.188489476828255</v>
+      </c>
+      <c r="AG2">
+        <v>1.18755673180149</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>-0.9289735338000383</v>
+      </c>
+      <c r="AM2">
+        <v>0.9670733777173066</v>
+      </c>
+      <c r="AN2">
+        <v>-1.177251493368894</v>
+      </c>
+      <c r="AO2">
+        <v>0.09126587126114025</v>
+      </c>
+      <c r="AP2">
+        <v>-1.484966144868667</v>
+      </c>
+      <c r="AQ2">
+        <v>2.679603106211793</v>
+      </c>
+      <c r="AR2">
+        <v>1.262755767512773</v>
+      </c>
+      <c r="AS2">
+        <v>0.03443988019145269</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
         <v>46308</v>
@@ -591,22 +900,22 @@
         <v>46307</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.2456298906748639</v>
+        <v>0.2415476484852667</v>
       </c>
       <c r="G3">
-        <v>1.880289322218486</v>
+        <v>1.872722056502411</v>
       </c>
       <c r="H3">
-        <v>2.115331892895837</v>
+        <v>2.111166392710875</v>
       </c>
       <c r="I3">
-        <v>0.4620090216199877</v>
+        <v>0.461292642165942</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -621,24 +930,108 @@
         <v>11</v>
       </c>
       <c r="N3">
-        <v>0.0561010913409366</v>
+        <v>0.05635854930365041</v>
       </c>
       <c r="O3">
-        <v>16.46400332822802</v>
+        <v>16.40885286994099</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.880289322218486</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.872722056502411</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>-0.9908040602135986</v>
+      </c>
+      <c r="U3">
+        <v>0.88181123092184</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9887132977728665</v>
+      </c>
+      <c r="Y3">
+        <v>0.9988690262117227</v>
+      </c>
+      <c r="Z3">
+        <v>0.01015572843885615</v>
+      </c>
+      <c r="AA3">
+        <v>0.3085495683883835</v>
+      </c>
+      <c r="AB3">
+        <v>168.015572570718</v>
+      </c>
+      <c r="AC3">
+        <v>-32.99999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>-0.9782040734703017</v>
+      </c>
+      <c r="AE3">
+        <v>0.2076458298307691</v>
+      </c>
+      <c r="AF3">
+        <v>1.619165703651004</v>
+      </c>
+      <c r="AG3">
+        <v>1.617334469681297</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>-0.6392904197165317</v>
+      </c>
+      <c r="AM3">
+        <v>0.8495361137341224</v>
+      </c>
+      <c r="AN3">
+        <v>-1.587004802603548</v>
+      </c>
+      <c r="AO3">
+        <v>0.2103964585847024</v>
+      </c>
+      <c r="AP3">
+        <v>-1.605093322667548</v>
+      </c>
+      <c r="AQ3">
+        <v>4.463323355156293</v>
+      </c>
+      <c r="AR3">
+        <v>1.2454008776845</v>
+      </c>
+      <c r="AS3">
+        <v>0.03492787439165116</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
         <v>46308</v>
@@ -647,7 +1040,7 @@
         <v>46307</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -688,13 +1081,97 @@
       <c r="Q4">
         <v>3.153280956122567</v>
       </c>
-      <c r="R4" t="b">
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4">
+        <v>-0.9812378977169776</v>
+      </c>
+      <c r="U4">
+        <v>0.99153940792491</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9991518981779877</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999294158090806</v>
+      </c>
+      <c r="Z4">
+        <v>0.0007775176310929055</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>-164.2540605542891</v>
+      </c>
+      <c r="AC4">
+        <v>-9</v>
+      </c>
+      <c r="AD4">
+        <v>-0.9624744710326638</v>
+      </c>
+      <c r="AE4">
+        <v>-0.2713722399406285</v>
+      </c>
+      <c r="AF4">
+        <v>2.550470524024249</v>
+      </c>
+      <c r="AG4">
+        <v>2.550290501125847</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4">
+        <v>-0.9624065355508453</v>
+      </c>
+      <c r="AM4">
+        <v>0.982841603090765</v>
+      </c>
+      <c r="AN4">
+        <v>-2.439417318172367</v>
+      </c>
+      <c r="AO4">
+        <v>-0.7369627437232636</v>
+      </c>
+      <c r="AP4">
+        <v>-3.727647648181441</v>
+      </c>
+      <c r="AQ4">
+        <v>4.310233809280708</v>
+      </c>
+      <c r="AR4">
+        <v>3.329366576306081</v>
+      </c>
+      <c r="AS4">
+        <v>0.03917355834808257</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>46308</v>
@@ -703,7 +1180,7 @@
         <v>46307</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -712,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.413009816926103</v>
+        <v>3.503562166633421</v>
       </c>
       <c r="H5">
-        <v>1.578001077019768</v>
+        <v>1.574578923579253</v>
       </c>
       <c r="I5">
-        <v>0.3842352387799441</v>
+        <v>0.3848847352289728</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -733,24 +1210,108 @@
         <v>16</v>
       </c>
       <c r="N5">
-        <v>0.139684348487454</v>
+        <v>0.1408658142194065</v>
       </c>
       <c r="O5">
-        <v>27.79195450613727</v>
+        <v>28.68748853111756</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.413009816926103</v>
-      </c>
-      <c r="R5" t="b">
+        <v>3.503562166633421</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5">
+        <v>-0.9808182008113934</v>
+      </c>
+      <c r="U5">
+        <v>0.9913440350160262</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9990716612711931</v>
+      </c>
+      <c r="Y5">
+        <v>0.9999033786035966</v>
+      </c>
+      <c r="Z5">
+        <v>0.0008317173324035032</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-164.0776871761149</v>
+      </c>
+      <c r="AC5">
+        <v>-9</v>
+      </c>
+      <c r="AD5">
+        <v>-0.961634548071471</v>
+      </c>
+      <c r="AE5">
+        <v>-0.2743337309835919</v>
+      </c>
+      <c r="AF5">
+        <v>2.901326940147094</v>
+      </c>
+      <c r="AG5">
+        <v>2.901046609886714</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5">
+        <v>-0.9615416335986066</v>
+      </c>
+      <c r="AM5">
+        <v>0.9828846523926651</v>
+      </c>
+      <c r="AN5">
+        <v>-2.771328789355583</v>
+      </c>
+      <c r="AO5">
+        <v>-0.8495958211085892</v>
+      </c>
+      <c r="AP5">
+        <v>-3.875838079564343</v>
+      </c>
+      <c r="AQ5">
+        <v>5.727641660372683</v>
+      </c>
+      <c r="AR5">
+        <v>3.359438477404302</v>
+      </c>
+      <c r="AS5">
+        <v>0.0371459636002333</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
         <v>46308</v>
@@ -759,7 +1320,7 @@
         <v>46307</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -800,13 +1361,97 @@
       <c r="Q6">
         <v>1.567658745515618</v>
       </c>
-      <c r="R6" t="b">
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>-0.9942412435910051</v>
+      </c>
+      <c r="U6">
+        <v>0.9973799764313247</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9997913531794099</v>
+      </c>
+      <c r="Y6">
+        <v>0.9998856672614895</v>
+      </c>
+      <c r="Z6">
+        <v>9.431408207960512E-05</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>171.2954337196475</v>
+      </c>
+      <c r="AC6">
+        <v>-3.000000000000004</v>
+      </c>
+      <c r="AD6">
+        <v>-0.9884818286923324</v>
+      </c>
+      <c r="AE6">
+        <v>0.1513395993950775</v>
+      </c>
+      <c r="AF6">
+        <v>1.261645766542345</v>
+      </c>
+      <c r="AG6">
+        <v>1.261501519126826</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>-0.9883688128578901</v>
+      </c>
+      <c r="AM6">
+        <v>0.9913550170259099</v>
+      </c>
+      <c r="AN6">
+        <v>-1.248061920355512</v>
+      </c>
+      <c r="AO6">
+        <v>0.1828314122820174</v>
+      </c>
+      <c r="AP6">
+        <v>-1.692333494607456</v>
+      </c>
+      <c r="AQ6">
+        <v>2.431053080095155</v>
+      </c>
+      <c r="AR6">
+        <v>1.495044984487824</v>
+      </c>
+      <c r="AS6">
+        <v>0.03433010082207424</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
         <v>46308</v>
@@ -815,7 +1460,7 @@
         <v>46307</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -824,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.041404400373534</v>
+        <v>2.053953351593582</v>
       </c>
       <c r="H7">
-        <v>1.583194362678269</v>
+        <v>1.583349977597354</v>
       </c>
       <c r="I7">
-        <v>0.3947359634454191</v>
+        <v>0.3942163825071034</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,30 +1484,114 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M7">
         <v>17</v>
       </c>
       <c r="N7">
-        <v>0.1398937950444324</v>
+        <v>0.1407671741011615</v>
       </c>
       <c r="O7">
-        <v>26.82527229998695</v>
+        <v>27.04831783442572</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.041404400373534</v>
-      </c>
-      <c r="R7" t="b">
+        <v>2.053953351593582</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>-0.9924318290308553</v>
+      </c>
+      <c r="U7">
+        <v>0.9965227220591538</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.999644003411595</v>
+      </c>
+      <c r="Y7">
+        <v>0.999713595981076</v>
+      </c>
+      <c r="Z7">
+        <v>6.95925694810251E-05</v>
+      </c>
+      <c r="AA7">
+        <v>0.90541915369835</v>
+      </c>
+      <c r="AB7">
+        <v>169.8551477164966</v>
+      </c>
+      <c r="AC7">
+        <v>-3.000000000000004</v>
+      </c>
+      <c r="AD7">
+        <v>-0.984365597748401</v>
+      </c>
+      <c r="AE7">
+        <v>0.1761373610834256</v>
+      </c>
+      <c r="AF7">
+        <v>1.732456585899435</v>
+      </c>
+      <c r="AG7">
+        <v>1.731960403370622</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>-0.9375459382447667</v>
+      </c>
+      <c r="AM7">
+        <v>0.9711683618887865</v>
+      </c>
+      <c r="AN7">
+        <v>-1.706882738923895</v>
+      </c>
+      <c r="AO7">
+        <v>0.2929514251590964</v>
+      </c>
+      <c r="AP7">
+        <v>-1.900573765259989</v>
+      </c>
+      <c r="AQ7">
+        <v>4.175049137250193</v>
+      </c>
+      <c r="AR7">
+        <v>1.571541160648133</v>
+      </c>
+      <c r="AS7">
+        <v>0.03416604512520295</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
         <v>46308</v>
@@ -871,7 +1600,7 @@
         <v>46307</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.353154044419519</v>
+        <v>2.421591097647279</v>
       </c>
       <c r="H8">
-        <v>1.58881945578636</v>
+        <v>1.575857287884828</v>
       </c>
       <c r="I8">
-        <v>0.4137011581698508</v>
+        <v>0.4114785846556477</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,27 +1627,111 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8">
-        <v>-0.1525840677584002</v>
+        <v>-0.1558123622597367</v>
       </c>
       <c r="O8">
-        <v>-38.73043148613205</v>
+        <v>-40.4070217956159</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.353154044419519</v>
-      </c>
-      <c r="R8" t="b">
+        <v>2.421591097647279</v>
+      </c>
+      <c r="R8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8">
+        <v>0.9849260705978544</v>
+      </c>
+      <c r="U8">
+        <v>0.9931832513933914</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9996480141988401</v>
+      </c>
+      <c r="Y8">
+        <v>0.9998660784974276</v>
+      </c>
+      <c r="Z8">
+        <v>0.0002180642985875059</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-14.10514811019718</v>
+      </c>
+      <c r="AC8">
+        <v>-4.999999999999995</v>
+      </c>
+      <c r="AD8">
+        <v>0.9698501222020469</v>
+      </c>
+      <c r="AE8">
+        <v>-0.2437021552319034</v>
+      </c>
+      <c r="AF8">
+        <v>1.98044824153044</v>
+      </c>
+      <c r="AG8">
+        <v>1.980183016926167</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>0.9697202384164115</v>
+      </c>
+      <c r="AM8">
+        <v>0.9861764905904619</v>
+      </c>
+      <c r="AN8">
+        <v>1.925079983758004</v>
+      </c>
+      <c r="AO8">
+        <v>-0.4620407768399371</v>
+      </c>
+      <c r="AP8">
+        <v>2.639692820720451</v>
+      </c>
+      <c r="AQ8">
+        <v>-3.923864906747239</v>
+      </c>
+      <c r="AR8">
+        <v>2.322718934029044</v>
+      </c>
+      <c r="AS8">
+        <v>0.03154449029501143</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
         <v>46308</v>
@@ -927,7 +1740,7 @@
         <v>46307</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1.929537385921455</v>
+        <v>1.930639250352429</v>
       </c>
       <c r="H9">
-        <v>3.160904277029335</v>
+        <v>3.166978424298089</v>
       </c>
       <c r="I9">
-        <v>0.6638938025442019</v>
+        <v>0.6619698092148621</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -957,24 +1770,108 @@
         <v>63</v>
       </c>
       <c r="N9">
-        <v>0.9530727304231129</v>
+        <v>0.9534432232811282</v>
       </c>
       <c r="O9">
-        <v>102.0888923177021</v>
+        <v>102.595635263333</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.929537385921455</v>
-      </c>
-      <c r="R9" t="b">
+        <v>1.930639250352429</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9">
+        <v>-0.9795423367062644</v>
+      </c>
+      <c r="U9">
+        <v>0.8407328846763799</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9996811855205955</v>
+      </c>
+      <c r="Y9">
+        <v>0.9997553326342432</v>
+      </c>
+      <c r="Z9">
+        <v>7.414711364772675E-05</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>-160.0647631826654</v>
+      </c>
+      <c r="AC9">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9400786162981162</v>
+      </c>
+      <c r="AE9">
+        <v>-0.3409577615761506</v>
+      </c>
+      <c r="AF9">
+        <v>1.44942270555179</v>
+      </c>
+      <c r="AG9">
+        <v>1.449068079116555</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL9">
+        <v>-0.4699243048697311</v>
+      </c>
+      <c r="AM9">
+        <v>0.7749428401187133</v>
+      </c>
+      <c r="AN9">
+        <v>-1.364347044964132</v>
+      </c>
+      <c r="AO9">
+        <v>-0.4878975160737243</v>
+      </c>
+      <c r="AP9">
+        <v>-2.8642164131662</v>
+      </c>
+      <c r="AQ9">
+        <v>1.012127000953872</v>
+      </c>
+      <c r="AR9">
+        <v>2.733038406265766</v>
+      </c>
+      <c r="AS9">
+        <v>0.04663407461804406</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
         <v>46308</v>
@@ -983,7 +1880,7 @@
         <v>46307</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.04448033581276137</v>
+        <v>0.05986987560256773</v>
       </c>
       <c r="H10">
-        <v>2.148456526426872</v>
+        <v>2.131826810403934</v>
       </c>
       <c r="I10">
-        <v>0.462973130567204</v>
+        <v>0.457287681591843</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1013,24 +1910,108 @@
         <v>2</v>
       </c>
       <c r="N10">
-        <v>-0.2136866606683508</v>
+        <v>-0.2398685411366574</v>
       </c>
       <c r="O10">
-        <v>-0.292007149766413</v>
+        <v>-0.327785219708462</v>
       </c>
       <c r="P10">
-        <v>0.7347229626032088</v>
+        <v>0.6822959902458934</v>
       </c>
       <c r="Q10">
-        <v>0.1676750322954994</v>
-      </c>
-      <c r="R10" t="b">
+        <v>0.188445451629349</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>0.738067466506483</v>
+      </c>
+      <c r="U10">
+        <v>0.7320751826858796</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9995532800554853</v>
+      </c>
+      <c r="Y10">
+        <v>0.9997792910318488</v>
+      </c>
+      <c r="Z10">
+        <v>0.0002260109763635443</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>76.53800372305302</v>
+      </c>
+      <c r="AC10">
+        <v>5.000000000000007</v>
+      </c>
+      <c r="AD10">
+        <v>0.2328003492134589</v>
+      </c>
+      <c r="AE10">
+        <v>0.9725245484850712</v>
+      </c>
+      <c r="AF10">
+        <v>0.7810471399871169</v>
+      </c>
+      <c r="AG10">
+        <v>0.780874755878773</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>0.1163744840442994</v>
+      </c>
+      <c r="AM10">
+        <v>0.5594596829097556</v>
+      </c>
+      <c r="AN10">
+        <v>0.1929176118059248</v>
+      </c>
+      <c r="AO10">
+        <v>0.7564869611555672</v>
+      </c>
+      <c r="AP10">
+        <v>0.008638114975920014</v>
+      </c>
+      <c r="AQ10">
+        <v>-0.9259049184787623</v>
+      </c>
+      <c r="AR10">
+        <v>0.1710167166703472</v>
+      </c>
+      <c r="AS10">
+        <v>0.06868782476952809</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
         <v>46308</v>
@@ -1039,7 +2020,7 @@
         <v>46307</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.408334433515801</v>
+        <v>1.415342175083034</v>
       </c>
       <c r="H11">
-        <v>2.122004931783422</v>
+        <v>2.121820948575316</v>
       </c>
       <c r="I11">
-        <v>0.4891160060861243</v>
+        <v>0.4890085367830694</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1069,18 +2050,102 @@
         <v>12</v>
       </c>
       <c r="N11">
-        <v>720.5803363798243</v>
+        <v>726.7391320447628</v>
       </c>
       <c r="O11">
-        <v>12.32641717138314</v>
+        <v>12.44378272267441</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.408334433515801</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.415342175083034</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>-0.9895171659088532</v>
+      </c>
+      <c r="U11">
+        <v>0.8448780551072674</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9800683771628391</v>
+      </c>
+      <c r="Y11">
+        <v>0.9983813217931343</v>
+      </c>
+      <c r="Z11">
+        <v>0.0183129446302952</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>165.7585179963324</v>
+      </c>
+      <c r="AC11">
+        <v>-43</v>
+      </c>
+      <c r="AD11">
+        <v>-0.9692674938874155</v>
+      </c>
+      <c r="AE11">
+        <v>0.2460091975784825</v>
+      </c>
+      <c r="AF11">
+        <v>1.224296263567554</v>
+      </c>
+      <c r="AG11">
+        <v>1.22231452188697</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>-0.4838492808592183</v>
+      </c>
+      <c r="AM11">
+        <v>0.7851395534657122</v>
+      </c>
+      <c r="AN11">
+        <v>-1.185725123855359</v>
+      </c>
+      <c r="AO11">
+        <v>0.1838522971462773</v>
+      </c>
+      <c r="AP11">
+        <v>-1.271948999062554</v>
+      </c>
+      <c r="AQ11">
+        <v>3.119219713132203</v>
+      </c>
+      <c r="AR11">
+        <v>1.020691304471279</v>
+      </c>
+      <c r="AS11">
+        <v>0.03382771552073009</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,90 @@
     <t>TerrainBundleSep</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedRawCoherence</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedSteeringGain</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>PhasedAmplitude</t>
+  </si>
+  <si>
+    <t>PhasedPower</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>FilterEnabled</t>
   </si>
   <si>
@@ -104,6 +188,63 @@
   </si>
   <si>
     <t>UP</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
   </si>
 </sst>
 </file>
@@ -465,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,19 +664,103 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C2" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>-1</v>
@@ -544,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.514216501539898</v>
+        <v>1.409466085787301</v>
       </c>
       <c r="H2">
-        <v>1.147025418109048</v>
+        <v>1.130598053381138</v>
       </c>
       <c r="I2">
-        <v>0.26567842693308</v>
+        <v>0.2636793178254253</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,51 +787,135 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N2">
-        <v>0.5268155130543062</v>
+        <v>0.4376966575181223</v>
       </c>
       <c r="O2">
-        <v>15.15704312116792</v>
+        <v>11.27337038276129</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.514216501539898</v>
-      </c>
-      <c r="R2" t="b">
+        <v>1.409466085787301</v>
+      </c>
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T2">
+        <v>-0.9936108756894084</v>
+      </c>
+      <c r="U2">
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2">
+        <v>0.9830789661578925</v>
+      </c>
+      <c r="Y2">
+        <v>0.9986663353030091</v>
+      </c>
+      <c r="Z2">
+        <v>0.0155873691451166</v>
+      </c>
+      <c r="AA2">
+        <v>0.8524073679593994</v>
+      </c>
+      <c r="AB2">
+        <v>170.5867373744173</v>
+      </c>
+      <c r="AC2">
+        <v>-39</v>
+      </c>
+      <c r="AD2">
+        <v>-0.9865343290569012</v>
+      </c>
+      <c r="AE2">
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AF2">
+        <v>1.174174108804757</v>
+      </c>
+      <c r="AG2">
+        <v>1.172608154247723</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AM2">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AN2">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AO2">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AP2">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AQ2">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AR2">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AS2">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AT2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.01556700568526159</v>
+        <v>0.249996583801431</v>
       </c>
       <c r="G3">
-        <v>1.67003601429171</v>
+        <v>1.877381592236885</v>
       </c>
       <c r="H3">
-        <v>2.117935791735294</v>
+        <v>2.107849925553058</v>
       </c>
       <c r="I3">
-        <v>0.4622928069517305</v>
+        <v>0.4609303681136894</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,36 +927,120 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N3">
-        <v>0.0612319205246435</v>
+        <v>0.05078727218478785</v>
       </c>
       <c r="O3">
-        <v>18.64593555943476</v>
+        <v>14.02686546827844</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.67003601429171</v>
-      </c>
-      <c r="R3" t="b">
+        <v>1.877381592236885</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3">
+        <v>-0.992675505904978</v>
+      </c>
+      <c r="U3">
+        <v>0.8837936080072615</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3">
+        <v>0.9791746236644459</v>
+      </c>
+      <c r="Y3">
+        <v>0.998360571119227</v>
+      </c>
+      <c r="Z3">
+        <v>0.01918594745478119</v>
+      </c>
+      <c r="AA3">
+        <v>0.302875974097834</v>
+      </c>
+      <c r="AB3">
+        <v>169.2744964234522</v>
+      </c>
+      <c r="AC3">
+        <v>-44</v>
+      </c>
+      <c r="AD3">
+        <v>-0.9825300550219199</v>
+      </c>
+      <c r="AE3">
+        <v>0.1861039789435543</v>
+      </c>
+      <c r="AF3">
+        <v>1.611686083375807</v>
+      </c>
+      <c r="AG3">
+        <v>1.60904383866398</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3">
+        <v>-0.6390080726695654</v>
+      </c>
+      <c r="AM3">
+        <v>0.8495928345362319</v>
+      </c>
+      <c r="AN3">
+        <v>-1.571999080587123</v>
+      </c>
+      <c r="AO3">
+        <v>0.1388823164316986</v>
+      </c>
+      <c r="AP3">
+        <v>-1.696045041873733</v>
+      </c>
+      <c r="AQ3">
+        <v>4.329319079501524</v>
+      </c>
+      <c r="AR3">
+        <v>1.334531895020916</v>
+      </c>
+      <c r="AS3">
+        <v>0.03445051121093546</v>
+      </c>
+      <c r="AT3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C4" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>-1</v>
@@ -656,13 +1049,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.12955570067431</v>
+        <v>3.061238907503078</v>
       </c>
       <c r="H4">
-        <v>2.1677143616516</v>
+        <v>2.144948439746529</v>
       </c>
       <c r="I4">
-        <v>0.5139469429628405</v>
+        <v>0.508413981025873</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,36 +1067,120 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N4">
-        <v>1.332415571710854</v>
+        <v>1.121462178765505</v>
       </c>
       <c r="O4">
-        <v>30.78187789431012</v>
+        <v>26.11956496875241</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.12955570067431</v>
-      </c>
-      <c r="R4" t="b">
+        <v>3.061238907503078</v>
+      </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4">
+        <v>-0.9746198314191159</v>
+      </c>
+      <c r="U4">
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4">
+        <v>0.9988690732883357</v>
+      </c>
+      <c r="Y4">
+        <v>0.9999069643803437</v>
+      </c>
+      <c r="Z4">
+        <v>0.001037891092007914</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>-161.6656935826206</v>
+      </c>
+      <c r="AC4">
+        <v>-10</v>
+      </c>
+      <c r="AD4">
+        <v>-0.9492373013588192</v>
+      </c>
+      <c r="AE4">
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AF4">
+        <v>2.525506296381413</v>
+      </c>
+      <c r="AG4">
+        <v>2.525271334338183</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AM4">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AN4">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AO4">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AP4">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AQ4">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AR4">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AS4">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AT4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C5" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -712,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.483974962867336</v>
+        <v>3.395165354385198</v>
       </c>
       <c r="H5">
-        <v>1.583387909078435</v>
+        <v>1.569230158922102</v>
       </c>
       <c r="I5">
-        <v>0.3894197385442892</v>
+        <v>0.3797330850051044</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,36 +1207,120 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N5">
-        <v>0.1531883710612005</v>
+        <v>0.1273382226672909</v>
       </c>
       <c r="O5">
-        <v>31.6318170332862</v>
+        <v>25.28343663795292</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.483974962867336</v>
-      </c>
-      <c r="R5" t="b">
+        <v>3.395165354385198</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5">
+        <v>-0.9766829969796371</v>
+      </c>
+      <c r="U5">
+        <v>0.989470875962453</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5">
+        <v>0.9983653756192612</v>
+      </c>
+      <c r="Y5">
+        <v>0.9998541092864648</v>
+      </c>
+      <c r="Z5">
+        <v>0.00148873366720359</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>-162.4326069517044</v>
+      </c>
+      <c r="AC5">
+        <v>-12</v>
+      </c>
+      <c r="AD5">
+        <v>-0.9533625917287122</v>
+      </c>
+      <c r="AE5">
+        <v>-0.3018273822772097</v>
+      </c>
+      <c r="AF5">
+        <v>2.829434226887861</v>
+      </c>
+      <c r="AG5">
+        <v>2.829021438709599</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5">
+        <v>-0.9532235049799471</v>
+      </c>
+      <c r="AM5">
+        <v>0.980174823462981</v>
+      </c>
+      <c r="AN5">
+        <v>-2.669941367678096</v>
+      </c>
+      <c r="AO5">
+        <v>-0.9224748832514461</v>
+      </c>
+      <c r="AP5">
+        <v>-3.823959005266689</v>
+      </c>
+      <c r="AQ5">
+        <v>5.345176519911814</v>
+      </c>
+      <c r="AR5">
+        <v>3.333493334301382</v>
+      </c>
+      <c r="AS5">
+        <v>0.03855261537263439</v>
+      </c>
+      <c r="AT5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C6" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -768,13 +1329,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.607245778193405</v>
+        <v>1.504100250601936</v>
       </c>
       <c r="H6">
-        <v>1.076848804313786</v>
+        <v>1.05594420166307</v>
       </c>
       <c r="I6">
-        <v>0.2801407766806749</v>
+        <v>0.2762929629565562</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,51 +1347,135 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N6">
-        <v>1.393965854761777</v>
+        <v>1.240579442678092</v>
       </c>
       <c r="O6">
-        <v>24.45829976647117</v>
+        <v>19.36978586921844</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.607245778193405</v>
-      </c>
-      <c r="R6" t="b">
+        <v>1.504100250601936</v>
+      </c>
+      <c r="R6" t="s">
+        <v>58</v>
+      </c>
+      <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6">
+        <v>-0.9944317966357554</v>
+      </c>
+      <c r="U6">
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6">
+        <v>0.9993821361914992</v>
+      </c>
+      <c r="Y6">
+        <v>0.999844833119245</v>
+      </c>
+      <c r="Z6">
+        <v>0.0004626969277458093</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>171.4408444705665</v>
+      </c>
+      <c r="AC6">
+        <v>-6.999999999999997</v>
+      </c>
+      <c r="AD6">
+        <v>-0.9888627291366784</v>
+      </c>
+      <c r="AE6">
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AF6">
+        <v>1.218537813310831</v>
+      </c>
+      <c r="AG6">
+        <v>1.218348736599258</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AM6">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AN6">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AO6">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AP6">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AQ6">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AR6">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AS6">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AT6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C7" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E7">
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0.9423515466031241</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1.942504454543852</v>
+        <v>2.055793720422582</v>
       </c>
       <c r="H7">
-        <v>1.591707850696433</v>
+        <v>1.575800022808146</v>
       </c>
       <c r="I7">
-        <v>0.3965133687688358</v>
+        <v>0.3923889515279693</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -839,39 +1484,123 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N7">
-        <v>0.1484068586027434</v>
+        <v>0.1316697360813863</v>
       </c>
       <c r="O7">
-        <v>29.78989204155713</v>
+        <v>23.93062839334551</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.942504454543852</v>
-      </c>
-      <c r="R7" t="b">
+        <v>2.055793720422582</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7">
+        <v>-0.987873502193279</v>
+      </c>
+      <c r="U7">
+        <v>0.9944785455584353</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7">
+        <v>0.9985420346456884</v>
+      </c>
+      <c r="Y7">
+        <v>0.9997418782858389</v>
+      </c>
+      <c r="Z7">
+        <v>0.001199843640150577</v>
+      </c>
+      <c r="AA7">
+        <v>0.909492657910695</v>
+      </c>
+      <c r="AB7">
+        <v>167.1577415465099</v>
+      </c>
+      <c r="AC7">
+        <v>-11</v>
+      </c>
+      <c r="AD7">
+        <v>-0.9749856861839791</v>
+      </c>
+      <c r="AE7">
+        <v>0.2222676578730147</v>
+      </c>
+      <c r="AF7">
+        <v>1.728995607025598</v>
+      </c>
+      <c r="AG7">
+        <v>1.728549315715735</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7">
+        <v>-0.9306237284556287</v>
+      </c>
+      <c r="AM7">
+        <v>0.969103005779609</v>
+      </c>
+      <c r="AN7">
+        <v>-1.692389824687916</v>
+      </c>
+      <c r="AO7">
+        <v>0.3413676704089463</v>
+      </c>
+      <c r="AP7">
+        <v>-1.971374147575125</v>
+      </c>
+      <c r="AQ7">
+        <v>3.946461092591154</v>
+      </c>
+      <c r="AR7">
+        <v>1.657084790809492</v>
+      </c>
+      <c r="AS7">
+        <v>0.03467259371844893</v>
+      </c>
+      <c r="AT7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C8" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -880,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2.525458690587854</v>
+        <v>2.495726305891031</v>
       </c>
       <c r="H8">
-        <v>1.599210470618046</v>
+        <v>1.564924548622461</v>
       </c>
       <c r="I8">
-        <v>0.417379508035403</v>
+        <v>0.407489295099085</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,36 +1627,120 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8">
-        <v>-0.1599273695328046</v>
+        <v>-0.148324654945674</v>
       </c>
       <c r="O8">
-        <v>-43.30303014136485</v>
+        <v>-39.31361547215906</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.525458690587854</v>
-      </c>
-      <c r="R8" t="b">
+        <v>2.495726305891031</v>
+      </c>
+      <c r="R8" t="s">
+        <v>60</v>
+      </c>
+      <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8">
+        <v>0.9893909414873521</v>
+      </c>
+      <c r="U8">
+        <v>0.9951752336444051</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8">
+        <v>0.9994426358848775</v>
+      </c>
+      <c r="Y8">
+        <v>0.9997972399003866</v>
+      </c>
+      <c r="Z8">
+        <v>0.0003546040155091301</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>-11.82453471546573</v>
+      </c>
+      <c r="AC8">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="AD8">
+        <v>0.9787797314446991</v>
+      </c>
+      <c r="AE8">
+        <v>-0.2049151954176232</v>
+      </c>
+      <c r="AF8">
+        <v>2.040881481502186</v>
+      </c>
+      <c r="AG8">
+        <v>2.040467672169698</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>0.9785812739688518</v>
+      </c>
+      <c r="AM8">
+        <v>0.9889795393949125</v>
+      </c>
+      <c r="AN8">
+        <v>2.001710751052217</v>
+      </c>
+      <c r="AO8">
+        <v>-0.3920580590569097</v>
+      </c>
+      <c r="AP8">
+        <v>2.651466514246533</v>
+      </c>
+      <c r="AQ8">
+        <v>-4.514083647108024</v>
+      </c>
+      <c r="AR8">
+        <v>2.276727884740602</v>
+      </c>
+      <c r="AS8">
+        <v>0.03055609335754993</v>
+      </c>
+      <c r="AT8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C9" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -936,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2.070892633006796</v>
+        <v>1.772050083852844</v>
       </c>
       <c r="H9">
-        <v>3.162624980574367</v>
+        <v>3.164895175691488</v>
       </c>
       <c r="I9">
-        <v>0.6625138839308368</v>
+        <v>0.6632881899924825</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,36 +1767,120 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N9">
-        <v>0.9658418384582321</v>
+        <v>0.9410497707757011</v>
       </c>
       <c r="O9">
-        <v>111.9028902090909</v>
+        <v>96.83360986997846</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.070892633006796</v>
-      </c>
-      <c r="R9" t="b">
+        <v>1.772050083852844</v>
+      </c>
+      <c r="R9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9">
+        <v>-0.9774719878463359</v>
+      </c>
+      <c r="U9">
+        <v>0.8397681994766076</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9">
+        <v>0.9985522643523761</v>
+      </c>
+      <c r="Y9">
+        <v>0.9996232197830258</v>
+      </c>
+      <c r="Z9">
+        <v>0.001070955430649723</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>-159.0685841963589</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>-0.9340087311689881</v>
+      </c>
+      <c r="AE9">
+        <v>-0.357250178586515</v>
+      </c>
+      <c r="AF9">
+        <v>1.328781940802602</v>
+      </c>
+      <c r="AG9">
+        <v>1.328281282054635</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL9">
+        <v>-0.4668284075783012</v>
+      </c>
+      <c r="AM9">
+        <v>0.7730708670312956</v>
+      </c>
+      <c r="AN9">
+        <v>-1.245880694328789</v>
+      </c>
+      <c r="AO9">
+        <v>-0.4564362172145745</v>
+      </c>
+      <c r="AP9">
+        <v>-2.653729337996243</v>
+      </c>
+      <c r="AQ9">
+        <v>0.7435308808855795</v>
+      </c>
+      <c r="AR9">
+        <v>2.553571094002639</v>
+      </c>
+      <c r="AS9">
+        <v>0.04666586162306566</v>
+      </c>
+      <c r="AT9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:46">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C10" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -992,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.1280705824382753</v>
+        <v>0.06615792576073938</v>
       </c>
       <c r="H10">
-        <v>2.149504157712137</v>
+        <v>2.130768853961548</v>
       </c>
       <c r="I10">
-        <v>0.4644989592491778</v>
+        <v>0.4558456962075934</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1010,36 +1907,120 @@
         <v>234</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>-0.3666473517760015</v>
+        <v>-0.1049184608324582</v>
       </c>
       <c r="O10">
-        <v>-0.5371279155406274</v>
+        <v>-0.1432613334296702</v>
       </c>
       <c r="P10">
-        <v>0.5263770085183455</v>
+        <v>0.6571310145802066</v>
       </c>
       <c r="Q10">
-        <v>0.2704061769417629</v>
-      </c>
-      <c r="R10" t="b">
+        <v>0.192953952016799</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10">
+        <v>0.7162025119611628</v>
+      </c>
+      <c r="U10">
+        <v>0.7222628639974663</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10">
+        <v>0.9998279877285189</v>
+      </c>
+      <c r="Y10">
+        <v>0.9998869344597723</v>
+      </c>
+      <c r="Z10">
+        <v>5.894673125339533E-05</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>80.28096206226725</v>
+      </c>
+      <c r="AC10">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AD10">
+        <v>0.1688168945785773</v>
+      </c>
+      <c r="AE10">
+        <v>0.9856474299184499</v>
+      </c>
+      <c r="AF10">
+        <v>0.9968508542326273</v>
+      </c>
+      <c r="AG10">
+        <v>0.9967381447522671</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL10">
+        <v>0.08439890360259611</v>
+      </c>
+      <c r="AM10">
+        <v>0.5355619450914663</v>
+      </c>
+      <c r="AN10">
+        <v>0.1757691715172014</v>
+      </c>
+      <c r="AO10">
+        <v>0.9810580982504591</v>
+      </c>
+      <c r="AP10">
+        <v>0.1037209690977838</v>
+      </c>
+      <c r="AQ10">
+        <v>-0.641657935670563</v>
+      </c>
+      <c r="AR10">
+        <v>0.1500875380662124</v>
+      </c>
+      <c r="AS10">
+        <v>0.1002903356201814</v>
+      </c>
+      <c r="AT10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:46">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C11" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1048,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.523816910000768</v>
+        <v>1.453657243820792</v>
       </c>
       <c r="H11">
-        <v>2.117615812309888</v>
+        <v>2.126652713971526</v>
       </c>
       <c r="I11">
-        <v>0.4876052935746903</v>
+        <v>0.4906097142253848</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,21 +2047,105 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N11">
-        <v>790.6598420775537</v>
+        <v>655.801719061159</v>
       </c>
       <c r="O11">
-        <v>13.82022209900271</v>
+        <v>10.89378089197991</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.523816910000768</v>
-      </c>
-      <c r="R11" t="b">
+        <v>1.453657243820792</v>
+      </c>
+      <c r="R11" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T11">
+        <v>-0.9987753755745803</v>
+      </c>
+      <c r="U11">
+        <v>0.8489103186503497</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11">
+        <v>0.9756859928972897</v>
+      </c>
+      <c r="Y11">
+        <v>0.9978455985671545</v>
+      </c>
+      <c r="Z11">
+        <v>0.02215960566986475</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>175.1425807481146</v>
+      </c>
+      <c r="AC11">
+        <v>-46.99999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>-0.9964085006983606</v>
+      </c>
+      <c r="AE11">
+        <v>0.08467644144651515</v>
+      </c>
+      <c r="AF11">
+        <v>1.23679653839303</v>
+      </c>
+      <c r="AG11">
+        <v>1.234131982158578</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11">
+        <v>-0.4971309183983783</v>
+      </c>
+      <c r="AM11">
+        <v>0.7932020759331244</v>
+      </c>
+      <c r="AN11">
+        <v>-1.206425120164056</v>
+      </c>
+      <c r="AO11">
+        <v>-0.02690346497028458</v>
+      </c>
+      <c r="AP11">
+        <v>-1.36143194983145</v>
+      </c>
+      <c r="AQ11">
+        <v>3.199793938222641</v>
+      </c>
+      <c r="AR11">
+        <v>1.089023131623034</v>
+      </c>
+      <c r="AS11">
+        <v>0.03310955849925291</v>
+      </c>
+      <c r="AT11" t="b">
         <v>1</v>
       </c>
     </row>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -529,10 +529,10 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C2" s="2">
         <v>46310</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46309</v>
       </c>
       <c r="D2" t="s">
         <v>28</v>
@@ -544,13 +544,13 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1.452442312096944</v>
+        <v>1.557021285332745</v>
       </c>
       <c r="H2">
-        <v>1.155441610781525</v>
+        <v>1.163512345201798</v>
       </c>
       <c r="I2">
-        <v>0.2667665348982067</v>
+        <v>0.2679150119779531</v>
       </c>
       <c r="J2">
         <v>6</v>
@@ -562,19 +562,19 @@
         <v>150</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2">
-        <v>0.5693508897195784</v>
+        <v>0.6131929523126987</v>
       </c>
       <c r="O2">
-        <v>16.24561796815269</v>
+        <v>16.50681895202144</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.452442312096944</v>
+        <v>1.557021285332745</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
@@ -585,10 +585,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C3" s="2">
         <v>46310</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46309</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -597,16 +597,16 @@
         <v>-1</v>
       </c>
       <c r="F3">
-        <v>0.1697557872680127</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1.814834491850261</v>
+        <v>1.650044990640423</v>
       </c>
       <c r="H3">
-        <v>2.120291700209089</v>
+        <v>2.122423236447284</v>
       </c>
       <c r="I3">
-        <v>0.4624717051540346</v>
+        <v>0.4624528739968619</v>
       </c>
       <c r="J3">
         <v>6</v>
@@ -618,19 +618,19 @@
         <v>226</v>
       </c>
       <c r="M3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N3">
-        <v>0.0664302308191532</v>
+        <v>0.07193470067628338</v>
       </c>
       <c r="O3">
-        <v>17.64415161199298</v>
+        <v>17.98206962713997</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>1.814834491850261</v>
+        <v>1.650044990640423</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C4" s="2">
         <v>46310</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46309</v>
       </c>
       <c r="D4" t="s">
         <v>28</v>
@@ -656,13 +656,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3.010903238989355</v>
+        <v>2.750920362893084</v>
       </c>
       <c r="H4">
-        <v>2.180383677004657</v>
+        <v>2.194229574565664</v>
       </c>
       <c r="I4">
-        <v>0.516865018771157</v>
+        <v>0.5197484130400072</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -674,19 +674,19 @@
         <v>147</v>
       </c>
       <c r="M4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4">
-        <v>1.439194708135059</v>
+        <v>1.544512680448004</v>
       </c>
       <c r="O4">
-        <v>31.58602588789904</v>
+        <v>32.78722900117062</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.010903238989355</v>
+        <v>2.750920362893084</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="B5" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C5" s="2">
         <v>46310</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46309</v>
       </c>
       <c r="D5" t="s">
         <v>28</v>
@@ -712,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3.129943962817249</v>
+        <v>2.68722717445719</v>
       </c>
       <c r="H5">
-        <v>1.588678524181683</v>
+        <v>1.594846116907876</v>
       </c>
       <c r="I5">
-        <v>0.3947057434192356</v>
+        <v>0.3998061450445698</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -730,19 +730,19 @@
         <v>227</v>
       </c>
       <c r="M5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5">
-        <v>0.166469238559121</v>
+        <v>0.1790699134540884</v>
       </c>
       <c r="O5">
-        <v>32.02651284633357</v>
+        <v>32.83534758817594</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.129943962817249</v>
+        <v>2.68722717445719</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C6" s="2">
         <v>46310</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46309</v>
       </c>
       <c r="D6" t="s">
         <v>28</v>
@@ -768,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1.588348665563468</v>
+        <v>1.412331220952477</v>
       </c>
       <c r="H6">
-        <v>1.088763534874031</v>
+        <v>1.103667223967558</v>
       </c>
       <c r="I6">
-        <v>0.2821009667425599</v>
+        <v>0.2839850080066988</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -786,19 +786,19 @@
         <v>160</v>
       </c>
       <c r="M6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6">
-        <v>1.46837277367586</v>
+        <v>1.540671964848931</v>
       </c>
       <c r="O6">
-        <v>24.72097217487666</v>
+        <v>25.27467483933109</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1.588348665563468</v>
+        <v>1.412331220952477</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
@@ -809,10 +809,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C7" s="2">
         <v>46310</v>
-      </c>
-      <c r="C7" s="2">
-        <v>46309</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -821,16 +821,16 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>0.7109350489484609</v>
+        <v>0.003963927485685947</v>
       </c>
       <c r="G7">
-        <v>1.770859756696896</v>
+        <v>1.216329779825541</v>
       </c>
       <c r="H7">
-        <v>1.602859512660267</v>
+        <v>1.612949111579927</v>
       </c>
       <c r="I7">
-        <v>0.3982274280024384</v>
+        <v>0.3997887993750104</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -842,19 +842,19 @@
         <v>241</v>
       </c>
       <c r="M7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N7">
-        <v>0.1564212356416902</v>
+        <v>0.1635456416115685</v>
       </c>
       <c r="O7">
-        <v>29.65130727755281</v>
+        <v>27.8240245784659</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.770859756696896</v>
+        <v>1.216329779825541</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C8" s="2">
         <v>46310</v>
-      </c>
-      <c r="C8" s="2">
-        <v>46309</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.3258904758995773</v>
       </c>
       <c r="G8">
-        <v>2.126585264677562</v>
+        <v>1.470273805584516</v>
       </c>
       <c r="H8">
-        <v>1.609039364845243</v>
+        <v>1.617932173907946</v>
       </c>
       <c r="I8">
-        <v>0.4208756104790778</v>
+        <v>0.4240387453998904</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -898,19 +898,19 @@
         <v>113</v>
       </c>
       <c r="M8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N8">
-        <v>-0.1670189526430422</v>
+        <v>-0.1732409842946532</v>
       </c>
       <c r="O8">
-        <v>-41.23561126889331</v>
+        <v>-38.13780611880102</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.126585264677562</v>
+        <v>1.470273805584516</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
@@ -921,10 +921,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C9" s="2">
         <v>46310</v>
-      </c>
-      <c r="C9" s="2">
-        <v>46309</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2.121349923282727</v>
+        <v>2.189763018164867</v>
       </c>
       <c r="H9">
-        <v>3.164181807591301</v>
+        <v>3.165590365368526</v>
       </c>
       <c r="I9">
-        <v>0.6611192218300914</v>
+        <v>0.6597716381982803</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -954,19 +954,19 @@
         <v>76</v>
       </c>
       <c r="M9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N9">
-        <v>0.9787347329261649</v>
+        <v>0.9921907064030681</v>
       </c>
       <c r="O9">
-        <v>114.9858285651528</v>
+        <v>111.7376816123777</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.121349923282727</v>
+        <v>2.189763018164867</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
@@ -977,10 +977,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C10" s="2">
         <v>46310</v>
-      </c>
-      <c r="C10" s="2">
-        <v>46309</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.06675906685707456</v>
+        <v>0.07459438107229401</v>
       </c>
       <c r="H10">
-        <v>2.15045201458928</v>
+        <v>2.151309599382887</v>
       </c>
       <c r="I10">
-        <v>0.4660602693981725</v>
+        <v>0.4676632207787486</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1010,19 +1010,19 @@
         <v>234</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-0.5289542320550329</v>
+        <v>-0.6732699427796683</v>
       </c>
       <c r="O10">
-        <v>-0.8260761056132996</v>
+        <v>-1.053925107498779</v>
       </c>
       <c r="P10">
-        <v>0.6442425455319755</v>
+        <v>0.5426006593786634</v>
       </c>
       <c r="Q10">
-        <v>0.1876533183455046</v>
+        <v>0.163083709239642</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
@@ -1033,10 +1033,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C11" s="2">
         <v>46310</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46309</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -1048,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>1.546170419007239</v>
+        <v>1.396343747592945</v>
       </c>
       <c r="H11">
-        <v>2.113644704214787</v>
+        <v>2.110051796890647</v>
       </c>
       <c r="I11">
-        <v>0.4862240033527571</v>
+        <v>0.4849715762735686</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1066,19 +1066,19 @@
         <v>213</v>
       </c>
       <c r="M11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N11">
-        <v>862.3314303992927</v>
+        <v>932.5488410754486</v>
       </c>
       <c r="O11">
-        <v>15.02422393965497</v>
+        <v>15.72244654594704</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>1.546170419007239</v>
+        <v>1.396343747592945</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>

--- a/public/data/files/latest_terrain_snapshot.xlsx
+++ b/public/data/files/latest_terrain_snapshot.xlsx
@@ -754,7 +754,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C2" s="2">
         <v>46304</v>
@@ -894,7 +894,7 @@
         <v>47</v>
       </c>
       <c r="B3" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C3" s="2">
         <v>46304</v>
@@ -1034,7 +1034,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C4" s="2">
         <v>46304</v>
@@ -1174,7 +1174,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C5" s="2">
         <v>46304</v>
@@ -1314,7 +1314,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C6" s="2">
         <v>46304</v>
@@ -1454,7 +1454,7 @@
         <v>51</v>
       </c>
       <c r="B7" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C7" s="2">
         <v>46304</v>
@@ -1594,7 +1594,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C8" s="2">
         <v>46304</v>
@@ -1734,7 +1734,7 @@
         <v>53</v>
       </c>
       <c r="B9" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C9" s="2">
         <v>46304</v>
@@ -1874,7 +1874,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C10" s="2">
         <v>46304</v>
@@ -2014,7 +2014,7 @@
         <v>55</v>
       </c>
       <c r="B11" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C11" s="2">
         <v>46304</v>
